--- a/money/finance-template.xlsx
+++ b/money/finance-template.xlsx
@@ -83,7 +83,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
@@ -102,6 +102,7 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -579,7 +580,7 @@
   <dimension ref="A1:H14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
@@ -590,73 +591,73 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="18" t="inlineStr">
+      <c r="A1" s="19" t="inlineStr">
         <is>
           <t>Месяц</t>
         </is>
       </c>
-      <c r="B1" s="18" t="inlineStr">
+      <c r="B1" s="19" t="inlineStr">
         <is>
           <t>Доходы (€)</t>
         </is>
       </c>
-      <c r="C1" s="18" t="inlineStr">
+      <c r="C1" s="19" t="inlineStr">
         <is>
           <t>Возвраты долгов (€)</t>
         </is>
       </c>
-      <c r="D1" s="18" t="inlineStr">
+      <c r="D1" s="19" t="inlineStr">
         <is>
           <t>Расходы (€)</t>
         </is>
       </c>
-      <c r="E1" s="18" t="inlineStr">
+      <c r="E1" s="19" t="inlineStr">
         <is>
           <t>Подписки (€)</t>
         </is>
       </c>
-      <c r="F1" s="18" t="inlineStr">
+      <c r="F1" s="19" t="inlineStr">
         <is>
           <t>Платежи по долгам (€)</t>
         </is>
       </c>
-      <c r="G1" s="18" t="inlineStr">
+      <c r="G1" s="19" t="inlineStr">
         <is>
           <t>Остаток (€)</t>
         </is>
       </c>
-      <c r="H1" s="18" t="inlineStr">
+      <c r="H1" s="19" t="inlineStr">
         <is>
           <t>Норма сбережений</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="19">
-        <f>DATE(YEAR(TODAY()),1,1)</f>
-        <v/>
-      </c>
-      <c r="B2" s="20">
+      <c r="A2" s="20">
+        <f>DATE(Настройки!$B$8,1,1)</f>
+        <v/>
+      </c>
+      <c r="B2" s="21">
         <f>SUMIFS(Операции!$D:$D,Операции!$B:$B,"Доход",Операции!$A:$A,"&gt;="&amp;$A2,Операции!$A:$A,"&lt;"&amp;EDATE($A2,1))</f>
         <v/>
       </c>
-      <c r="C2" s="20">
+      <c r="C2" s="21">
         <f>SUMIFS(Платежи!$C:$C,Платежи!$D:$D,"Мне должны",Платежи!$A:$A,"&gt;="&amp;$A2,Платежи!$A:$A,"&lt;"&amp;EDATE($A2,1))</f>
         <v/>
       </c>
-      <c r="D2" s="20">
+      <c r="D2" s="21">
         <f>SUMIFS(Операции!$D:$D,Операции!$B:$B,"Расход",Операции!$A:$A,"&gt;="&amp;$A2,Операции!$A:$A,"&lt;"&amp;EDATE($A2,1))</f>
         <v/>
       </c>
-      <c r="E2" s="20">
+      <c r="E2" s="21">
         <f>Подписки!$E$501</f>
         <v/>
       </c>
-      <c r="F2" s="20">
+      <c r="F2" s="21">
         <f>SUMIFS(Платежи!$C:$C,Платежи!$D:$D,"Я должен",Платежи!$A:$A,"&gt;="&amp;$A2,Платежи!$A:$A,"&lt;"&amp;EDATE($A2,1))</f>
         <v/>
       </c>
-      <c r="G2" s="20">
+      <c r="G2" s="21">
         <f>B2+C2-D2-E2-F2</f>
         <v/>
       </c>
@@ -666,31 +667,31 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="19">
+      <c r="A3" s="20">
         <f>EDATE(A2,1)</f>
         <v/>
       </c>
-      <c r="B3" s="20">
+      <c r="B3" s="21">
         <f>SUMIFS(Операции!$D:$D,Операции!$B:$B,"Доход",Операции!$A:$A,"&gt;="&amp;$A3,Операции!$A:$A,"&lt;"&amp;EDATE($A3,1))</f>
         <v/>
       </c>
-      <c r="C3" s="20">
+      <c r="C3" s="21">
         <f>SUMIFS(Платежи!$C:$C,Платежи!$D:$D,"Мне должны",Платежи!$A:$A,"&gt;="&amp;$A3,Платежи!$A:$A,"&lt;"&amp;EDATE($A3,1))</f>
         <v/>
       </c>
-      <c r="D3" s="20">
+      <c r="D3" s="21">
         <f>SUMIFS(Операции!$D:$D,Операции!$B:$B,"Расход",Операции!$A:$A,"&gt;="&amp;$A3,Операции!$A:$A,"&lt;"&amp;EDATE($A3,1))</f>
         <v/>
       </c>
-      <c r="E3" s="20">
+      <c r="E3" s="21">
         <f>Подписки!$E$501</f>
         <v/>
       </c>
-      <c r="F3" s="20">
+      <c r="F3" s="21">
         <f>SUMIFS(Платежи!$C:$C,Платежи!$D:$D,"Я должен",Платежи!$A:$A,"&gt;="&amp;$A3,Платежи!$A:$A,"&lt;"&amp;EDATE($A3,1))</f>
         <v/>
       </c>
-      <c r="G3" s="20">
+      <c r="G3" s="21">
         <f>B3+C3-D3-E3-F3</f>
         <v/>
       </c>
@@ -700,31 +701,31 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="19">
+      <c r="A4" s="20">
         <f>EDATE(A3,1)</f>
         <v/>
       </c>
-      <c r="B4" s="20">
+      <c r="B4" s="21">
         <f>SUMIFS(Операции!$D:$D,Операции!$B:$B,"Доход",Операции!$A:$A,"&gt;="&amp;$A4,Операции!$A:$A,"&lt;"&amp;EDATE($A4,1))</f>
         <v/>
       </c>
-      <c r="C4" s="20">
+      <c r="C4" s="21">
         <f>SUMIFS(Платежи!$C:$C,Платежи!$D:$D,"Мне должны",Платежи!$A:$A,"&gt;="&amp;$A4,Платежи!$A:$A,"&lt;"&amp;EDATE($A4,1))</f>
         <v/>
       </c>
-      <c r="D4" s="20">
+      <c r="D4" s="21">
         <f>SUMIFS(Операции!$D:$D,Операции!$B:$B,"Расход",Операции!$A:$A,"&gt;="&amp;$A4,Операции!$A:$A,"&lt;"&amp;EDATE($A4,1))</f>
         <v/>
       </c>
-      <c r="E4" s="20">
+      <c r="E4" s="21">
         <f>Подписки!$E$501</f>
         <v/>
       </c>
-      <c r="F4" s="20">
+      <c r="F4" s="21">
         <f>SUMIFS(Платежи!$C:$C,Платежи!$D:$D,"Я должен",Платежи!$A:$A,"&gt;="&amp;$A4,Платежи!$A:$A,"&lt;"&amp;EDATE($A4,1))</f>
         <v/>
       </c>
-      <c r="G4" s="20">
+      <c r="G4" s="21">
         <f>B4+C4-D4-E4-F4</f>
         <v/>
       </c>
@@ -734,31 +735,31 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="19">
+      <c r="A5" s="20">
         <f>EDATE(A4,1)</f>
         <v/>
       </c>
-      <c r="B5" s="20">
+      <c r="B5" s="21">
         <f>SUMIFS(Операции!$D:$D,Операции!$B:$B,"Доход",Операции!$A:$A,"&gt;="&amp;$A5,Операции!$A:$A,"&lt;"&amp;EDATE($A5,1))</f>
         <v/>
       </c>
-      <c r="C5" s="20">
+      <c r="C5" s="21">
         <f>SUMIFS(Платежи!$C:$C,Платежи!$D:$D,"Мне должны",Платежи!$A:$A,"&gt;="&amp;$A5,Платежи!$A:$A,"&lt;"&amp;EDATE($A5,1))</f>
         <v/>
       </c>
-      <c r="D5" s="20">
+      <c r="D5" s="21">
         <f>SUMIFS(Операции!$D:$D,Операции!$B:$B,"Расход",Операции!$A:$A,"&gt;="&amp;$A5,Операции!$A:$A,"&lt;"&amp;EDATE($A5,1))</f>
         <v/>
       </c>
-      <c r="E5" s="20">
+      <c r="E5" s="21">
         <f>Подписки!$E$501</f>
         <v/>
       </c>
-      <c r="F5" s="20">
+      <c r="F5" s="21">
         <f>SUMIFS(Платежи!$C:$C,Платежи!$D:$D,"Я должен",Платежи!$A:$A,"&gt;="&amp;$A5,Платежи!$A:$A,"&lt;"&amp;EDATE($A5,1))</f>
         <v/>
       </c>
-      <c r="G5" s="20">
+      <c r="G5" s="21">
         <f>B5+C5-D5-E5-F5</f>
         <v/>
       </c>
@@ -768,31 +769,31 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="19">
+      <c r="A6" s="20">
         <f>EDATE(A5,1)</f>
         <v/>
       </c>
-      <c r="B6" s="20">
+      <c r="B6" s="21">
         <f>SUMIFS(Операции!$D:$D,Операции!$B:$B,"Доход",Операции!$A:$A,"&gt;="&amp;$A6,Операции!$A:$A,"&lt;"&amp;EDATE($A6,1))</f>
         <v/>
       </c>
-      <c r="C6" s="20">
+      <c r="C6" s="21">
         <f>SUMIFS(Платежи!$C:$C,Платежи!$D:$D,"Мне должны",Платежи!$A:$A,"&gt;="&amp;$A6,Платежи!$A:$A,"&lt;"&amp;EDATE($A6,1))</f>
         <v/>
       </c>
-      <c r="D6" s="20">
+      <c r="D6" s="21">
         <f>SUMIFS(Операции!$D:$D,Операции!$B:$B,"Расход",Операции!$A:$A,"&gt;="&amp;$A6,Операции!$A:$A,"&lt;"&amp;EDATE($A6,1))</f>
         <v/>
       </c>
-      <c r="E6" s="20">
+      <c r="E6" s="21">
         <f>Подписки!$E$501</f>
         <v/>
       </c>
-      <c r="F6" s="20">
+      <c r="F6" s="21">
         <f>SUMIFS(Платежи!$C:$C,Платежи!$D:$D,"Я должен",Платежи!$A:$A,"&gt;="&amp;$A6,Платежи!$A:$A,"&lt;"&amp;EDATE($A6,1))</f>
         <v/>
       </c>
-      <c r="G6" s="20">
+      <c r="G6" s="21">
         <f>B6+C6-D6-E6-F6</f>
         <v/>
       </c>
@@ -802,31 +803,31 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="19">
+      <c r="A7" s="20">
         <f>EDATE(A6,1)</f>
         <v/>
       </c>
-      <c r="B7" s="20">
+      <c r="B7" s="21">
         <f>SUMIFS(Операции!$D:$D,Операции!$B:$B,"Доход",Операции!$A:$A,"&gt;="&amp;$A7,Операции!$A:$A,"&lt;"&amp;EDATE($A7,1))</f>
         <v/>
       </c>
-      <c r="C7" s="20">
+      <c r="C7" s="21">
         <f>SUMIFS(Платежи!$C:$C,Платежи!$D:$D,"Мне должны",Платежи!$A:$A,"&gt;="&amp;$A7,Платежи!$A:$A,"&lt;"&amp;EDATE($A7,1))</f>
         <v/>
       </c>
-      <c r="D7" s="20">
+      <c r="D7" s="21">
         <f>SUMIFS(Операции!$D:$D,Операции!$B:$B,"Расход",Операции!$A:$A,"&gt;="&amp;$A7,Операции!$A:$A,"&lt;"&amp;EDATE($A7,1))</f>
         <v/>
       </c>
-      <c r="E7" s="20">
+      <c r="E7" s="21">
         <f>Подписки!$E$501</f>
         <v/>
       </c>
-      <c r="F7" s="20">
+      <c r="F7" s="21">
         <f>SUMIFS(Платежи!$C:$C,Платежи!$D:$D,"Я должен",Платежи!$A:$A,"&gt;="&amp;$A7,Платежи!$A:$A,"&lt;"&amp;EDATE($A7,1))</f>
         <v/>
       </c>
-      <c r="G7" s="20">
+      <c r="G7" s="21">
         <f>B7+C7-D7-E7-F7</f>
         <v/>
       </c>
@@ -836,31 +837,31 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="19">
+      <c r="A8" s="20">
         <f>EDATE(A7,1)</f>
         <v/>
       </c>
-      <c r="B8" s="20">
+      <c r="B8" s="21">
         <f>SUMIFS(Операции!$D:$D,Операции!$B:$B,"Доход",Операции!$A:$A,"&gt;="&amp;$A8,Операции!$A:$A,"&lt;"&amp;EDATE($A8,1))</f>
         <v/>
       </c>
-      <c r="C8" s="20">
+      <c r="C8" s="21">
         <f>SUMIFS(Платежи!$C:$C,Платежи!$D:$D,"Мне должны",Платежи!$A:$A,"&gt;="&amp;$A8,Платежи!$A:$A,"&lt;"&amp;EDATE($A8,1))</f>
         <v/>
       </c>
-      <c r="D8" s="20">
+      <c r="D8" s="21">
         <f>SUMIFS(Операции!$D:$D,Операции!$B:$B,"Расход",Операции!$A:$A,"&gt;="&amp;$A8,Операции!$A:$A,"&lt;"&amp;EDATE($A8,1))</f>
         <v/>
       </c>
-      <c r="E8" s="20">
+      <c r="E8" s="21">
         <f>Подписки!$E$501</f>
         <v/>
       </c>
-      <c r="F8" s="20">
+      <c r="F8" s="21">
         <f>SUMIFS(Платежи!$C:$C,Платежи!$D:$D,"Я должен",Платежи!$A:$A,"&gt;="&amp;$A8,Платежи!$A:$A,"&lt;"&amp;EDATE($A8,1))</f>
         <v/>
       </c>
-      <c r="G8" s="20">
+      <c r="G8" s="21">
         <f>B8+C8-D8-E8-F8</f>
         <v/>
       </c>
@@ -870,31 +871,31 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="19">
+      <c r="A9" s="20">
         <f>EDATE(A8,1)</f>
         <v/>
       </c>
-      <c r="B9" s="20">
+      <c r="B9" s="21">
         <f>SUMIFS(Операции!$D:$D,Операции!$B:$B,"Доход",Операции!$A:$A,"&gt;="&amp;$A9,Операции!$A:$A,"&lt;"&amp;EDATE($A9,1))</f>
         <v/>
       </c>
-      <c r="C9" s="20">
+      <c r="C9" s="21">
         <f>SUMIFS(Платежи!$C:$C,Платежи!$D:$D,"Мне должны",Платежи!$A:$A,"&gt;="&amp;$A9,Платежи!$A:$A,"&lt;"&amp;EDATE($A9,1))</f>
         <v/>
       </c>
-      <c r="D9" s="20">
+      <c r="D9" s="21">
         <f>SUMIFS(Операции!$D:$D,Операции!$B:$B,"Расход",Операции!$A:$A,"&gt;="&amp;$A9,Операции!$A:$A,"&lt;"&amp;EDATE($A9,1))</f>
         <v/>
       </c>
-      <c r="E9" s="20">
+      <c r="E9" s="21">
         <f>Подписки!$E$501</f>
         <v/>
       </c>
-      <c r="F9" s="20">
+      <c r="F9" s="21">
         <f>SUMIFS(Платежи!$C:$C,Платежи!$D:$D,"Я должен",Платежи!$A:$A,"&gt;="&amp;$A9,Платежи!$A:$A,"&lt;"&amp;EDATE($A9,1))</f>
         <v/>
       </c>
-      <c r="G9" s="20">
+      <c r="G9" s="21">
         <f>B9+C9-D9-E9-F9</f>
         <v/>
       </c>
@@ -904,31 +905,31 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="19">
+      <c r="A10" s="20">
         <f>EDATE(A9,1)</f>
         <v/>
       </c>
-      <c r="B10" s="20">
+      <c r="B10" s="21">
         <f>SUMIFS(Операции!$D:$D,Операции!$B:$B,"Доход",Операции!$A:$A,"&gt;="&amp;$A10,Операции!$A:$A,"&lt;"&amp;EDATE($A10,1))</f>
         <v/>
       </c>
-      <c r="C10" s="20">
+      <c r="C10" s="21">
         <f>SUMIFS(Платежи!$C:$C,Платежи!$D:$D,"Мне должны",Платежи!$A:$A,"&gt;="&amp;$A10,Платежи!$A:$A,"&lt;"&amp;EDATE($A10,1))</f>
         <v/>
       </c>
-      <c r="D10" s="20">
+      <c r="D10" s="21">
         <f>SUMIFS(Операции!$D:$D,Операции!$B:$B,"Расход",Операции!$A:$A,"&gt;="&amp;$A10,Операции!$A:$A,"&lt;"&amp;EDATE($A10,1))</f>
         <v/>
       </c>
-      <c r="E10" s="20">
+      <c r="E10" s="21">
         <f>Подписки!$E$501</f>
         <v/>
       </c>
-      <c r="F10" s="20">
+      <c r="F10" s="21">
         <f>SUMIFS(Платежи!$C:$C,Платежи!$D:$D,"Я должен",Платежи!$A:$A,"&gt;="&amp;$A10,Платежи!$A:$A,"&lt;"&amp;EDATE($A10,1))</f>
         <v/>
       </c>
-      <c r="G10" s="20">
+      <c r="G10" s="21">
         <f>B10+C10-D10-E10-F10</f>
         <v/>
       </c>
@@ -938,31 +939,31 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="19">
+      <c r="A11" s="20">
         <f>EDATE(A10,1)</f>
         <v/>
       </c>
-      <c r="B11" s="20">
+      <c r="B11" s="21">
         <f>SUMIFS(Операции!$D:$D,Операции!$B:$B,"Доход",Операции!$A:$A,"&gt;="&amp;$A11,Операции!$A:$A,"&lt;"&amp;EDATE($A11,1))</f>
         <v/>
       </c>
-      <c r="C11" s="20">
+      <c r="C11" s="21">
         <f>SUMIFS(Платежи!$C:$C,Платежи!$D:$D,"Мне должны",Платежи!$A:$A,"&gt;="&amp;$A11,Платежи!$A:$A,"&lt;"&amp;EDATE($A11,1))</f>
         <v/>
       </c>
-      <c r="D11" s="20">
+      <c r="D11" s="21">
         <f>SUMIFS(Операции!$D:$D,Операции!$B:$B,"Расход",Операции!$A:$A,"&gt;="&amp;$A11,Операции!$A:$A,"&lt;"&amp;EDATE($A11,1))</f>
         <v/>
       </c>
-      <c r="E11" s="20">
+      <c r="E11" s="21">
         <f>Подписки!$E$501</f>
         <v/>
       </c>
-      <c r="F11" s="20">
+      <c r="F11" s="21">
         <f>SUMIFS(Платежи!$C:$C,Платежи!$D:$D,"Я должен",Платежи!$A:$A,"&gt;="&amp;$A11,Платежи!$A:$A,"&lt;"&amp;EDATE($A11,1))</f>
         <v/>
       </c>
-      <c r="G11" s="20">
+      <c r="G11" s="21">
         <f>B11+C11-D11-E11-F11</f>
         <v/>
       </c>
@@ -972,31 +973,31 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="19">
+      <c r="A12" s="20">
         <f>EDATE(A11,1)</f>
         <v/>
       </c>
-      <c r="B12" s="20">
+      <c r="B12" s="21">
         <f>SUMIFS(Операции!$D:$D,Операции!$B:$B,"Доход",Операции!$A:$A,"&gt;="&amp;$A12,Операции!$A:$A,"&lt;"&amp;EDATE($A12,1))</f>
         <v/>
       </c>
-      <c r="C12" s="20">
+      <c r="C12" s="21">
         <f>SUMIFS(Платежи!$C:$C,Платежи!$D:$D,"Мне должны",Платежи!$A:$A,"&gt;="&amp;$A12,Платежи!$A:$A,"&lt;"&amp;EDATE($A12,1))</f>
         <v/>
       </c>
-      <c r="D12" s="20">
+      <c r="D12" s="21">
         <f>SUMIFS(Операции!$D:$D,Операции!$B:$B,"Расход",Операции!$A:$A,"&gt;="&amp;$A12,Операции!$A:$A,"&lt;"&amp;EDATE($A12,1))</f>
         <v/>
       </c>
-      <c r="E12" s="20">
+      <c r="E12" s="21">
         <f>Подписки!$E$501</f>
         <v/>
       </c>
-      <c r="F12" s="20">
+      <c r="F12" s="21">
         <f>SUMIFS(Платежи!$C:$C,Платежи!$D:$D,"Я должен",Платежи!$A:$A,"&gt;="&amp;$A12,Платежи!$A:$A,"&lt;"&amp;EDATE($A12,1))</f>
         <v/>
       </c>
-      <c r="G12" s="20">
+      <c r="G12" s="21">
         <f>B12+C12-D12-E12-F12</f>
         <v/>
       </c>
@@ -1006,31 +1007,31 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="19">
+      <c r="A13" s="20">
         <f>EDATE(A12,1)</f>
         <v/>
       </c>
-      <c r="B13" s="20">
+      <c r="B13" s="21">
         <f>SUMIFS(Операции!$D:$D,Операции!$B:$B,"Доход",Операции!$A:$A,"&gt;="&amp;$A13,Операции!$A:$A,"&lt;"&amp;EDATE($A13,1))</f>
         <v/>
       </c>
-      <c r="C13" s="20">
+      <c r="C13" s="21">
         <f>SUMIFS(Платежи!$C:$C,Платежи!$D:$D,"Мне должны",Платежи!$A:$A,"&gt;="&amp;$A13,Платежи!$A:$A,"&lt;"&amp;EDATE($A13,1))</f>
         <v/>
       </c>
-      <c r="D13" s="20">
+      <c r="D13" s="21">
         <f>SUMIFS(Операции!$D:$D,Операции!$B:$B,"Расход",Операции!$A:$A,"&gt;="&amp;$A13,Операции!$A:$A,"&lt;"&amp;EDATE($A13,1))</f>
         <v/>
       </c>
-      <c r="E13" s="20">
+      <c r="E13" s="21">
         <f>Подписки!$E$501</f>
         <v/>
       </c>
-      <c r="F13" s="20">
+      <c r="F13" s="21">
         <f>SUMIFS(Платежи!$C:$C,Платежи!$D:$D,"Я должен",Платежи!$A:$A,"&gt;="&amp;$A13,Платежи!$A:$A,"&lt;"&amp;EDATE($A13,1))</f>
         <v/>
       </c>
-      <c r="G13" s="20">
+      <c r="G13" s="21">
         <f>B13+C13-D13-E13-F13</f>
         <v/>
       </c>
@@ -1045,27 +1046,27 @@
           <t>Итого за 12 месяцев</t>
         </is>
       </c>
-      <c r="B14" s="21">
+      <c r="B14" s="22">
         <f>SUM(B2:B13)</f>
         <v/>
       </c>
-      <c r="C14" s="21">
+      <c r="C14" s="22">
         <f>SUM(C2:C13)</f>
         <v/>
       </c>
-      <c r="D14" s="21">
+      <c r="D14" s="22">
         <f>SUM(D2:D13)</f>
         <v/>
       </c>
-      <c r="E14" s="21">
+      <c r="E14" s="22">
         <f>SUM(E2:E13)</f>
         <v/>
       </c>
-      <c r="F14" s="21">
+      <c r="F14" s="22">
         <f>SUM(F2:F13)</f>
         <v/>
       </c>
-      <c r="G14" s="21">
+      <c r="G14" s="22">
         <f>SUM(G2:G13)</f>
         <v/>
       </c>
@@ -1699,10 +1700,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B7"/>
+  <dimension ref="A1:B8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="46" customWidth="1" min="1" max="1"/>
+    <col width="52" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
@@ -1777,6 +1778,17 @@
       </c>
       <c r="B7" s="11">
         <f>B6*12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Год для сводки по месяцам (по умолчанию текущий)</t>
+        </is>
+      </c>
+      <c r="B8" s="16">
+        <f>YEAR(TODAY())</f>
         <v/>
       </c>
     </row>
@@ -7989,7 +8001,7 @@
     </row>
     <row r="2">
       <c r="D2" s="7" t="n"/>
-      <c r="E2" s="16" t="n"/>
+      <c r="E2" s="17" t="n"/>
       <c r="F2" s="7" t="n"/>
       <c r="G2" s="4" t="n"/>
       <c r="H2" s="7">
@@ -8007,7 +8019,7 @@
     </row>
     <row r="3">
       <c r="D3" s="7" t="n"/>
-      <c r="E3" s="16" t="n"/>
+      <c r="E3" s="17" t="n"/>
       <c r="F3" s="7" t="n"/>
       <c r="G3" s="4" t="n"/>
       <c r="H3" s="7">
@@ -8025,7 +8037,7 @@
     </row>
     <row r="4">
       <c r="D4" s="7" t="n"/>
-      <c r="E4" s="16" t="n"/>
+      <c r="E4" s="17" t="n"/>
       <c r="F4" s="7" t="n"/>
       <c r="G4" s="4" t="n"/>
       <c r="H4" s="7">
@@ -8043,7 +8055,7 @@
     </row>
     <row r="5">
       <c r="D5" s="7" t="n"/>
-      <c r="E5" s="16" t="n"/>
+      <c r="E5" s="17" t="n"/>
       <c r="F5" s="7" t="n"/>
       <c r="G5" s="4" t="n"/>
       <c r="H5" s="7">
@@ -8061,7 +8073,7 @@
     </row>
     <row r="6">
       <c r="D6" s="7" t="n"/>
-      <c r="E6" s="16" t="n"/>
+      <c r="E6" s="17" t="n"/>
       <c r="F6" s="7" t="n"/>
       <c r="G6" s="4" t="n"/>
       <c r="H6" s="7">
@@ -8079,7 +8091,7 @@
     </row>
     <row r="7">
       <c r="D7" s="7" t="n"/>
-      <c r="E7" s="16" t="n"/>
+      <c r="E7" s="17" t="n"/>
       <c r="F7" s="7" t="n"/>
       <c r="G7" s="4" t="n"/>
       <c r="H7" s="7">
@@ -8097,7 +8109,7 @@
     </row>
     <row r="8">
       <c r="D8" s="7" t="n"/>
-      <c r="E8" s="16" t="n"/>
+      <c r="E8" s="17" t="n"/>
       <c r="F8" s="7" t="n"/>
       <c r="G8" s="4" t="n"/>
       <c r="H8" s="7">
@@ -8115,7 +8127,7 @@
     </row>
     <row r="9">
       <c r="D9" s="7" t="n"/>
-      <c r="E9" s="16" t="n"/>
+      <c r="E9" s="17" t="n"/>
       <c r="F9" s="7" t="n"/>
       <c r="G9" s="4" t="n"/>
       <c r="H9" s="7">
@@ -8133,7 +8145,7 @@
     </row>
     <row r="10">
       <c r="D10" s="7" t="n"/>
-      <c r="E10" s="16" t="n"/>
+      <c r="E10" s="17" t="n"/>
       <c r="F10" s="7" t="n"/>
       <c r="G10" s="4" t="n"/>
       <c r="H10" s="7">
@@ -8151,7 +8163,7 @@
     </row>
     <row r="11">
       <c r="D11" s="7" t="n"/>
-      <c r="E11" s="16" t="n"/>
+      <c r="E11" s="17" t="n"/>
       <c r="F11" s="7" t="n"/>
       <c r="G11" s="4" t="n"/>
       <c r="H11" s="7">
@@ -8169,7 +8181,7 @@
     </row>
     <row r="12">
       <c r="D12" s="7" t="n"/>
-      <c r="E12" s="16" t="n"/>
+      <c r="E12" s="17" t="n"/>
       <c r="F12" s="7" t="n"/>
       <c r="G12" s="4" t="n"/>
       <c r="H12" s="7">
@@ -8187,7 +8199,7 @@
     </row>
     <row r="13">
       <c r="D13" s="7" t="n"/>
-      <c r="E13" s="16" t="n"/>
+      <c r="E13" s="17" t="n"/>
       <c r="F13" s="7" t="n"/>
       <c r="G13" s="4" t="n"/>
       <c r="H13" s="7">
@@ -8205,7 +8217,7 @@
     </row>
     <row r="14">
       <c r="D14" s="7" t="n"/>
-      <c r="E14" s="16" t="n"/>
+      <c r="E14" s="17" t="n"/>
       <c r="F14" s="7" t="n"/>
       <c r="G14" s="4" t="n"/>
       <c r="H14" s="7">
@@ -8223,7 +8235,7 @@
     </row>
     <row r="15">
       <c r="D15" s="7" t="n"/>
-      <c r="E15" s="16" t="n"/>
+      <c r="E15" s="17" t="n"/>
       <c r="F15" s="7" t="n"/>
       <c r="G15" s="4" t="n"/>
       <c r="H15" s="7">
@@ -8241,7 +8253,7 @@
     </row>
     <row r="16">
       <c r="D16" s="7" t="n"/>
-      <c r="E16" s="16" t="n"/>
+      <c r="E16" s="17" t="n"/>
       <c r="F16" s="7" t="n"/>
       <c r="G16" s="4" t="n"/>
       <c r="H16" s="7">
@@ -8259,7 +8271,7 @@
     </row>
     <row r="17">
       <c r="D17" s="7" t="n"/>
-      <c r="E17" s="16" t="n"/>
+      <c r="E17" s="17" t="n"/>
       <c r="F17" s="7" t="n"/>
       <c r="G17" s="4" t="n"/>
       <c r="H17" s="7">
@@ -8277,7 +8289,7 @@
     </row>
     <row r="18">
       <c r="D18" s="7" t="n"/>
-      <c r="E18" s="16" t="n"/>
+      <c r="E18" s="17" t="n"/>
       <c r="F18" s="7" t="n"/>
       <c r="G18" s="4" t="n"/>
       <c r="H18" s="7">
@@ -8295,7 +8307,7 @@
     </row>
     <row r="19">
       <c r="D19" s="7" t="n"/>
-      <c r="E19" s="16" t="n"/>
+      <c r="E19" s="17" t="n"/>
       <c r="F19" s="7" t="n"/>
       <c r="G19" s="4" t="n"/>
       <c r="H19" s="7">
@@ -8313,7 +8325,7 @@
     </row>
     <row r="20">
       <c r="D20" s="7" t="n"/>
-      <c r="E20" s="16" t="n"/>
+      <c r="E20" s="17" t="n"/>
       <c r="F20" s="7" t="n"/>
       <c r="G20" s="4" t="n"/>
       <c r="H20" s="7">
@@ -8331,7 +8343,7 @@
     </row>
     <row r="21">
       <c r="D21" s="7" t="n"/>
-      <c r="E21" s="16" t="n"/>
+      <c r="E21" s="17" t="n"/>
       <c r="F21" s="7" t="n"/>
       <c r="G21" s="4" t="n"/>
       <c r="H21" s="7">
@@ -8349,7 +8361,7 @@
     </row>
     <row r="22">
       <c r="D22" s="7" t="n"/>
-      <c r="E22" s="16" t="n"/>
+      <c r="E22" s="17" t="n"/>
       <c r="F22" s="7" t="n"/>
       <c r="G22" s="4" t="n"/>
       <c r="H22" s="7">
@@ -8367,7 +8379,7 @@
     </row>
     <row r="23">
       <c r="D23" s="7" t="n"/>
-      <c r="E23" s="16" t="n"/>
+      <c r="E23" s="17" t="n"/>
       <c r="F23" s="7" t="n"/>
       <c r="G23" s="4" t="n"/>
       <c r="H23" s="7">
@@ -8385,7 +8397,7 @@
     </row>
     <row r="24">
       <c r="D24" s="7" t="n"/>
-      <c r="E24" s="16" t="n"/>
+      <c r="E24" s="17" t="n"/>
       <c r="F24" s="7" t="n"/>
       <c r="G24" s="4" t="n"/>
       <c r="H24" s="7">
@@ -8403,7 +8415,7 @@
     </row>
     <row r="25">
       <c r="D25" s="7" t="n"/>
-      <c r="E25" s="16" t="n"/>
+      <c r="E25" s="17" t="n"/>
       <c r="F25" s="7" t="n"/>
       <c r="G25" s="4" t="n"/>
       <c r="H25" s="7">
@@ -8421,7 +8433,7 @@
     </row>
     <row r="26">
       <c r="D26" s="7" t="n"/>
-      <c r="E26" s="16" t="n"/>
+      <c r="E26" s="17" t="n"/>
       <c r="F26" s="7" t="n"/>
       <c r="G26" s="4" t="n"/>
       <c r="H26" s="7">
@@ -8439,7 +8451,7 @@
     </row>
     <row r="27">
       <c r="D27" s="7" t="n"/>
-      <c r="E27" s="16" t="n"/>
+      <c r="E27" s="17" t="n"/>
       <c r="F27" s="7" t="n"/>
       <c r="G27" s="4" t="n"/>
       <c r="H27" s="7">
@@ -8457,7 +8469,7 @@
     </row>
     <row r="28">
       <c r="D28" s="7" t="n"/>
-      <c r="E28" s="16" t="n"/>
+      <c r="E28" s="17" t="n"/>
       <c r="F28" s="7" t="n"/>
       <c r="G28" s="4" t="n"/>
       <c r="H28" s="7">
@@ -8475,7 +8487,7 @@
     </row>
     <row r="29">
       <c r="D29" s="7" t="n"/>
-      <c r="E29" s="16" t="n"/>
+      <c r="E29" s="17" t="n"/>
       <c r="F29" s="7" t="n"/>
       <c r="G29" s="4" t="n"/>
       <c r="H29" s="7">
@@ -8493,7 +8505,7 @@
     </row>
     <row r="30">
       <c r="D30" s="7" t="n"/>
-      <c r="E30" s="16" t="n"/>
+      <c r="E30" s="17" t="n"/>
       <c r="F30" s="7" t="n"/>
       <c r="G30" s="4" t="n"/>
       <c r="H30" s="7">
@@ -8511,7 +8523,7 @@
     </row>
     <row r="31">
       <c r="D31" s="7" t="n"/>
-      <c r="E31" s="16" t="n"/>
+      <c r="E31" s="17" t="n"/>
       <c r="F31" s="7" t="n"/>
       <c r="G31" s="4" t="n"/>
       <c r="H31" s="7">
@@ -8529,7 +8541,7 @@
     </row>
     <row r="32">
       <c r="D32" s="7" t="n"/>
-      <c r="E32" s="16" t="n"/>
+      <c r="E32" s="17" t="n"/>
       <c r="F32" s="7" t="n"/>
       <c r="G32" s="4" t="n"/>
       <c r="H32" s="7">
@@ -8547,7 +8559,7 @@
     </row>
     <row r="33">
       <c r="D33" s="7" t="n"/>
-      <c r="E33" s="16" t="n"/>
+      <c r="E33" s="17" t="n"/>
       <c r="F33" s="7" t="n"/>
       <c r="G33" s="4" t="n"/>
       <c r="H33" s="7">
@@ -8565,7 +8577,7 @@
     </row>
     <row r="34">
       <c r="D34" s="7" t="n"/>
-      <c r="E34" s="16" t="n"/>
+      <c r="E34" s="17" t="n"/>
       <c r="F34" s="7" t="n"/>
       <c r="G34" s="4" t="n"/>
       <c r="H34" s="7">
@@ -8583,7 +8595,7 @@
     </row>
     <row r="35">
       <c r="D35" s="7" t="n"/>
-      <c r="E35" s="16" t="n"/>
+      <c r="E35" s="17" t="n"/>
       <c r="F35" s="7" t="n"/>
       <c r="G35" s="4" t="n"/>
       <c r="H35" s="7">
@@ -8601,7 +8613,7 @@
     </row>
     <row r="36">
       <c r="D36" s="7" t="n"/>
-      <c r="E36" s="16" t="n"/>
+      <c r="E36" s="17" t="n"/>
       <c r="F36" s="7" t="n"/>
       <c r="G36" s="4" t="n"/>
       <c r="H36" s="7">
@@ -8619,7 +8631,7 @@
     </row>
     <row r="37">
       <c r="D37" s="7" t="n"/>
-      <c r="E37" s="16" t="n"/>
+      <c r="E37" s="17" t="n"/>
       <c r="F37" s="7" t="n"/>
       <c r="G37" s="4" t="n"/>
       <c r="H37" s="7">
@@ -8637,7 +8649,7 @@
     </row>
     <row r="38">
       <c r="D38" s="7" t="n"/>
-      <c r="E38" s="16" t="n"/>
+      <c r="E38" s="17" t="n"/>
       <c r="F38" s="7" t="n"/>
       <c r="G38" s="4" t="n"/>
       <c r="H38" s="7">
@@ -8655,7 +8667,7 @@
     </row>
     <row r="39">
       <c r="D39" s="7" t="n"/>
-      <c r="E39" s="16" t="n"/>
+      <c r="E39" s="17" t="n"/>
       <c r="F39" s="7" t="n"/>
       <c r="G39" s="4" t="n"/>
       <c r="H39" s="7">
@@ -8673,7 +8685,7 @@
     </row>
     <row r="40">
       <c r="D40" s="7" t="n"/>
-      <c r="E40" s="16" t="n"/>
+      <c r="E40" s="17" t="n"/>
       <c r="F40" s="7" t="n"/>
       <c r="G40" s="4" t="n"/>
       <c r="H40" s="7">
@@ -8691,7 +8703,7 @@
     </row>
     <row r="41">
       <c r="D41" s="7" t="n"/>
-      <c r="E41" s="16" t="n"/>
+      <c r="E41" s="17" t="n"/>
       <c r="F41" s="7" t="n"/>
       <c r="G41" s="4" t="n"/>
       <c r="H41" s="7">
@@ -8709,7 +8721,7 @@
     </row>
     <row r="42">
       <c r="D42" s="7" t="n"/>
-      <c r="E42" s="16" t="n"/>
+      <c r="E42" s="17" t="n"/>
       <c r="F42" s="7" t="n"/>
       <c r="G42" s="4" t="n"/>
       <c r="H42" s="7">
@@ -8727,7 +8739,7 @@
     </row>
     <row r="43">
       <c r="D43" s="7" t="n"/>
-      <c r="E43" s="16" t="n"/>
+      <c r="E43" s="17" t="n"/>
       <c r="F43" s="7" t="n"/>
       <c r="G43" s="4" t="n"/>
       <c r="H43" s="7">
@@ -8745,7 +8757,7 @@
     </row>
     <row r="44">
       <c r="D44" s="7" t="n"/>
-      <c r="E44" s="16" t="n"/>
+      <c r="E44" s="17" t="n"/>
       <c r="F44" s="7" t="n"/>
       <c r="G44" s="4" t="n"/>
       <c r="H44" s="7">
@@ -8763,7 +8775,7 @@
     </row>
     <row r="45">
       <c r="D45" s="7" t="n"/>
-      <c r="E45" s="16" t="n"/>
+      <c r="E45" s="17" t="n"/>
       <c r="F45" s="7" t="n"/>
       <c r="G45" s="4" t="n"/>
       <c r="H45" s="7">
@@ -8781,7 +8793,7 @@
     </row>
     <row r="46">
       <c r="D46" s="7" t="n"/>
-      <c r="E46" s="16" t="n"/>
+      <c r="E46" s="17" t="n"/>
       <c r="F46" s="7" t="n"/>
       <c r="G46" s="4" t="n"/>
       <c r="H46" s="7">
@@ -8799,7 +8811,7 @@
     </row>
     <row r="47">
       <c r="D47" s="7" t="n"/>
-      <c r="E47" s="16" t="n"/>
+      <c r="E47" s="17" t="n"/>
       <c r="F47" s="7" t="n"/>
       <c r="G47" s="4" t="n"/>
       <c r="H47" s="7">
@@ -8817,7 +8829,7 @@
     </row>
     <row r="48">
       <c r="D48" s="7" t="n"/>
-      <c r="E48" s="16" t="n"/>
+      <c r="E48" s="17" t="n"/>
       <c r="F48" s="7" t="n"/>
       <c r="G48" s="4" t="n"/>
       <c r="H48" s="7">
@@ -8835,7 +8847,7 @@
     </row>
     <row r="49">
       <c r="D49" s="7" t="n"/>
-      <c r="E49" s="16" t="n"/>
+      <c r="E49" s="17" t="n"/>
       <c r="F49" s="7" t="n"/>
       <c r="G49" s="4" t="n"/>
       <c r="H49" s="7">
@@ -8853,7 +8865,7 @@
     </row>
     <row r="50">
       <c r="D50" s="7" t="n"/>
-      <c r="E50" s="16" t="n"/>
+      <c r="E50" s="17" t="n"/>
       <c r="F50" s="7" t="n"/>
       <c r="G50" s="4" t="n"/>
       <c r="H50" s="7">
@@ -8871,7 +8883,7 @@
     </row>
     <row r="51">
       <c r="D51" s="7" t="n"/>
-      <c r="E51" s="16" t="n"/>
+      <c r="E51" s="17" t="n"/>
       <c r="F51" s="7" t="n"/>
       <c r="G51" s="4" t="n"/>
       <c r="H51" s="7">
@@ -8889,7 +8901,7 @@
     </row>
     <row r="52">
       <c r="D52" s="7" t="n"/>
-      <c r="E52" s="16" t="n"/>
+      <c r="E52" s="17" t="n"/>
       <c r="F52" s="7" t="n"/>
       <c r="G52" s="4" t="n"/>
       <c r="H52" s="7">
@@ -8907,7 +8919,7 @@
     </row>
     <row r="53">
       <c r="D53" s="7" t="n"/>
-      <c r="E53" s="16" t="n"/>
+      <c r="E53" s="17" t="n"/>
       <c r="F53" s="7" t="n"/>
       <c r="G53" s="4" t="n"/>
       <c r="H53" s="7">
@@ -8925,7 +8937,7 @@
     </row>
     <row r="54">
       <c r="D54" s="7" t="n"/>
-      <c r="E54" s="16" t="n"/>
+      <c r="E54" s="17" t="n"/>
       <c r="F54" s="7" t="n"/>
       <c r="G54" s="4" t="n"/>
       <c r="H54" s="7">
@@ -8943,7 +8955,7 @@
     </row>
     <row r="55">
       <c r="D55" s="7" t="n"/>
-      <c r="E55" s="16" t="n"/>
+      <c r="E55" s="17" t="n"/>
       <c r="F55" s="7" t="n"/>
       <c r="G55" s="4" t="n"/>
       <c r="H55" s="7">
@@ -8961,7 +8973,7 @@
     </row>
     <row r="56">
       <c r="D56" s="7" t="n"/>
-      <c r="E56" s="16" t="n"/>
+      <c r="E56" s="17" t="n"/>
       <c r="F56" s="7" t="n"/>
       <c r="G56" s="4" t="n"/>
       <c r="H56" s="7">
@@ -8979,7 +8991,7 @@
     </row>
     <row r="57">
       <c r="D57" s="7" t="n"/>
-      <c r="E57" s="16" t="n"/>
+      <c r="E57" s="17" t="n"/>
       <c r="F57" s="7" t="n"/>
       <c r="G57" s="4" t="n"/>
       <c r="H57" s="7">
@@ -8997,7 +9009,7 @@
     </row>
     <row r="58">
       <c r="D58" s="7" t="n"/>
-      <c r="E58" s="16" t="n"/>
+      <c r="E58" s="17" t="n"/>
       <c r="F58" s="7" t="n"/>
       <c r="G58" s="4" t="n"/>
       <c r="H58" s="7">
@@ -9015,7 +9027,7 @@
     </row>
     <row r="59">
       <c r="D59" s="7" t="n"/>
-      <c r="E59" s="16" t="n"/>
+      <c r="E59" s="17" t="n"/>
       <c r="F59" s="7" t="n"/>
       <c r="G59" s="4" t="n"/>
       <c r="H59" s="7">
@@ -9033,7 +9045,7 @@
     </row>
     <row r="60">
       <c r="D60" s="7" t="n"/>
-      <c r="E60" s="16" t="n"/>
+      <c r="E60" s="17" t="n"/>
       <c r="F60" s="7" t="n"/>
       <c r="G60" s="4" t="n"/>
       <c r="H60" s="7">
@@ -9051,7 +9063,7 @@
     </row>
     <row r="61">
       <c r="D61" s="7" t="n"/>
-      <c r="E61" s="16" t="n"/>
+      <c r="E61" s="17" t="n"/>
       <c r="F61" s="7" t="n"/>
       <c r="G61" s="4" t="n"/>
       <c r="H61" s="7">
@@ -9069,7 +9081,7 @@
     </row>
     <row r="62">
       <c r="D62" s="7" t="n"/>
-      <c r="E62" s="16" t="n"/>
+      <c r="E62" s="17" t="n"/>
       <c r="F62" s="7" t="n"/>
       <c r="G62" s="4" t="n"/>
       <c r="H62" s="7">
@@ -9087,7 +9099,7 @@
     </row>
     <row r="63">
       <c r="D63" s="7" t="n"/>
-      <c r="E63" s="16" t="n"/>
+      <c r="E63" s="17" t="n"/>
       <c r="F63" s="7" t="n"/>
       <c r="G63" s="4" t="n"/>
       <c r="H63" s="7">
@@ -9105,7 +9117,7 @@
     </row>
     <row r="64">
       <c r="D64" s="7" t="n"/>
-      <c r="E64" s="16" t="n"/>
+      <c r="E64" s="17" t="n"/>
       <c r="F64" s="7" t="n"/>
       <c r="G64" s="4" t="n"/>
       <c r="H64" s="7">
@@ -9123,7 +9135,7 @@
     </row>
     <row r="65">
       <c r="D65" s="7" t="n"/>
-      <c r="E65" s="16" t="n"/>
+      <c r="E65" s="17" t="n"/>
       <c r="F65" s="7" t="n"/>
       <c r="G65" s="4" t="n"/>
       <c r="H65" s="7">
@@ -9141,7 +9153,7 @@
     </row>
     <row r="66">
       <c r="D66" s="7" t="n"/>
-      <c r="E66" s="16" t="n"/>
+      <c r="E66" s="17" t="n"/>
       <c r="F66" s="7" t="n"/>
       <c r="G66" s="4" t="n"/>
       <c r="H66" s="7">
@@ -9159,7 +9171,7 @@
     </row>
     <row r="67">
       <c r="D67" s="7" t="n"/>
-      <c r="E67" s="16" t="n"/>
+      <c r="E67" s="17" t="n"/>
       <c r="F67" s="7" t="n"/>
       <c r="G67" s="4" t="n"/>
       <c r="H67" s="7">
@@ -9177,7 +9189,7 @@
     </row>
     <row r="68">
       <c r="D68" s="7" t="n"/>
-      <c r="E68" s="16" t="n"/>
+      <c r="E68" s="17" t="n"/>
       <c r="F68" s="7" t="n"/>
       <c r="G68" s="4" t="n"/>
       <c r="H68" s="7">
@@ -9195,7 +9207,7 @@
     </row>
     <row r="69">
       <c r="D69" s="7" t="n"/>
-      <c r="E69" s="16" t="n"/>
+      <c r="E69" s="17" t="n"/>
       <c r="F69" s="7" t="n"/>
       <c r="G69" s="4" t="n"/>
       <c r="H69" s="7">
@@ -9213,7 +9225,7 @@
     </row>
     <row r="70">
       <c r="D70" s="7" t="n"/>
-      <c r="E70" s="16" t="n"/>
+      <c r="E70" s="17" t="n"/>
       <c r="F70" s="7" t="n"/>
       <c r="G70" s="4" t="n"/>
       <c r="H70" s="7">
@@ -9231,7 +9243,7 @@
     </row>
     <row r="71">
       <c r="D71" s="7" t="n"/>
-      <c r="E71" s="16" t="n"/>
+      <c r="E71" s="17" t="n"/>
       <c r="F71" s="7" t="n"/>
       <c r="G71" s="4" t="n"/>
       <c r="H71" s="7">
@@ -9249,7 +9261,7 @@
     </row>
     <row r="72">
       <c r="D72" s="7" t="n"/>
-      <c r="E72" s="16" t="n"/>
+      <c r="E72" s="17" t="n"/>
       <c r="F72" s="7" t="n"/>
       <c r="G72" s="4" t="n"/>
       <c r="H72" s="7">
@@ -9267,7 +9279,7 @@
     </row>
     <row r="73">
       <c r="D73" s="7" t="n"/>
-      <c r="E73" s="16" t="n"/>
+      <c r="E73" s="17" t="n"/>
       <c r="F73" s="7" t="n"/>
       <c r="G73" s="4" t="n"/>
       <c r="H73" s="7">
@@ -9285,7 +9297,7 @@
     </row>
     <row r="74">
       <c r="D74" s="7" t="n"/>
-      <c r="E74" s="16" t="n"/>
+      <c r="E74" s="17" t="n"/>
       <c r="F74" s="7" t="n"/>
       <c r="G74" s="4" t="n"/>
       <c r="H74" s="7">
@@ -9303,7 +9315,7 @@
     </row>
     <row r="75">
       <c r="D75" s="7" t="n"/>
-      <c r="E75" s="16" t="n"/>
+      <c r="E75" s="17" t="n"/>
       <c r="F75" s="7" t="n"/>
       <c r="G75" s="4" t="n"/>
       <c r="H75" s="7">
@@ -9321,7 +9333,7 @@
     </row>
     <row r="76">
       <c r="D76" s="7" t="n"/>
-      <c r="E76" s="16" t="n"/>
+      <c r="E76" s="17" t="n"/>
       <c r="F76" s="7" t="n"/>
       <c r="G76" s="4" t="n"/>
       <c r="H76" s="7">
@@ -9339,7 +9351,7 @@
     </row>
     <row r="77">
       <c r="D77" s="7" t="n"/>
-      <c r="E77" s="16" t="n"/>
+      <c r="E77" s="17" t="n"/>
       <c r="F77" s="7" t="n"/>
       <c r="G77" s="4" t="n"/>
       <c r="H77" s="7">
@@ -9357,7 +9369,7 @@
     </row>
     <row r="78">
       <c r="D78" s="7" t="n"/>
-      <c r="E78" s="16" t="n"/>
+      <c r="E78" s="17" t="n"/>
       <c r="F78" s="7" t="n"/>
       <c r="G78" s="4" t="n"/>
       <c r="H78" s="7">
@@ -9375,7 +9387,7 @@
     </row>
     <row r="79">
       <c r="D79" s="7" t="n"/>
-      <c r="E79" s="16" t="n"/>
+      <c r="E79" s="17" t="n"/>
       <c r="F79" s="7" t="n"/>
       <c r="G79" s="4" t="n"/>
       <c r="H79" s="7">
@@ -9393,7 +9405,7 @@
     </row>
     <row r="80">
       <c r="D80" s="7" t="n"/>
-      <c r="E80" s="16" t="n"/>
+      <c r="E80" s="17" t="n"/>
       <c r="F80" s="7" t="n"/>
       <c r="G80" s="4" t="n"/>
       <c r="H80" s="7">
@@ -9411,7 +9423,7 @@
     </row>
     <row r="81">
       <c r="D81" s="7" t="n"/>
-      <c r="E81" s="16" t="n"/>
+      <c r="E81" s="17" t="n"/>
       <c r="F81" s="7" t="n"/>
       <c r="G81" s="4" t="n"/>
       <c r="H81" s="7">
@@ -9429,7 +9441,7 @@
     </row>
     <row r="82">
       <c r="D82" s="7" t="n"/>
-      <c r="E82" s="16" t="n"/>
+      <c r="E82" s="17" t="n"/>
       <c r="F82" s="7" t="n"/>
       <c r="G82" s="4" t="n"/>
       <c r="H82" s="7">
@@ -9447,7 +9459,7 @@
     </row>
     <row r="83">
       <c r="D83" s="7" t="n"/>
-      <c r="E83" s="16" t="n"/>
+      <c r="E83" s="17" t="n"/>
       <c r="F83" s="7" t="n"/>
       <c r="G83" s="4" t="n"/>
       <c r="H83" s="7">
@@ -9465,7 +9477,7 @@
     </row>
     <row r="84">
       <c r="D84" s="7" t="n"/>
-      <c r="E84" s="16" t="n"/>
+      <c r="E84" s="17" t="n"/>
       <c r="F84" s="7" t="n"/>
       <c r="G84" s="4" t="n"/>
       <c r="H84" s="7">
@@ -9483,7 +9495,7 @@
     </row>
     <row r="85">
       <c r="D85" s="7" t="n"/>
-      <c r="E85" s="16" t="n"/>
+      <c r="E85" s="17" t="n"/>
       <c r="F85" s="7" t="n"/>
       <c r="G85" s="4" t="n"/>
       <c r="H85" s="7">
@@ -9501,7 +9513,7 @@
     </row>
     <row r="86">
       <c r="D86" s="7" t="n"/>
-      <c r="E86" s="16" t="n"/>
+      <c r="E86" s="17" t="n"/>
       <c r="F86" s="7" t="n"/>
       <c r="G86" s="4" t="n"/>
       <c r="H86" s="7">
@@ -9519,7 +9531,7 @@
     </row>
     <row r="87">
       <c r="D87" s="7" t="n"/>
-      <c r="E87" s="16" t="n"/>
+      <c r="E87" s="17" t="n"/>
       <c r="F87" s="7" t="n"/>
       <c r="G87" s="4" t="n"/>
       <c r="H87" s="7">
@@ -9537,7 +9549,7 @@
     </row>
     <row r="88">
       <c r="D88" s="7" t="n"/>
-      <c r="E88" s="16" t="n"/>
+      <c r="E88" s="17" t="n"/>
       <c r="F88" s="7" t="n"/>
       <c r="G88" s="4" t="n"/>
       <c r="H88" s="7">
@@ -9555,7 +9567,7 @@
     </row>
     <row r="89">
       <c r="D89" s="7" t="n"/>
-      <c r="E89" s="16" t="n"/>
+      <c r="E89" s="17" t="n"/>
       <c r="F89" s="7" t="n"/>
       <c r="G89" s="4" t="n"/>
       <c r="H89" s="7">
@@ -9573,7 +9585,7 @@
     </row>
     <row r="90">
       <c r="D90" s="7" t="n"/>
-      <c r="E90" s="16" t="n"/>
+      <c r="E90" s="17" t="n"/>
       <c r="F90" s="7" t="n"/>
       <c r="G90" s="4" t="n"/>
       <c r="H90" s="7">
@@ -9591,7 +9603,7 @@
     </row>
     <row r="91">
       <c r="D91" s="7" t="n"/>
-      <c r="E91" s="16" t="n"/>
+      <c r="E91" s="17" t="n"/>
       <c r="F91" s="7" t="n"/>
       <c r="G91" s="4" t="n"/>
       <c r="H91" s="7">
@@ -9609,7 +9621,7 @@
     </row>
     <row r="92">
       <c r="D92" s="7" t="n"/>
-      <c r="E92" s="16" t="n"/>
+      <c r="E92" s="17" t="n"/>
       <c r="F92" s="7" t="n"/>
       <c r="G92" s="4" t="n"/>
       <c r="H92" s="7">
@@ -9627,7 +9639,7 @@
     </row>
     <row r="93">
       <c r="D93" s="7" t="n"/>
-      <c r="E93" s="16" t="n"/>
+      <c r="E93" s="17" t="n"/>
       <c r="F93" s="7" t="n"/>
       <c r="G93" s="4" t="n"/>
       <c r="H93" s="7">
@@ -9645,7 +9657,7 @@
     </row>
     <row r="94">
       <c r="D94" s="7" t="n"/>
-      <c r="E94" s="16" t="n"/>
+      <c r="E94" s="17" t="n"/>
       <c r="F94" s="7" t="n"/>
       <c r="G94" s="4" t="n"/>
       <c r="H94" s="7">
@@ -9663,7 +9675,7 @@
     </row>
     <row r="95">
       <c r="D95" s="7" t="n"/>
-      <c r="E95" s="16" t="n"/>
+      <c r="E95" s="17" t="n"/>
       <c r="F95" s="7" t="n"/>
       <c r="G95" s="4" t="n"/>
       <c r="H95" s="7">
@@ -9681,7 +9693,7 @@
     </row>
     <row r="96">
       <c r="D96" s="7" t="n"/>
-      <c r="E96" s="16" t="n"/>
+      <c r="E96" s="17" t="n"/>
       <c r="F96" s="7" t="n"/>
       <c r="G96" s="4" t="n"/>
       <c r="H96" s="7">
@@ -9699,7 +9711,7 @@
     </row>
     <row r="97">
       <c r="D97" s="7" t="n"/>
-      <c r="E97" s="16" t="n"/>
+      <c r="E97" s="17" t="n"/>
       <c r="F97" s="7" t="n"/>
       <c r="G97" s="4" t="n"/>
       <c r="H97" s="7">
@@ -9717,7 +9729,7 @@
     </row>
     <row r="98">
       <c r="D98" s="7" t="n"/>
-      <c r="E98" s="16" t="n"/>
+      <c r="E98" s="17" t="n"/>
       <c r="F98" s="7" t="n"/>
       <c r="G98" s="4" t="n"/>
       <c r="H98" s="7">
@@ -9735,7 +9747,7 @@
     </row>
     <row r="99">
       <c r="D99" s="7" t="n"/>
-      <c r="E99" s="16" t="n"/>
+      <c r="E99" s="17" t="n"/>
       <c r="F99" s="7" t="n"/>
       <c r="G99" s="4" t="n"/>
       <c r="H99" s="7">
@@ -9753,7 +9765,7 @@
     </row>
     <row r="100">
       <c r="D100" s="7" t="n"/>
-      <c r="E100" s="16" t="n"/>
+      <c r="E100" s="17" t="n"/>
       <c r="F100" s="7" t="n"/>
       <c r="G100" s="4" t="n"/>
       <c r="H100" s="7">
@@ -9771,7 +9783,7 @@
     </row>
     <row r="101">
       <c r="D101" s="7" t="n"/>
-      <c r="E101" s="16" t="n"/>
+      <c r="E101" s="17" t="n"/>
       <c r="F101" s="7" t="n"/>
       <c r="G101" s="4" t="n"/>
       <c r="H101" s="7">
@@ -9789,7 +9801,7 @@
     </row>
     <row r="102">
       <c r="D102" s="7" t="n"/>
-      <c r="E102" s="16" t="n"/>
+      <c r="E102" s="17" t="n"/>
       <c r="F102" s="7" t="n"/>
       <c r="G102" s="4" t="n"/>
       <c r="H102" s="7">
@@ -9807,7 +9819,7 @@
     </row>
     <row r="103">
       <c r="D103" s="7" t="n"/>
-      <c r="E103" s="16" t="n"/>
+      <c r="E103" s="17" t="n"/>
       <c r="F103" s="7" t="n"/>
       <c r="G103" s="4" t="n"/>
       <c r="H103" s="7">
@@ -9825,7 +9837,7 @@
     </row>
     <row r="104">
       <c r="D104" s="7" t="n"/>
-      <c r="E104" s="16" t="n"/>
+      <c r="E104" s="17" t="n"/>
       <c r="F104" s="7" t="n"/>
       <c r="G104" s="4" t="n"/>
       <c r="H104" s="7">
@@ -9843,7 +9855,7 @@
     </row>
     <row r="105">
       <c r="D105" s="7" t="n"/>
-      <c r="E105" s="16" t="n"/>
+      <c r="E105" s="17" t="n"/>
       <c r="F105" s="7" t="n"/>
       <c r="G105" s="4" t="n"/>
       <c r="H105" s="7">
@@ -9861,7 +9873,7 @@
     </row>
     <row r="106">
       <c r="D106" s="7" t="n"/>
-      <c r="E106" s="16" t="n"/>
+      <c r="E106" s="17" t="n"/>
       <c r="F106" s="7" t="n"/>
       <c r="G106" s="4" t="n"/>
       <c r="H106" s="7">
@@ -9879,7 +9891,7 @@
     </row>
     <row r="107">
       <c r="D107" s="7" t="n"/>
-      <c r="E107" s="16" t="n"/>
+      <c r="E107" s="17" t="n"/>
       <c r="F107" s="7" t="n"/>
       <c r="G107" s="4" t="n"/>
       <c r="H107" s="7">
@@ -9897,7 +9909,7 @@
     </row>
     <row r="108">
       <c r="D108" s="7" t="n"/>
-      <c r="E108" s="16" t="n"/>
+      <c r="E108" s="17" t="n"/>
       <c r="F108" s="7" t="n"/>
       <c r="G108" s="4" t="n"/>
       <c r="H108" s="7">
@@ -9915,7 +9927,7 @@
     </row>
     <row r="109">
       <c r="D109" s="7" t="n"/>
-      <c r="E109" s="16" t="n"/>
+      <c r="E109" s="17" t="n"/>
       <c r="F109" s="7" t="n"/>
       <c r="G109" s="4" t="n"/>
       <c r="H109" s="7">
@@ -9933,7 +9945,7 @@
     </row>
     <row r="110">
       <c r="D110" s="7" t="n"/>
-      <c r="E110" s="16" t="n"/>
+      <c r="E110" s="17" t="n"/>
       <c r="F110" s="7" t="n"/>
       <c r="G110" s="4" t="n"/>
       <c r="H110" s="7">
@@ -9951,7 +9963,7 @@
     </row>
     <row r="111">
       <c r="D111" s="7" t="n"/>
-      <c r="E111" s="16" t="n"/>
+      <c r="E111" s="17" t="n"/>
       <c r="F111" s="7" t="n"/>
       <c r="G111" s="4" t="n"/>
       <c r="H111" s="7">
@@ -9969,7 +9981,7 @@
     </row>
     <row r="112">
       <c r="D112" s="7" t="n"/>
-      <c r="E112" s="16" t="n"/>
+      <c r="E112" s="17" t="n"/>
       <c r="F112" s="7" t="n"/>
       <c r="G112" s="4" t="n"/>
       <c r="H112" s="7">
@@ -9987,7 +9999,7 @@
     </row>
     <row r="113">
       <c r="D113" s="7" t="n"/>
-      <c r="E113" s="16" t="n"/>
+      <c r="E113" s="17" t="n"/>
       <c r="F113" s="7" t="n"/>
       <c r="G113" s="4" t="n"/>
       <c r="H113" s="7">
@@ -10005,7 +10017,7 @@
     </row>
     <row r="114">
       <c r="D114" s="7" t="n"/>
-      <c r="E114" s="16" t="n"/>
+      <c r="E114" s="17" t="n"/>
       <c r="F114" s="7" t="n"/>
       <c r="G114" s="4" t="n"/>
       <c r="H114" s="7">
@@ -10023,7 +10035,7 @@
     </row>
     <row r="115">
       <c r="D115" s="7" t="n"/>
-      <c r="E115" s="16" t="n"/>
+      <c r="E115" s="17" t="n"/>
       <c r="F115" s="7" t="n"/>
       <c r="G115" s="4" t="n"/>
       <c r="H115" s="7">
@@ -10041,7 +10053,7 @@
     </row>
     <row r="116">
       <c r="D116" s="7" t="n"/>
-      <c r="E116" s="16" t="n"/>
+      <c r="E116" s="17" t="n"/>
       <c r="F116" s="7" t="n"/>
       <c r="G116" s="4" t="n"/>
       <c r="H116" s="7">
@@ -10059,7 +10071,7 @@
     </row>
     <row r="117">
       <c r="D117" s="7" t="n"/>
-      <c r="E117" s="16" t="n"/>
+      <c r="E117" s="17" t="n"/>
       <c r="F117" s="7" t="n"/>
       <c r="G117" s="4" t="n"/>
       <c r="H117" s="7">
@@ -10077,7 +10089,7 @@
     </row>
     <row r="118">
       <c r="D118" s="7" t="n"/>
-      <c r="E118" s="16" t="n"/>
+      <c r="E118" s="17" t="n"/>
       <c r="F118" s="7" t="n"/>
       <c r="G118" s="4" t="n"/>
       <c r="H118" s="7">
@@ -10095,7 +10107,7 @@
     </row>
     <row r="119">
       <c r="D119" s="7" t="n"/>
-      <c r="E119" s="16" t="n"/>
+      <c r="E119" s="17" t="n"/>
       <c r="F119" s="7" t="n"/>
       <c r="G119" s="4" t="n"/>
       <c r="H119" s="7">
@@ -10113,7 +10125,7 @@
     </row>
     <row r="120">
       <c r="D120" s="7" t="n"/>
-      <c r="E120" s="16" t="n"/>
+      <c r="E120" s="17" t="n"/>
       <c r="F120" s="7" t="n"/>
       <c r="G120" s="4" t="n"/>
       <c r="H120" s="7">
@@ -10131,7 +10143,7 @@
     </row>
     <row r="121">
       <c r="D121" s="7" t="n"/>
-      <c r="E121" s="16" t="n"/>
+      <c r="E121" s="17" t="n"/>
       <c r="F121" s="7" t="n"/>
       <c r="G121" s="4" t="n"/>
       <c r="H121" s="7">
@@ -10149,7 +10161,7 @@
     </row>
     <row r="122">
       <c r="D122" s="7" t="n"/>
-      <c r="E122" s="16" t="n"/>
+      <c r="E122" s="17" t="n"/>
       <c r="F122" s="7" t="n"/>
       <c r="G122" s="4" t="n"/>
       <c r="H122" s="7">
@@ -10167,7 +10179,7 @@
     </row>
     <row r="123">
       <c r="D123" s="7" t="n"/>
-      <c r="E123" s="16" t="n"/>
+      <c r="E123" s="17" t="n"/>
       <c r="F123" s="7" t="n"/>
       <c r="G123" s="4" t="n"/>
       <c r="H123" s="7">
@@ -10185,7 +10197,7 @@
     </row>
     <row r="124">
       <c r="D124" s="7" t="n"/>
-      <c r="E124" s="16" t="n"/>
+      <c r="E124" s="17" t="n"/>
       <c r="F124" s="7" t="n"/>
       <c r="G124" s="4" t="n"/>
       <c r="H124" s="7">
@@ -10203,7 +10215,7 @@
     </row>
     <row r="125">
       <c r="D125" s="7" t="n"/>
-      <c r="E125" s="16" t="n"/>
+      <c r="E125" s="17" t="n"/>
       <c r="F125" s="7" t="n"/>
       <c r="G125" s="4" t="n"/>
       <c r="H125" s="7">
@@ -10221,7 +10233,7 @@
     </row>
     <row r="126">
       <c r="D126" s="7" t="n"/>
-      <c r="E126" s="16" t="n"/>
+      <c r="E126" s="17" t="n"/>
       <c r="F126" s="7" t="n"/>
       <c r="G126" s="4" t="n"/>
       <c r="H126" s="7">
@@ -10239,7 +10251,7 @@
     </row>
     <row r="127">
       <c r="D127" s="7" t="n"/>
-      <c r="E127" s="16" t="n"/>
+      <c r="E127" s="17" t="n"/>
       <c r="F127" s="7" t="n"/>
       <c r="G127" s="4" t="n"/>
       <c r="H127" s="7">
@@ -10257,7 +10269,7 @@
     </row>
     <row r="128">
       <c r="D128" s="7" t="n"/>
-      <c r="E128" s="16" t="n"/>
+      <c r="E128" s="17" t="n"/>
       <c r="F128" s="7" t="n"/>
       <c r="G128" s="4" t="n"/>
       <c r="H128" s="7">
@@ -10275,7 +10287,7 @@
     </row>
     <row r="129">
       <c r="D129" s="7" t="n"/>
-      <c r="E129" s="16" t="n"/>
+      <c r="E129" s="17" t="n"/>
       <c r="F129" s="7" t="n"/>
       <c r="G129" s="4" t="n"/>
       <c r="H129" s="7">
@@ -10293,7 +10305,7 @@
     </row>
     <row r="130">
       <c r="D130" s="7" t="n"/>
-      <c r="E130" s="16" t="n"/>
+      <c r="E130" s="17" t="n"/>
       <c r="F130" s="7" t="n"/>
       <c r="G130" s="4" t="n"/>
       <c r="H130" s="7">
@@ -10311,7 +10323,7 @@
     </row>
     <row r="131">
       <c r="D131" s="7" t="n"/>
-      <c r="E131" s="16" t="n"/>
+      <c r="E131" s="17" t="n"/>
       <c r="F131" s="7" t="n"/>
       <c r="G131" s="4" t="n"/>
       <c r="H131" s="7">
@@ -10329,7 +10341,7 @@
     </row>
     <row r="132">
       <c r="D132" s="7" t="n"/>
-      <c r="E132" s="16" t="n"/>
+      <c r="E132" s="17" t="n"/>
       <c r="F132" s="7" t="n"/>
       <c r="G132" s="4" t="n"/>
       <c r="H132" s="7">
@@ -10347,7 +10359,7 @@
     </row>
     <row r="133">
       <c r="D133" s="7" t="n"/>
-      <c r="E133" s="16" t="n"/>
+      <c r="E133" s="17" t="n"/>
       <c r="F133" s="7" t="n"/>
       <c r="G133" s="4" t="n"/>
       <c r="H133" s="7">
@@ -10365,7 +10377,7 @@
     </row>
     <row r="134">
       <c r="D134" s="7" t="n"/>
-      <c r="E134" s="16" t="n"/>
+      <c r="E134" s="17" t="n"/>
       <c r="F134" s="7" t="n"/>
       <c r="G134" s="4" t="n"/>
       <c r="H134" s="7">
@@ -10383,7 +10395,7 @@
     </row>
     <row r="135">
       <c r="D135" s="7" t="n"/>
-      <c r="E135" s="16" t="n"/>
+      <c r="E135" s="17" t="n"/>
       <c r="F135" s="7" t="n"/>
       <c r="G135" s="4" t="n"/>
       <c r="H135" s="7">
@@ -10401,7 +10413,7 @@
     </row>
     <row r="136">
       <c r="D136" s="7" t="n"/>
-      <c r="E136" s="16" t="n"/>
+      <c r="E136" s="17" t="n"/>
       <c r="F136" s="7" t="n"/>
       <c r="G136" s="4" t="n"/>
       <c r="H136" s="7">
@@ -10419,7 +10431,7 @@
     </row>
     <row r="137">
       <c r="D137" s="7" t="n"/>
-      <c r="E137" s="16" t="n"/>
+      <c r="E137" s="17" t="n"/>
       <c r="F137" s="7" t="n"/>
       <c r="G137" s="4" t="n"/>
       <c r="H137" s="7">
@@ -10437,7 +10449,7 @@
     </row>
     <row r="138">
       <c r="D138" s="7" t="n"/>
-      <c r="E138" s="16" t="n"/>
+      <c r="E138" s="17" t="n"/>
       <c r="F138" s="7" t="n"/>
       <c r="G138" s="4" t="n"/>
       <c r="H138" s="7">
@@ -10455,7 +10467,7 @@
     </row>
     <row r="139">
       <c r="D139" s="7" t="n"/>
-      <c r="E139" s="16" t="n"/>
+      <c r="E139" s="17" t="n"/>
       <c r="F139" s="7" t="n"/>
       <c r="G139" s="4" t="n"/>
       <c r="H139" s="7">
@@ -10473,7 +10485,7 @@
     </row>
     <row r="140">
       <c r="D140" s="7" t="n"/>
-      <c r="E140" s="16" t="n"/>
+      <c r="E140" s="17" t="n"/>
       <c r="F140" s="7" t="n"/>
       <c r="G140" s="4" t="n"/>
       <c r="H140" s="7">
@@ -10491,7 +10503,7 @@
     </row>
     <row r="141">
       <c r="D141" s="7" t="n"/>
-      <c r="E141" s="16" t="n"/>
+      <c r="E141" s="17" t="n"/>
       <c r="F141" s="7" t="n"/>
       <c r="G141" s="4" t="n"/>
       <c r="H141" s="7">
@@ -10509,7 +10521,7 @@
     </row>
     <row r="142">
       <c r="D142" s="7" t="n"/>
-      <c r="E142" s="16" t="n"/>
+      <c r="E142" s="17" t="n"/>
       <c r="F142" s="7" t="n"/>
       <c r="G142" s="4" t="n"/>
       <c r="H142" s="7">
@@ -10527,7 +10539,7 @@
     </row>
     <row r="143">
       <c r="D143" s="7" t="n"/>
-      <c r="E143" s="16" t="n"/>
+      <c r="E143" s="17" t="n"/>
       <c r="F143" s="7" t="n"/>
       <c r="G143" s="4" t="n"/>
       <c r="H143" s="7">
@@ -10545,7 +10557,7 @@
     </row>
     <row r="144">
       <c r="D144" s="7" t="n"/>
-      <c r="E144" s="16" t="n"/>
+      <c r="E144" s="17" t="n"/>
       <c r="F144" s="7" t="n"/>
       <c r="G144" s="4" t="n"/>
       <c r="H144" s="7">
@@ -10563,7 +10575,7 @@
     </row>
     <row r="145">
       <c r="D145" s="7" t="n"/>
-      <c r="E145" s="16" t="n"/>
+      <c r="E145" s="17" t="n"/>
       <c r="F145" s="7" t="n"/>
       <c r="G145" s="4" t="n"/>
       <c r="H145" s="7">
@@ -10581,7 +10593,7 @@
     </row>
     <row r="146">
       <c r="D146" s="7" t="n"/>
-      <c r="E146" s="16" t="n"/>
+      <c r="E146" s="17" t="n"/>
       <c r="F146" s="7" t="n"/>
       <c r="G146" s="4" t="n"/>
       <c r="H146" s="7">
@@ -10599,7 +10611,7 @@
     </row>
     <row r="147">
       <c r="D147" s="7" t="n"/>
-      <c r="E147" s="16" t="n"/>
+      <c r="E147" s="17" t="n"/>
       <c r="F147" s="7" t="n"/>
       <c r="G147" s="4" t="n"/>
       <c r="H147" s="7">
@@ -10617,7 +10629,7 @@
     </row>
     <row r="148">
       <c r="D148" s="7" t="n"/>
-      <c r="E148" s="16" t="n"/>
+      <c r="E148" s="17" t="n"/>
       <c r="F148" s="7" t="n"/>
       <c r="G148" s="4" t="n"/>
       <c r="H148" s="7">
@@ -10635,7 +10647,7 @@
     </row>
     <row r="149">
       <c r="D149" s="7" t="n"/>
-      <c r="E149" s="16" t="n"/>
+      <c r="E149" s="17" t="n"/>
       <c r="F149" s="7" t="n"/>
       <c r="G149" s="4" t="n"/>
       <c r="H149" s="7">
@@ -10653,7 +10665,7 @@
     </row>
     <row r="150">
       <c r="D150" s="7" t="n"/>
-      <c r="E150" s="16" t="n"/>
+      <c r="E150" s="17" t="n"/>
       <c r="F150" s="7" t="n"/>
       <c r="G150" s="4" t="n"/>
       <c r="H150" s="7">
@@ -10671,7 +10683,7 @@
     </row>
     <row r="151">
       <c r="D151" s="7" t="n"/>
-      <c r="E151" s="16" t="n"/>
+      <c r="E151" s="17" t="n"/>
       <c r="F151" s="7" t="n"/>
       <c r="G151" s="4" t="n"/>
       <c r="H151" s="7">
@@ -10689,7 +10701,7 @@
     </row>
     <row r="152">
       <c r="D152" s="7" t="n"/>
-      <c r="E152" s="16" t="n"/>
+      <c r="E152" s="17" t="n"/>
       <c r="F152" s="7" t="n"/>
       <c r="G152" s="4" t="n"/>
       <c r="H152" s="7">
@@ -10707,7 +10719,7 @@
     </row>
     <row r="153">
       <c r="D153" s="7" t="n"/>
-      <c r="E153" s="16" t="n"/>
+      <c r="E153" s="17" t="n"/>
       <c r="F153" s="7" t="n"/>
       <c r="G153" s="4" t="n"/>
       <c r="H153" s="7">
@@ -10725,7 +10737,7 @@
     </row>
     <row r="154">
       <c r="D154" s="7" t="n"/>
-      <c r="E154" s="16" t="n"/>
+      <c r="E154" s="17" t="n"/>
       <c r="F154" s="7" t="n"/>
       <c r="G154" s="4" t="n"/>
       <c r="H154" s="7">
@@ -10743,7 +10755,7 @@
     </row>
     <row r="155">
       <c r="D155" s="7" t="n"/>
-      <c r="E155" s="16" t="n"/>
+      <c r="E155" s="17" t="n"/>
       <c r="F155" s="7" t="n"/>
       <c r="G155" s="4" t="n"/>
       <c r="H155" s="7">
@@ -10761,7 +10773,7 @@
     </row>
     <row r="156">
       <c r="D156" s="7" t="n"/>
-      <c r="E156" s="16" t="n"/>
+      <c r="E156" s="17" t="n"/>
       <c r="F156" s="7" t="n"/>
       <c r="G156" s="4" t="n"/>
       <c r="H156" s="7">
@@ -10779,7 +10791,7 @@
     </row>
     <row r="157">
       <c r="D157" s="7" t="n"/>
-      <c r="E157" s="16" t="n"/>
+      <c r="E157" s="17" t="n"/>
       <c r="F157" s="7" t="n"/>
       <c r="G157" s="4" t="n"/>
       <c r="H157" s="7">
@@ -10797,7 +10809,7 @@
     </row>
     <row r="158">
       <c r="D158" s="7" t="n"/>
-      <c r="E158" s="16" t="n"/>
+      <c r="E158" s="17" t="n"/>
       <c r="F158" s="7" t="n"/>
       <c r="G158" s="4" t="n"/>
       <c r="H158" s="7">
@@ -10815,7 +10827,7 @@
     </row>
     <row r="159">
       <c r="D159" s="7" t="n"/>
-      <c r="E159" s="16" t="n"/>
+      <c r="E159" s="17" t="n"/>
       <c r="F159" s="7" t="n"/>
       <c r="G159" s="4" t="n"/>
       <c r="H159" s="7">
@@ -10833,7 +10845,7 @@
     </row>
     <row r="160">
       <c r="D160" s="7" t="n"/>
-      <c r="E160" s="16" t="n"/>
+      <c r="E160" s="17" t="n"/>
       <c r="F160" s="7" t="n"/>
       <c r="G160" s="4" t="n"/>
       <c r="H160" s="7">
@@ -10851,7 +10863,7 @@
     </row>
     <row r="161">
       <c r="D161" s="7" t="n"/>
-      <c r="E161" s="16" t="n"/>
+      <c r="E161" s="17" t="n"/>
       <c r="F161" s="7" t="n"/>
       <c r="G161" s="4" t="n"/>
       <c r="H161" s="7">
@@ -10869,7 +10881,7 @@
     </row>
     <row r="162">
       <c r="D162" s="7" t="n"/>
-      <c r="E162" s="16" t="n"/>
+      <c r="E162" s="17" t="n"/>
       <c r="F162" s="7" t="n"/>
       <c r="G162" s="4" t="n"/>
       <c r="H162" s="7">
@@ -10887,7 +10899,7 @@
     </row>
     <row r="163">
       <c r="D163" s="7" t="n"/>
-      <c r="E163" s="16" t="n"/>
+      <c r="E163" s="17" t="n"/>
       <c r="F163" s="7" t="n"/>
       <c r="G163" s="4" t="n"/>
       <c r="H163" s="7">
@@ -10905,7 +10917,7 @@
     </row>
     <row r="164">
       <c r="D164" s="7" t="n"/>
-      <c r="E164" s="16" t="n"/>
+      <c r="E164" s="17" t="n"/>
       <c r="F164" s="7" t="n"/>
       <c r="G164" s="4" t="n"/>
       <c r="H164" s="7">
@@ -10923,7 +10935,7 @@
     </row>
     <row r="165">
       <c r="D165" s="7" t="n"/>
-      <c r="E165" s="16" t="n"/>
+      <c r="E165" s="17" t="n"/>
       <c r="F165" s="7" t="n"/>
       <c r="G165" s="4" t="n"/>
       <c r="H165" s="7">
@@ -10941,7 +10953,7 @@
     </row>
     <row r="166">
       <c r="D166" s="7" t="n"/>
-      <c r="E166" s="16" t="n"/>
+      <c r="E166" s="17" t="n"/>
       <c r="F166" s="7" t="n"/>
       <c r="G166" s="4" t="n"/>
       <c r="H166" s="7">
@@ -10959,7 +10971,7 @@
     </row>
     <row r="167">
       <c r="D167" s="7" t="n"/>
-      <c r="E167" s="16" t="n"/>
+      <c r="E167" s="17" t="n"/>
       <c r="F167" s="7" t="n"/>
       <c r="G167" s="4" t="n"/>
       <c r="H167" s="7">
@@ -10977,7 +10989,7 @@
     </row>
     <row r="168">
       <c r="D168" s="7" t="n"/>
-      <c r="E168" s="16" t="n"/>
+      <c r="E168" s="17" t="n"/>
       <c r="F168" s="7" t="n"/>
       <c r="G168" s="4" t="n"/>
       <c r="H168" s="7">
@@ -10995,7 +11007,7 @@
     </row>
     <row r="169">
       <c r="D169" s="7" t="n"/>
-      <c r="E169" s="16" t="n"/>
+      <c r="E169" s="17" t="n"/>
       <c r="F169" s="7" t="n"/>
       <c r="G169" s="4" t="n"/>
       <c r="H169" s="7">
@@ -11013,7 +11025,7 @@
     </row>
     <row r="170">
       <c r="D170" s="7" t="n"/>
-      <c r="E170" s="16" t="n"/>
+      <c r="E170" s="17" t="n"/>
       <c r="F170" s="7" t="n"/>
       <c r="G170" s="4" t="n"/>
       <c r="H170" s="7">
@@ -11031,7 +11043,7 @@
     </row>
     <row r="171">
       <c r="D171" s="7" t="n"/>
-      <c r="E171" s="16" t="n"/>
+      <c r="E171" s="17" t="n"/>
       <c r="F171" s="7" t="n"/>
       <c r="G171" s="4" t="n"/>
       <c r="H171" s="7">
@@ -11049,7 +11061,7 @@
     </row>
     <row r="172">
       <c r="D172" s="7" t="n"/>
-      <c r="E172" s="16" t="n"/>
+      <c r="E172" s="17" t="n"/>
       <c r="F172" s="7" t="n"/>
       <c r="G172" s="4" t="n"/>
       <c r="H172" s="7">
@@ -11067,7 +11079,7 @@
     </row>
     <row r="173">
       <c r="D173" s="7" t="n"/>
-      <c r="E173" s="16" t="n"/>
+      <c r="E173" s="17" t="n"/>
       <c r="F173" s="7" t="n"/>
       <c r="G173" s="4" t="n"/>
       <c r="H173" s="7">
@@ -11085,7 +11097,7 @@
     </row>
     <row r="174">
       <c r="D174" s="7" t="n"/>
-      <c r="E174" s="16" t="n"/>
+      <c r="E174" s="17" t="n"/>
       <c r="F174" s="7" t="n"/>
       <c r="G174" s="4" t="n"/>
       <c r="H174" s="7">
@@ -11103,7 +11115,7 @@
     </row>
     <row r="175">
       <c r="D175" s="7" t="n"/>
-      <c r="E175" s="16" t="n"/>
+      <c r="E175" s="17" t="n"/>
       <c r="F175" s="7" t="n"/>
       <c r="G175" s="4" t="n"/>
       <c r="H175" s="7">
@@ -11121,7 +11133,7 @@
     </row>
     <row r="176">
       <c r="D176" s="7" t="n"/>
-      <c r="E176" s="16" t="n"/>
+      <c r="E176" s="17" t="n"/>
       <c r="F176" s="7" t="n"/>
       <c r="G176" s="4" t="n"/>
       <c r="H176" s="7">
@@ -11139,7 +11151,7 @@
     </row>
     <row r="177">
       <c r="D177" s="7" t="n"/>
-      <c r="E177" s="16" t="n"/>
+      <c r="E177" s="17" t="n"/>
       <c r="F177" s="7" t="n"/>
       <c r="G177" s="4" t="n"/>
       <c r="H177" s="7">
@@ -11157,7 +11169,7 @@
     </row>
     <row r="178">
       <c r="D178" s="7" t="n"/>
-      <c r="E178" s="16" t="n"/>
+      <c r="E178" s="17" t="n"/>
       <c r="F178" s="7" t="n"/>
       <c r="G178" s="4" t="n"/>
       <c r="H178" s="7">
@@ -11175,7 +11187,7 @@
     </row>
     <row r="179">
       <c r="D179" s="7" t="n"/>
-      <c r="E179" s="16" t="n"/>
+      <c r="E179" s="17" t="n"/>
       <c r="F179" s="7" t="n"/>
       <c r="G179" s="4" t="n"/>
       <c r="H179" s="7">
@@ -11193,7 +11205,7 @@
     </row>
     <row r="180">
       <c r="D180" s="7" t="n"/>
-      <c r="E180" s="16" t="n"/>
+      <c r="E180" s="17" t="n"/>
       <c r="F180" s="7" t="n"/>
       <c r="G180" s="4" t="n"/>
       <c r="H180" s="7">
@@ -11211,7 +11223,7 @@
     </row>
     <row r="181">
       <c r="D181" s="7" t="n"/>
-      <c r="E181" s="16" t="n"/>
+      <c r="E181" s="17" t="n"/>
       <c r="F181" s="7" t="n"/>
       <c r="G181" s="4" t="n"/>
       <c r="H181" s="7">
@@ -11229,7 +11241,7 @@
     </row>
     <row r="182">
       <c r="D182" s="7" t="n"/>
-      <c r="E182" s="16" t="n"/>
+      <c r="E182" s="17" t="n"/>
       <c r="F182" s="7" t="n"/>
       <c r="G182" s="4" t="n"/>
       <c r="H182" s="7">
@@ -11247,7 +11259,7 @@
     </row>
     <row r="183">
       <c r="D183" s="7" t="n"/>
-      <c r="E183" s="16" t="n"/>
+      <c r="E183" s="17" t="n"/>
       <c r="F183" s="7" t="n"/>
       <c r="G183" s="4" t="n"/>
       <c r="H183" s="7">
@@ -11265,7 +11277,7 @@
     </row>
     <row r="184">
       <c r="D184" s="7" t="n"/>
-      <c r="E184" s="16" t="n"/>
+      <c r="E184" s="17" t="n"/>
       <c r="F184" s="7" t="n"/>
       <c r="G184" s="4" t="n"/>
       <c r="H184" s="7">
@@ -11283,7 +11295,7 @@
     </row>
     <row r="185">
       <c r="D185" s="7" t="n"/>
-      <c r="E185" s="16" t="n"/>
+      <c r="E185" s="17" t="n"/>
       <c r="F185" s="7" t="n"/>
       <c r="G185" s="4" t="n"/>
       <c r="H185" s="7">
@@ -11301,7 +11313,7 @@
     </row>
     <row r="186">
       <c r="D186" s="7" t="n"/>
-      <c r="E186" s="16" t="n"/>
+      <c r="E186" s="17" t="n"/>
       <c r="F186" s="7" t="n"/>
       <c r="G186" s="4" t="n"/>
       <c r="H186" s="7">
@@ -11319,7 +11331,7 @@
     </row>
     <row r="187">
       <c r="D187" s="7" t="n"/>
-      <c r="E187" s="16" t="n"/>
+      <c r="E187" s="17" t="n"/>
       <c r="F187" s="7" t="n"/>
       <c r="G187" s="4" t="n"/>
       <c r="H187" s="7">
@@ -11337,7 +11349,7 @@
     </row>
     <row r="188">
       <c r="D188" s="7" t="n"/>
-      <c r="E188" s="16" t="n"/>
+      <c r="E188" s="17" t="n"/>
       <c r="F188" s="7" t="n"/>
       <c r="G188" s="4" t="n"/>
       <c r="H188" s="7">
@@ -11355,7 +11367,7 @@
     </row>
     <row r="189">
       <c r="D189" s="7" t="n"/>
-      <c r="E189" s="16" t="n"/>
+      <c r="E189" s="17" t="n"/>
       <c r="F189" s="7" t="n"/>
       <c r="G189" s="4" t="n"/>
       <c r="H189" s="7">
@@ -11373,7 +11385,7 @@
     </row>
     <row r="190">
       <c r="D190" s="7" t="n"/>
-      <c r="E190" s="16" t="n"/>
+      <c r="E190" s="17" t="n"/>
       <c r="F190" s="7" t="n"/>
       <c r="G190" s="4" t="n"/>
       <c r="H190" s="7">
@@ -11391,7 +11403,7 @@
     </row>
     <row r="191">
       <c r="D191" s="7" t="n"/>
-      <c r="E191" s="16" t="n"/>
+      <c r="E191" s="17" t="n"/>
       <c r="F191" s="7" t="n"/>
       <c r="G191" s="4" t="n"/>
       <c r="H191" s="7">
@@ -11409,7 +11421,7 @@
     </row>
     <row r="192">
       <c r="D192" s="7" t="n"/>
-      <c r="E192" s="16" t="n"/>
+      <c r="E192" s="17" t="n"/>
       <c r="F192" s="7" t="n"/>
       <c r="G192" s="4" t="n"/>
       <c r="H192" s="7">
@@ -11427,7 +11439,7 @@
     </row>
     <row r="193">
       <c r="D193" s="7" t="n"/>
-      <c r="E193" s="16" t="n"/>
+      <c r="E193" s="17" t="n"/>
       <c r="F193" s="7" t="n"/>
       <c r="G193" s="4" t="n"/>
       <c r="H193" s="7">
@@ -11445,7 +11457,7 @@
     </row>
     <row r="194">
       <c r="D194" s="7" t="n"/>
-      <c r="E194" s="16" t="n"/>
+      <c r="E194" s="17" t="n"/>
       <c r="F194" s="7" t="n"/>
       <c r="G194" s="4" t="n"/>
       <c r="H194" s="7">
@@ -11463,7 +11475,7 @@
     </row>
     <row r="195">
       <c r="D195" s="7" t="n"/>
-      <c r="E195" s="16" t="n"/>
+      <c r="E195" s="17" t="n"/>
       <c r="F195" s="7" t="n"/>
       <c r="G195" s="4" t="n"/>
       <c r="H195" s="7">
@@ -11481,7 +11493,7 @@
     </row>
     <row r="196">
       <c r="D196" s="7" t="n"/>
-      <c r="E196" s="16" t="n"/>
+      <c r="E196" s="17" t="n"/>
       <c r="F196" s="7" t="n"/>
       <c r="G196" s="4" t="n"/>
       <c r="H196" s="7">
@@ -11499,7 +11511,7 @@
     </row>
     <row r="197">
       <c r="D197" s="7" t="n"/>
-      <c r="E197" s="16" t="n"/>
+      <c r="E197" s="17" t="n"/>
       <c r="F197" s="7" t="n"/>
       <c r="G197" s="4" t="n"/>
       <c r="H197" s="7">
@@ -11517,7 +11529,7 @@
     </row>
     <row r="198">
       <c r="D198" s="7" t="n"/>
-      <c r="E198" s="16" t="n"/>
+      <c r="E198" s="17" t="n"/>
       <c r="F198" s="7" t="n"/>
       <c r="G198" s="4" t="n"/>
       <c r="H198" s="7">
@@ -11535,7 +11547,7 @@
     </row>
     <row r="199">
       <c r="D199" s="7" t="n"/>
-      <c r="E199" s="16" t="n"/>
+      <c r="E199" s="17" t="n"/>
       <c r="F199" s="7" t="n"/>
       <c r="G199" s="4" t="n"/>
       <c r="H199" s="7">
@@ -11553,7 +11565,7 @@
     </row>
     <row r="200">
       <c r="D200" s="7" t="n"/>
-      <c r="E200" s="16" t="n"/>
+      <c r="E200" s="17" t="n"/>
       <c r="F200" s="7" t="n"/>
       <c r="G200" s="4" t="n"/>
       <c r="H200" s="7">
@@ -11571,7 +11583,7 @@
     </row>
     <row r="201">
       <c r="D201" s="7" t="n"/>
-      <c r="E201" s="16" t="n"/>
+      <c r="E201" s="17" t="n"/>
       <c r="F201" s="7" t="n"/>
       <c r="G201" s="4" t="n"/>
       <c r="H201" s="7">
@@ -11589,7 +11601,7 @@
     </row>
     <row r="202">
       <c r="D202" s="7" t="n"/>
-      <c r="E202" s="16" t="n"/>
+      <c r="E202" s="17" t="n"/>
       <c r="F202" s="7" t="n"/>
       <c r="G202" s="4" t="n"/>
       <c r="H202" s="7">
@@ -11607,7 +11619,7 @@
     </row>
     <row r="203">
       <c r="D203" s="7" t="n"/>
-      <c r="E203" s="16" t="n"/>
+      <c r="E203" s="17" t="n"/>
       <c r="F203" s="7" t="n"/>
       <c r="G203" s="4" t="n"/>
       <c r="H203" s="7">
@@ -11625,7 +11637,7 @@
     </row>
     <row r="204">
       <c r="D204" s="7" t="n"/>
-      <c r="E204" s="16" t="n"/>
+      <c r="E204" s="17" t="n"/>
       <c r="F204" s="7" t="n"/>
       <c r="G204" s="4" t="n"/>
       <c r="H204" s="7">
@@ -11643,7 +11655,7 @@
     </row>
     <row r="205">
       <c r="D205" s="7" t="n"/>
-      <c r="E205" s="16" t="n"/>
+      <c r="E205" s="17" t="n"/>
       <c r="F205" s="7" t="n"/>
       <c r="G205" s="4" t="n"/>
       <c r="H205" s="7">
@@ -11661,7 +11673,7 @@
     </row>
     <row r="206">
       <c r="D206" s="7" t="n"/>
-      <c r="E206" s="16" t="n"/>
+      <c r="E206" s="17" t="n"/>
       <c r="F206" s="7" t="n"/>
       <c r="G206" s="4" t="n"/>
       <c r="H206" s="7">
@@ -11679,7 +11691,7 @@
     </row>
     <row r="207">
       <c r="D207" s="7" t="n"/>
-      <c r="E207" s="16" t="n"/>
+      <c r="E207" s="17" t="n"/>
       <c r="F207" s="7" t="n"/>
       <c r="G207" s="4" t="n"/>
       <c r="H207" s="7">
@@ -11697,7 +11709,7 @@
     </row>
     <row r="208">
       <c r="D208" s="7" t="n"/>
-      <c r="E208" s="16" t="n"/>
+      <c r="E208" s="17" t="n"/>
       <c r="F208" s="7" t="n"/>
       <c r="G208" s="4" t="n"/>
       <c r="H208" s="7">
@@ -11715,7 +11727,7 @@
     </row>
     <row r="209">
       <c r="D209" s="7" t="n"/>
-      <c r="E209" s="16" t="n"/>
+      <c r="E209" s="17" t="n"/>
       <c r="F209" s="7" t="n"/>
       <c r="G209" s="4" t="n"/>
       <c r="H209" s="7">
@@ -11733,7 +11745,7 @@
     </row>
     <row r="210">
       <c r="D210" s="7" t="n"/>
-      <c r="E210" s="16" t="n"/>
+      <c r="E210" s="17" t="n"/>
       <c r="F210" s="7" t="n"/>
       <c r="G210" s="4" t="n"/>
       <c r="H210" s="7">
@@ -11751,7 +11763,7 @@
     </row>
     <row r="211">
       <c r="D211" s="7" t="n"/>
-      <c r="E211" s="16" t="n"/>
+      <c r="E211" s="17" t="n"/>
       <c r="F211" s="7" t="n"/>
       <c r="G211" s="4" t="n"/>
       <c r="H211" s="7">
@@ -11769,7 +11781,7 @@
     </row>
     <row r="212">
       <c r="D212" s="7" t="n"/>
-      <c r="E212" s="16" t="n"/>
+      <c r="E212" s="17" t="n"/>
       <c r="F212" s="7" t="n"/>
       <c r="G212" s="4" t="n"/>
       <c r="H212" s="7">
@@ -11787,7 +11799,7 @@
     </row>
     <row r="213">
       <c r="D213" s="7" t="n"/>
-      <c r="E213" s="16" t="n"/>
+      <c r="E213" s="17" t="n"/>
       <c r="F213" s="7" t="n"/>
       <c r="G213" s="4" t="n"/>
       <c r="H213" s="7">
@@ -11805,7 +11817,7 @@
     </row>
     <row r="214">
       <c r="D214" s="7" t="n"/>
-      <c r="E214" s="16" t="n"/>
+      <c r="E214" s="17" t="n"/>
       <c r="F214" s="7" t="n"/>
       <c r="G214" s="4" t="n"/>
       <c r="H214" s="7">
@@ -11823,7 +11835,7 @@
     </row>
     <row r="215">
       <c r="D215" s="7" t="n"/>
-      <c r="E215" s="16" t="n"/>
+      <c r="E215" s="17" t="n"/>
       <c r="F215" s="7" t="n"/>
       <c r="G215" s="4" t="n"/>
       <c r="H215" s="7">
@@ -11841,7 +11853,7 @@
     </row>
     <row r="216">
       <c r="D216" s="7" t="n"/>
-      <c r="E216" s="16" t="n"/>
+      <c r="E216" s="17" t="n"/>
       <c r="F216" s="7" t="n"/>
       <c r="G216" s="4" t="n"/>
       <c r="H216" s="7">
@@ -11859,7 +11871,7 @@
     </row>
     <row r="217">
       <c r="D217" s="7" t="n"/>
-      <c r="E217" s="16" t="n"/>
+      <c r="E217" s="17" t="n"/>
       <c r="F217" s="7" t="n"/>
       <c r="G217" s="4" t="n"/>
       <c r="H217" s="7">
@@ -11877,7 +11889,7 @@
     </row>
     <row r="218">
       <c r="D218" s="7" t="n"/>
-      <c r="E218" s="16" t="n"/>
+      <c r="E218" s="17" t="n"/>
       <c r="F218" s="7" t="n"/>
       <c r="G218" s="4" t="n"/>
       <c r="H218" s="7">
@@ -11895,7 +11907,7 @@
     </row>
     <row r="219">
       <c r="D219" s="7" t="n"/>
-      <c r="E219" s="16" t="n"/>
+      <c r="E219" s="17" t="n"/>
       <c r="F219" s="7" t="n"/>
       <c r="G219" s="4" t="n"/>
       <c r="H219" s="7">
@@ -11913,7 +11925,7 @@
     </row>
     <row r="220">
       <c r="D220" s="7" t="n"/>
-      <c r="E220" s="16" t="n"/>
+      <c r="E220" s="17" t="n"/>
       <c r="F220" s="7" t="n"/>
       <c r="G220" s="4" t="n"/>
       <c r="H220" s="7">
@@ -11931,7 +11943,7 @@
     </row>
     <row r="221">
       <c r="D221" s="7" t="n"/>
-      <c r="E221" s="16" t="n"/>
+      <c r="E221" s="17" t="n"/>
       <c r="F221" s="7" t="n"/>
       <c r="G221" s="4" t="n"/>
       <c r="H221" s="7">
@@ -11949,7 +11961,7 @@
     </row>
     <row r="222">
       <c r="D222" s="7" t="n"/>
-      <c r="E222" s="16" t="n"/>
+      <c r="E222" s="17" t="n"/>
       <c r="F222" s="7" t="n"/>
       <c r="G222" s="4" t="n"/>
       <c r="H222" s="7">
@@ -11967,7 +11979,7 @@
     </row>
     <row r="223">
       <c r="D223" s="7" t="n"/>
-      <c r="E223" s="16" t="n"/>
+      <c r="E223" s="17" t="n"/>
       <c r="F223" s="7" t="n"/>
       <c r="G223" s="4" t="n"/>
       <c r="H223" s="7">
@@ -11985,7 +11997,7 @@
     </row>
     <row r="224">
       <c r="D224" s="7" t="n"/>
-      <c r="E224" s="16" t="n"/>
+      <c r="E224" s="17" t="n"/>
       <c r="F224" s="7" t="n"/>
       <c r="G224" s="4" t="n"/>
       <c r="H224" s="7">
@@ -12003,7 +12015,7 @@
     </row>
     <row r="225">
       <c r="D225" s="7" t="n"/>
-      <c r="E225" s="16" t="n"/>
+      <c r="E225" s="17" t="n"/>
       <c r="F225" s="7" t="n"/>
       <c r="G225" s="4" t="n"/>
       <c r="H225" s="7">
@@ -12021,7 +12033,7 @@
     </row>
     <row r="226">
       <c r="D226" s="7" t="n"/>
-      <c r="E226" s="16" t="n"/>
+      <c r="E226" s="17" t="n"/>
       <c r="F226" s="7" t="n"/>
       <c r="G226" s="4" t="n"/>
       <c r="H226" s="7">
@@ -12039,7 +12051,7 @@
     </row>
     <row r="227">
       <c r="D227" s="7" t="n"/>
-      <c r="E227" s="16" t="n"/>
+      <c r="E227" s="17" t="n"/>
       <c r="F227" s="7" t="n"/>
       <c r="G227" s="4" t="n"/>
       <c r="H227" s="7">
@@ -12057,7 +12069,7 @@
     </row>
     <row r="228">
       <c r="D228" s="7" t="n"/>
-      <c r="E228" s="16" t="n"/>
+      <c r="E228" s="17" t="n"/>
       <c r="F228" s="7" t="n"/>
       <c r="G228" s="4" t="n"/>
       <c r="H228" s="7">
@@ -12075,7 +12087,7 @@
     </row>
     <row r="229">
       <c r="D229" s="7" t="n"/>
-      <c r="E229" s="16" t="n"/>
+      <c r="E229" s="17" t="n"/>
       <c r="F229" s="7" t="n"/>
       <c r="G229" s="4" t="n"/>
       <c r="H229" s="7">
@@ -12093,7 +12105,7 @@
     </row>
     <row r="230">
       <c r="D230" s="7" t="n"/>
-      <c r="E230" s="16" t="n"/>
+      <c r="E230" s="17" t="n"/>
       <c r="F230" s="7" t="n"/>
       <c r="G230" s="4" t="n"/>
       <c r="H230" s="7">
@@ -12111,7 +12123,7 @@
     </row>
     <row r="231">
       <c r="D231" s="7" t="n"/>
-      <c r="E231" s="16" t="n"/>
+      <c r="E231" s="17" t="n"/>
       <c r="F231" s="7" t="n"/>
       <c r="G231" s="4" t="n"/>
       <c r="H231" s="7">
@@ -12129,7 +12141,7 @@
     </row>
     <row r="232">
       <c r="D232" s="7" t="n"/>
-      <c r="E232" s="16" t="n"/>
+      <c r="E232" s="17" t="n"/>
       <c r="F232" s="7" t="n"/>
       <c r="G232" s="4" t="n"/>
       <c r="H232" s="7">
@@ -12147,7 +12159,7 @@
     </row>
     <row r="233">
       <c r="D233" s="7" t="n"/>
-      <c r="E233" s="16" t="n"/>
+      <c r="E233" s="17" t="n"/>
       <c r="F233" s="7" t="n"/>
       <c r="G233" s="4" t="n"/>
       <c r="H233" s="7">
@@ -12165,7 +12177,7 @@
     </row>
     <row r="234">
       <c r="D234" s="7" t="n"/>
-      <c r="E234" s="16" t="n"/>
+      <c r="E234" s="17" t="n"/>
       <c r="F234" s="7" t="n"/>
       <c r="G234" s="4" t="n"/>
       <c r="H234" s="7">
@@ -12183,7 +12195,7 @@
     </row>
     <row r="235">
       <c r="D235" s="7" t="n"/>
-      <c r="E235" s="16" t="n"/>
+      <c r="E235" s="17" t="n"/>
       <c r="F235" s="7" t="n"/>
       <c r="G235" s="4" t="n"/>
       <c r="H235" s="7">
@@ -12201,7 +12213,7 @@
     </row>
     <row r="236">
       <c r="D236" s="7" t="n"/>
-      <c r="E236" s="16" t="n"/>
+      <c r="E236" s="17" t="n"/>
       <c r="F236" s="7" t="n"/>
       <c r="G236" s="4" t="n"/>
       <c r="H236" s="7">
@@ -12219,7 +12231,7 @@
     </row>
     <row r="237">
       <c r="D237" s="7" t="n"/>
-      <c r="E237" s="16" t="n"/>
+      <c r="E237" s="17" t="n"/>
       <c r="F237" s="7" t="n"/>
       <c r="G237" s="4" t="n"/>
       <c r="H237" s="7">
@@ -12237,7 +12249,7 @@
     </row>
     <row r="238">
       <c r="D238" s="7" t="n"/>
-      <c r="E238" s="16" t="n"/>
+      <c r="E238" s="17" t="n"/>
       <c r="F238" s="7" t="n"/>
       <c r="G238" s="4" t="n"/>
       <c r="H238" s="7">
@@ -12255,7 +12267,7 @@
     </row>
     <row r="239">
       <c r="D239" s="7" t="n"/>
-      <c r="E239" s="16" t="n"/>
+      <c r="E239" s="17" t="n"/>
       <c r="F239" s="7" t="n"/>
       <c r="G239" s="4" t="n"/>
       <c r="H239" s="7">
@@ -12273,7 +12285,7 @@
     </row>
     <row r="240">
       <c r="D240" s="7" t="n"/>
-      <c r="E240" s="16" t="n"/>
+      <c r="E240" s="17" t="n"/>
       <c r="F240" s="7" t="n"/>
       <c r="G240" s="4" t="n"/>
       <c r="H240" s="7">
@@ -12291,7 +12303,7 @@
     </row>
     <row r="241">
       <c r="D241" s="7" t="n"/>
-      <c r="E241" s="16" t="n"/>
+      <c r="E241" s="17" t="n"/>
       <c r="F241" s="7" t="n"/>
       <c r="G241" s="4" t="n"/>
       <c r="H241" s="7">
@@ -12309,7 +12321,7 @@
     </row>
     <row r="242">
       <c r="D242" s="7" t="n"/>
-      <c r="E242" s="16" t="n"/>
+      <c r="E242" s="17" t="n"/>
       <c r="F242" s="7" t="n"/>
       <c r="G242" s="4" t="n"/>
       <c r="H242" s="7">
@@ -12327,7 +12339,7 @@
     </row>
     <row r="243">
       <c r="D243" s="7" t="n"/>
-      <c r="E243" s="16" t="n"/>
+      <c r="E243" s="17" t="n"/>
       <c r="F243" s="7" t="n"/>
       <c r="G243" s="4" t="n"/>
       <c r="H243" s="7">
@@ -12345,7 +12357,7 @@
     </row>
     <row r="244">
       <c r="D244" s="7" t="n"/>
-      <c r="E244" s="16" t="n"/>
+      <c r="E244" s="17" t="n"/>
       <c r="F244" s="7" t="n"/>
       <c r="G244" s="4" t="n"/>
       <c r="H244" s="7">
@@ -12363,7 +12375,7 @@
     </row>
     <row r="245">
       <c r="D245" s="7" t="n"/>
-      <c r="E245" s="16" t="n"/>
+      <c r="E245" s="17" t="n"/>
       <c r="F245" s="7" t="n"/>
       <c r="G245" s="4" t="n"/>
       <c r="H245" s="7">
@@ -12381,7 +12393,7 @@
     </row>
     <row r="246">
       <c r="D246" s="7" t="n"/>
-      <c r="E246" s="16" t="n"/>
+      <c r="E246" s="17" t="n"/>
       <c r="F246" s="7" t="n"/>
       <c r="G246" s="4" t="n"/>
       <c r="H246" s="7">
@@ -12399,7 +12411,7 @@
     </row>
     <row r="247">
       <c r="D247" s="7" t="n"/>
-      <c r="E247" s="16" t="n"/>
+      <c r="E247" s="17" t="n"/>
       <c r="F247" s="7" t="n"/>
       <c r="G247" s="4" t="n"/>
       <c r="H247" s="7">
@@ -12417,7 +12429,7 @@
     </row>
     <row r="248">
       <c r="D248" s="7" t="n"/>
-      <c r="E248" s="16" t="n"/>
+      <c r="E248" s="17" t="n"/>
       <c r="F248" s="7" t="n"/>
       <c r="G248" s="4" t="n"/>
       <c r="H248" s="7">
@@ -12435,7 +12447,7 @@
     </row>
     <row r="249">
       <c r="D249" s="7" t="n"/>
-      <c r="E249" s="16" t="n"/>
+      <c r="E249" s="17" t="n"/>
       <c r="F249" s="7" t="n"/>
       <c r="G249" s="4" t="n"/>
       <c r="H249" s="7">
@@ -12453,7 +12465,7 @@
     </row>
     <row r="250">
       <c r="D250" s="7" t="n"/>
-      <c r="E250" s="16" t="n"/>
+      <c r="E250" s="17" t="n"/>
       <c r="F250" s="7" t="n"/>
       <c r="G250" s="4" t="n"/>
       <c r="H250" s="7">
@@ -12471,7 +12483,7 @@
     </row>
     <row r="251">
       <c r="D251" s="7" t="n"/>
-      <c r="E251" s="16" t="n"/>
+      <c r="E251" s="17" t="n"/>
       <c r="F251" s="7" t="n"/>
       <c r="G251" s="4" t="n"/>
       <c r="H251" s="7">
@@ -12489,7 +12501,7 @@
     </row>
     <row r="252">
       <c r="D252" s="7" t="n"/>
-      <c r="E252" s="16" t="n"/>
+      <c r="E252" s="17" t="n"/>
       <c r="F252" s="7" t="n"/>
       <c r="G252" s="4" t="n"/>
       <c r="H252" s="7">
@@ -12507,7 +12519,7 @@
     </row>
     <row r="253">
       <c r="D253" s="7" t="n"/>
-      <c r="E253" s="16" t="n"/>
+      <c r="E253" s="17" t="n"/>
       <c r="F253" s="7" t="n"/>
       <c r="G253" s="4" t="n"/>
       <c r="H253" s="7">
@@ -12525,7 +12537,7 @@
     </row>
     <row r="254">
       <c r="D254" s="7" t="n"/>
-      <c r="E254" s="16" t="n"/>
+      <c r="E254" s="17" t="n"/>
       <c r="F254" s="7" t="n"/>
       <c r="G254" s="4" t="n"/>
       <c r="H254" s="7">
@@ -12543,7 +12555,7 @@
     </row>
     <row r="255">
       <c r="D255" s="7" t="n"/>
-      <c r="E255" s="16" t="n"/>
+      <c r="E255" s="17" t="n"/>
       <c r="F255" s="7" t="n"/>
       <c r="G255" s="4" t="n"/>
       <c r="H255" s="7">
@@ -12561,7 +12573,7 @@
     </row>
     <row r="256">
       <c r="D256" s="7" t="n"/>
-      <c r="E256" s="16" t="n"/>
+      <c r="E256" s="17" t="n"/>
       <c r="F256" s="7" t="n"/>
       <c r="G256" s="4" t="n"/>
       <c r="H256" s="7">
@@ -12579,7 +12591,7 @@
     </row>
     <row r="257">
       <c r="D257" s="7" t="n"/>
-      <c r="E257" s="16" t="n"/>
+      <c r="E257" s="17" t="n"/>
       <c r="F257" s="7" t="n"/>
       <c r="G257" s="4" t="n"/>
       <c r="H257" s="7">
@@ -12597,7 +12609,7 @@
     </row>
     <row r="258">
       <c r="D258" s="7" t="n"/>
-      <c r="E258" s="16" t="n"/>
+      <c r="E258" s="17" t="n"/>
       <c r="F258" s="7" t="n"/>
       <c r="G258" s="4" t="n"/>
       <c r="H258" s="7">
@@ -12615,7 +12627,7 @@
     </row>
     <row r="259">
       <c r="D259" s="7" t="n"/>
-      <c r="E259" s="16" t="n"/>
+      <c r="E259" s="17" t="n"/>
       <c r="F259" s="7" t="n"/>
       <c r="G259" s="4" t="n"/>
       <c r="H259" s="7">
@@ -12633,7 +12645,7 @@
     </row>
     <row r="260">
       <c r="D260" s="7" t="n"/>
-      <c r="E260" s="16" t="n"/>
+      <c r="E260" s="17" t="n"/>
       <c r="F260" s="7" t="n"/>
       <c r="G260" s="4" t="n"/>
       <c r="H260" s="7">
@@ -12651,7 +12663,7 @@
     </row>
     <row r="261">
       <c r="D261" s="7" t="n"/>
-      <c r="E261" s="16" t="n"/>
+      <c r="E261" s="17" t="n"/>
       <c r="F261" s="7" t="n"/>
       <c r="G261" s="4" t="n"/>
       <c r="H261" s="7">
@@ -12669,7 +12681,7 @@
     </row>
     <row r="262">
       <c r="D262" s="7" t="n"/>
-      <c r="E262" s="16" t="n"/>
+      <c r="E262" s="17" t="n"/>
       <c r="F262" s="7" t="n"/>
       <c r="G262" s="4" t="n"/>
       <c r="H262" s="7">
@@ -12687,7 +12699,7 @@
     </row>
     <row r="263">
       <c r="D263" s="7" t="n"/>
-      <c r="E263" s="16" t="n"/>
+      <c r="E263" s="17" t="n"/>
       <c r="F263" s="7" t="n"/>
       <c r="G263" s="4" t="n"/>
       <c r="H263" s="7">
@@ -12705,7 +12717,7 @@
     </row>
     <row r="264">
       <c r="D264" s="7" t="n"/>
-      <c r="E264" s="16" t="n"/>
+      <c r="E264" s="17" t="n"/>
       <c r="F264" s="7" t="n"/>
       <c r="G264" s="4" t="n"/>
       <c r="H264" s="7">
@@ -12723,7 +12735,7 @@
     </row>
     <row r="265">
       <c r="D265" s="7" t="n"/>
-      <c r="E265" s="16" t="n"/>
+      <c r="E265" s="17" t="n"/>
       <c r="F265" s="7" t="n"/>
       <c r="G265" s="4" t="n"/>
       <c r="H265" s="7">
@@ -12741,7 +12753,7 @@
     </row>
     <row r="266">
       <c r="D266" s="7" t="n"/>
-      <c r="E266" s="16" t="n"/>
+      <c r="E266" s="17" t="n"/>
       <c r="F266" s="7" t="n"/>
       <c r="G266" s="4" t="n"/>
       <c r="H266" s="7">
@@ -12759,7 +12771,7 @@
     </row>
     <row r="267">
       <c r="D267" s="7" t="n"/>
-      <c r="E267" s="16" t="n"/>
+      <c r="E267" s="17" t="n"/>
       <c r="F267" s="7" t="n"/>
       <c r="G267" s="4" t="n"/>
       <c r="H267" s="7">
@@ -12777,7 +12789,7 @@
     </row>
     <row r="268">
       <c r="D268" s="7" t="n"/>
-      <c r="E268" s="16" t="n"/>
+      <c r="E268" s="17" t="n"/>
       <c r="F268" s="7" t="n"/>
       <c r="G268" s="4" t="n"/>
       <c r="H268" s="7">
@@ -12795,7 +12807,7 @@
     </row>
     <row r="269">
       <c r="D269" s="7" t="n"/>
-      <c r="E269" s="16" t="n"/>
+      <c r="E269" s="17" t="n"/>
       <c r="F269" s="7" t="n"/>
       <c r="G269" s="4" t="n"/>
       <c r="H269" s="7">
@@ -12813,7 +12825,7 @@
     </row>
     <row r="270">
       <c r="D270" s="7" t="n"/>
-      <c r="E270" s="16" t="n"/>
+      <c r="E270" s="17" t="n"/>
       <c r="F270" s="7" t="n"/>
       <c r="G270" s="4" t="n"/>
       <c r="H270" s="7">
@@ -12831,7 +12843,7 @@
     </row>
     <row r="271">
       <c r="D271" s="7" t="n"/>
-      <c r="E271" s="16" t="n"/>
+      <c r="E271" s="17" t="n"/>
       <c r="F271" s="7" t="n"/>
       <c r="G271" s="4" t="n"/>
       <c r="H271" s="7">
@@ -12849,7 +12861,7 @@
     </row>
     <row r="272">
       <c r="D272" s="7" t="n"/>
-      <c r="E272" s="16" t="n"/>
+      <c r="E272" s="17" t="n"/>
       <c r="F272" s="7" t="n"/>
       <c r="G272" s="4" t="n"/>
       <c r="H272" s="7">
@@ -12867,7 +12879,7 @@
     </row>
     <row r="273">
       <c r="D273" s="7" t="n"/>
-      <c r="E273" s="16" t="n"/>
+      <c r="E273" s="17" t="n"/>
       <c r="F273" s="7" t="n"/>
       <c r="G273" s="4" t="n"/>
       <c r="H273" s="7">
@@ -12885,7 +12897,7 @@
     </row>
     <row r="274">
       <c r="D274" s="7" t="n"/>
-      <c r="E274" s="16" t="n"/>
+      <c r="E274" s="17" t="n"/>
       <c r="F274" s="7" t="n"/>
       <c r="G274" s="4" t="n"/>
       <c r="H274" s="7">
@@ -12903,7 +12915,7 @@
     </row>
     <row r="275">
       <c r="D275" s="7" t="n"/>
-      <c r="E275" s="16" t="n"/>
+      <c r="E275" s="17" t="n"/>
       <c r="F275" s="7" t="n"/>
       <c r="G275" s="4" t="n"/>
       <c r="H275" s="7">
@@ -12921,7 +12933,7 @@
     </row>
     <row r="276">
       <c r="D276" s="7" t="n"/>
-      <c r="E276" s="16" t="n"/>
+      <c r="E276" s="17" t="n"/>
       <c r="F276" s="7" t="n"/>
       <c r="G276" s="4" t="n"/>
       <c r="H276" s="7">
@@ -12939,7 +12951,7 @@
     </row>
     <row r="277">
       <c r="D277" s="7" t="n"/>
-      <c r="E277" s="16" t="n"/>
+      <c r="E277" s="17" t="n"/>
       <c r="F277" s="7" t="n"/>
       <c r="G277" s="4" t="n"/>
       <c r="H277" s="7">
@@ -12957,7 +12969,7 @@
     </row>
     <row r="278">
       <c r="D278" s="7" t="n"/>
-      <c r="E278" s="16" t="n"/>
+      <c r="E278" s="17" t="n"/>
       <c r="F278" s="7" t="n"/>
       <c r="G278" s="4" t="n"/>
       <c r="H278" s="7">
@@ -12975,7 +12987,7 @@
     </row>
     <row r="279">
       <c r="D279" s="7" t="n"/>
-      <c r="E279" s="16" t="n"/>
+      <c r="E279" s="17" t="n"/>
       <c r="F279" s="7" t="n"/>
       <c r="G279" s="4" t="n"/>
       <c r="H279" s="7">
@@ -12993,7 +13005,7 @@
     </row>
     <row r="280">
       <c r="D280" s="7" t="n"/>
-      <c r="E280" s="16" t="n"/>
+      <c r="E280" s="17" t="n"/>
       <c r="F280" s="7" t="n"/>
       <c r="G280" s="4" t="n"/>
       <c r="H280" s="7">
@@ -13011,7 +13023,7 @@
     </row>
     <row r="281">
       <c r="D281" s="7" t="n"/>
-      <c r="E281" s="16" t="n"/>
+      <c r="E281" s="17" t="n"/>
       <c r="F281" s="7" t="n"/>
       <c r="G281" s="4" t="n"/>
       <c r="H281" s="7">
@@ -13029,7 +13041,7 @@
     </row>
     <row r="282">
       <c r="D282" s="7" t="n"/>
-      <c r="E282" s="16" t="n"/>
+      <c r="E282" s="17" t="n"/>
       <c r="F282" s="7" t="n"/>
       <c r="G282" s="4" t="n"/>
       <c r="H282" s="7">
@@ -13047,7 +13059,7 @@
     </row>
     <row r="283">
       <c r="D283" s="7" t="n"/>
-      <c r="E283" s="16" t="n"/>
+      <c r="E283" s="17" t="n"/>
       <c r="F283" s="7" t="n"/>
       <c r="G283" s="4" t="n"/>
       <c r="H283" s="7">
@@ -13065,7 +13077,7 @@
     </row>
     <row r="284">
       <c r="D284" s="7" t="n"/>
-      <c r="E284" s="16" t="n"/>
+      <c r="E284" s="17" t="n"/>
       <c r="F284" s="7" t="n"/>
       <c r="G284" s="4" t="n"/>
       <c r="H284" s="7">
@@ -13083,7 +13095,7 @@
     </row>
     <row r="285">
       <c r="D285" s="7" t="n"/>
-      <c r="E285" s="16" t="n"/>
+      <c r="E285" s="17" t="n"/>
       <c r="F285" s="7" t="n"/>
       <c r="G285" s="4" t="n"/>
       <c r="H285" s="7">
@@ -13101,7 +13113,7 @@
     </row>
     <row r="286">
       <c r="D286" s="7" t="n"/>
-      <c r="E286" s="16" t="n"/>
+      <c r="E286" s="17" t="n"/>
       <c r="F286" s="7" t="n"/>
       <c r="G286" s="4" t="n"/>
       <c r="H286" s="7">
@@ -13119,7 +13131,7 @@
     </row>
     <row r="287">
       <c r="D287" s="7" t="n"/>
-      <c r="E287" s="16" t="n"/>
+      <c r="E287" s="17" t="n"/>
       <c r="F287" s="7" t="n"/>
       <c r="G287" s="4" t="n"/>
       <c r="H287" s="7">
@@ -13137,7 +13149,7 @@
     </row>
     <row r="288">
       <c r="D288" s="7" t="n"/>
-      <c r="E288" s="16" t="n"/>
+      <c r="E288" s="17" t="n"/>
       <c r="F288" s="7" t="n"/>
       <c r="G288" s="4" t="n"/>
       <c r="H288" s="7">
@@ -13155,7 +13167,7 @@
     </row>
     <row r="289">
       <c r="D289" s="7" t="n"/>
-      <c r="E289" s="16" t="n"/>
+      <c r="E289" s="17" t="n"/>
       <c r="F289" s="7" t="n"/>
       <c r="G289" s="4" t="n"/>
       <c r="H289" s="7">
@@ -13173,7 +13185,7 @@
     </row>
     <row r="290">
       <c r="D290" s="7" t="n"/>
-      <c r="E290" s="16" t="n"/>
+      <c r="E290" s="17" t="n"/>
       <c r="F290" s="7" t="n"/>
       <c r="G290" s="4" t="n"/>
       <c r="H290" s="7">
@@ -13191,7 +13203,7 @@
     </row>
     <row r="291">
       <c r="D291" s="7" t="n"/>
-      <c r="E291" s="16" t="n"/>
+      <c r="E291" s="17" t="n"/>
       <c r="F291" s="7" t="n"/>
       <c r="G291" s="4" t="n"/>
       <c r="H291" s="7">
@@ -13209,7 +13221,7 @@
     </row>
     <row r="292">
       <c r="D292" s="7" t="n"/>
-      <c r="E292" s="16" t="n"/>
+      <c r="E292" s="17" t="n"/>
       <c r="F292" s="7" t="n"/>
       <c r="G292" s="4" t="n"/>
       <c r="H292" s="7">
@@ -13227,7 +13239,7 @@
     </row>
     <row r="293">
       <c r="D293" s="7" t="n"/>
-      <c r="E293" s="16" t="n"/>
+      <c r="E293" s="17" t="n"/>
       <c r="F293" s="7" t="n"/>
       <c r="G293" s="4" t="n"/>
       <c r="H293" s="7">
@@ -13245,7 +13257,7 @@
     </row>
     <row r="294">
       <c r="D294" s="7" t="n"/>
-      <c r="E294" s="16" t="n"/>
+      <c r="E294" s="17" t="n"/>
       <c r="F294" s="7" t="n"/>
       <c r="G294" s="4" t="n"/>
       <c r="H294" s="7">
@@ -13263,7 +13275,7 @@
     </row>
     <row r="295">
       <c r="D295" s="7" t="n"/>
-      <c r="E295" s="16" t="n"/>
+      <c r="E295" s="17" t="n"/>
       <c r="F295" s="7" t="n"/>
       <c r="G295" s="4" t="n"/>
       <c r="H295" s="7">
@@ -13281,7 +13293,7 @@
     </row>
     <row r="296">
       <c r="D296" s="7" t="n"/>
-      <c r="E296" s="16" t="n"/>
+      <c r="E296" s="17" t="n"/>
       <c r="F296" s="7" t="n"/>
       <c r="G296" s="4" t="n"/>
       <c r="H296" s="7">
@@ -13299,7 +13311,7 @@
     </row>
     <row r="297">
       <c r="D297" s="7" t="n"/>
-      <c r="E297" s="16" t="n"/>
+      <c r="E297" s="17" t="n"/>
       <c r="F297" s="7" t="n"/>
       <c r="G297" s="4" t="n"/>
       <c r="H297" s="7">
@@ -13317,7 +13329,7 @@
     </row>
     <row r="298">
       <c r="D298" s="7" t="n"/>
-      <c r="E298" s="16" t="n"/>
+      <c r="E298" s="17" t="n"/>
       <c r="F298" s="7" t="n"/>
       <c r="G298" s="4" t="n"/>
       <c r="H298" s="7">
@@ -13335,7 +13347,7 @@
     </row>
     <row r="299">
       <c r="D299" s="7" t="n"/>
-      <c r="E299" s="16" t="n"/>
+      <c r="E299" s="17" t="n"/>
       <c r="F299" s="7" t="n"/>
       <c r="G299" s="4" t="n"/>
       <c r="H299" s="7">
@@ -13353,7 +13365,7 @@
     </row>
     <row r="300">
       <c r="D300" s="7" t="n"/>
-      <c r="E300" s="16" t="n"/>
+      <c r="E300" s="17" t="n"/>
       <c r="F300" s="7" t="n"/>
       <c r="G300" s="4" t="n"/>
       <c r="H300" s="7">
@@ -13371,7 +13383,7 @@
     </row>
     <row r="301">
       <c r="D301" s="7" t="n"/>
-      <c r="E301" s="16" t="n"/>
+      <c r="E301" s="17" t="n"/>
       <c r="F301" s="7" t="n"/>
       <c r="G301" s="4" t="n"/>
       <c r="H301" s="7">
@@ -13389,7 +13401,7 @@
     </row>
     <row r="302">
       <c r="D302" s="7" t="n"/>
-      <c r="E302" s="16" t="n"/>
+      <c r="E302" s="17" t="n"/>
       <c r="F302" s="7" t="n"/>
       <c r="G302" s="4" t="n"/>
       <c r="H302" s="7">
@@ -13407,7 +13419,7 @@
     </row>
     <row r="303">
       <c r="D303" s="7" t="n"/>
-      <c r="E303" s="16" t="n"/>
+      <c r="E303" s="17" t="n"/>
       <c r="F303" s="7" t="n"/>
       <c r="G303" s="4" t="n"/>
       <c r="H303" s="7">
@@ -13425,7 +13437,7 @@
     </row>
     <row r="304">
       <c r="D304" s="7" t="n"/>
-      <c r="E304" s="16" t="n"/>
+      <c r="E304" s="17" t="n"/>
       <c r="F304" s="7" t="n"/>
       <c r="G304" s="4" t="n"/>
       <c r="H304" s="7">
@@ -13443,7 +13455,7 @@
     </row>
     <row r="305">
       <c r="D305" s="7" t="n"/>
-      <c r="E305" s="16" t="n"/>
+      <c r="E305" s="17" t="n"/>
       <c r="F305" s="7" t="n"/>
       <c r="G305" s="4" t="n"/>
       <c r="H305" s="7">
@@ -13461,7 +13473,7 @@
     </row>
     <row r="306">
       <c r="D306" s="7" t="n"/>
-      <c r="E306" s="16" t="n"/>
+      <c r="E306" s="17" t="n"/>
       <c r="F306" s="7" t="n"/>
       <c r="G306" s="4" t="n"/>
       <c r="H306" s="7">
@@ -13479,7 +13491,7 @@
     </row>
     <row r="307">
       <c r="D307" s="7" t="n"/>
-      <c r="E307" s="16" t="n"/>
+      <c r="E307" s="17" t="n"/>
       <c r="F307" s="7" t="n"/>
       <c r="G307" s="4" t="n"/>
       <c r="H307" s="7">
@@ -13497,7 +13509,7 @@
     </row>
     <row r="308">
       <c r="D308" s="7" t="n"/>
-      <c r="E308" s="16" t="n"/>
+      <c r="E308" s="17" t="n"/>
       <c r="F308" s="7" t="n"/>
       <c r="G308" s="4" t="n"/>
       <c r="H308" s="7">
@@ -13515,7 +13527,7 @@
     </row>
     <row r="309">
       <c r="D309" s="7" t="n"/>
-      <c r="E309" s="16" t="n"/>
+      <c r="E309" s="17" t="n"/>
       <c r="F309" s="7" t="n"/>
       <c r="G309" s="4" t="n"/>
       <c r="H309" s="7">
@@ -13533,7 +13545,7 @@
     </row>
     <row r="310">
       <c r="D310" s="7" t="n"/>
-      <c r="E310" s="16" t="n"/>
+      <c r="E310" s="17" t="n"/>
       <c r="F310" s="7" t="n"/>
       <c r="G310" s="4" t="n"/>
       <c r="H310" s="7">
@@ -13551,7 +13563,7 @@
     </row>
     <row r="311">
       <c r="D311" s="7" t="n"/>
-      <c r="E311" s="16" t="n"/>
+      <c r="E311" s="17" t="n"/>
       <c r="F311" s="7" t="n"/>
       <c r="G311" s="4" t="n"/>
       <c r="H311" s="7">
@@ -13569,7 +13581,7 @@
     </row>
     <row r="312">
       <c r="D312" s="7" t="n"/>
-      <c r="E312" s="16" t="n"/>
+      <c r="E312" s="17" t="n"/>
       <c r="F312" s="7" t="n"/>
       <c r="G312" s="4" t="n"/>
       <c r="H312" s="7">
@@ -13587,7 +13599,7 @@
     </row>
     <row r="313">
       <c r="D313" s="7" t="n"/>
-      <c r="E313" s="16" t="n"/>
+      <c r="E313" s="17" t="n"/>
       <c r="F313" s="7" t="n"/>
       <c r="G313" s="4" t="n"/>
       <c r="H313" s="7">
@@ -13605,7 +13617,7 @@
     </row>
     <row r="314">
       <c r="D314" s="7" t="n"/>
-      <c r="E314" s="16" t="n"/>
+      <c r="E314" s="17" t="n"/>
       <c r="F314" s="7" t="n"/>
       <c r="G314" s="4" t="n"/>
       <c r="H314" s="7">
@@ -13623,7 +13635,7 @@
     </row>
     <row r="315">
       <c r="D315" s="7" t="n"/>
-      <c r="E315" s="16" t="n"/>
+      <c r="E315" s="17" t="n"/>
       <c r="F315" s="7" t="n"/>
       <c r="G315" s="4" t="n"/>
       <c r="H315" s="7">
@@ -13641,7 +13653,7 @@
     </row>
     <row r="316">
       <c r="D316" s="7" t="n"/>
-      <c r="E316" s="16" t="n"/>
+      <c r="E316" s="17" t="n"/>
       <c r="F316" s="7" t="n"/>
       <c r="G316" s="4" t="n"/>
       <c r="H316" s="7">
@@ -13659,7 +13671,7 @@
     </row>
     <row r="317">
       <c r="D317" s="7" t="n"/>
-      <c r="E317" s="16" t="n"/>
+      <c r="E317" s="17" t="n"/>
       <c r="F317" s="7" t="n"/>
       <c r="G317" s="4" t="n"/>
       <c r="H317" s="7">
@@ -13677,7 +13689,7 @@
     </row>
     <row r="318">
       <c r="D318" s="7" t="n"/>
-      <c r="E318" s="16" t="n"/>
+      <c r="E318" s="17" t="n"/>
       <c r="F318" s="7" t="n"/>
       <c r="G318" s="4" t="n"/>
       <c r="H318" s="7">
@@ -13695,7 +13707,7 @@
     </row>
     <row r="319">
       <c r="D319" s="7" t="n"/>
-      <c r="E319" s="16" t="n"/>
+      <c r="E319" s="17" t="n"/>
       <c r="F319" s="7" t="n"/>
       <c r="G319" s="4" t="n"/>
       <c r="H319" s="7">
@@ -13713,7 +13725,7 @@
     </row>
     <row r="320">
       <c r="D320" s="7" t="n"/>
-      <c r="E320" s="16" t="n"/>
+      <c r="E320" s="17" t="n"/>
       <c r="F320" s="7" t="n"/>
       <c r="G320" s="4" t="n"/>
       <c r="H320" s="7">
@@ -13731,7 +13743,7 @@
     </row>
     <row r="321">
       <c r="D321" s="7" t="n"/>
-      <c r="E321" s="16" t="n"/>
+      <c r="E321" s="17" t="n"/>
       <c r="F321" s="7" t="n"/>
       <c r="G321" s="4" t="n"/>
       <c r="H321" s="7">
@@ -13749,7 +13761,7 @@
     </row>
     <row r="322">
       <c r="D322" s="7" t="n"/>
-      <c r="E322" s="16" t="n"/>
+      <c r="E322" s="17" t="n"/>
       <c r="F322" s="7" t="n"/>
       <c r="G322" s="4" t="n"/>
       <c r="H322" s="7">
@@ -13767,7 +13779,7 @@
     </row>
     <row r="323">
       <c r="D323" s="7" t="n"/>
-      <c r="E323" s="16" t="n"/>
+      <c r="E323" s="17" t="n"/>
       <c r="F323" s="7" t="n"/>
       <c r="G323" s="4" t="n"/>
       <c r="H323" s="7">
@@ -13785,7 +13797,7 @@
     </row>
     <row r="324">
       <c r="D324" s="7" t="n"/>
-      <c r="E324" s="16" t="n"/>
+      <c r="E324" s="17" t="n"/>
       <c r="F324" s="7" t="n"/>
       <c r="G324" s="4" t="n"/>
       <c r="H324" s="7">
@@ -13803,7 +13815,7 @@
     </row>
     <row r="325">
       <c r="D325" s="7" t="n"/>
-      <c r="E325" s="16" t="n"/>
+      <c r="E325" s="17" t="n"/>
       <c r="F325" s="7" t="n"/>
       <c r="G325" s="4" t="n"/>
       <c r="H325" s="7">
@@ -13821,7 +13833,7 @@
     </row>
     <row r="326">
       <c r="D326" s="7" t="n"/>
-      <c r="E326" s="16" t="n"/>
+      <c r="E326" s="17" t="n"/>
       <c r="F326" s="7" t="n"/>
       <c r="G326" s="4" t="n"/>
       <c r="H326" s="7">
@@ -13839,7 +13851,7 @@
     </row>
     <row r="327">
       <c r="D327" s="7" t="n"/>
-      <c r="E327" s="16" t="n"/>
+      <c r="E327" s="17" t="n"/>
       <c r="F327" s="7" t="n"/>
       <c r="G327" s="4" t="n"/>
       <c r="H327" s="7">
@@ -13857,7 +13869,7 @@
     </row>
     <row r="328">
       <c r="D328" s="7" t="n"/>
-      <c r="E328" s="16" t="n"/>
+      <c r="E328" s="17" t="n"/>
       <c r="F328" s="7" t="n"/>
       <c r="G328" s="4" t="n"/>
       <c r="H328" s="7">
@@ -13875,7 +13887,7 @@
     </row>
     <row r="329">
       <c r="D329" s="7" t="n"/>
-      <c r="E329" s="16" t="n"/>
+      <c r="E329" s="17" t="n"/>
       <c r="F329" s="7" t="n"/>
       <c r="G329" s="4" t="n"/>
       <c r="H329" s="7">
@@ -13893,7 +13905,7 @@
     </row>
     <row r="330">
       <c r="D330" s="7" t="n"/>
-      <c r="E330" s="16" t="n"/>
+      <c r="E330" s="17" t="n"/>
       <c r="F330" s="7" t="n"/>
       <c r="G330" s="4" t="n"/>
       <c r="H330" s="7">
@@ -13911,7 +13923,7 @@
     </row>
     <row r="331">
       <c r="D331" s="7" t="n"/>
-      <c r="E331" s="16" t="n"/>
+      <c r="E331" s="17" t="n"/>
       <c r="F331" s="7" t="n"/>
       <c r="G331" s="4" t="n"/>
       <c r="H331" s="7">
@@ -13929,7 +13941,7 @@
     </row>
     <row r="332">
       <c r="D332" s="7" t="n"/>
-      <c r="E332" s="16" t="n"/>
+      <c r="E332" s="17" t="n"/>
       <c r="F332" s="7" t="n"/>
       <c r="G332" s="4" t="n"/>
       <c r="H332" s="7">
@@ -13947,7 +13959,7 @@
     </row>
     <row r="333">
       <c r="D333" s="7" t="n"/>
-      <c r="E333" s="16" t="n"/>
+      <c r="E333" s="17" t="n"/>
       <c r="F333" s="7" t="n"/>
       <c r="G333" s="4" t="n"/>
       <c r="H333" s="7">
@@ -13965,7 +13977,7 @@
     </row>
     <row r="334">
       <c r="D334" s="7" t="n"/>
-      <c r="E334" s="16" t="n"/>
+      <c r="E334" s="17" t="n"/>
       <c r="F334" s="7" t="n"/>
       <c r="G334" s="4" t="n"/>
       <c r="H334" s="7">
@@ -13983,7 +13995,7 @@
     </row>
     <row r="335">
       <c r="D335" s="7" t="n"/>
-      <c r="E335" s="16" t="n"/>
+      <c r="E335" s="17" t="n"/>
       <c r="F335" s="7" t="n"/>
       <c r="G335" s="4" t="n"/>
       <c r="H335" s="7">
@@ -14001,7 +14013,7 @@
     </row>
     <row r="336">
       <c r="D336" s="7" t="n"/>
-      <c r="E336" s="16" t="n"/>
+      <c r="E336" s="17" t="n"/>
       <c r="F336" s="7" t="n"/>
       <c r="G336" s="4" t="n"/>
       <c r="H336" s="7">
@@ -14019,7 +14031,7 @@
     </row>
     <row r="337">
       <c r="D337" s="7" t="n"/>
-      <c r="E337" s="16" t="n"/>
+      <c r="E337" s="17" t="n"/>
       <c r="F337" s="7" t="n"/>
       <c r="G337" s="4" t="n"/>
       <c r="H337" s="7">
@@ -14037,7 +14049,7 @@
     </row>
     <row r="338">
       <c r="D338" s="7" t="n"/>
-      <c r="E338" s="16" t="n"/>
+      <c r="E338" s="17" t="n"/>
       <c r="F338" s="7" t="n"/>
       <c r="G338" s="4" t="n"/>
       <c r="H338" s="7">
@@ -14055,7 +14067,7 @@
     </row>
     <row r="339">
       <c r="D339" s="7" t="n"/>
-      <c r="E339" s="16" t="n"/>
+      <c r="E339" s="17" t="n"/>
       <c r="F339" s="7" t="n"/>
       <c r="G339" s="4" t="n"/>
       <c r="H339" s="7">
@@ -14073,7 +14085,7 @@
     </row>
     <row r="340">
       <c r="D340" s="7" t="n"/>
-      <c r="E340" s="16" t="n"/>
+      <c r="E340" s="17" t="n"/>
       <c r="F340" s="7" t="n"/>
       <c r="G340" s="4" t="n"/>
       <c r="H340" s="7">
@@ -14091,7 +14103,7 @@
     </row>
     <row r="341">
       <c r="D341" s="7" t="n"/>
-      <c r="E341" s="16" t="n"/>
+      <c r="E341" s="17" t="n"/>
       <c r="F341" s="7" t="n"/>
       <c r="G341" s="4" t="n"/>
       <c r="H341" s="7">
@@ -14109,7 +14121,7 @@
     </row>
     <row r="342">
       <c r="D342" s="7" t="n"/>
-      <c r="E342" s="16" t="n"/>
+      <c r="E342" s="17" t="n"/>
       <c r="F342" s="7" t="n"/>
       <c r="G342" s="4" t="n"/>
       <c r="H342" s="7">
@@ -14127,7 +14139,7 @@
     </row>
     <row r="343">
       <c r="D343" s="7" t="n"/>
-      <c r="E343" s="16" t="n"/>
+      <c r="E343" s="17" t="n"/>
       <c r="F343" s="7" t="n"/>
       <c r="G343" s="4" t="n"/>
       <c r="H343" s="7">
@@ -14145,7 +14157,7 @@
     </row>
     <row r="344">
       <c r="D344" s="7" t="n"/>
-      <c r="E344" s="16" t="n"/>
+      <c r="E344" s="17" t="n"/>
       <c r="F344" s="7" t="n"/>
       <c r="G344" s="4" t="n"/>
       <c r="H344" s="7">
@@ -14163,7 +14175,7 @@
     </row>
     <row r="345">
       <c r="D345" s="7" t="n"/>
-      <c r="E345" s="16" t="n"/>
+      <c r="E345" s="17" t="n"/>
       <c r="F345" s="7" t="n"/>
       <c r="G345" s="4" t="n"/>
       <c r="H345" s="7">
@@ -14181,7 +14193,7 @@
     </row>
     <row r="346">
       <c r="D346" s="7" t="n"/>
-      <c r="E346" s="16" t="n"/>
+      <c r="E346" s="17" t="n"/>
       <c r="F346" s="7" t="n"/>
       <c r="G346" s="4" t="n"/>
       <c r="H346" s="7">
@@ -14199,7 +14211,7 @@
     </row>
     <row r="347">
       <c r="D347" s="7" t="n"/>
-      <c r="E347" s="16" t="n"/>
+      <c r="E347" s="17" t="n"/>
       <c r="F347" s="7" t="n"/>
       <c r="G347" s="4" t="n"/>
       <c r="H347" s="7">
@@ -14217,7 +14229,7 @@
     </row>
     <row r="348">
       <c r="D348" s="7" t="n"/>
-      <c r="E348" s="16" t="n"/>
+      <c r="E348" s="17" t="n"/>
       <c r="F348" s="7" t="n"/>
       <c r="G348" s="4" t="n"/>
       <c r="H348" s="7">
@@ -14235,7 +14247,7 @@
     </row>
     <row r="349">
       <c r="D349" s="7" t="n"/>
-      <c r="E349" s="16" t="n"/>
+      <c r="E349" s="17" t="n"/>
       <c r="F349" s="7" t="n"/>
       <c r="G349" s="4" t="n"/>
       <c r="H349" s="7">
@@ -14253,7 +14265,7 @@
     </row>
     <row r="350">
       <c r="D350" s="7" t="n"/>
-      <c r="E350" s="16" t="n"/>
+      <c r="E350" s="17" t="n"/>
       <c r="F350" s="7" t="n"/>
       <c r="G350" s="4" t="n"/>
       <c r="H350" s="7">
@@ -14271,7 +14283,7 @@
     </row>
     <row r="351">
       <c r="D351" s="7" t="n"/>
-      <c r="E351" s="16" t="n"/>
+      <c r="E351" s="17" t="n"/>
       <c r="F351" s="7" t="n"/>
       <c r="G351" s="4" t="n"/>
       <c r="H351" s="7">
@@ -14289,7 +14301,7 @@
     </row>
     <row r="352">
       <c r="D352" s="7" t="n"/>
-      <c r="E352" s="16" t="n"/>
+      <c r="E352" s="17" t="n"/>
       <c r="F352" s="7" t="n"/>
       <c r="G352" s="4" t="n"/>
       <c r="H352" s="7">
@@ -14307,7 +14319,7 @@
     </row>
     <row r="353">
       <c r="D353" s="7" t="n"/>
-      <c r="E353" s="16" t="n"/>
+      <c r="E353" s="17" t="n"/>
       <c r="F353" s="7" t="n"/>
       <c r="G353" s="4" t="n"/>
       <c r="H353" s="7">
@@ -14325,7 +14337,7 @@
     </row>
     <row r="354">
       <c r="D354" s="7" t="n"/>
-      <c r="E354" s="16" t="n"/>
+      <c r="E354" s="17" t="n"/>
       <c r="F354" s="7" t="n"/>
       <c r="G354" s="4" t="n"/>
       <c r="H354" s="7">
@@ -14343,7 +14355,7 @@
     </row>
     <row r="355">
       <c r="D355" s="7" t="n"/>
-      <c r="E355" s="16" t="n"/>
+      <c r="E355" s="17" t="n"/>
       <c r="F355" s="7" t="n"/>
       <c r="G355" s="4" t="n"/>
       <c r="H355" s="7">
@@ -14361,7 +14373,7 @@
     </row>
     <row r="356">
       <c r="D356" s="7" t="n"/>
-      <c r="E356" s="16" t="n"/>
+      <c r="E356" s="17" t="n"/>
       <c r="F356" s="7" t="n"/>
       <c r="G356" s="4" t="n"/>
       <c r="H356" s="7">
@@ -14379,7 +14391,7 @@
     </row>
     <row r="357">
       <c r="D357" s="7" t="n"/>
-      <c r="E357" s="16" t="n"/>
+      <c r="E357" s="17" t="n"/>
       <c r="F357" s="7" t="n"/>
       <c r="G357" s="4" t="n"/>
       <c r="H357" s="7">
@@ -14397,7 +14409,7 @@
     </row>
     <row r="358">
       <c r="D358" s="7" t="n"/>
-      <c r="E358" s="16" t="n"/>
+      <c r="E358" s="17" t="n"/>
       <c r="F358" s="7" t="n"/>
       <c r="G358" s="4" t="n"/>
       <c r="H358" s="7">
@@ -14415,7 +14427,7 @@
     </row>
     <row r="359">
       <c r="D359" s="7" t="n"/>
-      <c r="E359" s="16" t="n"/>
+      <c r="E359" s="17" t="n"/>
       <c r="F359" s="7" t="n"/>
       <c r="G359" s="4" t="n"/>
       <c r="H359" s="7">
@@ -14433,7 +14445,7 @@
     </row>
     <row r="360">
       <c r="D360" s="7" t="n"/>
-      <c r="E360" s="16" t="n"/>
+      <c r="E360" s="17" t="n"/>
       <c r="F360" s="7" t="n"/>
       <c r="G360" s="4" t="n"/>
       <c r="H360" s="7">
@@ -14451,7 +14463,7 @@
     </row>
     <row r="361">
       <c r="D361" s="7" t="n"/>
-      <c r="E361" s="16" t="n"/>
+      <c r="E361" s="17" t="n"/>
       <c r="F361" s="7" t="n"/>
       <c r="G361" s="4" t="n"/>
       <c r="H361" s="7">
@@ -14469,7 +14481,7 @@
     </row>
     <row r="362">
       <c r="D362" s="7" t="n"/>
-      <c r="E362" s="16" t="n"/>
+      <c r="E362" s="17" t="n"/>
       <c r="F362" s="7" t="n"/>
       <c r="G362" s="4" t="n"/>
       <c r="H362" s="7">
@@ -14487,7 +14499,7 @@
     </row>
     <row r="363">
       <c r="D363" s="7" t="n"/>
-      <c r="E363" s="16" t="n"/>
+      <c r="E363" s="17" t="n"/>
       <c r="F363" s="7" t="n"/>
       <c r="G363" s="4" t="n"/>
       <c r="H363" s="7">
@@ -14505,7 +14517,7 @@
     </row>
     <row r="364">
       <c r="D364" s="7" t="n"/>
-      <c r="E364" s="16" t="n"/>
+      <c r="E364" s="17" t="n"/>
       <c r="F364" s="7" t="n"/>
       <c r="G364" s="4" t="n"/>
       <c r="H364" s="7">
@@ -14523,7 +14535,7 @@
     </row>
     <row r="365">
       <c r="D365" s="7" t="n"/>
-      <c r="E365" s="16" t="n"/>
+      <c r="E365" s="17" t="n"/>
       <c r="F365" s="7" t="n"/>
       <c r="G365" s="4" t="n"/>
       <c r="H365" s="7">
@@ -14541,7 +14553,7 @@
     </row>
     <row r="366">
       <c r="D366" s="7" t="n"/>
-      <c r="E366" s="16" t="n"/>
+      <c r="E366" s="17" t="n"/>
       <c r="F366" s="7" t="n"/>
       <c r="G366" s="4" t="n"/>
       <c r="H366" s="7">
@@ -14559,7 +14571,7 @@
     </row>
     <row r="367">
       <c r="D367" s="7" t="n"/>
-      <c r="E367" s="16" t="n"/>
+      <c r="E367" s="17" t="n"/>
       <c r="F367" s="7" t="n"/>
       <c r="G367" s="4" t="n"/>
       <c r="H367" s="7">
@@ -14577,7 +14589,7 @@
     </row>
     <row r="368">
       <c r="D368" s="7" t="n"/>
-      <c r="E368" s="16" t="n"/>
+      <c r="E368" s="17" t="n"/>
       <c r="F368" s="7" t="n"/>
       <c r="G368" s="4" t="n"/>
       <c r="H368" s="7">
@@ -14595,7 +14607,7 @@
     </row>
     <row r="369">
       <c r="D369" s="7" t="n"/>
-      <c r="E369" s="16" t="n"/>
+      <c r="E369" s="17" t="n"/>
       <c r="F369" s="7" t="n"/>
       <c r="G369" s="4" t="n"/>
       <c r="H369" s="7">
@@ -14613,7 +14625,7 @@
     </row>
     <row r="370">
       <c r="D370" s="7" t="n"/>
-      <c r="E370" s="16" t="n"/>
+      <c r="E370" s="17" t="n"/>
       <c r="F370" s="7" t="n"/>
       <c r="G370" s="4" t="n"/>
       <c r="H370" s="7">
@@ -14631,7 +14643,7 @@
     </row>
     <row r="371">
       <c r="D371" s="7" t="n"/>
-      <c r="E371" s="16" t="n"/>
+      <c r="E371" s="17" t="n"/>
       <c r="F371" s="7" t="n"/>
       <c r="G371" s="4" t="n"/>
       <c r="H371" s="7">
@@ -14649,7 +14661,7 @@
     </row>
     <row r="372">
       <c r="D372" s="7" t="n"/>
-      <c r="E372" s="16" t="n"/>
+      <c r="E372" s="17" t="n"/>
       <c r="F372" s="7" t="n"/>
       <c r="G372" s="4" t="n"/>
       <c r="H372" s="7">
@@ -14667,7 +14679,7 @@
     </row>
     <row r="373">
       <c r="D373" s="7" t="n"/>
-      <c r="E373" s="16" t="n"/>
+      <c r="E373" s="17" t="n"/>
       <c r="F373" s="7" t="n"/>
       <c r="G373" s="4" t="n"/>
       <c r="H373" s="7">
@@ -14685,7 +14697,7 @@
     </row>
     <row r="374">
       <c r="D374" s="7" t="n"/>
-      <c r="E374" s="16" t="n"/>
+      <c r="E374" s="17" t="n"/>
       <c r="F374" s="7" t="n"/>
       <c r="G374" s="4" t="n"/>
       <c r="H374" s="7">
@@ -14703,7 +14715,7 @@
     </row>
     <row r="375">
       <c r="D375" s="7" t="n"/>
-      <c r="E375" s="16" t="n"/>
+      <c r="E375" s="17" t="n"/>
       <c r="F375" s="7" t="n"/>
       <c r="G375" s="4" t="n"/>
       <c r="H375" s="7">
@@ -14721,7 +14733,7 @@
     </row>
     <row r="376">
       <c r="D376" s="7" t="n"/>
-      <c r="E376" s="16" t="n"/>
+      <c r="E376" s="17" t="n"/>
       <c r="F376" s="7" t="n"/>
       <c r="G376" s="4" t="n"/>
       <c r="H376" s="7">
@@ -14739,7 +14751,7 @@
     </row>
     <row r="377">
       <c r="D377" s="7" t="n"/>
-      <c r="E377" s="16" t="n"/>
+      <c r="E377" s="17" t="n"/>
       <c r="F377" s="7" t="n"/>
       <c r="G377" s="4" t="n"/>
       <c r="H377" s="7">
@@ -14757,7 +14769,7 @@
     </row>
     <row r="378">
       <c r="D378" s="7" t="n"/>
-      <c r="E378" s="16" t="n"/>
+      <c r="E378" s="17" t="n"/>
       <c r="F378" s="7" t="n"/>
       <c r="G378" s="4" t="n"/>
       <c r="H378" s="7">
@@ -14775,7 +14787,7 @@
     </row>
     <row r="379">
       <c r="D379" s="7" t="n"/>
-      <c r="E379" s="16" t="n"/>
+      <c r="E379" s="17" t="n"/>
       <c r="F379" s="7" t="n"/>
       <c r="G379" s="4" t="n"/>
       <c r="H379" s="7">
@@ -14793,7 +14805,7 @@
     </row>
     <row r="380">
       <c r="D380" s="7" t="n"/>
-      <c r="E380" s="16" t="n"/>
+      <c r="E380" s="17" t="n"/>
       <c r="F380" s="7" t="n"/>
       <c r="G380" s="4" t="n"/>
       <c r="H380" s="7">
@@ -14811,7 +14823,7 @@
     </row>
     <row r="381">
       <c r="D381" s="7" t="n"/>
-      <c r="E381" s="16" t="n"/>
+      <c r="E381" s="17" t="n"/>
       <c r="F381" s="7" t="n"/>
       <c r="G381" s="4" t="n"/>
       <c r="H381" s="7">
@@ -14829,7 +14841,7 @@
     </row>
     <row r="382">
       <c r="D382" s="7" t="n"/>
-      <c r="E382" s="16" t="n"/>
+      <c r="E382" s="17" t="n"/>
       <c r="F382" s="7" t="n"/>
       <c r="G382" s="4" t="n"/>
       <c r="H382" s="7">
@@ -14847,7 +14859,7 @@
     </row>
     <row r="383">
       <c r="D383" s="7" t="n"/>
-      <c r="E383" s="16" t="n"/>
+      <c r="E383" s="17" t="n"/>
       <c r="F383" s="7" t="n"/>
       <c r="G383" s="4" t="n"/>
       <c r="H383" s="7">
@@ -14865,7 +14877,7 @@
     </row>
     <row r="384">
       <c r="D384" s="7" t="n"/>
-      <c r="E384" s="16" t="n"/>
+      <c r="E384" s="17" t="n"/>
       <c r="F384" s="7" t="n"/>
       <c r="G384" s="4" t="n"/>
       <c r="H384" s="7">
@@ -14883,7 +14895,7 @@
     </row>
     <row r="385">
       <c r="D385" s="7" t="n"/>
-      <c r="E385" s="16" t="n"/>
+      <c r="E385" s="17" t="n"/>
       <c r="F385" s="7" t="n"/>
       <c r="G385" s="4" t="n"/>
       <c r="H385" s="7">
@@ -14901,7 +14913,7 @@
     </row>
     <row r="386">
       <c r="D386" s="7" t="n"/>
-      <c r="E386" s="16" t="n"/>
+      <c r="E386" s="17" t="n"/>
       <c r="F386" s="7" t="n"/>
       <c r="G386" s="4" t="n"/>
       <c r="H386" s="7">
@@ -14919,7 +14931,7 @@
     </row>
     <row r="387">
       <c r="D387" s="7" t="n"/>
-      <c r="E387" s="16" t="n"/>
+      <c r="E387" s="17" t="n"/>
       <c r="F387" s="7" t="n"/>
       <c r="G387" s="4" t="n"/>
       <c r="H387" s="7">
@@ -14937,7 +14949,7 @@
     </row>
     <row r="388">
       <c r="D388" s="7" t="n"/>
-      <c r="E388" s="16" t="n"/>
+      <c r="E388" s="17" t="n"/>
       <c r="F388" s="7" t="n"/>
       <c r="G388" s="4" t="n"/>
       <c r="H388" s="7">
@@ -14955,7 +14967,7 @@
     </row>
     <row r="389">
       <c r="D389" s="7" t="n"/>
-      <c r="E389" s="16" t="n"/>
+      <c r="E389" s="17" t="n"/>
       <c r="F389" s="7" t="n"/>
       <c r="G389" s="4" t="n"/>
       <c r="H389" s="7">
@@ -14973,7 +14985,7 @@
     </row>
     <row r="390">
       <c r="D390" s="7" t="n"/>
-      <c r="E390" s="16" t="n"/>
+      <c r="E390" s="17" t="n"/>
       <c r="F390" s="7" t="n"/>
       <c r="G390" s="4" t="n"/>
       <c r="H390" s="7">
@@ -14991,7 +15003,7 @@
     </row>
     <row r="391">
       <c r="D391" s="7" t="n"/>
-      <c r="E391" s="16" t="n"/>
+      <c r="E391" s="17" t="n"/>
       <c r="F391" s="7" t="n"/>
       <c r="G391" s="4" t="n"/>
       <c r="H391" s="7">
@@ -15009,7 +15021,7 @@
     </row>
     <row r="392">
       <c r="D392" s="7" t="n"/>
-      <c r="E392" s="16" t="n"/>
+      <c r="E392" s="17" t="n"/>
       <c r="F392" s="7" t="n"/>
       <c r="G392" s="4" t="n"/>
       <c r="H392" s="7">
@@ -15027,7 +15039,7 @@
     </row>
     <row r="393">
       <c r="D393" s="7" t="n"/>
-      <c r="E393" s="16" t="n"/>
+      <c r="E393" s="17" t="n"/>
       <c r="F393" s="7" t="n"/>
       <c r="G393" s="4" t="n"/>
       <c r="H393" s="7">
@@ -15045,7 +15057,7 @@
     </row>
     <row r="394">
       <c r="D394" s="7" t="n"/>
-      <c r="E394" s="16" t="n"/>
+      <c r="E394" s="17" t="n"/>
       <c r="F394" s="7" t="n"/>
       <c r="G394" s="4" t="n"/>
       <c r="H394" s="7">
@@ -15063,7 +15075,7 @@
     </row>
     <row r="395">
       <c r="D395" s="7" t="n"/>
-      <c r="E395" s="16" t="n"/>
+      <c r="E395" s="17" t="n"/>
       <c r="F395" s="7" t="n"/>
       <c r="G395" s="4" t="n"/>
       <c r="H395" s="7">
@@ -15081,7 +15093,7 @@
     </row>
     <row r="396">
       <c r="D396" s="7" t="n"/>
-      <c r="E396" s="16" t="n"/>
+      <c r="E396" s="17" t="n"/>
       <c r="F396" s="7" t="n"/>
       <c r="G396" s="4" t="n"/>
       <c r="H396" s="7">
@@ -15099,7 +15111,7 @@
     </row>
     <row r="397">
       <c r="D397" s="7" t="n"/>
-      <c r="E397" s="16" t="n"/>
+      <c r="E397" s="17" t="n"/>
       <c r="F397" s="7" t="n"/>
       <c r="G397" s="4" t="n"/>
       <c r="H397" s="7">
@@ -15117,7 +15129,7 @@
     </row>
     <row r="398">
       <c r="D398" s="7" t="n"/>
-      <c r="E398" s="16" t="n"/>
+      <c r="E398" s="17" t="n"/>
       <c r="F398" s="7" t="n"/>
       <c r="G398" s="4" t="n"/>
       <c r="H398" s="7">
@@ -15135,7 +15147,7 @@
     </row>
     <row r="399">
       <c r="D399" s="7" t="n"/>
-      <c r="E399" s="16" t="n"/>
+      <c r="E399" s="17" t="n"/>
       <c r="F399" s="7" t="n"/>
       <c r="G399" s="4" t="n"/>
       <c r="H399" s="7">
@@ -15153,7 +15165,7 @@
     </row>
     <row r="400">
       <c r="D400" s="7" t="n"/>
-      <c r="E400" s="16" t="n"/>
+      <c r="E400" s="17" t="n"/>
       <c r="F400" s="7" t="n"/>
       <c r="G400" s="4" t="n"/>
       <c r="H400" s="7">
@@ -15171,7 +15183,7 @@
     </row>
     <row r="401">
       <c r="D401" s="7" t="n"/>
-      <c r="E401" s="16" t="n"/>
+      <c r="E401" s="17" t="n"/>
       <c r="F401" s="7" t="n"/>
       <c r="G401" s="4" t="n"/>
       <c r="H401" s="7">
@@ -15189,7 +15201,7 @@
     </row>
     <row r="402">
       <c r="D402" s="7" t="n"/>
-      <c r="E402" s="16" t="n"/>
+      <c r="E402" s="17" t="n"/>
       <c r="F402" s="7" t="n"/>
       <c r="G402" s="4" t="n"/>
       <c r="H402" s="7">
@@ -15207,7 +15219,7 @@
     </row>
     <row r="403">
       <c r="D403" s="7" t="n"/>
-      <c r="E403" s="16" t="n"/>
+      <c r="E403" s="17" t="n"/>
       <c r="F403" s="7" t="n"/>
       <c r="G403" s="4" t="n"/>
       <c r="H403" s="7">
@@ -15225,7 +15237,7 @@
     </row>
     <row r="404">
       <c r="D404" s="7" t="n"/>
-      <c r="E404" s="16" t="n"/>
+      <c r="E404" s="17" t="n"/>
       <c r="F404" s="7" t="n"/>
       <c r="G404" s="4" t="n"/>
       <c r="H404" s="7">
@@ -15243,7 +15255,7 @@
     </row>
     <row r="405">
       <c r="D405" s="7" t="n"/>
-      <c r="E405" s="16" t="n"/>
+      <c r="E405" s="17" t="n"/>
       <c r="F405" s="7" t="n"/>
       <c r="G405" s="4" t="n"/>
       <c r="H405" s="7">
@@ -15261,7 +15273,7 @@
     </row>
     <row r="406">
       <c r="D406" s="7" t="n"/>
-      <c r="E406" s="16" t="n"/>
+      <c r="E406" s="17" t="n"/>
       <c r="F406" s="7" t="n"/>
       <c r="G406" s="4" t="n"/>
       <c r="H406" s="7">
@@ -15279,7 +15291,7 @@
     </row>
     <row r="407">
       <c r="D407" s="7" t="n"/>
-      <c r="E407" s="16" t="n"/>
+      <c r="E407" s="17" t="n"/>
       <c r="F407" s="7" t="n"/>
       <c r="G407" s="4" t="n"/>
       <c r="H407" s="7">
@@ -15297,7 +15309,7 @@
     </row>
     <row r="408">
       <c r="D408" s="7" t="n"/>
-      <c r="E408" s="16" t="n"/>
+      <c r="E408" s="17" t="n"/>
       <c r="F408" s="7" t="n"/>
       <c r="G408" s="4" t="n"/>
       <c r="H408" s="7">
@@ -15315,7 +15327,7 @@
     </row>
     <row r="409">
       <c r="D409" s="7" t="n"/>
-      <c r="E409" s="16" t="n"/>
+      <c r="E409" s="17" t="n"/>
       <c r="F409" s="7" t="n"/>
       <c r="G409" s="4" t="n"/>
       <c r="H409" s="7">
@@ -15333,7 +15345,7 @@
     </row>
     <row r="410">
       <c r="D410" s="7" t="n"/>
-      <c r="E410" s="16" t="n"/>
+      <c r="E410" s="17" t="n"/>
       <c r="F410" s="7" t="n"/>
       <c r="G410" s="4" t="n"/>
       <c r="H410" s="7">
@@ -15351,7 +15363,7 @@
     </row>
     <row r="411">
       <c r="D411" s="7" t="n"/>
-      <c r="E411" s="16" t="n"/>
+      <c r="E411" s="17" t="n"/>
       <c r="F411" s="7" t="n"/>
       <c r="G411" s="4" t="n"/>
       <c r="H411" s="7">
@@ -15369,7 +15381,7 @@
     </row>
     <row r="412">
       <c r="D412" s="7" t="n"/>
-      <c r="E412" s="16" t="n"/>
+      <c r="E412" s="17" t="n"/>
       <c r="F412" s="7" t="n"/>
       <c r="G412" s="4" t="n"/>
       <c r="H412" s="7">
@@ -15387,7 +15399,7 @@
     </row>
     <row r="413">
       <c r="D413" s="7" t="n"/>
-      <c r="E413" s="16" t="n"/>
+      <c r="E413" s="17" t="n"/>
       <c r="F413" s="7" t="n"/>
       <c r="G413" s="4" t="n"/>
       <c r="H413" s="7">
@@ -15405,7 +15417,7 @@
     </row>
     <row r="414">
       <c r="D414" s="7" t="n"/>
-      <c r="E414" s="16" t="n"/>
+      <c r="E414" s="17" t="n"/>
       <c r="F414" s="7" t="n"/>
       <c r="G414" s="4" t="n"/>
       <c r="H414" s="7">
@@ -15423,7 +15435,7 @@
     </row>
     <row r="415">
       <c r="D415" s="7" t="n"/>
-      <c r="E415" s="16" t="n"/>
+      <c r="E415" s="17" t="n"/>
       <c r="F415" s="7" t="n"/>
       <c r="G415" s="4" t="n"/>
       <c r="H415" s="7">
@@ -15441,7 +15453,7 @@
     </row>
     <row r="416">
       <c r="D416" s="7" t="n"/>
-      <c r="E416" s="16" t="n"/>
+      <c r="E416" s="17" t="n"/>
       <c r="F416" s="7" t="n"/>
       <c r="G416" s="4" t="n"/>
       <c r="H416" s="7">
@@ -15459,7 +15471,7 @@
     </row>
     <row r="417">
       <c r="D417" s="7" t="n"/>
-      <c r="E417" s="16" t="n"/>
+      <c r="E417" s="17" t="n"/>
       <c r="F417" s="7" t="n"/>
       <c r="G417" s="4" t="n"/>
       <c r="H417" s="7">
@@ -15477,7 +15489,7 @@
     </row>
     <row r="418">
       <c r="D418" s="7" t="n"/>
-      <c r="E418" s="16" t="n"/>
+      <c r="E418" s="17" t="n"/>
       <c r="F418" s="7" t="n"/>
       <c r="G418" s="4" t="n"/>
       <c r="H418" s="7">
@@ -15495,7 +15507,7 @@
     </row>
     <row r="419">
       <c r="D419" s="7" t="n"/>
-      <c r="E419" s="16" t="n"/>
+      <c r="E419" s="17" t="n"/>
       <c r="F419" s="7" t="n"/>
       <c r="G419" s="4" t="n"/>
       <c r="H419" s="7">
@@ -15513,7 +15525,7 @@
     </row>
     <row r="420">
       <c r="D420" s="7" t="n"/>
-      <c r="E420" s="16" t="n"/>
+      <c r="E420" s="17" t="n"/>
       <c r="F420" s="7" t="n"/>
       <c r="G420" s="4" t="n"/>
       <c r="H420" s="7">
@@ -15531,7 +15543,7 @@
     </row>
     <row r="421">
       <c r="D421" s="7" t="n"/>
-      <c r="E421" s="16" t="n"/>
+      <c r="E421" s="17" t="n"/>
       <c r="F421" s="7" t="n"/>
       <c r="G421" s="4" t="n"/>
       <c r="H421" s="7">
@@ -15549,7 +15561,7 @@
     </row>
     <row r="422">
       <c r="D422" s="7" t="n"/>
-      <c r="E422" s="16" t="n"/>
+      <c r="E422" s="17" t="n"/>
       <c r="F422" s="7" t="n"/>
       <c r="G422" s="4" t="n"/>
       <c r="H422" s="7">
@@ -15567,7 +15579,7 @@
     </row>
     <row r="423">
       <c r="D423" s="7" t="n"/>
-      <c r="E423" s="16" t="n"/>
+      <c r="E423" s="17" t="n"/>
       <c r="F423" s="7" t="n"/>
       <c r="G423" s="4" t="n"/>
       <c r="H423" s="7">
@@ -15585,7 +15597,7 @@
     </row>
     <row r="424">
       <c r="D424" s="7" t="n"/>
-      <c r="E424" s="16" t="n"/>
+      <c r="E424" s="17" t="n"/>
       <c r="F424" s="7" t="n"/>
       <c r="G424" s="4" t="n"/>
       <c r="H424" s="7">
@@ -15603,7 +15615,7 @@
     </row>
     <row r="425">
       <c r="D425" s="7" t="n"/>
-      <c r="E425" s="16" t="n"/>
+      <c r="E425" s="17" t="n"/>
       <c r="F425" s="7" t="n"/>
       <c r="G425" s="4" t="n"/>
       <c r="H425" s="7">
@@ -15621,7 +15633,7 @@
     </row>
     <row r="426">
       <c r="D426" s="7" t="n"/>
-      <c r="E426" s="16" t="n"/>
+      <c r="E426" s="17" t="n"/>
       <c r="F426" s="7" t="n"/>
       <c r="G426" s="4" t="n"/>
       <c r="H426" s="7">
@@ -15639,7 +15651,7 @@
     </row>
     <row r="427">
       <c r="D427" s="7" t="n"/>
-      <c r="E427" s="16" t="n"/>
+      <c r="E427" s="17" t="n"/>
       <c r="F427" s="7" t="n"/>
       <c r="G427" s="4" t="n"/>
       <c r="H427" s="7">
@@ -15657,7 +15669,7 @@
     </row>
     <row r="428">
       <c r="D428" s="7" t="n"/>
-      <c r="E428" s="16" t="n"/>
+      <c r="E428" s="17" t="n"/>
       <c r="F428" s="7" t="n"/>
       <c r="G428" s="4" t="n"/>
       <c r="H428" s="7">
@@ -15675,7 +15687,7 @@
     </row>
     <row r="429">
       <c r="D429" s="7" t="n"/>
-      <c r="E429" s="16" t="n"/>
+      <c r="E429" s="17" t="n"/>
       <c r="F429" s="7" t="n"/>
       <c r="G429" s="4" t="n"/>
       <c r="H429" s="7">
@@ -15693,7 +15705,7 @@
     </row>
     <row r="430">
       <c r="D430" s="7" t="n"/>
-      <c r="E430" s="16" t="n"/>
+      <c r="E430" s="17" t="n"/>
       <c r="F430" s="7" t="n"/>
       <c r="G430" s="4" t="n"/>
       <c r="H430" s="7">
@@ -15711,7 +15723,7 @@
     </row>
     <row r="431">
       <c r="D431" s="7" t="n"/>
-      <c r="E431" s="16" t="n"/>
+      <c r="E431" s="17" t="n"/>
       <c r="F431" s="7" t="n"/>
       <c r="G431" s="4" t="n"/>
       <c r="H431" s="7">
@@ -15729,7 +15741,7 @@
     </row>
     <row r="432">
       <c r="D432" s="7" t="n"/>
-      <c r="E432" s="16" t="n"/>
+      <c r="E432" s="17" t="n"/>
       <c r="F432" s="7" t="n"/>
       <c r="G432" s="4" t="n"/>
       <c r="H432" s="7">
@@ -15747,7 +15759,7 @@
     </row>
     <row r="433">
       <c r="D433" s="7" t="n"/>
-      <c r="E433" s="16" t="n"/>
+      <c r="E433" s="17" t="n"/>
       <c r="F433" s="7" t="n"/>
       <c r="G433" s="4" t="n"/>
       <c r="H433" s="7">
@@ -15765,7 +15777,7 @@
     </row>
     <row r="434">
       <c r="D434" s="7" t="n"/>
-      <c r="E434" s="16" t="n"/>
+      <c r="E434" s="17" t="n"/>
       <c r="F434" s="7" t="n"/>
       <c r="G434" s="4" t="n"/>
       <c r="H434" s="7">
@@ -15783,7 +15795,7 @@
     </row>
     <row r="435">
       <c r="D435" s="7" t="n"/>
-      <c r="E435" s="16" t="n"/>
+      <c r="E435" s="17" t="n"/>
       <c r="F435" s="7" t="n"/>
       <c r="G435" s="4" t="n"/>
       <c r="H435" s="7">
@@ -15801,7 +15813,7 @@
     </row>
     <row r="436">
       <c r="D436" s="7" t="n"/>
-      <c r="E436" s="16" t="n"/>
+      <c r="E436" s="17" t="n"/>
       <c r="F436" s="7" t="n"/>
       <c r="G436" s="4" t="n"/>
       <c r="H436" s="7">
@@ -15819,7 +15831,7 @@
     </row>
     <row r="437">
       <c r="D437" s="7" t="n"/>
-      <c r="E437" s="16" t="n"/>
+      <c r="E437" s="17" t="n"/>
       <c r="F437" s="7" t="n"/>
       <c r="G437" s="4" t="n"/>
       <c r="H437" s="7">
@@ -15837,7 +15849,7 @@
     </row>
     <row r="438">
       <c r="D438" s="7" t="n"/>
-      <c r="E438" s="16" t="n"/>
+      <c r="E438" s="17" t="n"/>
       <c r="F438" s="7" t="n"/>
       <c r="G438" s="4" t="n"/>
       <c r="H438" s="7">
@@ -15855,7 +15867,7 @@
     </row>
     <row r="439">
       <c r="D439" s="7" t="n"/>
-      <c r="E439" s="16" t="n"/>
+      <c r="E439" s="17" t="n"/>
       <c r="F439" s="7" t="n"/>
       <c r="G439" s="4" t="n"/>
       <c r="H439" s="7">
@@ -15873,7 +15885,7 @@
     </row>
     <row r="440">
       <c r="D440" s="7" t="n"/>
-      <c r="E440" s="16" t="n"/>
+      <c r="E440" s="17" t="n"/>
       <c r="F440" s="7" t="n"/>
       <c r="G440" s="4" t="n"/>
       <c r="H440" s="7">
@@ -15891,7 +15903,7 @@
     </row>
     <row r="441">
       <c r="D441" s="7" t="n"/>
-      <c r="E441" s="16" t="n"/>
+      <c r="E441" s="17" t="n"/>
       <c r="F441" s="7" t="n"/>
       <c r="G441" s="4" t="n"/>
       <c r="H441" s="7">
@@ -15909,7 +15921,7 @@
     </row>
     <row r="442">
       <c r="D442" s="7" t="n"/>
-      <c r="E442" s="16" t="n"/>
+      <c r="E442" s="17" t="n"/>
       <c r="F442" s="7" t="n"/>
       <c r="G442" s="4" t="n"/>
       <c r="H442" s="7">
@@ -15927,7 +15939,7 @@
     </row>
     <row r="443">
       <c r="D443" s="7" t="n"/>
-      <c r="E443" s="16" t="n"/>
+      <c r="E443" s="17" t="n"/>
       <c r="F443" s="7" t="n"/>
       <c r="G443" s="4" t="n"/>
       <c r="H443" s="7">
@@ -15945,7 +15957,7 @@
     </row>
     <row r="444">
       <c r="D444" s="7" t="n"/>
-      <c r="E444" s="16" t="n"/>
+      <c r="E444" s="17" t="n"/>
       <c r="F444" s="7" t="n"/>
       <c r="G444" s="4" t="n"/>
       <c r="H444" s="7">
@@ -15963,7 +15975,7 @@
     </row>
     <row r="445">
       <c r="D445" s="7" t="n"/>
-      <c r="E445" s="16" t="n"/>
+      <c r="E445" s="17" t="n"/>
       <c r="F445" s="7" t="n"/>
       <c r="G445" s="4" t="n"/>
       <c r="H445" s="7">
@@ -15981,7 +15993,7 @@
     </row>
     <row r="446">
       <c r="D446" s="7" t="n"/>
-      <c r="E446" s="16" t="n"/>
+      <c r="E446" s="17" t="n"/>
       <c r="F446" s="7" t="n"/>
       <c r="G446" s="4" t="n"/>
       <c r="H446" s="7">
@@ -15999,7 +16011,7 @@
     </row>
     <row r="447">
       <c r="D447" s="7" t="n"/>
-      <c r="E447" s="16" t="n"/>
+      <c r="E447" s="17" t="n"/>
       <c r="F447" s="7" t="n"/>
       <c r="G447" s="4" t="n"/>
       <c r="H447" s="7">
@@ -16017,7 +16029,7 @@
     </row>
     <row r="448">
       <c r="D448" s="7" t="n"/>
-      <c r="E448" s="16" t="n"/>
+      <c r="E448" s="17" t="n"/>
       <c r="F448" s="7" t="n"/>
       <c r="G448" s="4" t="n"/>
       <c r="H448" s="7">
@@ -16035,7 +16047,7 @@
     </row>
     <row r="449">
       <c r="D449" s="7" t="n"/>
-      <c r="E449" s="16" t="n"/>
+      <c r="E449" s="17" t="n"/>
       <c r="F449" s="7" t="n"/>
       <c r="G449" s="4" t="n"/>
       <c r="H449" s="7">
@@ -16053,7 +16065,7 @@
     </row>
     <row r="450">
       <c r="D450" s="7" t="n"/>
-      <c r="E450" s="16" t="n"/>
+      <c r="E450" s="17" t="n"/>
       <c r="F450" s="7" t="n"/>
       <c r="G450" s="4" t="n"/>
       <c r="H450" s="7">
@@ -16071,7 +16083,7 @@
     </row>
     <row r="451">
       <c r="D451" s="7" t="n"/>
-      <c r="E451" s="16" t="n"/>
+      <c r="E451" s="17" t="n"/>
       <c r="F451" s="7" t="n"/>
       <c r="G451" s="4" t="n"/>
       <c r="H451" s="7">
@@ -16089,7 +16101,7 @@
     </row>
     <row r="452">
       <c r="D452" s="7" t="n"/>
-      <c r="E452" s="16" t="n"/>
+      <c r="E452" s="17" t="n"/>
       <c r="F452" s="7" t="n"/>
       <c r="G452" s="4" t="n"/>
       <c r="H452" s="7">
@@ -16107,7 +16119,7 @@
     </row>
     <row r="453">
       <c r="D453" s="7" t="n"/>
-      <c r="E453" s="16" t="n"/>
+      <c r="E453" s="17" t="n"/>
       <c r="F453" s="7" t="n"/>
       <c r="G453" s="4" t="n"/>
       <c r="H453" s="7">
@@ -16125,7 +16137,7 @@
     </row>
     <row r="454">
       <c r="D454" s="7" t="n"/>
-      <c r="E454" s="16" t="n"/>
+      <c r="E454" s="17" t="n"/>
       <c r="F454" s="7" t="n"/>
       <c r="G454" s="4" t="n"/>
       <c r="H454" s="7">
@@ -16143,7 +16155,7 @@
     </row>
     <row r="455">
       <c r="D455" s="7" t="n"/>
-      <c r="E455" s="16" t="n"/>
+      <c r="E455" s="17" t="n"/>
       <c r="F455" s="7" t="n"/>
       <c r="G455" s="4" t="n"/>
       <c r="H455" s="7">
@@ -16161,7 +16173,7 @@
     </row>
     <row r="456">
       <c r="D456" s="7" t="n"/>
-      <c r="E456" s="16" t="n"/>
+      <c r="E456" s="17" t="n"/>
       <c r="F456" s="7" t="n"/>
       <c r="G456" s="4" t="n"/>
       <c r="H456" s="7">
@@ -16179,7 +16191,7 @@
     </row>
     <row r="457">
       <c r="D457" s="7" t="n"/>
-      <c r="E457" s="16" t="n"/>
+      <c r="E457" s="17" t="n"/>
       <c r="F457" s="7" t="n"/>
       <c r="G457" s="4" t="n"/>
       <c r="H457" s="7">
@@ -16197,7 +16209,7 @@
     </row>
     <row r="458">
       <c r="D458" s="7" t="n"/>
-      <c r="E458" s="16" t="n"/>
+      <c r="E458" s="17" t="n"/>
       <c r="F458" s="7" t="n"/>
       <c r="G458" s="4" t="n"/>
       <c r="H458" s="7">
@@ -16215,7 +16227,7 @@
     </row>
     <row r="459">
       <c r="D459" s="7" t="n"/>
-      <c r="E459" s="16" t="n"/>
+      <c r="E459" s="17" t="n"/>
       <c r="F459" s="7" t="n"/>
       <c r="G459" s="4" t="n"/>
       <c r="H459" s="7">
@@ -16233,7 +16245,7 @@
     </row>
     <row r="460">
       <c r="D460" s="7" t="n"/>
-      <c r="E460" s="16" t="n"/>
+      <c r="E460" s="17" t="n"/>
       <c r="F460" s="7" t="n"/>
       <c r="G460" s="4" t="n"/>
       <c r="H460" s="7">
@@ -16251,7 +16263,7 @@
     </row>
     <row r="461">
       <c r="D461" s="7" t="n"/>
-      <c r="E461" s="16" t="n"/>
+      <c r="E461" s="17" t="n"/>
       <c r="F461" s="7" t="n"/>
       <c r="G461" s="4" t="n"/>
       <c r="H461" s="7">
@@ -16269,7 +16281,7 @@
     </row>
     <row r="462">
       <c r="D462" s="7" t="n"/>
-      <c r="E462" s="16" t="n"/>
+      <c r="E462" s="17" t="n"/>
       <c r="F462" s="7" t="n"/>
       <c r="G462" s="4" t="n"/>
       <c r="H462" s="7">
@@ -16287,7 +16299,7 @@
     </row>
     <row r="463">
       <c r="D463" s="7" t="n"/>
-      <c r="E463" s="16" t="n"/>
+      <c r="E463" s="17" t="n"/>
       <c r="F463" s="7" t="n"/>
       <c r="G463" s="4" t="n"/>
       <c r="H463" s="7">
@@ -16305,7 +16317,7 @@
     </row>
     <row r="464">
       <c r="D464" s="7" t="n"/>
-      <c r="E464" s="16" t="n"/>
+      <c r="E464" s="17" t="n"/>
       <c r="F464" s="7" t="n"/>
       <c r="G464" s="4" t="n"/>
       <c r="H464" s="7">
@@ -16323,7 +16335,7 @@
     </row>
     <row r="465">
       <c r="D465" s="7" t="n"/>
-      <c r="E465" s="16" t="n"/>
+      <c r="E465" s="17" t="n"/>
       <c r="F465" s="7" t="n"/>
       <c r="G465" s="4" t="n"/>
       <c r="H465" s="7">
@@ -16341,7 +16353,7 @@
     </row>
     <row r="466">
       <c r="D466" s="7" t="n"/>
-      <c r="E466" s="16" t="n"/>
+      <c r="E466" s="17" t="n"/>
       <c r="F466" s="7" t="n"/>
       <c r="G466" s="4" t="n"/>
       <c r="H466" s="7">
@@ -16359,7 +16371,7 @@
     </row>
     <row r="467">
       <c r="D467" s="7" t="n"/>
-      <c r="E467" s="16" t="n"/>
+      <c r="E467" s="17" t="n"/>
       <c r="F467" s="7" t="n"/>
       <c r="G467" s="4" t="n"/>
       <c r="H467" s="7">
@@ -16377,7 +16389,7 @@
     </row>
     <row r="468">
       <c r="D468" s="7" t="n"/>
-      <c r="E468" s="16" t="n"/>
+      <c r="E468" s="17" t="n"/>
       <c r="F468" s="7" t="n"/>
       <c r="G468" s="4" t="n"/>
       <c r="H468" s="7">
@@ -16395,7 +16407,7 @@
     </row>
     <row r="469">
       <c r="D469" s="7" t="n"/>
-      <c r="E469" s="16" t="n"/>
+      <c r="E469" s="17" t="n"/>
       <c r="F469" s="7" t="n"/>
       <c r="G469" s="4" t="n"/>
       <c r="H469" s="7">
@@ -16413,7 +16425,7 @@
     </row>
     <row r="470">
       <c r="D470" s="7" t="n"/>
-      <c r="E470" s="16" t="n"/>
+      <c r="E470" s="17" t="n"/>
       <c r="F470" s="7" t="n"/>
       <c r="G470" s="4" t="n"/>
       <c r="H470" s="7">
@@ -16431,7 +16443,7 @@
     </row>
     <row r="471">
       <c r="D471" s="7" t="n"/>
-      <c r="E471" s="16" t="n"/>
+      <c r="E471" s="17" t="n"/>
       <c r="F471" s="7" t="n"/>
       <c r="G471" s="4" t="n"/>
       <c r="H471" s="7">
@@ -16449,7 +16461,7 @@
     </row>
     <row r="472">
       <c r="D472" s="7" t="n"/>
-      <c r="E472" s="16" t="n"/>
+      <c r="E472" s="17" t="n"/>
       <c r="F472" s="7" t="n"/>
       <c r="G472" s="4" t="n"/>
       <c r="H472" s="7">
@@ -16467,7 +16479,7 @@
     </row>
     <row r="473">
       <c r="D473" s="7" t="n"/>
-      <c r="E473" s="16" t="n"/>
+      <c r="E473" s="17" t="n"/>
       <c r="F473" s="7" t="n"/>
       <c r="G473" s="4" t="n"/>
       <c r="H473" s="7">
@@ -16485,7 +16497,7 @@
     </row>
     <row r="474">
       <c r="D474" s="7" t="n"/>
-      <c r="E474" s="16" t="n"/>
+      <c r="E474" s="17" t="n"/>
       <c r="F474" s="7" t="n"/>
       <c r="G474" s="4" t="n"/>
       <c r="H474" s="7">
@@ -16503,7 +16515,7 @@
     </row>
     <row r="475">
       <c r="D475" s="7" t="n"/>
-      <c r="E475" s="16" t="n"/>
+      <c r="E475" s="17" t="n"/>
       <c r="F475" s="7" t="n"/>
       <c r="G475" s="4" t="n"/>
       <c r="H475" s="7">
@@ -16521,7 +16533,7 @@
     </row>
     <row r="476">
       <c r="D476" s="7" t="n"/>
-      <c r="E476" s="16" t="n"/>
+      <c r="E476" s="17" t="n"/>
       <c r="F476" s="7" t="n"/>
       <c r="G476" s="4" t="n"/>
       <c r="H476" s="7">
@@ -16539,7 +16551,7 @@
     </row>
     <row r="477">
       <c r="D477" s="7" t="n"/>
-      <c r="E477" s="16" t="n"/>
+      <c r="E477" s="17" t="n"/>
       <c r="F477" s="7" t="n"/>
       <c r="G477" s="4" t="n"/>
       <c r="H477" s="7">
@@ -16557,7 +16569,7 @@
     </row>
     <row r="478">
       <c r="D478" s="7" t="n"/>
-      <c r="E478" s="16" t="n"/>
+      <c r="E478" s="17" t="n"/>
       <c r="F478" s="7" t="n"/>
       <c r="G478" s="4" t="n"/>
       <c r="H478" s="7">
@@ -16575,7 +16587,7 @@
     </row>
     <row r="479">
       <c r="D479" s="7" t="n"/>
-      <c r="E479" s="16" t="n"/>
+      <c r="E479" s="17" t="n"/>
       <c r="F479" s="7" t="n"/>
       <c r="G479" s="4" t="n"/>
       <c r="H479" s="7">
@@ -16593,7 +16605,7 @@
     </row>
     <row r="480">
       <c r="D480" s="7" t="n"/>
-      <c r="E480" s="16" t="n"/>
+      <c r="E480" s="17" t="n"/>
       <c r="F480" s="7" t="n"/>
       <c r="G480" s="4" t="n"/>
       <c r="H480" s="7">
@@ -16611,7 +16623,7 @@
     </row>
     <row r="481">
       <c r="D481" s="7" t="n"/>
-      <c r="E481" s="16" t="n"/>
+      <c r="E481" s="17" t="n"/>
       <c r="F481" s="7" t="n"/>
       <c r="G481" s="4" t="n"/>
       <c r="H481" s="7">
@@ -16629,7 +16641,7 @@
     </row>
     <row r="482">
       <c r="D482" s="7" t="n"/>
-      <c r="E482" s="16" t="n"/>
+      <c r="E482" s="17" t="n"/>
       <c r="F482" s="7" t="n"/>
       <c r="G482" s="4" t="n"/>
       <c r="H482" s="7">
@@ -16647,7 +16659,7 @@
     </row>
     <row r="483">
       <c r="D483" s="7" t="n"/>
-      <c r="E483" s="16" t="n"/>
+      <c r="E483" s="17" t="n"/>
       <c r="F483" s="7" t="n"/>
       <c r="G483" s="4" t="n"/>
       <c r="H483" s="7">
@@ -16665,7 +16677,7 @@
     </row>
     <row r="484">
       <c r="D484" s="7" t="n"/>
-      <c r="E484" s="16" t="n"/>
+      <c r="E484" s="17" t="n"/>
       <c r="F484" s="7" t="n"/>
       <c r="G484" s="4" t="n"/>
       <c r="H484" s="7">
@@ -16683,7 +16695,7 @@
     </row>
     <row r="485">
       <c r="D485" s="7" t="n"/>
-      <c r="E485" s="16" t="n"/>
+      <c r="E485" s="17" t="n"/>
       <c r="F485" s="7" t="n"/>
       <c r="G485" s="4" t="n"/>
       <c r="H485" s="7">
@@ -16701,7 +16713,7 @@
     </row>
     <row r="486">
       <c r="D486" s="7" t="n"/>
-      <c r="E486" s="16" t="n"/>
+      <c r="E486" s="17" t="n"/>
       <c r="F486" s="7" t="n"/>
       <c r="G486" s="4" t="n"/>
       <c r="H486" s="7">
@@ -16719,7 +16731,7 @@
     </row>
     <row r="487">
       <c r="D487" s="7" t="n"/>
-      <c r="E487" s="16" t="n"/>
+      <c r="E487" s="17" t="n"/>
       <c r="F487" s="7" t="n"/>
       <c r="G487" s="4" t="n"/>
       <c r="H487" s="7">
@@ -16737,7 +16749,7 @@
     </row>
     <row r="488">
       <c r="D488" s="7" t="n"/>
-      <c r="E488" s="16" t="n"/>
+      <c r="E488" s="17" t="n"/>
       <c r="F488" s="7" t="n"/>
       <c r="G488" s="4" t="n"/>
       <c r="H488" s="7">
@@ -16755,7 +16767,7 @@
     </row>
     <row r="489">
       <c r="D489" s="7" t="n"/>
-      <c r="E489" s="16" t="n"/>
+      <c r="E489" s="17" t="n"/>
       <c r="F489" s="7" t="n"/>
       <c r="G489" s="4" t="n"/>
       <c r="H489" s="7">
@@ -16773,7 +16785,7 @@
     </row>
     <row r="490">
       <c r="D490" s="7" t="n"/>
-      <c r="E490" s="16" t="n"/>
+      <c r="E490" s="17" t="n"/>
       <c r="F490" s="7" t="n"/>
       <c r="G490" s="4" t="n"/>
       <c r="H490" s="7">
@@ -16791,7 +16803,7 @@
     </row>
     <row r="491">
       <c r="D491" s="7" t="n"/>
-      <c r="E491" s="16" t="n"/>
+      <c r="E491" s="17" t="n"/>
       <c r="F491" s="7" t="n"/>
       <c r="G491" s="4" t="n"/>
       <c r="H491" s="7">
@@ -16809,7 +16821,7 @@
     </row>
     <row r="492">
       <c r="D492" s="7" t="n"/>
-      <c r="E492" s="16" t="n"/>
+      <c r="E492" s="17" t="n"/>
       <c r="F492" s="7" t="n"/>
       <c r="G492" s="4" t="n"/>
       <c r="H492" s="7">
@@ -16827,7 +16839,7 @@
     </row>
     <row r="493">
       <c r="D493" s="7" t="n"/>
-      <c r="E493" s="16" t="n"/>
+      <c r="E493" s="17" t="n"/>
       <c r="F493" s="7" t="n"/>
       <c r="G493" s="4" t="n"/>
       <c r="H493" s="7">
@@ -16845,7 +16857,7 @@
     </row>
     <row r="494">
       <c r="D494" s="7" t="n"/>
-      <c r="E494" s="16" t="n"/>
+      <c r="E494" s="17" t="n"/>
       <c r="F494" s="7" t="n"/>
       <c r="G494" s="4" t="n"/>
       <c r="H494" s="7">
@@ -16863,7 +16875,7 @@
     </row>
     <row r="495">
       <c r="D495" s="7" t="n"/>
-      <c r="E495" s="16" t="n"/>
+      <c r="E495" s="17" t="n"/>
       <c r="F495" s="7" t="n"/>
       <c r="G495" s="4" t="n"/>
       <c r="H495" s="7">
@@ -16881,7 +16893,7 @@
     </row>
     <row r="496">
       <c r="D496" s="7" t="n"/>
-      <c r="E496" s="16" t="n"/>
+      <c r="E496" s="17" t="n"/>
       <c r="F496" s="7" t="n"/>
       <c r="G496" s="4" t="n"/>
       <c r="H496" s="7">
@@ -16899,7 +16911,7 @@
     </row>
     <row r="497">
       <c r="D497" s="7" t="n"/>
-      <c r="E497" s="16" t="n"/>
+      <c r="E497" s="17" t="n"/>
       <c r="F497" s="7" t="n"/>
       <c r="G497" s="4" t="n"/>
       <c r="H497" s="7">
@@ -16917,7 +16929,7 @@
     </row>
     <row r="498">
       <c r="D498" s="7" t="n"/>
-      <c r="E498" s="16" t="n"/>
+      <c r="E498" s="17" t="n"/>
       <c r="F498" s="7" t="n"/>
       <c r="G498" s="4" t="n"/>
       <c r="H498" s="7">
@@ -16935,7 +16947,7 @@
     </row>
     <row r="499">
       <c r="D499" s="7" t="n"/>
-      <c r="E499" s="16" t="n"/>
+      <c r="E499" s="17" t="n"/>
       <c r="F499" s="7" t="n"/>
       <c r="G499" s="4" t="n"/>
       <c r="H499" s="7">
@@ -16953,7 +16965,7 @@
     </row>
     <row r="500">
       <c r="D500" s="7" t="n"/>
-      <c r="E500" s="16" t="n"/>
+      <c r="E500" s="17" t="n"/>
       <c r="F500" s="7" t="n"/>
       <c r="G500" s="4" t="n"/>
       <c r="H500" s="7">
@@ -25581,7 +25593,7 @@
         <f>SUM(E2:E500)</f>
         <v/>
       </c>
-      <c r="F501" s="17">
+      <c r="F501" s="18">
         <f>IF(D501=0,"",(E501-D501)/D501)</f>
         <v/>
       </c>

--- a/money/finance-template.xlsx
+++ b/money/finance-template.xlsx
@@ -15,9 +15,10 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Долги" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Платежи" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Инвестиции" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Баланс" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Сводка по месяцам" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Списки" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Портфель" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Баланс" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Сводка по месяцам" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Списки" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -26,14 +27,17 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="5">
+  <numFmts count="8">
     <numFmt numFmtId="164" formatCode="#,##0 &quot;€&quot;"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
     <numFmt numFmtId="166" formatCode="dd.mm.yyyy"/>
     <numFmt numFmtId="167" formatCode="#,##0.00 &quot;€&quot;"/>
     <numFmt numFmtId="168" formatCode="mmmm yyyy"/>
+    <numFmt numFmtId="169" formatCode="0%;-0%;"/>
+    <numFmt numFmtId="170" formatCode="0.00%;-0.00%;"/>
+    <numFmt numFmtId="171" formatCode="#,##0.00 &quot;€&quot;;-#,##0.00 &quot;€&quot;;"/>
   </numFmts>
-  <fonts count="13">
+  <fonts count="15">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -51,6 +55,10 @@
     <font>
       <b val="1"/>
       <sz val="12"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="007F7F7F"/>
     </font>
     <font>
       <name val="Arial"/>
@@ -76,6 +84,12 @@
       <name val="Arial"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <i val="1"/>
+      <color rgb="007F7F7F"/>
       <sz val="10"/>
     </font>
     <font>
@@ -163,44 +177,51 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="168" fontId="4" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="10" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="10" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="4" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="10" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="1" fontId="10" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="5" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="12" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="12" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="5" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="12" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="12" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="5" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="1" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="1" fontId="5" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="4" fillId="5" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="2" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="4" fillId="5" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="168" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="6" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="6" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="5" fillId="5" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="5" fillId="5" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="6" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="170" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="171" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="10" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="4" fillId="5" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="5" fillId="5" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -567,7 +588,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A12"/>
+  <dimension ref="A1:A13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -646,12 +667,19 @@
     <row r="11" ht="22" customHeight="1">
       <c r="A11" s="2" t="inlineStr">
         <is>
+          <t>10. Портфель — выберите состав в B3 и сумму в месяц в B4. Ниже прогноз и сколько откладывать.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="22" customHeight="1">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
           <t>Жёлтые ячейки — то, что нужно заполнять. Остальное считается автоматически.</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="22" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
+    <row r="13" ht="22" customHeight="1">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>Ожидаемая доходность — номинальная, без гарантий. Налоги и инфляция в расчёт не входят.</t>
         </is>
@@ -663,6 +691,3061 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00548235"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D501"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="14" t="inlineStr">
+        <is>
+          <t>Тип актива</t>
+        </is>
+      </c>
+      <c r="B1" s="14" t="inlineStr">
+        <is>
+          <t>Название</t>
+        </is>
+      </c>
+      <c r="C1" s="14" t="inlineStr">
+        <is>
+          <t>Стоимость (€)</t>
+        </is>
+      </c>
+      <c r="D1" s="14" t="inlineStr">
+        <is>
+          <t>Дата обновления</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="15" t="n"/>
+      <c r="B2" s="15" t="n"/>
+      <c r="C2" s="22" t="n"/>
+      <c r="D2" s="21" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="15" t="n"/>
+      <c r="B3" s="15" t="n"/>
+      <c r="C3" s="22" t="n"/>
+      <c r="D3" s="21" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="15" t="n"/>
+      <c r="B4" s="15" t="n"/>
+      <c r="C4" s="22" t="n"/>
+      <c r="D4" s="21" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="15" t="n"/>
+      <c r="B5" s="15" t="n"/>
+      <c r="C5" s="22" t="n"/>
+      <c r="D5" s="21" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="15" t="n"/>
+      <c r="B6" s="15" t="n"/>
+      <c r="C6" s="22" t="n"/>
+      <c r="D6" s="21" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="15" t="n"/>
+      <c r="B7" s="15" t="n"/>
+      <c r="C7" s="22" t="n"/>
+      <c r="D7" s="21" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="15" t="n"/>
+      <c r="B8" s="15" t="n"/>
+      <c r="C8" s="22" t="n"/>
+      <c r="D8" s="21" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="15" t="n"/>
+      <c r="B9" s="15" t="n"/>
+      <c r="C9" s="22" t="n"/>
+      <c r="D9" s="21" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="15" t="n"/>
+      <c r="B10" s="15" t="n"/>
+      <c r="C10" s="22" t="n"/>
+      <c r="D10" s="21" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="15" t="n"/>
+      <c r="B11" s="15" t="n"/>
+      <c r="C11" s="22" t="n"/>
+      <c r="D11" s="21" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="15" t="n"/>
+      <c r="B12" s="15" t="n"/>
+      <c r="C12" s="22" t="n"/>
+      <c r="D12" s="21" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="15" t="n"/>
+      <c r="B13" s="15" t="n"/>
+      <c r="C13" s="22" t="n"/>
+      <c r="D13" s="21" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="15" t="n"/>
+      <c r="B14" s="15" t="n"/>
+      <c r="C14" s="22" t="n"/>
+      <c r="D14" s="21" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="15" t="n"/>
+      <c r="B15" s="15" t="n"/>
+      <c r="C15" s="22" t="n"/>
+      <c r="D15" s="21" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="15" t="n"/>
+      <c r="B16" s="15" t="n"/>
+      <c r="C16" s="22" t="n"/>
+      <c r="D16" s="21" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="15" t="n"/>
+      <c r="B17" s="15" t="n"/>
+      <c r="C17" s="22" t="n"/>
+      <c r="D17" s="21" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="15" t="n"/>
+      <c r="B18" s="15" t="n"/>
+      <c r="C18" s="22" t="n"/>
+      <c r="D18" s="21" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="15" t="n"/>
+      <c r="B19" s="15" t="n"/>
+      <c r="C19" s="22" t="n"/>
+      <c r="D19" s="21" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="15" t="n"/>
+      <c r="B20" s="15" t="n"/>
+      <c r="C20" s="22" t="n"/>
+      <c r="D20" s="21" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="15" t="n"/>
+      <c r="B21" s="15" t="n"/>
+      <c r="C21" s="22" t="n"/>
+      <c r="D21" s="21" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="15" t="n"/>
+      <c r="B22" s="15" t="n"/>
+      <c r="C22" s="22" t="n"/>
+      <c r="D22" s="21" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="15" t="n"/>
+      <c r="B23" s="15" t="n"/>
+      <c r="C23" s="22" t="n"/>
+      <c r="D23" s="21" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="15" t="n"/>
+      <c r="B24" s="15" t="n"/>
+      <c r="C24" s="22" t="n"/>
+      <c r="D24" s="21" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="15" t="n"/>
+      <c r="B25" s="15" t="n"/>
+      <c r="C25" s="22" t="n"/>
+      <c r="D25" s="21" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="15" t="n"/>
+      <c r="B26" s="15" t="n"/>
+      <c r="C26" s="22" t="n"/>
+      <c r="D26" s="21" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="15" t="n"/>
+      <c r="B27" s="15" t="n"/>
+      <c r="C27" s="22" t="n"/>
+      <c r="D27" s="21" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="15" t="n"/>
+      <c r="B28" s="15" t="n"/>
+      <c r="C28" s="22" t="n"/>
+      <c r="D28" s="21" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="15" t="n"/>
+      <c r="B29" s="15" t="n"/>
+      <c r="C29" s="22" t="n"/>
+      <c r="D29" s="21" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="15" t="n"/>
+      <c r="B30" s="15" t="n"/>
+      <c r="C30" s="22" t="n"/>
+      <c r="D30" s="21" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="15" t="n"/>
+      <c r="B31" s="15" t="n"/>
+      <c r="C31" s="22" t="n"/>
+      <c r="D31" s="21" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="15" t="n"/>
+      <c r="B32" s="15" t="n"/>
+      <c r="C32" s="22" t="n"/>
+      <c r="D32" s="21" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="15" t="n"/>
+      <c r="B33" s="15" t="n"/>
+      <c r="C33" s="22" t="n"/>
+      <c r="D33" s="21" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="15" t="n"/>
+      <c r="B34" s="15" t="n"/>
+      <c r="C34" s="22" t="n"/>
+      <c r="D34" s="21" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="15" t="n"/>
+      <c r="B35" s="15" t="n"/>
+      <c r="C35" s="22" t="n"/>
+      <c r="D35" s="21" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="15" t="n"/>
+      <c r="B36" s="15" t="n"/>
+      <c r="C36" s="22" t="n"/>
+      <c r="D36" s="21" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="15" t="n"/>
+      <c r="B37" s="15" t="n"/>
+      <c r="C37" s="22" t="n"/>
+      <c r="D37" s="21" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="15" t="n"/>
+      <c r="B38" s="15" t="n"/>
+      <c r="C38" s="22" t="n"/>
+      <c r="D38" s="21" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="15" t="n"/>
+      <c r="B39" s="15" t="n"/>
+      <c r="C39" s="22" t="n"/>
+      <c r="D39" s="21" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="15" t="n"/>
+      <c r="B40" s="15" t="n"/>
+      <c r="C40" s="22" t="n"/>
+      <c r="D40" s="21" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="15" t="n"/>
+      <c r="B41" s="15" t="n"/>
+      <c r="C41" s="22" t="n"/>
+      <c r="D41" s="21" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="15" t="n"/>
+      <c r="B42" s="15" t="n"/>
+      <c r="C42" s="22" t="n"/>
+      <c r="D42" s="21" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="15" t="n"/>
+      <c r="B43" s="15" t="n"/>
+      <c r="C43" s="22" t="n"/>
+      <c r="D43" s="21" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="15" t="n"/>
+      <c r="B44" s="15" t="n"/>
+      <c r="C44" s="22" t="n"/>
+      <c r="D44" s="21" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="15" t="n"/>
+      <c r="B45" s="15" t="n"/>
+      <c r="C45" s="22" t="n"/>
+      <c r="D45" s="21" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="15" t="n"/>
+      <c r="B46" s="15" t="n"/>
+      <c r="C46" s="22" t="n"/>
+      <c r="D46" s="21" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="15" t="n"/>
+      <c r="B47" s="15" t="n"/>
+      <c r="C47" s="22" t="n"/>
+      <c r="D47" s="21" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="15" t="n"/>
+      <c r="B48" s="15" t="n"/>
+      <c r="C48" s="22" t="n"/>
+      <c r="D48" s="21" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="15" t="n"/>
+      <c r="B49" s="15" t="n"/>
+      <c r="C49" s="22" t="n"/>
+      <c r="D49" s="21" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="15" t="n"/>
+      <c r="B50" s="15" t="n"/>
+      <c r="C50" s="22" t="n"/>
+      <c r="D50" s="21" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="15" t="n"/>
+      <c r="B51" s="15" t="n"/>
+      <c r="C51" s="22" t="n"/>
+      <c r="D51" s="21" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="15" t="n"/>
+      <c r="B52" s="15" t="n"/>
+      <c r="C52" s="22" t="n"/>
+      <c r="D52" s="21" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="15" t="n"/>
+      <c r="B53" s="15" t="n"/>
+      <c r="C53" s="22" t="n"/>
+      <c r="D53" s="21" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="15" t="n"/>
+      <c r="B54" s="15" t="n"/>
+      <c r="C54" s="22" t="n"/>
+      <c r="D54" s="21" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="15" t="n"/>
+      <c r="B55" s="15" t="n"/>
+      <c r="C55" s="22" t="n"/>
+      <c r="D55" s="21" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="15" t="n"/>
+      <c r="B56" s="15" t="n"/>
+      <c r="C56" s="22" t="n"/>
+      <c r="D56" s="21" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="15" t="n"/>
+      <c r="B57" s="15" t="n"/>
+      <c r="C57" s="22" t="n"/>
+      <c r="D57" s="21" t="n"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="15" t="n"/>
+      <c r="B58" s="15" t="n"/>
+      <c r="C58" s="22" t="n"/>
+      <c r="D58" s="21" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="15" t="n"/>
+      <c r="B59" s="15" t="n"/>
+      <c r="C59" s="22" t="n"/>
+      <c r="D59" s="21" t="n"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="15" t="n"/>
+      <c r="B60" s="15" t="n"/>
+      <c r="C60" s="22" t="n"/>
+      <c r="D60" s="21" t="n"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="15" t="n"/>
+      <c r="B61" s="15" t="n"/>
+      <c r="C61" s="22" t="n"/>
+      <c r="D61" s="21" t="n"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="15" t="n"/>
+      <c r="B62" s="15" t="n"/>
+      <c r="C62" s="22" t="n"/>
+      <c r="D62" s="21" t="n"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="15" t="n"/>
+      <c r="B63" s="15" t="n"/>
+      <c r="C63" s="22" t="n"/>
+      <c r="D63" s="21" t="n"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="15" t="n"/>
+      <c r="B64" s="15" t="n"/>
+      <c r="C64" s="22" t="n"/>
+      <c r="D64" s="21" t="n"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="15" t="n"/>
+      <c r="B65" s="15" t="n"/>
+      <c r="C65" s="22" t="n"/>
+      <c r="D65" s="21" t="n"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="15" t="n"/>
+      <c r="B66" s="15" t="n"/>
+      <c r="C66" s="22" t="n"/>
+      <c r="D66" s="21" t="n"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="15" t="n"/>
+      <c r="B67" s="15" t="n"/>
+      <c r="C67" s="22" t="n"/>
+      <c r="D67" s="21" t="n"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="15" t="n"/>
+      <c r="B68" s="15" t="n"/>
+      <c r="C68" s="22" t="n"/>
+      <c r="D68" s="21" t="n"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="15" t="n"/>
+      <c r="B69" s="15" t="n"/>
+      <c r="C69" s="22" t="n"/>
+      <c r="D69" s="21" t="n"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="15" t="n"/>
+      <c r="B70" s="15" t="n"/>
+      <c r="C70" s="22" t="n"/>
+      <c r="D70" s="21" t="n"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="15" t="n"/>
+      <c r="B71" s="15" t="n"/>
+      <c r="C71" s="22" t="n"/>
+      <c r="D71" s="21" t="n"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="15" t="n"/>
+      <c r="B72" s="15" t="n"/>
+      <c r="C72" s="22" t="n"/>
+      <c r="D72" s="21" t="n"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="15" t="n"/>
+      <c r="B73" s="15" t="n"/>
+      <c r="C73" s="22" t="n"/>
+      <c r="D73" s="21" t="n"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="15" t="n"/>
+      <c r="B74" s="15" t="n"/>
+      <c r="C74" s="22" t="n"/>
+      <c r="D74" s="21" t="n"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="15" t="n"/>
+      <c r="B75" s="15" t="n"/>
+      <c r="C75" s="22" t="n"/>
+      <c r="D75" s="21" t="n"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="15" t="n"/>
+      <c r="B76" s="15" t="n"/>
+      <c r="C76" s="22" t="n"/>
+      <c r="D76" s="21" t="n"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="15" t="n"/>
+      <c r="B77" s="15" t="n"/>
+      <c r="C77" s="22" t="n"/>
+      <c r="D77" s="21" t="n"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="15" t="n"/>
+      <c r="B78" s="15" t="n"/>
+      <c r="C78" s="22" t="n"/>
+      <c r="D78" s="21" t="n"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="15" t="n"/>
+      <c r="B79" s="15" t="n"/>
+      <c r="C79" s="22" t="n"/>
+      <c r="D79" s="21" t="n"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="15" t="n"/>
+      <c r="B80" s="15" t="n"/>
+      <c r="C80" s="22" t="n"/>
+      <c r="D80" s="21" t="n"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="15" t="n"/>
+      <c r="B81" s="15" t="n"/>
+      <c r="C81" s="22" t="n"/>
+      <c r="D81" s="21" t="n"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="15" t="n"/>
+      <c r="B82" s="15" t="n"/>
+      <c r="C82" s="22" t="n"/>
+      <c r="D82" s="21" t="n"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="15" t="n"/>
+      <c r="B83" s="15" t="n"/>
+      <c r="C83" s="22" t="n"/>
+      <c r="D83" s="21" t="n"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="15" t="n"/>
+      <c r="B84" s="15" t="n"/>
+      <c r="C84" s="22" t="n"/>
+      <c r="D84" s="21" t="n"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="15" t="n"/>
+      <c r="B85" s="15" t="n"/>
+      <c r="C85" s="22" t="n"/>
+      <c r="D85" s="21" t="n"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="15" t="n"/>
+      <c r="B86" s="15" t="n"/>
+      <c r="C86" s="22" t="n"/>
+      <c r="D86" s="21" t="n"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="15" t="n"/>
+      <c r="B87" s="15" t="n"/>
+      <c r="C87" s="22" t="n"/>
+      <c r="D87" s="21" t="n"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="15" t="n"/>
+      <c r="B88" s="15" t="n"/>
+      <c r="C88" s="22" t="n"/>
+      <c r="D88" s="21" t="n"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="15" t="n"/>
+      <c r="B89" s="15" t="n"/>
+      <c r="C89" s="22" t="n"/>
+      <c r="D89" s="21" t="n"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="15" t="n"/>
+      <c r="B90" s="15" t="n"/>
+      <c r="C90" s="22" t="n"/>
+      <c r="D90" s="21" t="n"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="15" t="n"/>
+      <c r="B91" s="15" t="n"/>
+      <c r="C91" s="22" t="n"/>
+      <c r="D91" s="21" t="n"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="15" t="n"/>
+      <c r="B92" s="15" t="n"/>
+      <c r="C92" s="22" t="n"/>
+      <c r="D92" s="21" t="n"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="15" t="n"/>
+      <c r="B93" s="15" t="n"/>
+      <c r="C93" s="22" t="n"/>
+      <c r="D93" s="21" t="n"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="15" t="n"/>
+      <c r="B94" s="15" t="n"/>
+      <c r="C94" s="22" t="n"/>
+      <c r="D94" s="21" t="n"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="15" t="n"/>
+      <c r="B95" s="15" t="n"/>
+      <c r="C95" s="22" t="n"/>
+      <c r="D95" s="21" t="n"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="15" t="n"/>
+      <c r="B96" s="15" t="n"/>
+      <c r="C96" s="22" t="n"/>
+      <c r="D96" s="21" t="n"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="15" t="n"/>
+      <c r="B97" s="15" t="n"/>
+      <c r="C97" s="22" t="n"/>
+      <c r="D97" s="21" t="n"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="15" t="n"/>
+      <c r="B98" s="15" t="n"/>
+      <c r="C98" s="22" t="n"/>
+      <c r="D98" s="21" t="n"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="15" t="n"/>
+      <c r="B99" s="15" t="n"/>
+      <c r="C99" s="22" t="n"/>
+      <c r="D99" s="21" t="n"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="15" t="n"/>
+      <c r="B100" s="15" t="n"/>
+      <c r="C100" s="22" t="n"/>
+      <c r="D100" s="21" t="n"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="15" t="n"/>
+      <c r="B101" s="15" t="n"/>
+      <c r="C101" s="22" t="n"/>
+      <c r="D101" s="21" t="n"/>
+    </row>
+    <row r="102">
+      <c r="A102" s="15" t="n"/>
+      <c r="B102" s="15" t="n"/>
+      <c r="C102" s="22" t="n"/>
+      <c r="D102" s="21" t="n"/>
+    </row>
+    <row r="103">
+      <c r="A103" s="15" t="n"/>
+      <c r="B103" s="15" t="n"/>
+      <c r="C103" s="22" t="n"/>
+      <c r="D103" s="21" t="n"/>
+    </row>
+    <row r="104">
+      <c r="A104" s="15" t="n"/>
+      <c r="B104" s="15" t="n"/>
+      <c r="C104" s="22" t="n"/>
+      <c r="D104" s="21" t="n"/>
+    </row>
+    <row r="105">
+      <c r="A105" s="15" t="n"/>
+      <c r="B105" s="15" t="n"/>
+      <c r="C105" s="22" t="n"/>
+      <c r="D105" s="21" t="n"/>
+    </row>
+    <row r="106">
+      <c r="A106" s="15" t="n"/>
+      <c r="B106" s="15" t="n"/>
+      <c r="C106" s="22" t="n"/>
+      <c r="D106" s="21" t="n"/>
+    </row>
+    <row r="107">
+      <c r="A107" s="15" t="n"/>
+      <c r="B107" s="15" t="n"/>
+      <c r="C107" s="22" t="n"/>
+      <c r="D107" s="21" t="n"/>
+    </row>
+    <row r="108">
+      <c r="A108" s="15" t="n"/>
+      <c r="B108" s="15" t="n"/>
+      <c r="C108" s="22" t="n"/>
+      <c r="D108" s="21" t="n"/>
+    </row>
+    <row r="109">
+      <c r="A109" s="15" t="n"/>
+      <c r="B109" s="15" t="n"/>
+      <c r="C109" s="22" t="n"/>
+      <c r="D109" s="21" t="n"/>
+    </row>
+    <row r="110">
+      <c r="A110" s="15" t="n"/>
+      <c r="B110" s="15" t="n"/>
+      <c r="C110" s="22" t="n"/>
+      <c r="D110" s="21" t="n"/>
+    </row>
+    <row r="111">
+      <c r="A111" s="15" t="n"/>
+      <c r="B111" s="15" t="n"/>
+      <c r="C111" s="22" t="n"/>
+      <c r="D111" s="21" t="n"/>
+    </row>
+    <row r="112">
+      <c r="A112" s="15" t="n"/>
+      <c r="B112" s="15" t="n"/>
+      <c r="C112" s="22" t="n"/>
+      <c r="D112" s="21" t="n"/>
+    </row>
+    <row r="113">
+      <c r="A113" s="15" t="n"/>
+      <c r="B113" s="15" t="n"/>
+      <c r="C113" s="22" t="n"/>
+      <c r="D113" s="21" t="n"/>
+    </row>
+    <row r="114">
+      <c r="A114" s="15" t="n"/>
+      <c r="B114" s="15" t="n"/>
+      <c r="C114" s="22" t="n"/>
+      <c r="D114" s="21" t="n"/>
+    </row>
+    <row r="115">
+      <c r="A115" s="15" t="n"/>
+      <c r="B115" s="15" t="n"/>
+      <c r="C115" s="22" t="n"/>
+      <c r="D115" s="21" t="n"/>
+    </row>
+    <row r="116">
+      <c r="A116" s="15" t="n"/>
+      <c r="B116" s="15" t="n"/>
+      <c r="C116" s="22" t="n"/>
+      <c r="D116" s="21" t="n"/>
+    </row>
+    <row r="117">
+      <c r="A117" s="15" t="n"/>
+      <c r="B117" s="15" t="n"/>
+      <c r="C117" s="22" t="n"/>
+      <c r="D117" s="21" t="n"/>
+    </row>
+    <row r="118">
+      <c r="A118" s="15" t="n"/>
+      <c r="B118" s="15" t="n"/>
+      <c r="C118" s="22" t="n"/>
+      <c r="D118" s="21" t="n"/>
+    </row>
+    <row r="119">
+      <c r="A119" s="15" t="n"/>
+      <c r="B119" s="15" t="n"/>
+      <c r="C119" s="22" t="n"/>
+      <c r="D119" s="21" t="n"/>
+    </row>
+    <row r="120">
+      <c r="A120" s="15" t="n"/>
+      <c r="B120" s="15" t="n"/>
+      <c r="C120" s="22" t="n"/>
+      <c r="D120" s="21" t="n"/>
+    </row>
+    <row r="121">
+      <c r="A121" s="15" t="n"/>
+      <c r="B121" s="15" t="n"/>
+      <c r="C121" s="22" t="n"/>
+      <c r="D121" s="21" t="n"/>
+    </row>
+    <row r="122">
+      <c r="A122" s="15" t="n"/>
+      <c r="B122" s="15" t="n"/>
+      <c r="C122" s="22" t="n"/>
+      <c r="D122" s="21" t="n"/>
+    </row>
+    <row r="123">
+      <c r="A123" s="15" t="n"/>
+      <c r="B123" s="15" t="n"/>
+      <c r="C123" s="22" t="n"/>
+      <c r="D123" s="21" t="n"/>
+    </row>
+    <row r="124">
+      <c r="A124" s="15" t="n"/>
+      <c r="B124" s="15" t="n"/>
+      <c r="C124" s="22" t="n"/>
+      <c r="D124" s="21" t="n"/>
+    </row>
+    <row r="125">
+      <c r="A125" s="15" t="n"/>
+      <c r="B125" s="15" t="n"/>
+      <c r="C125" s="22" t="n"/>
+      <c r="D125" s="21" t="n"/>
+    </row>
+    <row r="126">
+      <c r="A126" s="15" t="n"/>
+      <c r="B126" s="15" t="n"/>
+      <c r="C126" s="22" t="n"/>
+      <c r="D126" s="21" t="n"/>
+    </row>
+    <row r="127">
+      <c r="A127" s="15" t="n"/>
+      <c r="B127" s="15" t="n"/>
+      <c r="C127" s="22" t="n"/>
+      <c r="D127" s="21" t="n"/>
+    </row>
+    <row r="128">
+      <c r="A128" s="15" t="n"/>
+      <c r="B128" s="15" t="n"/>
+      <c r="C128" s="22" t="n"/>
+      <c r="D128" s="21" t="n"/>
+    </row>
+    <row r="129">
+      <c r="A129" s="15" t="n"/>
+      <c r="B129" s="15" t="n"/>
+      <c r="C129" s="22" t="n"/>
+      <c r="D129" s="21" t="n"/>
+    </row>
+    <row r="130">
+      <c r="A130" s="15" t="n"/>
+      <c r="B130" s="15" t="n"/>
+      <c r="C130" s="22" t="n"/>
+      <c r="D130" s="21" t="n"/>
+    </row>
+    <row r="131">
+      <c r="A131" s="15" t="n"/>
+      <c r="B131" s="15" t="n"/>
+      <c r="C131" s="22" t="n"/>
+      <c r="D131" s="21" t="n"/>
+    </row>
+    <row r="132">
+      <c r="A132" s="15" t="n"/>
+      <c r="B132" s="15" t="n"/>
+      <c r="C132" s="22" t="n"/>
+      <c r="D132" s="21" t="n"/>
+    </row>
+    <row r="133">
+      <c r="A133" s="15" t="n"/>
+      <c r="B133" s="15" t="n"/>
+      <c r="C133" s="22" t="n"/>
+      <c r="D133" s="21" t="n"/>
+    </row>
+    <row r="134">
+      <c r="A134" s="15" t="n"/>
+      <c r="B134" s="15" t="n"/>
+      <c r="C134" s="22" t="n"/>
+      <c r="D134" s="21" t="n"/>
+    </row>
+    <row r="135">
+      <c r="A135" s="15" t="n"/>
+      <c r="B135" s="15" t="n"/>
+      <c r="C135" s="22" t="n"/>
+      <c r="D135" s="21" t="n"/>
+    </row>
+    <row r="136">
+      <c r="A136" s="15" t="n"/>
+      <c r="B136" s="15" t="n"/>
+      <c r="C136" s="22" t="n"/>
+      <c r="D136" s="21" t="n"/>
+    </row>
+    <row r="137">
+      <c r="A137" s="15" t="n"/>
+      <c r="B137" s="15" t="n"/>
+      <c r="C137" s="22" t="n"/>
+      <c r="D137" s="21" t="n"/>
+    </row>
+    <row r="138">
+      <c r="A138" s="15" t="n"/>
+      <c r="B138" s="15" t="n"/>
+      <c r="C138" s="22" t="n"/>
+      <c r="D138" s="21" t="n"/>
+    </row>
+    <row r="139">
+      <c r="A139" s="15" t="n"/>
+      <c r="B139" s="15" t="n"/>
+      <c r="C139" s="22" t="n"/>
+      <c r="D139" s="21" t="n"/>
+    </row>
+    <row r="140">
+      <c r="A140" s="15" t="n"/>
+      <c r="B140" s="15" t="n"/>
+      <c r="C140" s="22" t="n"/>
+      <c r="D140" s="21" t="n"/>
+    </row>
+    <row r="141">
+      <c r="A141" s="15" t="n"/>
+      <c r="B141" s="15" t="n"/>
+      <c r="C141" s="22" t="n"/>
+      <c r="D141" s="21" t="n"/>
+    </row>
+    <row r="142">
+      <c r="A142" s="15" t="n"/>
+      <c r="B142" s="15" t="n"/>
+      <c r="C142" s="22" t="n"/>
+      <c r="D142" s="21" t="n"/>
+    </row>
+    <row r="143">
+      <c r="A143" s="15" t="n"/>
+      <c r="B143" s="15" t="n"/>
+      <c r="C143" s="22" t="n"/>
+      <c r="D143" s="21" t="n"/>
+    </row>
+    <row r="144">
+      <c r="A144" s="15" t="n"/>
+      <c r="B144" s="15" t="n"/>
+      <c r="C144" s="22" t="n"/>
+      <c r="D144" s="21" t="n"/>
+    </row>
+    <row r="145">
+      <c r="A145" s="15" t="n"/>
+      <c r="B145" s="15" t="n"/>
+      <c r="C145" s="22" t="n"/>
+      <c r="D145" s="21" t="n"/>
+    </row>
+    <row r="146">
+      <c r="A146" s="15" t="n"/>
+      <c r="B146" s="15" t="n"/>
+      <c r="C146" s="22" t="n"/>
+      <c r="D146" s="21" t="n"/>
+    </row>
+    <row r="147">
+      <c r="A147" s="15" t="n"/>
+      <c r="B147" s="15" t="n"/>
+      <c r="C147" s="22" t="n"/>
+      <c r="D147" s="21" t="n"/>
+    </row>
+    <row r="148">
+      <c r="A148" s="15" t="n"/>
+      <c r="B148" s="15" t="n"/>
+      <c r="C148" s="22" t="n"/>
+      <c r="D148" s="21" t="n"/>
+    </row>
+    <row r="149">
+      <c r="A149" s="15" t="n"/>
+      <c r="B149" s="15" t="n"/>
+      <c r="C149" s="22" t="n"/>
+      <c r="D149" s="21" t="n"/>
+    </row>
+    <row r="150">
+      <c r="A150" s="15" t="n"/>
+      <c r="B150" s="15" t="n"/>
+      <c r="C150" s="22" t="n"/>
+      <c r="D150" s="21" t="n"/>
+    </row>
+    <row r="151">
+      <c r="A151" s="15" t="n"/>
+      <c r="B151" s="15" t="n"/>
+      <c r="C151" s="22" t="n"/>
+      <c r="D151" s="21" t="n"/>
+    </row>
+    <row r="152">
+      <c r="A152" s="15" t="n"/>
+      <c r="B152" s="15" t="n"/>
+      <c r="C152" s="22" t="n"/>
+      <c r="D152" s="21" t="n"/>
+    </row>
+    <row r="153">
+      <c r="A153" s="15" t="n"/>
+      <c r="B153" s="15" t="n"/>
+      <c r="C153" s="22" t="n"/>
+      <c r="D153" s="21" t="n"/>
+    </row>
+    <row r="154">
+      <c r="A154" s="15" t="n"/>
+      <c r="B154" s="15" t="n"/>
+      <c r="C154" s="22" t="n"/>
+      <c r="D154" s="21" t="n"/>
+    </row>
+    <row r="155">
+      <c r="A155" s="15" t="n"/>
+      <c r="B155" s="15" t="n"/>
+      <c r="C155" s="22" t="n"/>
+      <c r="D155" s="21" t="n"/>
+    </row>
+    <row r="156">
+      <c r="A156" s="15" t="n"/>
+      <c r="B156" s="15" t="n"/>
+      <c r="C156" s="22" t="n"/>
+      <c r="D156" s="21" t="n"/>
+    </row>
+    <row r="157">
+      <c r="A157" s="15" t="n"/>
+      <c r="B157" s="15" t="n"/>
+      <c r="C157" s="22" t="n"/>
+      <c r="D157" s="21" t="n"/>
+    </row>
+    <row r="158">
+      <c r="A158" s="15" t="n"/>
+      <c r="B158" s="15" t="n"/>
+      <c r="C158" s="22" t="n"/>
+      <c r="D158" s="21" t="n"/>
+    </row>
+    <row r="159">
+      <c r="A159" s="15" t="n"/>
+      <c r="B159" s="15" t="n"/>
+      <c r="C159" s="22" t="n"/>
+      <c r="D159" s="21" t="n"/>
+    </row>
+    <row r="160">
+      <c r="A160" s="15" t="n"/>
+      <c r="B160" s="15" t="n"/>
+      <c r="C160" s="22" t="n"/>
+      <c r="D160" s="21" t="n"/>
+    </row>
+    <row r="161">
+      <c r="A161" s="15" t="n"/>
+      <c r="B161" s="15" t="n"/>
+      <c r="C161" s="22" t="n"/>
+      <c r="D161" s="21" t="n"/>
+    </row>
+    <row r="162">
+      <c r="A162" s="15" t="n"/>
+      <c r="B162" s="15" t="n"/>
+      <c r="C162" s="22" t="n"/>
+      <c r="D162" s="21" t="n"/>
+    </row>
+    <row r="163">
+      <c r="A163" s="15" t="n"/>
+      <c r="B163" s="15" t="n"/>
+      <c r="C163" s="22" t="n"/>
+      <c r="D163" s="21" t="n"/>
+    </row>
+    <row r="164">
+      <c r="A164" s="15" t="n"/>
+      <c r="B164" s="15" t="n"/>
+      <c r="C164" s="22" t="n"/>
+      <c r="D164" s="21" t="n"/>
+    </row>
+    <row r="165">
+      <c r="A165" s="15" t="n"/>
+      <c r="B165" s="15" t="n"/>
+      <c r="C165" s="22" t="n"/>
+      <c r="D165" s="21" t="n"/>
+    </row>
+    <row r="166">
+      <c r="A166" s="15" t="n"/>
+      <c r="B166" s="15" t="n"/>
+      <c r="C166" s="22" t="n"/>
+      <c r="D166" s="21" t="n"/>
+    </row>
+    <row r="167">
+      <c r="A167" s="15" t="n"/>
+      <c r="B167" s="15" t="n"/>
+      <c r="C167" s="22" t="n"/>
+      <c r="D167" s="21" t="n"/>
+    </row>
+    <row r="168">
+      <c r="A168" s="15" t="n"/>
+      <c r="B168" s="15" t="n"/>
+      <c r="C168" s="22" t="n"/>
+      <c r="D168" s="21" t="n"/>
+    </row>
+    <row r="169">
+      <c r="A169" s="15" t="n"/>
+      <c r="B169" s="15" t="n"/>
+      <c r="C169" s="22" t="n"/>
+      <c r="D169" s="21" t="n"/>
+    </row>
+    <row r="170">
+      <c r="A170" s="15" t="n"/>
+      <c r="B170" s="15" t="n"/>
+      <c r="C170" s="22" t="n"/>
+      <c r="D170" s="21" t="n"/>
+    </row>
+    <row r="171">
+      <c r="A171" s="15" t="n"/>
+      <c r="B171" s="15" t="n"/>
+      <c r="C171" s="22" t="n"/>
+      <c r="D171" s="21" t="n"/>
+    </row>
+    <row r="172">
+      <c r="A172" s="15" t="n"/>
+      <c r="B172" s="15" t="n"/>
+      <c r="C172" s="22" t="n"/>
+      <c r="D172" s="21" t="n"/>
+    </row>
+    <row r="173">
+      <c r="A173" s="15" t="n"/>
+      <c r="B173" s="15" t="n"/>
+      <c r="C173" s="22" t="n"/>
+      <c r="D173" s="21" t="n"/>
+    </row>
+    <row r="174">
+      <c r="A174" s="15" t="n"/>
+      <c r="B174" s="15" t="n"/>
+      <c r="C174" s="22" t="n"/>
+      <c r="D174" s="21" t="n"/>
+    </row>
+    <row r="175">
+      <c r="A175" s="15" t="n"/>
+      <c r="B175" s="15" t="n"/>
+      <c r="C175" s="22" t="n"/>
+      <c r="D175" s="21" t="n"/>
+    </row>
+    <row r="176">
+      <c r="A176" s="15" t="n"/>
+      <c r="B176" s="15" t="n"/>
+      <c r="C176" s="22" t="n"/>
+      <c r="D176" s="21" t="n"/>
+    </row>
+    <row r="177">
+      <c r="A177" s="15" t="n"/>
+      <c r="B177" s="15" t="n"/>
+      <c r="C177" s="22" t="n"/>
+      <c r="D177" s="21" t="n"/>
+    </row>
+    <row r="178">
+      <c r="A178" s="15" t="n"/>
+      <c r="B178" s="15" t="n"/>
+      <c r="C178" s="22" t="n"/>
+      <c r="D178" s="21" t="n"/>
+    </row>
+    <row r="179">
+      <c r="A179" s="15" t="n"/>
+      <c r="B179" s="15" t="n"/>
+      <c r="C179" s="22" t="n"/>
+      <c r="D179" s="21" t="n"/>
+    </row>
+    <row r="180">
+      <c r="A180" s="15" t="n"/>
+      <c r="B180" s="15" t="n"/>
+      <c r="C180" s="22" t="n"/>
+      <c r="D180" s="21" t="n"/>
+    </row>
+    <row r="181">
+      <c r="A181" s="15" t="n"/>
+      <c r="B181" s="15" t="n"/>
+      <c r="C181" s="22" t="n"/>
+      <c r="D181" s="21" t="n"/>
+    </row>
+    <row r="182">
+      <c r="A182" s="15" t="n"/>
+      <c r="B182" s="15" t="n"/>
+      <c r="C182" s="22" t="n"/>
+      <c r="D182" s="21" t="n"/>
+    </row>
+    <row r="183">
+      <c r="A183" s="15" t="n"/>
+      <c r="B183" s="15" t="n"/>
+      <c r="C183" s="22" t="n"/>
+      <c r="D183" s="21" t="n"/>
+    </row>
+    <row r="184">
+      <c r="A184" s="15" t="n"/>
+      <c r="B184" s="15" t="n"/>
+      <c r="C184" s="22" t="n"/>
+      <c r="D184" s="21" t="n"/>
+    </row>
+    <row r="185">
+      <c r="A185" s="15" t="n"/>
+      <c r="B185" s="15" t="n"/>
+      <c r="C185" s="22" t="n"/>
+      <c r="D185" s="21" t="n"/>
+    </row>
+    <row r="186">
+      <c r="A186" s="15" t="n"/>
+      <c r="B186" s="15" t="n"/>
+      <c r="C186" s="22" t="n"/>
+      <c r="D186" s="21" t="n"/>
+    </row>
+    <row r="187">
+      <c r="A187" s="15" t="n"/>
+      <c r="B187" s="15" t="n"/>
+      <c r="C187" s="22" t="n"/>
+      <c r="D187" s="21" t="n"/>
+    </row>
+    <row r="188">
+      <c r="A188" s="15" t="n"/>
+      <c r="B188" s="15" t="n"/>
+      <c r="C188" s="22" t="n"/>
+      <c r="D188" s="21" t="n"/>
+    </row>
+    <row r="189">
+      <c r="A189" s="15" t="n"/>
+      <c r="B189" s="15" t="n"/>
+      <c r="C189" s="22" t="n"/>
+      <c r="D189" s="21" t="n"/>
+    </row>
+    <row r="190">
+      <c r="A190" s="15" t="n"/>
+      <c r="B190" s="15" t="n"/>
+      <c r="C190" s="22" t="n"/>
+      <c r="D190" s="21" t="n"/>
+    </row>
+    <row r="191">
+      <c r="A191" s="15" t="n"/>
+      <c r="B191" s="15" t="n"/>
+      <c r="C191" s="22" t="n"/>
+      <c r="D191" s="21" t="n"/>
+    </row>
+    <row r="192">
+      <c r="A192" s="15" t="n"/>
+      <c r="B192" s="15" t="n"/>
+      <c r="C192" s="22" t="n"/>
+      <c r="D192" s="21" t="n"/>
+    </row>
+    <row r="193">
+      <c r="A193" s="15" t="n"/>
+      <c r="B193" s="15" t="n"/>
+      <c r="C193" s="22" t="n"/>
+      <c r="D193" s="21" t="n"/>
+    </row>
+    <row r="194">
+      <c r="A194" s="15" t="n"/>
+      <c r="B194" s="15" t="n"/>
+      <c r="C194" s="22" t="n"/>
+      <c r="D194" s="21" t="n"/>
+    </row>
+    <row r="195">
+      <c r="A195" s="15" t="n"/>
+      <c r="B195" s="15" t="n"/>
+      <c r="C195" s="22" t="n"/>
+      <c r="D195" s="21" t="n"/>
+    </row>
+    <row r="196">
+      <c r="A196" s="15" t="n"/>
+      <c r="B196" s="15" t="n"/>
+      <c r="C196" s="22" t="n"/>
+      <c r="D196" s="21" t="n"/>
+    </row>
+    <row r="197">
+      <c r="A197" s="15" t="n"/>
+      <c r="B197" s="15" t="n"/>
+      <c r="C197" s="22" t="n"/>
+      <c r="D197" s="21" t="n"/>
+    </row>
+    <row r="198">
+      <c r="A198" s="15" t="n"/>
+      <c r="B198" s="15" t="n"/>
+      <c r="C198" s="22" t="n"/>
+      <c r="D198" s="21" t="n"/>
+    </row>
+    <row r="199">
+      <c r="A199" s="15" t="n"/>
+      <c r="B199" s="15" t="n"/>
+      <c r="C199" s="22" t="n"/>
+      <c r="D199" s="21" t="n"/>
+    </row>
+    <row r="200">
+      <c r="A200" s="15" t="n"/>
+      <c r="B200" s="15" t="n"/>
+      <c r="C200" s="22" t="n"/>
+      <c r="D200" s="21" t="n"/>
+    </row>
+    <row r="201">
+      <c r="A201" s="15" t="n"/>
+      <c r="B201" s="15" t="n"/>
+      <c r="C201" s="22" t="n"/>
+      <c r="D201" s="21" t="n"/>
+    </row>
+    <row r="202">
+      <c r="A202" s="15" t="n"/>
+      <c r="B202" s="15" t="n"/>
+      <c r="C202" s="22" t="n"/>
+      <c r="D202" s="21" t="n"/>
+    </row>
+    <row r="203">
+      <c r="A203" s="15" t="n"/>
+      <c r="B203" s="15" t="n"/>
+      <c r="C203" s="22" t="n"/>
+      <c r="D203" s="21" t="n"/>
+    </row>
+    <row r="204">
+      <c r="A204" s="15" t="n"/>
+      <c r="B204" s="15" t="n"/>
+      <c r="C204" s="22" t="n"/>
+      <c r="D204" s="21" t="n"/>
+    </row>
+    <row r="205">
+      <c r="A205" s="15" t="n"/>
+      <c r="B205" s="15" t="n"/>
+      <c r="C205" s="22" t="n"/>
+      <c r="D205" s="21" t="n"/>
+    </row>
+    <row r="206">
+      <c r="A206" s="15" t="n"/>
+      <c r="B206" s="15" t="n"/>
+      <c r="C206" s="22" t="n"/>
+      <c r="D206" s="21" t="n"/>
+    </row>
+    <row r="207">
+      <c r="A207" s="15" t="n"/>
+      <c r="B207" s="15" t="n"/>
+      <c r="C207" s="22" t="n"/>
+      <c r="D207" s="21" t="n"/>
+    </row>
+    <row r="208">
+      <c r="A208" s="15" t="n"/>
+      <c r="B208" s="15" t="n"/>
+      <c r="C208" s="22" t="n"/>
+      <c r="D208" s="21" t="n"/>
+    </row>
+    <row r="209">
+      <c r="A209" s="15" t="n"/>
+      <c r="B209" s="15" t="n"/>
+      <c r="C209" s="22" t="n"/>
+      <c r="D209" s="21" t="n"/>
+    </row>
+    <row r="210">
+      <c r="A210" s="15" t="n"/>
+      <c r="B210" s="15" t="n"/>
+      <c r="C210" s="22" t="n"/>
+      <c r="D210" s="21" t="n"/>
+    </row>
+    <row r="211">
+      <c r="A211" s="15" t="n"/>
+      <c r="B211" s="15" t="n"/>
+      <c r="C211" s="22" t="n"/>
+      <c r="D211" s="21" t="n"/>
+    </row>
+    <row r="212">
+      <c r="A212" s="15" t="n"/>
+      <c r="B212" s="15" t="n"/>
+      <c r="C212" s="22" t="n"/>
+      <c r="D212" s="21" t="n"/>
+    </row>
+    <row r="213">
+      <c r="A213" s="15" t="n"/>
+      <c r="B213" s="15" t="n"/>
+      <c r="C213" s="22" t="n"/>
+      <c r="D213" s="21" t="n"/>
+    </row>
+    <row r="214">
+      <c r="A214" s="15" t="n"/>
+      <c r="B214" s="15" t="n"/>
+      <c r="C214" s="22" t="n"/>
+      <c r="D214" s="21" t="n"/>
+    </row>
+    <row r="215">
+      <c r="A215" s="15" t="n"/>
+      <c r="B215" s="15" t="n"/>
+      <c r="C215" s="22" t="n"/>
+      <c r="D215" s="21" t="n"/>
+    </row>
+    <row r="216">
+      <c r="A216" s="15" t="n"/>
+      <c r="B216" s="15" t="n"/>
+      <c r="C216" s="22" t="n"/>
+      <c r="D216" s="21" t="n"/>
+    </row>
+    <row r="217">
+      <c r="A217" s="15" t="n"/>
+      <c r="B217" s="15" t="n"/>
+      <c r="C217" s="22" t="n"/>
+      <c r="D217" s="21" t="n"/>
+    </row>
+    <row r="218">
+      <c r="A218" s="15" t="n"/>
+      <c r="B218" s="15" t="n"/>
+      <c r="C218" s="22" t="n"/>
+      <c r="D218" s="21" t="n"/>
+    </row>
+    <row r="219">
+      <c r="A219" s="15" t="n"/>
+      <c r="B219" s="15" t="n"/>
+      <c r="C219" s="22" t="n"/>
+      <c r="D219" s="21" t="n"/>
+    </row>
+    <row r="220">
+      <c r="A220" s="15" t="n"/>
+      <c r="B220" s="15" t="n"/>
+      <c r="C220" s="22" t="n"/>
+      <c r="D220" s="21" t="n"/>
+    </row>
+    <row r="221">
+      <c r="A221" s="15" t="n"/>
+      <c r="B221" s="15" t="n"/>
+      <c r="C221" s="22" t="n"/>
+      <c r="D221" s="21" t="n"/>
+    </row>
+    <row r="222">
+      <c r="A222" s="15" t="n"/>
+      <c r="B222" s="15" t="n"/>
+      <c r="C222" s="22" t="n"/>
+      <c r="D222" s="21" t="n"/>
+    </row>
+    <row r="223">
+      <c r="A223" s="15" t="n"/>
+      <c r="B223" s="15" t="n"/>
+      <c r="C223" s="22" t="n"/>
+      <c r="D223" s="21" t="n"/>
+    </row>
+    <row r="224">
+      <c r="A224" s="15" t="n"/>
+      <c r="B224" s="15" t="n"/>
+      <c r="C224" s="22" t="n"/>
+      <c r="D224" s="21" t="n"/>
+    </row>
+    <row r="225">
+      <c r="A225" s="15" t="n"/>
+      <c r="B225" s="15" t="n"/>
+      <c r="C225" s="22" t="n"/>
+      <c r="D225" s="21" t="n"/>
+    </row>
+    <row r="226">
+      <c r="A226" s="15" t="n"/>
+      <c r="B226" s="15" t="n"/>
+      <c r="C226" s="22" t="n"/>
+      <c r="D226" s="21" t="n"/>
+    </row>
+    <row r="227">
+      <c r="A227" s="15" t="n"/>
+      <c r="B227" s="15" t="n"/>
+      <c r="C227" s="22" t="n"/>
+      <c r="D227" s="21" t="n"/>
+    </row>
+    <row r="228">
+      <c r="A228" s="15" t="n"/>
+      <c r="B228" s="15" t="n"/>
+      <c r="C228" s="22" t="n"/>
+      <c r="D228" s="21" t="n"/>
+    </row>
+    <row r="229">
+      <c r="A229" s="15" t="n"/>
+      <c r="B229" s="15" t="n"/>
+      <c r="C229" s="22" t="n"/>
+      <c r="D229" s="21" t="n"/>
+    </row>
+    <row r="230">
+      <c r="A230" s="15" t="n"/>
+      <c r="B230" s="15" t="n"/>
+      <c r="C230" s="22" t="n"/>
+      <c r="D230" s="21" t="n"/>
+    </row>
+    <row r="231">
+      <c r="A231" s="15" t="n"/>
+      <c r="B231" s="15" t="n"/>
+      <c r="C231" s="22" t="n"/>
+      <c r="D231" s="21" t="n"/>
+    </row>
+    <row r="232">
+      <c r="A232" s="15" t="n"/>
+      <c r="B232" s="15" t="n"/>
+      <c r="C232" s="22" t="n"/>
+      <c r="D232" s="21" t="n"/>
+    </row>
+    <row r="233">
+      <c r="A233" s="15" t="n"/>
+      <c r="B233" s="15" t="n"/>
+      <c r="C233" s="22" t="n"/>
+      <c r="D233" s="21" t="n"/>
+    </row>
+    <row r="234">
+      <c r="A234" s="15" t="n"/>
+      <c r="B234" s="15" t="n"/>
+      <c r="C234" s="22" t="n"/>
+      <c r="D234" s="21" t="n"/>
+    </row>
+    <row r="235">
+      <c r="A235" s="15" t="n"/>
+      <c r="B235" s="15" t="n"/>
+      <c r="C235" s="22" t="n"/>
+      <c r="D235" s="21" t="n"/>
+    </row>
+    <row r="236">
+      <c r="A236" s="15" t="n"/>
+      <c r="B236" s="15" t="n"/>
+      <c r="C236" s="22" t="n"/>
+      <c r="D236" s="21" t="n"/>
+    </row>
+    <row r="237">
+      <c r="A237" s="15" t="n"/>
+      <c r="B237" s="15" t="n"/>
+      <c r="C237" s="22" t="n"/>
+      <c r="D237" s="21" t="n"/>
+    </row>
+    <row r="238">
+      <c r="A238" s="15" t="n"/>
+      <c r="B238" s="15" t="n"/>
+      <c r="C238" s="22" t="n"/>
+      <c r="D238" s="21" t="n"/>
+    </row>
+    <row r="239">
+      <c r="A239" s="15" t="n"/>
+      <c r="B239" s="15" t="n"/>
+      <c r="C239" s="22" t="n"/>
+      <c r="D239" s="21" t="n"/>
+    </row>
+    <row r="240">
+      <c r="A240" s="15" t="n"/>
+      <c r="B240" s="15" t="n"/>
+      <c r="C240" s="22" t="n"/>
+      <c r="D240" s="21" t="n"/>
+    </row>
+    <row r="241">
+      <c r="A241" s="15" t="n"/>
+      <c r="B241" s="15" t="n"/>
+      <c r="C241" s="22" t="n"/>
+      <c r="D241" s="21" t="n"/>
+    </row>
+    <row r="242">
+      <c r="A242" s="15" t="n"/>
+      <c r="B242" s="15" t="n"/>
+      <c r="C242" s="22" t="n"/>
+      <c r="D242" s="21" t="n"/>
+    </row>
+    <row r="243">
+      <c r="A243" s="15" t="n"/>
+      <c r="B243" s="15" t="n"/>
+      <c r="C243" s="22" t="n"/>
+      <c r="D243" s="21" t="n"/>
+    </row>
+    <row r="244">
+      <c r="A244" s="15" t="n"/>
+      <c r="B244" s="15" t="n"/>
+      <c r="C244" s="22" t="n"/>
+      <c r="D244" s="21" t="n"/>
+    </row>
+    <row r="245">
+      <c r="A245" s="15" t="n"/>
+      <c r="B245" s="15" t="n"/>
+      <c r="C245" s="22" t="n"/>
+      <c r="D245" s="21" t="n"/>
+    </row>
+    <row r="246">
+      <c r="A246" s="15" t="n"/>
+      <c r="B246" s="15" t="n"/>
+      <c r="C246" s="22" t="n"/>
+      <c r="D246" s="21" t="n"/>
+    </row>
+    <row r="247">
+      <c r="A247" s="15" t="n"/>
+      <c r="B247" s="15" t="n"/>
+      <c r="C247" s="22" t="n"/>
+      <c r="D247" s="21" t="n"/>
+    </row>
+    <row r="248">
+      <c r="A248" s="15" t="n"/>
+      <c r="B248" s="15" t="n"/>
+      <c r="C248" s="22" t="n"/>
+      <c r="D248" s="21" t="n"/>
+    </row>
+    <row r="249">
+      <c r="A249" s="15" t="n"/>
+      <c r="B249" s="15" t="n"/>
+      <c r="C249" s="22" t="n"/>
+      <c r="D249" s="21" t="n"/>
+    </row>
+    <row r="250">
+      <c r="A250" s="15" t="n"/>
+      <c r="B250" s="15" t="n"/>
+      <c r="C250" s="22" t="n"/>
+      <c r="D250" s="21" t="n"/>
+    </row>
+    <row r="251">
+      <c r="A251" s="15" t="n"/>
+      <c r="B251" s="15" t="n"/>
+      <c r="C251" s="22" t="n"/>
+      <c r="D251" s="21" t="n"/>
+    </row>
+    <row r="252">
+      <c r="A252" s="15" t="n"/>
+      <c r="B252" s="15" t="n"/>
+      <c r="C252" s="22" t="n"/>
+      <c r="D252" s="21" t="n"/>
+    </row>
+    <row r="253">
+      <c r="A253" s="15" t="n"/>
+      <c r="B253" s="15" t="n"/>
+      <c r="C253" s="22" t="n"/>
+      <c r="D253" s="21" t="n"/>
+    </row>
+    <row r="254">
+      <c r="A254" s="15" t="n"/>
+      <c r="B254" s="15" t="n"/>
+      <c r="C254" s="22" t="n"/>
+      <c r="D254" s="21" t="n"/>
+    </row>
+    <row r="255">
+      <c r="A255" s="15" t="n"/>
+      <c r="B255" s="15" t="n"/>
+      <c r="C255" s="22" t="n"/>
+      <c r="D255" s="21" t="n"/>
+    </row>
+    <row r="256">
+      <c r="A256" s="15" t="n"/>
+      <c r="B256" s="15" t="n"/>
+      <c r="C256" s="22" t="n"/>
+      <c r="D256" s="21" t="n"/>
+    </row>
+    <row r="257">
+      <c r="A257" s="15" t="n"/>
+      <c r="B257" s="15" t="n"/>
+      <c r="C257" s="22" t="n"/>
+      <c r="D257" s="21" t="n"/>
+    </row>
+    <row r="258">
+      <c r="A258" s="15" t="n"/>
+      <c r="B258" s="15" t="n"/>
+      <c r="C258" s="22" t="n"/>
+      <c r="D258" s="21" t="n"/>
+    </row>
+    <row r="259">
+      <c r="A259" s="15" t="n"/>
+      <c r="B259" s="15" t="n"/>
+      <c r="C259" s="22" t="n"/>
+      <c r="D259" s="21" t="n"/>
+    </row>
+    <row r="260">
+      <c r="A260" s="15" t="n"/>
+      <c r="B260" s="15" t="n"/>
+      <c r="C260" s="22" t="n"/>
+      <c r="D260" s="21" t="n"/>
+    </row>
+    <row r="261">
+      <c r="A261" s="15" t="n"/>
+      <c r="B261" s="15" t="n"/>
+      <c r="C261" s="22" t="n"/>
+      <c r="D261" s="21" t="n"/>
+    </row>
+    <row r="262">
+      <c r="A262" s="15" t="n"/>
+      <c r="B262" s="15" t="n"/>
+      <c r="C262" s="22" t="n"/>
+      <c r="D262" s="21" t="n"/>
+    </row>
+    <row r="263">
+      <c r="A263" s="15" t="n"/>
+      <c r="B263" s="15" t="n"/>
+      <c r="C263" s="22" t="n"/>
+      <c r="D263" s="21" t="n"/>
+    </row>
+    <row r="264">
+      <c r="A264" s="15" t="n"/>
+      <c r="B264" s="15" t="n"/>
+      <c r="C264" s="22" t="n"/>
+      <c r="D264" s="21" t="n"/>
+    </row>
+    <row r="265">
+      <c r="A265" s="15" t="n"/>
+      <c r="B265" s="15" t="n"/>
+      <c r="C265" s="22" t="n"/>
+      <c r="D265" s="21" t="n"/>
+    </row>
+    <row r="266">
+      <c r="A266" s="15" t="n"/>
+      <c r="B266" s="15" t="n"/>
+      <c r="C266" s="22" t="n"/>
+      <c r="D266" s="21" t="n"/>
+    </row>
+    <row r="267">
+      <c r="A267" s="15" t="n"/>
+      <c r="B267" s="15" t="n"/>
+      <c r="C267" s="22" t="n"/>
+      <c r="D267" s="21" t="n"/>
+    </row>
+    <row r="268">
+      <c r="A268" s="15" t="n"/>
+      <c r="B268" s="15" t="n"/>
+      <c r="C268" s="22" t="n"/>
+      <c r="D268" s="21" t="n"/>
+    </row>
+    <row r="269">
+      <c r="A269" s="15" t="n"/>
+      <c r="B269" s="15" t="n"/>
+      <c r="C269" s="22" t="n"/>
+      <c r="D269" s="21" t="n"/>
+    </row>
+    <row r="270">
+      <c r="A270" s="15" t="n"/>
+      <c r="B270" s="15" t="n"/>
+      <c r="C270" s="22" t="n"/>
+      <c r="D270" s="21" t="n"/>
+    </row>
+    <row r="271">
+      <c r="A271" s="15" t="n"/>
+      <c r="B271" s="15" t="n"/>
+      <c r="C271" s="22" t="n"/>
+      <c r="D271" s="21" t="n"/>
+    </row>
+    <row r="272">
+      <c r="A272" s="15" t="n"/>
+      <c r="B272" s="15" t="n"/>
+      <c r="C272" s="22" t="n"/>
+      <c r="D272" s="21" t="n"/>
+    </row>
+    <row r="273">
+      <c r="A273" s="15" t="n"/>
+      <c r="B273" s="15" t="n"/>
+      <c r="C273" s="22" t="n"/>
+      <c r="D273" s="21" t="n"/>
+    </row>
+    <row r="274">
+      <c r="A274" s="15" t="n"/>
+      <c r="B274" s="15" t="n"/>
+      <c r="C274" s="22" t="n"/>
+      <c r="D274" s="21" t="n"/>
+    </row>
+    <row r="275">
+      <c r="A275" s="15" t="n"/>
+      <c r="B275" s="15" t="n"/>
+      <c r="C275" s="22" t="n"/>
+      <c r="D275" s="21" t="n"/>
+    </row>
+    <row r="276">
+      <c r="A276" s="15" t="n"/>
+      <c r="B276" s="15" t="n"/>
+      <c r="C276" s="22" t="n"/>
+      <c r="D276" s="21" t="n"/>
+    </row>
+    <row r="277">
+      <c r="A277" s="15" t="n"/>
+      <c r="B277" s="15" t="n"/>
+      <c r="C277" s="22" t="n"/>
+      <c r="D277" s="21" t="n"/>
+    </row>
+    <row r="278">
+      <c r="A278" s="15" t="n"/>
+      <c r="B278" s="15" t="n"/>
+      <c r="C278" s="22" t="n"/>
+      <c r="D278" s="21" t="n"/>
+    </row>
+    <row r="279">
+      <c r="A279" s="15" t="n"/>
+      <c r="B279" s="15" t="n"/>
+      <c r="C279" s="22" t="n"/>
+      <c r="D279" s="21" t="n"/>
+    </row>
+    <row r="280">
+      <c r="A280" s="15" t="n"/>
+      <c r="B280" s="15" t="n"/>
+      <c r="C280" s="22" t="n"/>
+      <c r="D280" s="21" t="n"/>
+    </row>
+    <row r="281">
+      <c r="A281" s="15" t="n"/>
+      <c r="B281" s="15" t="n"/>
+      <c r="C281" s="22" t="n"/>
+      <c r="D281" s="21" t="n"/>
+    </row>
+    <row r="282">
+      <c r="A282" s="15" t="n"/>
+      <c r="B282" s="15" t="n"/>
+      <c r="C282" s="22" t="n"/>
+      <c r="D282" s="21" t="n"/>
+    </row>
+    <row r="283">
+      <c r="A283" s="15" t="n"/>
+      <c r="B283" s="15" t="n"/>
+      <c r="C283" s="22" t="n"/>
+      <c r="D283" s="21" t="n"/>
+    </row>
+    <row r="284">
+      <c r="A284" s="15" t="n"/>
+      <c r="B284" s="15" t="n"/>
+      <c r="C284" s="22" t="n"/>
+      <c r="D284" s="21" t="n"/>
+    </row>
+    <row r="285">
+      <c r="A285" s="15" t="n"/>
+      <c r="B285" s="15" t="n"/>
+      <c r="C285" s="22" t="n"/>
+      <c r="D285" s="21" t="n"/>
+    </row>
+    <row r="286">
+      <c r="A286" s="15" t="n"/>
+      <c r="B286" s="15" t="n"/>
+      <c r="C286" s="22" t="n"/>
+      <c r="D286" s="21" t="n"/>
+    </row>
+    <row r="287">
+      <c r="A287" s="15" t="n"/>
+      <c r="B287" s="15" t="n"/>
+      <c r="C287" s="22" t="n"/>
+      <c r="D287" s="21" t="n"/>
+    </row>
+    <row r="288">
+      <c r="A288" s="15" t="n"/>
+      <c r="B288" s="15" t="n"/>
+      <c r="C288" s="22" t="n"/>
+      <c r="D288" s="21" t="n"/>
+    </row>
+    <row r="289">
+      <c r="A289" s="15" t="n"/>
+      <c r="B289" s="15" t="n"/>
+      <c r="C289" s="22" t="n"/>
+      <c r="D289" s="21" t="n"/>
+    </row>
+    <row r="290">
+      <c r="A290" s="15" t="n"/>
+      <c r="B290" s="15" t="n"/>
+      <c r="C290" s="22" t="n"/>
+      <c r="D290" s="21" t="n"/>
+    </row>
+    <row r="291">
+      <c r="A291" s="15" t="n"/>
+      <c r="B291" s="15" t="n"/>
+      <c r="C291" s="22" t="n"/>
+      <c r="D291" s="21" t="n"/>
+    </row>
+    <row r="292">
+      <c r="A292" s="15" t="n"/>
+      <c r="B292" s="15" t="n"/>
+      <c r="C292" s="22" t="n"/>
+      <c r="D292" s="21" t="n"/>
+    </row>
+    <row r="293">
+      <c r="A293" s="15" t="n"/>
+      <c r="B293" s="15" t="n"/>
+      <c r="C293" s="22" t="n"/>
+      <c r="D293" s="21" t="n"/>
+    </row>
+    <row r="294">
+      <c r="A294" s="15" t="n"/>
+      <c r="B294" s="15" t="n"/>
+      <c r="C294" s="22" t="n"/>
+      <c r="D294" s="21" t="n"/>
+    </row>
+    <row r="295">
+      <c r="A295" s="15" t="n"/>
+      <c r="B295" s="15" t="n"/>
+      <c r="C295" s="22" t="n"/>
+      <c r="D295" s="21" t="n"/>
+    </row>
+    <row r="296">
+      <c r="A296" s="15" t="n"/>
+      <c r="B296" s="15" t="n"/>
+      <c r="C296" s="22" t="n"/>
+      <c r="D296" s="21" t="n"/>
+    </row>
+    <row r="297">
+      <c r="A297" s="15" t="n"/>
+      <c r="B297" s="15" t="n"/>
+      <c r="C297" s="22" t="n"/>
+      <c r="D297" s="21" t="n"/>
+    </row>
+    <row r="298">
+      <c r="A298" s="15" t="n"/>
+      <c r="B298" s="15" t="n"/>
+      <c r="C298" s="22" t="n"/>
+      <c r="D298" s="21" t="n"/>
+    </row>
+    <row r="299">
+      <c r="A299" s="15" t="n"/>
+      <c r="B299" s="15" t="n"/>
+      <c r="C299" s="22" t="n"/>
+      <c r="D299" s="21" t="n"/>
+    </row>
+    <row r="300">
+      <c r="A300" s="15" t="n"/>
+      <c r="B300" s="15" t="n"/>
+      <c r="C300" s="22" t="n"/>
+      <c r="D300" s="21" t="n"/>
+    </row>
+    <row r="301">
+      <c r="A301" s="15" t="n"/>
+      <c r="B301" s="15" t="n"/>
+      <c r="C301" s="22" t="n"/>
+      <c r="D301" s="21" t="n"/>
+    </row>
+    <row r="302">
+      <c r="A302" s="15" t="n"/>
+      <c r="B302" s="15" t="n"/>
+      <c r="C302" s="22" t="n"/>
+      <c r="D302" s="21" t="n"/>
+    </row>
+    <row r="303">
+      <c r="A303" s="15" t="n"/>
+      <c r="B303" s="15" t="n"/>
+      <c r="C303" s="22" t="n"/>
+      <c r="D303" s="21" t="n"/>
+    </row>
+    <row r="304">
+      <c r="A304" s="15" t="n"/>
+      <c r="B304" s="15" t="n"/>
+      <c r="C304" s="22" t="n"/>
+      <c r="D304" s="21" t="n"/>
+    </row>
+    <row r="305">
+      <c r="A305" s="15" t="n"/>
+      <c r="B305" s="15" t="n"/>
+      <c r="C305" s="22" t="n"/>
+      <c r="D305" s="21" t="n"/>
+    </row>
+    <row r="306">
+      <c r="A306" s="15" t="n"/>
+      <c r="B306" s="15" t="n"/>
+      <c r="C306" s="22" t="n"/>
+      <c r="D306" s="21" t="n"/>
+    </row>
+    <row r="307">
+      <c r="A307" s="15" t="n"/>
+      <c r="B307" s="15" t="n"/>
+      <c r="C307" s="22" t="n"/>
+      <c r="D307" s="21" t="n"/>
+    </row>
+    <row r="308">
+      <c r="A308" s="15" t="n"/>
+      <c r="B308" s="15" t="n"/>
+      <c r="C308" s="22" t="n"/>
+      <c r="D308" s="21" t="n"/>
+    </row>
+    <row r="309">
+      <c r="A309" s="15" t="n"/>
+      <c r="B309" s="15" t="n"/>
+      <c r="C309" s="22" t="n"/>
+      <c r="D309" s="21" t="n"/>
+    </row>
+    <row r="310">
+      <c r="A310" s="15" t="n"/>
+      <c r="B310" s="15" t="n"/>
+      <c r="C310" s="22" t="n"/>
+      <c r="D310" s="21" t="n"/>
+    </row>
+    <row r="311">
+      <c r="A311" s="15" t="n"/>
+      <c r="B311" s="15" t="n"/>
+      <c r="C311" s="22" t="n"/>
+      <c r="D311" s="21" t="n"/>
+    </row>
+    <row r="312">
+      <c r="A312" s="15" t="n"/>
+      <c r="B312" s="15" t="n"/>
+      <c r="C312" s="22" t="n"/>
+      <c r="D312" s="21" t="n"/>
+    </row>
+    <row r="313">
+      <c r="A313" s="15" t="n"/>
+      <c r="B313" s="15" t="n"/>
+      <c r="C313" s="22" t="n"/>
+      <c r="D313" s="21" t="n"/>
+    </row>
+    <row r="314">
+      <c r="A314" s="15" t="n"/>
+      <c r="B314" s="15" t="n"/>
+      <c r="C314" s="22" t="n"/>
+      <c r="D314" s="21" t="n"/>
+    </row>
+    <row r="315">
+      <c r="A315" s="15" t="n"/>
+      <c r="B315" s="15" t="n"/>
+      <c r="C315" s="22" t="n"/>
+      <c r="D315" s="21" t="n"/>
+    </row>
+    <row r="316">
+      <c r="A316" s="15" t="n"/>
+      <c r="B316" s="15" t="n"/>
+      <c r="C316" s="22" t="n"/>
+      <c r="D316" s="21" t="n"/>
+    </row>
+    <row r="317">
+      <c r="A317" s="15" t="n"/>
+      <c r="B317" s="15" t="n"/>
+      <c r="C317" s="22" t="n"/>
+      <c r="D317" s="21" t="n"/>
+    </row>
+    <row r="318">
+      <c r="A318" s="15" t="n"/>
+      <c r="B318" s="15" t="n"/>
+      <c r="C318" s="22" t="n"/>
+      <c r="D318" s="21" t="n"/>
+    </row>
+    <row r="319">
+      <c r="A319" s="15" t="n"/>
+      <c r="B319" s="15" t="n"/>
+      <c r="C319" s="22" t="n"/>
+      <c r="D319" s="21" t="n"/>
+    </row>
+    <row r="320">
+      <c r="A320" s="15" t="n"/>
+      <c r="B320" s="15" t="n"/>
+      <c r="C320" s="22" t="n"/>
+      <c r="D320" s="21" t="n"/>
+    </row>
+    <row r="321">
+      <c r="A321" s="15" t="n"/>
+      <c r="B321" s="15" t="n"/>
+      <c r="C321" s="22" t="n"/>
+      <c r="D321" s="21" t="n"/>
+    </row>
+    <row r="322">
+      <c r="A322" s="15" t="n"/>
+      <c r="B322" s="15" t="n"/>
+      <c r="C322" s="22" t="n"/>
+      <c r="D322" s="21" t="n"/>
+    </row>
+    <row r="323">
+      <c r="A323" s="15" t="n"/>
+      <c r="B323" s="15" t="n"/>
+      <c r="C323" s="22" t="n"/>
+      <c r="D323" s="21" t="n"/>
+    </row>
+    <row r="324">
+      <c r="A324" s="15" t="n"/>
+      <c r="B324" s="15" t="n"/>
+      <c r="C324" s="22" t="n"/>
+      <c r="D324" s="21" t="n"/>
+    </row>
+    <row r="325">
+      <c r="A325" s="15" t="n"/>
+      <c r="B325" s="15" t="n"/>
+      <c r="C325" s="22" t="n"/>
+      <c r="D325" s="21" t="n"/>
+    </row>
+    <row r="326">
+      <c r="A326" s="15" t="n"/>
+      <c r="B326" s="15" t="n"/>
+      <c r="C326" s="22" t="n"/>
+      <c r="D326" s="21" t="n"/>
+    </row>
+    <row r="327">
+      <c r="A327" s="15" t="n"/>
+      <c r="B327" s="15" t="n"/>
+      <c r="C327" s="22" t="n"/>
+      <c r="D327" s="21" t="n"/>
+    </row>
+    <row r="328">
+      <c r="A328" s="15" t="n"/>
+      <c r="B328" s="15" t="n"/>
+      <c r="C328" s="22" t="n"/>
+      <c r="D328" s="21" t="n"/>
+    </row>
+    <row r="329">
+      <c r="A329" s="15" t="n"/>
+      <c r="B329" s="15" t="n"/>
+      <c r="C329" s="22" t="n"/>
+      <c r="D329" s="21" t="n"/>
+    </row>
+    <row r="330">
+      <c r="A330" s="15" t="n"/>
+      <c r="B330" s="15" t="n"/>
+      <c r="C330" s="22" t="n"/>
+      <c r="D330" s="21" t="n"/>
+    </row>
+    <row r="331">
+      <c r="A331" s="15" t="n"/>
+      <c r="B331" s="15" t="n"/>
+      <c r="C331" s="22" t="n"/>
+      <c r="D331" s="21" t="n"/>
+    </row>
+    <row r="332">
+      <c r="A332" s="15" t="n"/>
+      <c r="B332" s="15" t="n"/>
+      <c r="C332" s="22" t="n"/>
+      <c r="D332" s="21" t="n"/>
+    </row>
+    <row r="333">
+      <c r="A333" s="15" t="n"/>
+      <c r="B333" s="15" t="n"/>
+      <c r="C333" s="22" t="n"/>
+      <c r="D333" s="21" t="n"/>
+    </row>
+    <row r="334">
+      <c r="A334" s="15" t="n"/>
+      <c r="B334" s="15" t="n"/>
+      <c r="C334" s="22" t="n"/>
+      <c r="D334" s="21" t="n"/>
+    </row>
+    <row r="335">
+      <c r="A335" s="15" t="n"/>
+      <c r="B335" s="15" t="n"/>
+      <c r="C335" s="22" t="n"/>
+      <c r="D335" s="21" t="n"/>
+    </row>
+    <row r="336">
+      <c r="A336" s="15" t="n"/>
+      <c r="B336" s="15" t="n"/>
+      <c r="C336" s="22" t="n"/>
+      <c r="D336" s="21" t="n"/>
+    </row>
+    <row r="337">
+      <c r="A337" s="15" t="n"/>
+      <c r="B337" s="15" t="n"/>
+      <c r="C337" s="22" t="n"/>
+      <c r="D337" s="21" t="n"/>
+    </row>
+    <row r="338">
+      <c r="A338" s="15" t="n"/>
+      <c r="B338" s="15" t="n"/>
+      <c r="C338" s="22" t="n"/>
+      <c r="D338" s="21" t="n"/>
+    </row>
+    <row r="339">
+      <c r="A339" s="15" t="n"/>
+      <c r="B339" s="15" t="n"/>
+      <c r="C339" s="22" t="n"/>
+      <c r="D339" s="21" t="n"/>
+    </row>
+    <row r="340">
+      <c r="A340" s="15" t="n"/>
+      <c r="B340" s="15" t="n"/>
+      <c r="C340" s="22" t="n"/>
+      <c r="D340" s="21" t="n"/>
+    </row>
+    <row r="341">
+      <c r="A341" s="15" t="n"/>
+      <c r="B341" s="15" t="n"/>
+      <c r="C341" s="22" t="n"/>
+      <c r="D341" s="21" t="n"/>
+    </row>
+    <row r="342">
+      <c r="A342" s="15" t="n"/>
+      <c r="B342" s="15" t="n"/>
+      <c r="C342" s="22" t="n"/>
+      <c r="D342" s="21" t="n"/>
+    </row>
+    <row r="343">
+      <c r="A343" s="15" t="n"/>
+      <c r="B343" s="15" t="n"/>
+      <c r="C343" s="22" t="n"/>
+      <c r="D343" s="21" t="n"/>
+    </row>
+    <row r="344">
+      <c r="A344" s="15" t="n"/>
+      <c r="B344" s="15" t="n"/>
+      <c r="C344" s="22" t="n"/>
+      <c r="D344" s="21" t="n"/>
+    </row>
+    <row r="345">
+      <c r="A345" s="15" t="n"/>
+      <c r="B345" s="15" t="n"/>
+      <c r="C345" s="22" t="n"/>
+      <c r="D345" s="21" t="n"/>
+    </row>
+    <row r="346">
+      <c r="A346" s="15" t="n"/>
+      <c r="B346" s="15" t="n"/>
+      <c r="C346" s="22" t="n"/>
+      <c r="D346" s="21" t="n"/>
+    </row>
+    <row r="347">
+      <c r="A347" s="15" t="n"/>
+      <c r="B347" s="15" t="n"/>
+      <c r="C347" s="22" t="n"/>
+      <c r="D347" s="21" t="n"/>
+    </row>
+    <row r="348">
+      <c r="A348" s="15" t="n"/>
+      <c r="B348" s="15" t="n"/>
+      <c r="C348" s="22" t="n"/>
+      <c r="D348" s="21" t="n"/>
+    </row>
+    <row r="349">
+      <c r="A349" s="15" t="n"/>
+      <c r="B349" s="15" t="n"/>
+      <c r="C349" s="22" t="n"/>
+      <c r="D349" s="21" t="n"/>
+    </row>
+    <row r="350">
+      <c r="A350" s="15" t="n"/>
+      <c r="B350" s="15" t="n"/>
+      <c r="C350" s="22" t="n"/>
+      <c r="D350" s="21" t="n"/>
+    </row>
+    <row r="351">
+      <c r="A351" s="15" t="n"/>
+      <c r="B351" s="15" t="n"/>
+      <c r="C351" s="22" t="n"/>
+      <c r="D351" s="21" t="n"/>
+    </row>
+    <row r="352">
+      <c r="A352" s="15" t="n"/>
+      <c r="B352" s="15" t="n"/>
+      <c r="C352" s="22" t="n"/>
+      <c r="D352" s="21" t="n"/>
+    </row>
+    <row r="353">
+      <c r="A353" s="15" t="n"/>
+      <c r="B353" s="15" t="n"/>
+      <c r="C353" s="22" t="n"/>
+      <c r="D353" s="21" t="n"/>
+    </row>
+    <row r="354">
+      <c r="A354" s="15" t="n"/>
+      <c r="B354" s="15" t="n"/>
+      <c r="C354" s="22" t="n"/>
+      <c r="D354" s="21" t="n"/>
+    </row>
+    <row r="355">
+      <c r="A355" s="15" t="n"/>
+      <c r="B355" s="15" t="n"/>
+      <c r="C355" s="22" t="n"/>
+      <c r="D355" s="21" t="n"/>
+    </row>
+    <row r="356">
+      <c r="A356" s="15" t="n"/>
+      <c r="B356" s="15" t="n"/>
+      <c r="C356" s="22" t="n"/>
+      <c r="D356" s="21" t="n"/>
+    </row>
+    <row r="357">
+      <c r="A357" s="15" t="n"/>
+      <c r="B357" s="15" t="n"/>
+      <c r="C357" s="22" t="n"/>
+      <c r="D357" s="21" t="n"/>
+    </row>
+    <row r="358">
+      <c r="A358" s="15" t="n"/>
+      <c r="B358" s="15" t="n"/>
+      <c r="C358" s="22" t="n"/>
+      <c r="D358" s="21" t="n"/>
+    </row>
+    <row r="359">
+      <c r="A359" s="15" t="n"/>
+      <c r="B359" s="15" t="n"/>
+      <c r="C359" s="22" t="n"/>
+      <c r="D359" s="21" t="n"/>
+    </row>
+    <row r="360">
+      <c r="A360" s="15" t="n"/>
+      <c r="B360" s="15" t="n"/>
+      <c r="C360" s="22" t="n"/>
+      <c r="D360" s="21" t="n"/>
+    </row>
+    <row r="361">
+      <c r="A361" s="15" t="n"/>
+      <c r="B361" s="15" t="n"/>
+      <c r="C361" s="22" t="n"/>
+      <c r="D361" s="21" t="n"/>
+    </row>
+    <row r="362">
+      <c r="A362" s="15" t="n"/>
+      <c r="B362" s="15" t="n"/>
+      <c r="C362" s="22" t="n"/>
+      <c r="D362" s="21" t="n"/>
+    </row>
+    <row r="363">
+      <c r="A363" s="15" t="n"/>
+      <c r="B363" s="15" t="n"/>
+      <c r="C363" s="22" t="n"/>
+      <c r="D363" s="21" t="n"/>
+    </row>
+    <row r="364">
+      <c r="A364" s="15" t="n"/>
+      <c r="B364" s="15" t="n"/>
+      <c r="C364" s="22" t="n"/>
+      <c r="D364" s="21" t="n"/>
+    </row>
+    <row r="365">
+      <c r="A365" s="15" t="n"/>
+      <c r="B365" s="15" t="n"/>
+      <c r="C365" s="22" t="n"/>
+      <c r="D365" s="21" t="n"/>
+    </row>
+    <row r="366">
+      <c r="A366" s="15" t="n"/>
+      <c r="B366" s="15" t="n"/>
+      <c r="C366" s="22" t="n"/>
+      <c r="D366" s="21" t="n"/>
+    </row>
+    <row r="367">
+      <c r="A367" s="15" t="n"/>
+      <c r="B367" s="15" t="n"/>
+      <c r="C367" s="22" t="n"/>
+      <c r="D367" s="21" t="n"/>
+    </row>
+    <row r="368">
+      <c r="A368" s="15" t="n"/>
+      <c r="B368" s="15" t="n"/>
+      <c r="C368" s="22" t="n"/>
+      <c r="D368" s="21" t="n"/>
+    </row>
+    <row r="369">
+      <c r="A369" s="15" t="n"/>
+      <c r="B369" s="15" t="n"/>
+      <c r="C369" s="22" t="n"/>
+      <c r="D369" s="21" t="n"/>
+    </row>
+    <row r="370">
+      <c r="A370" s="15" t="n"/>
+      <c r="B370" s="15" t="n"/>
+      <c r="C370" s="22" t="n"/>
+      <c r="D370" s="21" t="n"/>
+    </row>
+    <row r="371">
+      <c r="A371" s="15" t="n"/>
+      <c r="B371" s="15" t="n"/>
+      <c r="C371" s="22" t="n"/>
+      <c r="D371" s="21" t="n"/>
+    </row>
+    <row r="372">
+      <c r="A372" s="15" t="n"/>
+      <c r="B372" s="15" t="n"/>
+      <c r="C372" s="22" t="n"/>
+      <c r="D372" s="21" t="n"/>
+    </row>
+    <row r="373">
+      <c r="A373" s="15" t="n"/>
+      <c r="B373" s="15" t="n"/>
+      <c r="C373" s="22" t="n"/>
+      <c r="D373" s="21" t="n"/>
+    </row>
+    <row r="374">
+      <c r="A374" s="15" t="n"/>
+      <c r="B374" s="15" t="n"/>
+      <c r="C374" s="22" t="n"/>
+      <c r="D374" s="21" t="n"/>
+    </row>
+    <row r="375">
+      <c r="A375" s="15" t="n"/>
+      <c r="B375" s="15" t="n"/>
+      <c r="C375" s="22" t="n"/>
+      <c r="D375" s="21" t="n"/>
+    </row>
+    <row r="376">
+      <c r="A376" s="15" t="n"/>
+      <c r="B376" s="15" t="n"/>
+      <c r="C376" s="22" t="n"/>
+      <c r="D376" s="21" t="n"/>
+    </row>
+    <row r="377">
+      <c r="A377" s="15" t="n"/>
+      <c r="B377" s="15" t="n"/>
+      <c r="C377" s="22" t="n"/>
+      <c r="D377" s="21" t="n"/>
+    </row>
+    <row r="378">
+      <c r="A378" s="15" t="n"/>
+      <c r="B378" s="15" t="n"/>
+      <c r="C378" s="22" t="n"/>
+      <c r="D378" s="21" t="n"/>
+    </row>
+    <row r="379">
+      <c r="A379" s="15" t="n"/>
+      <c r="B379" s="15" t="n"/>
+      <c r="C379" s="22" t="n"/>
+      <c r="D379" s="21" t="n"/>
+    </row>
+    <row r="380">
+      <c r="A380" s="15" t="n"/>
+      <c r="B380" s="15" t="n"/>
+      <c r="C380" s="22" t="n"/>
+      <c r="D380" s="21" t="n"/>
+    </row>
+    <row r="381">
+      <c r="A381" s="15" t="n"/>
+      <c r="B381" s="15" t="n"/>
+      <c r="C381" s="22" t="n"/>
+      <c r="D381" s="21" t="n"/>
+    </row>
+    <row r="382">
+      <c r="A382" s="15" t="n"/>
+      <c r="B382" s="15" t="n"/>
+      <c r="C382" s="22" t="n"/>
+      <c r="D382" s="21" t="n"/>
+    </row>
+    <row r="383">
+      <c r="A383" s="15" t="n"/>
+      <c r="B383" s="15" t="n"/>
+      <c r="C383" s="22" t="n"/>
+      <c r="D383" s="21" t="n"/>
+    </row>
+    <row r="384">
+      <c r="A384" s="15" t="n"/>
+      <c r="B384" s="15" t="n"/>
+      <c r="C384" s="22" t="n"/>
+      <c r="D384" s="21" t="n"/>
+    </row>
+    <row r="385">
+      <c r="A385" s="15" t="n"/>
+      <c r="B385" s="15" t="n"/>
+      <c r="C385" s="22" t="n"/>
+      <c r="D385" s="21" t="n"/>
+    </row>
+    <row r="386">
+      <c r="A386" s="15" t="n"/>
+      <c r="B386" s="15" t="n"/>
+      <c r="C386" s="22" t="n"/>
+      <c r="D386" s="21" t="n"/>
+    </row>
+    <row r="387">
+      <c r="A387" s="15" t="n"/>
+      <c r="B387" s="15" t="n"/>
+      <c r="C387" s="22" t="n"/>
+      <c r="D387" s="21" t="n"/>
+    </row>
+    <row r="388">
+      <c r="A388" s="15" t="n"/>
+      <c r="B388" s="15" t="n"/>
+      <c r="C388" s="22" t="n"/>
+      <c r="D388" s="21" t="n"/>
+    </row>
+    <row r="389">
+      <c r="A389" s="15" t="n"/>
+      <c r="B389" s="15" t="n"/>
+      <c r="C389" s="22" t="n"/>
+      <c r="D389" s="21" t="n"/>
+    </row>
+    <row r="390">
+      <c r="A390" s="15" t="n"/>
+      <c r="B390" s="15" t="n"/>
+      <c r="C390" s="22" t="n"/>
+      <c r="D390" s="21" t="n"/>
+    </row>
+    <row r="391">
+      <c r="A391" s="15" t="n"/>
+      <c r="B391" s="15" t="n"/>
+      <c r="C391" s="22" t="n"/>
+      <c r="D391" s="21" t="n"/>
+    </row>
+    <row r="392">
+      <c r="A392" s="15" t="n"/>
+      <c r="B392" s="15" t="n"/>
+      <c r="C392" s="22" t="n"/>
+      <c r="D392" s="21" t="n"/>
+    </row>
+    <row r="393">
+      <c r="A393" s="15" t="n"/>
+      <c r="B393" s="15" t="n"/>
+      <c r="C393" s="22" t="n"/>
+      <c r="D393" s="21" t="n"/>
+    </row>
+    <row r="394">
+      <c r="A394" s="15" t="n"/>
+      <c r="B394" s="15" t="n"/>
+      <c r="C394" s="22" t="n"/>
+      <c r="D394" s="21" t="n"/>
+    </row>
+    <row r="395">
+      <c r="A395" s="15" t="n"/>
+      <c r="B395" s="15" t="n"/>
+      <c r="C395" s="22" t="n"/>
+      <c r="D395" s="21" t="n"/>
+    </row>
+    <row r="396">
+      <c r="A396" s="15" t="n"/>
+      <c r="B396" s="15" t="n"/>
+      <c r="C396" s="22" t="n"/>
+      <c r="D396" s="21" t="n"/>
+    </row>
+    <row r="397">
+      <c r="A397" s="15" t="n"/>
+      <c r="B397" s="15" t="n"/>
+      <c r="C397" s="22" t="n"/>
+      <c r="D397" s="21" t="n"/>
+    </row>
+    <row r="398">
+      <c r="A398" s="15" t="n"/>
+      <c r="B398" s="15" t="n"/>
+      <c r="C398" s="22" t="n"/>
+      <c r="D398" s="21" t="n"/>
+    </row>
+    <row r="399">
+      <c r="A399" s="15" t="n"/>
+      <c r="B399" s="15" t="n"/>
+      <c r="C399" s="22" t="n"/>
+      <c r="D399" s="21" t="n"/>
+    </row>
+    <row r="400">
+      <c r="A400" s="15" t="n"/>
+      <c r="B400" s="15" t="n"/>
+      <c r="C400" s="22" t="n"/>
+      <c r="D400" s="21" t="n"/>
+    </row>
+    <row r="401">
+      <c r="A401" s="15" t="n"/>
+      <c r="B401" s="15" t="n"/>
+      <c r="C401" s="22" t="n"/>
+      <c r="D401" s="21" t="n"/>
+    </row>
+    <row r="402">
+      <c r="A402" s="15" t="n"/>
+      <c r="B402" s="15" t="n"/>
+      <c r="C402" s="22" t="n"/>
+      <c r="D402" s="21" t="n"/>
+    </row>
+    <row r="403">
+      <c r="A403" s="15" t="n"/>
+      <c r="B403" s="15" t="n"/>
+      <c r="C403" s="22" t="n"/>
+      <c r="D403" s="21" t="n"/>
+    </row>
+    <row r="404">
+      <c r="A404" s="15" t="n"/>
+      <c r="B404" s="15" t="n"/>
+      <c r="C404" s="22" t="n"/>
+      <c r="D404" s="21" t="n"/>
+    </row>
+    <row r="405">
+      <c r="A405" s="15" t="n"/>
+      <c r="B405" s="15" t="n"/>
+      <c r="C405" s="22" t="n"/>
+      <c r="D405" s="21" t="n"/>
+    </row>
+    <row r="406">
+      <c r="A406" s="15" t="n"/>
+      <c r="B406" s="15" t="n"/>
+      <c r="C406" s="22" t="n"/>
+      <c r="D406" s="21" t="n"/>
+    </row>
+    <row r="407">
+      <c r="A407" s="15" t="n"/>
+      <c r="B407" s="15" t="n"/>
+      <c r="C407" s="22" t="n"/>
+      <c r="D407" s="21" t="n"/>
+    </row>
+    <row r="408">
+      <c r="A408" s="15" t="n"/>
+      <c r="B408" s="15" t="n"/>
+      <c r="C408" s="22" t="n"/>
+      <c r="D408" s="21" t="n"/>
+    </row>
+    <row r="409">
+      <c r="A409" s="15" t="n"/>
+      <c r="B409" s="15" t="n"/>
+      <c r="C409" s="22" t="n"/>
+      <c r="D409" s="21" t="n"/>
+    </row>
+    <row r="410">
+      <c r="A410" s="15" t="n"/>
+      <c r="B410" s="15" t="n"/>
+      <c r="C410" s="22" t="n"/>
+      <c r="D410" s="21" t="n"/>
+    </row>
+    <row r="411">
+      <c r="A411" s="15" t="n"/>
+      <c r="B411" s="15" t="n"/>
+      <c r="C411" s="22" t="n"/>
+      <c r="D411" s="21" t="n"/>
+    </row>
+    <row r="412">
+      <c r="A412" s="15" t="n"/>
+      <c r="B412" s="15" t="n"/>
+      <c r="C412" s="22" t="n"/>
+      <c r="D412" s="21" t="n"/>
+    </row>
+    <row r="413">
+      <c r="A413" s="15" t="n"/>
+      <c r="B413" s="15" t="n"/>
+      <c r="C413" s="22" t="n"/>
+      <c r="D413" s="21" t="n"/>
+    </row>
+    <row r="414">
+      <c r="A414" s="15" t="n"/>
+      <c r="B414" s="15" t="n"/>
+      <c r="C414" s="22" t="n"/>
+      <c r="D414" s="21" t="n"/>
+    </row>
+    <row r="415">
+      <c r="A415" s="15" t="n"/>
+      <c r="B415" s="15" t="n"/>
+      <c r="C415" s="22" t="n"/>
+      <c r="D415" s="21" t="n"/>
+    </row>
+    <row r="416">
+      <c r="A416" s="15" t="n"/>
+      <c r="B416" s="15" t="n"/>
+      <c r="C416" s="22" t="n"/>
+      <c r="D416" s="21" t="n"/>
+    </row>
+    <row r="417">
+      <c r="A417" s="15" t="n"/>
+      <c r="B417" s="15" t="n"/>
+      <c r="C417" s="22" t="n"/>
+      <c r="D417" s="21" t="n"/>
+    </row>
+    <row r="418">
+      <c r="A418" s="15" t="n"/>
+      <c r="B418" s="15" t="n"/>
+      <c r="C418" s="22" t="n"/>
+      <c r="D418" s="21" t="n"/>
+    </row>
+    <row r="419">
+      <c r="A419" s="15" t="n"/>
+      <c r="B419" s="15" t="n"/>
+      <c r="C419" s="22" t="n"/>
+      <c r="D419" s="21" t="n"/>
+    </row>
+    <row r="420">
+      <c r="A420" s="15" t="n"/>
+      <c r="B420" s="15" t="n"/>
+      <c r="C420" s="22" t="n"/>
+      <c r="D420" s="21" t="n"/>
+    </row>
+    <row r="421">
+      <c r="A421" s="15" t="n"/>
+      <c r="B421" s="15" t="n"/>
+      <c r="C421" s="22" t="n"/>
+      <c r="D421" s="21" t="n"/>
+    </row>
+    <row r="422">
+      <c r="A422" s="15" t="n"/>
+      <c r="B422" s="15" t="n"/>
+      <c r="C422" s="22" t="n"/>
+      <c r="D422" s="21" t="n"/>
+    </row>
+    <row r="423">
+      <c r="A423" s="15" t="n"/>
+      <c r="B423" s="15" t="n"/>
+      <c r="C423" s="22" t="n"/>
+      <c r="D423" s="21" t="n"/>
+    </row>
+    <row r="424">
+      <c r="A424" s="15" t="n"/>
+      <c r="B424" s="15" t="n"/>
+      <c r="C424" s="22" t="n"/>
+      <c r="D424" s="21" t="n"/>
+    </row>
+    <row r="425">
+      <c r="A425" s="15" t="n"/>
+      <c r="B425" s="15" t="n"/>
+      <c r="C425" s="22" t="n"/>
+      <c r="D425" s="21" t="n"/>
+    </row>
+    <row r="426">
+      <c r="A426" s="15" t="n"/>
+      <c r="B426" s="15" t="n"/>
+      <c r="C426" s="22" t="n"/>
+      <c r="D426" s="21" t="n"/>
+    </row>
+    <row r="427">
+      <c r="A427" s="15" t="n"/>
+      <c r="B427" s="15" t="n"/>
+      <c r="C427" s="22" t="n"/>
+      <c r="D427" s="21" t="n"/>
+    </row>
+    <row r="428">
+      <c r="A428" s="15" t="n"/>
+      <c r="B428" s="15" t="n"/>
+      <c r="C428" s="22" t="n"/>
+      <c r="D428" s="21" t="n"/>
+    </row>
+    <row r="429">
+      <c r="A429" s="15" t="n"/>
+      <c r="B429" s="15" t="n"/>
+      <c r="C429" s="22" t="n"/>
+      <c r="D429" s="21" t="n"/>
+    </row>
+    <row r="430">
+      <c r="A430" s="15" t="n"/>
+      <c r="B430" s="15" t="n"/>
+      <c r="C430" s="22" t="n"/>
+      <c r="D430" s="21" t="n"/>
+    </row>
+    <row r="431">
+      <c r="A431" s="15" t="n"/>
+      <c r="B431" s="15" t="n"/>
+      <c r="C431" s="22" t="n"/>
+      <c r="D431" s="21" t="n"/>
+    </row>
+    <row r="432">
+      <c r="A432" s="15" t="n"/>
+      <c r="B432" s="15" t="n"/>
+      <c r="C432" s="22" t="n"/>
+      <c r="D432" s="21" t="n"/>
+    </row>
+    <row r="433">
+      <c r="A433" s="15" t="n"/>
+      <c r="B433" s="15" t="n"/>
+      <c r="C433" s="22" t="n"/>
+      <c r="D433" s="21" t="n"/>
+    </row>
+    <row r="434">
+      <c r="A434" s="15" t="n"/>
+      <c r="B434" s="15" t="n"/>
+      <c r="C434" s="22" t="n"/>
+      <c r="D434" s="21" t="n"/>
+    </row>
+    <row r="435">
+      <c r="A435" s="15" t="n"/>
+      <c r="B435" s="15" t="n"/>
+      <c r="C435" s="22" t="n"/>
+      <c r="D435" s="21" t="n"/>
+    </row>
+    <row r="436">
+      <c r="A436" s="15" t="n"/>
+      <c r="B436" s="15" t="n"/>
+      <c r="C436" s="22" t="n"/>
+      <c r="D436" s="21" t="n"/>
+    </row>
+    <row r="437">
+      <c r="A437" s="15" t="n"/>
+      <c r="B437" s="15" t="n"/>
+      <c r="C437" s="22" t="n"/>
+      <c r="D437" s="21" t="n"/>
+    </row>
+    <row r="438">
+      <c r="A438" s="15" t="n"/>
+      <c r="B438" s="15" t="n"/>
+      <c r="C438" s="22" t="n"/>
+      <c r="D438" s="21" t="n"/>
+    </row>
+    <row r="439">
+      <c r="A439" s="15" t="n"/>
+      <c r="B439" s="15" t="n"/>
+      <c r="C439" s="22" t="n"/>
+      <c r="D439" s="21" t="n"/>
+    </row>
+    <row r="440">
+      <c r="A440" s="15" t="n"/>
+      <c r="B440" s="15" t="n"/>
+      <c r="C440" s="22" t="n"/>
+      <c r="D440" s="21" t="n"/>
+    </row>
+    <row r="441">
+      <c r="A441" s="15" t="n"/>
+      <c r="B441" s="15" t="n"/>
+      <c r="C441" s="22" t="n"/>
+      <c r="D441" s="21" t="n"/>
+    </row>
+    <row r="442">
+      <c r="A442" s="15" t="n"/>
+      <c r="B442" s="15" t="n"/>
+      <c r="C442" s="22" t="n"/>
+      <c r="D442" s="21" t="n"/>
+    </row>
+    <row r="443">
+      <c r="A443" s="15" t="n"/>
+      <c r="B443" s="15" t="n"/>
+      <c r="C443" s="22" t="n"/>
+      <c r="D443" s="21" t="n"/>
+    </row>
+    <row r="444">
+      <c r="A444" s="15" t="n"/>
+      <c r="B444" s="15" t="n"/>
+      <c r="C444" s="22" t="n"/>
+      <c r="D444" s="21" t="n"/>
+    </row>
+    <row r="445">
+      <c r="A445" s="15" t="n"/>
+      <c r="B445" s="15" t="n"/>
+      <c r="C445" s="22" t="n"/>
+      <c r="D445" s="21" t="n"/>
+    </row>
+    <row r="446">
+      <c r="A446" s="15" t="n"/>
+      <c r="B446" s="15" t="n"/>
+      <c r="C446" s="22" t="n"/>
+      <c r="D446" s="21" t="n"/>
+    </row>
+    <row r="447">
+      <c r="A447" s="15" t="n"/>
+      <c r="B447" s="15" t="n"/>
+      <c r="C447" s="22" t="n"/>
+      <c r="D447" s="21" t="n"/>
+    </row>
+    <row r="448">
+      <c r="A448" s="15" t="n"/>
+      <c r="B448" s="15" t="n"/>
+      <c r="C448" s="22" t="n"/>
+      <c r="D448" s="21" t="n"/>
+    </row>
+    <row r="449">
+      <c r="A449" s="15" t="n"/>
+      <c r="B449" s="15" t="n"/>
+      <c r="C449" s="22" t="n"/>
+      <c r="D449" s="21" t="n"/>
+    </row>
+    <row r="450">
+      <c r="A450" s="15" t="n"/>
+      <c r="B450" s="15" t="n"/>
+      <c r="C450" s="22" t="n"/>
+      <c r="D450" s="21" t="n"/>
+    </row>
+    <row r="451">
+      <c r="A451" s="15" t="n"/>
+      <c r="B451" s="15" t="n"/>
+      <c r="C451" s="22" t="n"/>
+      <c r="D451" s="21" t="n"/>
+    </row>
+    <row r="452">
+      <c r="A452" s="15" t="n"/>
+      <c r="B452" s="15" t="n"/>
+      <c r="C452" s="22" t="n"/>
+      <c r="D452" s="21" t="n"/>
+    </row>
+    <row r="453">
+      <c r="A453" s="15" t="n"/>
+      <c r="B453" s="15" t="n"/>
+      <c r="C453" s="22" t="n"/>
+      <c r="D453" s="21" t="n"/>
+    </row>
+    <row r="454">
+      <c r="A454" s="15" t="n"/>
+      <c r="B454" s="15" t="n"/>
+      <c r="C454" s="22" t="n"/>
+      <c r="D454" s="21" t="n"/>
+    </row>
+    <row r="455">
+      <c r="A455" s="15" t="n"/>
+      <c r="B455" s="15" t="n"/>
+      <c r="C455" s="22" t="n"/>
+      <c r="D455" s="21" t="n"/>
+    </row>
+    <row r="456">
+      <c r="A456" s="15" t="n"/>
+      <c r="B456" s="15" t="n"/>
+      <c r="C456" s="22" t="n"/>
+      <c r="D456" s="21" t="n"/>
+    </row>
+    <row r="457">
+      <c r="A457" s="15" t="n"/>
+      <c r="B457" s="15" t="n"/>
+      <c r="C457" s="22" t="n"/>
+      <c r="D457" s="21" t="n"/>
+    </row>
+    <row r="458">
+      <c r="A458" s="15" t="n"/>
+      <c r="B458" s="15" t="n"/>
+      <c r="C458" s="22" t="n"/>
+      <c r="D458" s="21" t="n"/>
+    </row>
+    <row r="459">
+      <c r="A459" s="15" t="n"/>
+      <c r="B459" s="15" t="n"/>
+      <c r="C459" s="22" t="n"/>
+      <c r="D459" s="21" t="n"/>
+    </row>
+    <row r="460">
+      <c r="A460" s="15" t="n"/>
+      <c r="B460" s="15" t="n"/>
+      <c r="C460" s="22" t="n"/>
+      <c r="D460" s="21" t="n"/>
+    </row>
+    <row r="461">
+      <c r="A461" s="15" t="n"/>
+      <c r="B461" s="15" t="n"/>
+      <c r="C461" s="22" t="n"/>
+      <c r="D461" s="21" t="n"/>
+    </row>
+    <row r="462">
+      <c r="A462" s="15" t="n"/>
+      <c r="B462" s="15" t="n"/>
+      <c r="C462" s="22" t="n"/>
+      <c r="D462" s="21" t="n"/>
+    </row>
+    <row r="463">
+      <c r="A463" s="15" t="n"/>
+      <c r="B463" s="15" t="n"/>
+      <c r="C463" s="22" t="n"/>
+      <c r="D463" s="21" t="n"/>
+    </row>
+    <row r="464">
+      <c r="A464" s="15" t="n"/>
+      <c r="B464" s="15" t="n"/>
+      <c r="C464" s="22" t="n"/>
+      <c r="D464" s="21" t="n"/>
+    </row>
+    <row r="465">
+      <c r="A465" s="15" t="n"/>
+      <c r="B465" s="15" t="n"/>
+      <c r="C465" s="22" t="n"/>
+      <c r="D465" s="21" t="n"/>
+    </row>
+    <row r="466">
+      <c r="A466" s="15" t="n"/>
+      <c r="B466" s="15" t="n"/>
+      <c r="C466" s="22" t="n"/>
+      <c r="D466" s="21" t="n"/>
+    </row>
+    <row r="467">
+      <c r="A467" s="15" t="n"/>
+      <c r="B467" s="15" t="n"/>
+      <c r="C467" s="22" t="n"/>
+      <c r="D467" s="21" t="n"/>
+    </row>
+    <row r="468">
+      <c r="A468" s="15" t="n"/>
+      <c r="B468" s="15" t="n"/>
+      <c r="C468" s="22" t="n"/>
+      <c r="D468" s="21" t="n"/>
+    </row>
+    <row r="469">
+      <c r="A469" s="15" t="n"/>
+      <c r="B469" s="15" t="n"/>
+      <c r="C469" s="22" t="n"/>
+      <c r="D469" s="21" t="n"/>
+    </row>
+    <row r="470">
+      <c r="A470" s="15" t="n"/>
+      <c r="B470" s="15" t="n"/>
+      <c r="C470" s="22" t="n"/>
+      <c r="D470" s="21" t="n"/>
+    </row>
+    <row r="471">
+      <c r="A471" s="15" t="n"/>
+      <c r="B471" s="15" t="n"/>
+      <c r="C471" s="22" t="n"/>
+      <c r="D471" s="21" t="n"/>
+    </row>
+    <row r="472">
+      <c r="A472" s="15" t="n"/>
+      <c r="B472" s="15" t="n"/>
+      <c r="C472" s="22" t="n"/>
+      <c r="D472" s="21" t="n"/>
+    </row>
+    <row r="473">
+      <c r="A473" s="15" t="n"/>
+      <c r="B473" s="15" t="n"/>
+      <c r="C473" s="22" t="n"/>
+      <c r="D473" s="21" t="n"/>
+    </row>
+    <row r="474">
+      <c r="A474" s="15" t="n"/>
+      <c r="B474" s="15" t="n"/>
+      <c r="C474" s="22" t="n"/>
+      <c r="D474" s="21" t="n"/>
+    </row>
+    <row r="475">
+      <c r="A475" s="15" t="n"/>
+      <c r="B475" s="15" t="n"/>
+      <c r="C475" s="22" t="n"/>
+      <c r="D475" s="21" t="n"/>
+    </row>
+    <row r="476">
+      <c r="A476" s="15" t="n"/>
+      <c r="B476" s="15" t="n"/>
+      <c r="C476" s="22" t="n"/>
+      <c r="D476" s="21" t="n"/>
+    </row>
+    <row r="477">
+      <c r="A477" s="15" t="n"/>
+      <c r="B477" s="15" t="n"/>
+      <c r="C477" s="22" t="n"/>
+      <c r="D477" s="21" t="n"/>
+    </row>
+    <row r="478">
+      <c r="A478" s="15" t="n"/>
+      <c r="B478" s="15" t="n"/>
+      <c r="C478" s="22" t="n"/>
+      <c r="D478" s="21" t="n"/>
+    </row>
+    <row r="479">
+      <c r="A479" s="15" t="n"/>
+      <c r="B479" s="15" t="n"/>
+      <c r="C479" s="22" t="n"/>
+      <c r="D479" s="21" t="n"/>
+    </row>
+    <row r="480">
+      <c r="A480" s="15" t="n"/>
+      <c r="B480" s="15" t="n"/>
+      <c r="C480" s="22" t="n"/>
+      <c r="D480" s="21" t="n"/>
+    </row>
+    <row r="481">
+      <c r="A481" s="15" t="n"/>
+      <c r="B481" s="15" t="n"/>
+      <c r="C481" s="22" t="n"/>
+      <c r="D481" s="21" t="n"/>
+    </row>
+    <row r="482">
+      <c r="A482" s="15" t="n"/>
+      <c r="B482" s="15" t="n"/>
+      <c r="C482" s="22" t="n"/>
+      <c r="D482" s="21" t="n"/>
+    </row>
+    <row r="483">
+      <c r="A483" s="15" t="n"/>
+      <c r="B483" s="15" t="n"/>
+      <c r="C483" s="22" t="n"/>
+      <c r="D483" s="21" t="n"/>
+    </row>
+    <row r="484">
+      <c r="A484" s="15" t="n"/>
+      <c r="B484" s="15" t="n"/>
+      <c r="C484" s="22" t="n"/>
+      <c r="D484" s="21" t="n"/>
+    </row>
+    <row r="485">
+      <c r="A485" s="15" t="n"/>
+      <c r="B485" s="15" t="n"/>
+      <c r="C485" s="22" t="n"/>
+      <c r="D485" s="21" t="n"/>
+    </row>
+    <row r="486">
+      <c r="A486" s="15" t="n"/>
+      <c r="B486" s="15" t="n"/>
+      <c r="C486" s="22" t="n"/>
+      <c r="D486" s="21" t="n"/>
+    </row>
+    <row r="487">
+      <c r="A487" s="15" t="n"/>
+      <c r="B487" s="15" t="n"/>
+      <c r="C487" s="22" t="n"/>
+      <c r="D487" s="21" t="n"/>
+    </row>
+    <row r="488">
+      <c r="A488" s="15" t="n"/>
+      <c r="B488" s="15" t="n"/>
+      <c r="C488" s="22" t="n"/>
+      <c r="D488" s="21" t="n"/>
+    </row>
+    <row r="489">
+      <c r="A489" s="15" t="n"/>
+      <c r="B489" s="15" t="n"/>
+      <c r="C489" s="22" t="n"/>
+      <c r="D489" s="21" t="n"/>
+    </row>
+    <row r="490">
+      <c r="A490" s="15" t="n"/>
+      <c r="B490" s="15" t="n"/>
+      <c r="C490" s="22" t="n"/>
+      <c r="D490" s="21" t="n"/>
+    </row>
+    <row r="491">
+      <c r="A491" s="15" t="n"/>
+      <c r="B491" s="15" t="n"/>
+      <c r="C491" s="22" t="n"/>
+      <c r="D491" s="21" t="n"/>
+    </row>
+    <row r="492">
+      <c r="A492" s="15" t="n"/>
+      <c r="B492" s="15" t="n"/>
+      <c r="C492" s="22" t="n"/>
+      <c r="D492" s="21" t="n"/>
+    </row>
+    <row r="493">
+      <c r="A493" s="15" t="n"/>
+      <c r="B493" s="15" t="n"/>
+      <c r="C493" s="22" t="n"/>
+      <c r="D493" s="21" t="n"/>
+    </row>
+    <row r="494">
+      <c r="A494" s="15" t="n"/>
+      <c r="B494" s="15" t="n"/>
+      <c r="C494" s="22" t="n"/>
+      <c r="D494" s="21" t="n"/>
+    </row>
+    <row r="495">
+      <c r="A495" s="15" t="n"/>
+      <c r="B495" s="15" t="n"/>
+      <c r="C495" s="22" t="n"/>
+      <c r="D495" s="21" t="n"/>
+    </row>
+    <row r="496">
+      <c r="A496" s="15" t="n"/>
+      <c r="B496" s="15" t="n"/>
+      <c r="C496" s="22" t="n"/>
+      <c r="D496" s="21" t="n"/>
+    </row>
+    <row r="497">
+      <c r="A497" s="15" t="n"/>
+      <c r="B497" s="15" t="n"/>
+      <c r="C497" s="22" t="n"/>
+      <c r="D497" s="21" t="n"/>
+    </row>
+    <row r="498">
+      <c r="A498" s="15" t="n"/>
+      <c r="B498" s="15" t="n"/>
+      <c r="C498" s="22" t="n"/>
+      <c r="D498" s="21" t="n"/>
+    </row>
+    <row r="499">
+      <c r="A499" s="15" t="n"/>
+      <c r="B499" s="15" t="n"/>
+      <c r="C499" s="22" t="n"/>
+      <c r="D499" s="21" t="n"/>
+    </row>
+    <row r="500">
+      <c r="A500" s="15" t="n"/>
+      <c r="B500" s="15" t="n"/>
+      <c r="C500" s="22" t="n"/>
+      <c r="D500" s="21" t="n"/>
+    </row>
+    <row r="501">
+      <c r="A501" s="4" t="n"/>
+      <c r="B501" s="24" t="inlineStr">
+        <is>
+          <t>Итого активов:</t>
+        </is>
+      </c>
+      <c r="C501" s="23">
+        <f>SUM(C2:C500)</f>
+        <v/>
+      </c>
+      <c r="D501" s="4" t="n"/>
+    </row>
+  </sheetData>
+  <dataValidations count="1">
+    <dataValidation sqref="A2:A500" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Нет в списке" error="Выберите значение из списка. Новые значения добавьте на листе «Списки»." type="list">
+      <formula1>Списки!$H$2:$H$6</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="001F3864"/>
@@ -725,31 +3808,31 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="28">
+      <c r="A2" s="36">
         <f>DATE(Настройки!$B$8,1,1)</f>
         <v/>
       </c>
-      <c r="B2" s="29">
+      <c r="B2" s="28">
         <f>SUMIFS(Операции!$D:$D,Операции!$B:$B,"Доход",Операции!$A:$A,"&gt;="&amp;$A2,Операции!$A:$A,"&lt;"&amp;EDATE($A2,1))</f>
         <v/>
       </c>
-      <c r="C2" s="29">
+      <c r="C2" s="28">
         <f>SUMIFS(Платежи!$C:$C,Платежи!$D:$D,"Мне должны",Платежи!$A:$A,"&gt;="&amp;$A2,Платежи!$A:$A,"&lt;"&amp;EDATE($A2,1))</f>
         <v/>
       </c>
-      <c r="D2" s="29">
+      <c r="D2" s="28">
         <f>SUMIFS(Операции!$D:$D,Операции!$B:$B,"Расход",Операции!$A:$A,"&gt;="&amp;$A2,Операции!$A:$A,"&lt;"&amp;EDATE($A2,1))</f>
         <v/>
       </c>
-      <c r="E2" s="29">
+      <c r="E2" s="28">
         <f>Подписки!$E$501</f>
         <v/>
       </c>
-      <c r="F2" s="29">
+      <c r="F2" s="28">
         <f>SUMIFS(Платежи!$C:$C,Платежи!$D:$D,"Я должен",Платежи!$A:$A,"&gt;="&amp;$A2,Платежи!$A:$A,"&lt;"&amp;EDATE($A2,1))</f>
         <v/>
       </c>
-      <c r="G2" s="29">
+      <c r="G2" s="28">
         <f>B2+C2-D2-E2-F2</f>
         <v/>
       </c>
@@ -759,31 +3842,31 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="28">
+      <c r="A3" s="36">
         <f>EDATE(A2,1)</f>
         <v/>
       </c>
-      <c r="B3" s="29">
+      <c r="B3" s="28">
         <f>SUMIFS(Операции!$D:$D,Операции!$B:$B,"Доход",Операции!$A:$A,"&gt;="&amp;$A3,Операции!$A:$A,"&lt;"&amp;EDATE($A3,1))</f>
         <v/>
       </c>
-      <c r="C3" s="29">
+      <c r="C3" s="28">
         <f>SUMIFS(Платежи!$C:$C,Платежи!$D:$D,"Мне должны",Платежи!$A:$A,"&gt;="&amp;$A3,Платежи!$A:$A,"&lt;"&amp;EDATE($A3,1))</f>
         <v/>
       </c>
-      <c r="D3" s="29">
+      <c r="D3" s="28">
         <f>SUMIFS(Операции!$D:$D,Операции!$B:$B,"Расход",Операции!$A:$A,"&gt;="&amp;$A3,Операции!$A:$A,"&lt;"&amp;EDATE($A3,1))</f>
         <v/>
       </c>
-      <c r="E3" s="29">
+      <c r="E3" s="28">
         <f>Подписки!$E$501</f>
         <v/>
       </c>
-      <c r="F3" s="29">
+      <c r="F3" s="28">
         <f>SUMIFS(Платежи!$C:$C,Платежи!$D:$D,"Я должен",Платежи!$A:$A,"&gt;="&amp;$A3,Платежи!$A:$A,"&lt;"&amp;EDATE($A3,1))</f>
         <v/>
       </c>
-      <c r="G3" s="29">
+      <c r="G3" s="28">
         <f>B3+C3-D3-E3-F3</f>
         <v/>
       </c>
@@ -793,31 +3876,31 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="28">
+      <c r="A4" s="36">
         <f>EDATE(A3,1)</f>
         <v/>
       </c>
-      <c r="B4" s="29">
+      <c r="B4" s="28">
         <f>SUMIFS(Операции!$D:$D,Операции!$B:$B,"Доход",Операции!$A:$A,"&gt;="&amp;$A4,Операции!$A:$A,"&lt;"&amp;EDATE($A4,1))</f>
         <v/>
       </c>
-      <c r="C4" s="29">
+      <c r="C4" s="28">
         <f>SUMIFS(Платежи!$C:$C,Платежи!$D:$D,"Мне должны",Платежи!$A:$A,"&gt;="&amp;$A4,Платежи!$A:$A,"&lt;"&amp;EDATE($A4,1))</f>
         <v/>
       </c>
-      <c r="D4" s="29">
+      <c r="D4" s="28">
         <f>SUMIFS(Операции!$D:$D,Операции!$B:$B,"Расход",Операции!$A:$A,"&gt;="&amp;$A4,Операции!$A:$A,"&lt;"&amp;EDATE($A4,1))</f>
         <v/>
       </c>
-      <c r="E4" s="29">
+      <c r="E4" s="28">
         <f>Подписки!$E$501</f>
         <v/>
       </c>
-      <c r="F4" s="29">
+      <c r="F4" s="28">
         <f>SUMIFS(Платежи!$C:$C,Платежи!$D:$D,"Я должен",Платежи!$A:$A,"&gt;="&amp;$A4,Платежи!$A:$A,"&lt;"&amp;EDATE($A4,1))</f>
         <v/>
       </c>
-      <c r="G4" s="29">
+      <c r="G4" s="28">
         <f>B4+C4-D4-E4-F4</f>
         <v/>
       </c>
@@ -827,31 +3910,31 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="28">
+      <c r="A5" s="36">
         <f>EDATE(A4,1)</f>
         <v/>
       </c>
-      <c r="B5" s="29">
+      <c r="B5" s="28">
         <f>SUMIFS(Операции!$D:$D,Операции!$B:$B,"Доход",Операции!$A:$A,"&gt;="&amp;$A5,Операции!$A:$A,"&lt;"&amp;EDATE($A5,1))</f>
         <v/>
       </c>
-      <c r="C5" s="29">
+      <c r="C5" s="28">
         <f>SUMIFS(Платежи!$C:$C,Платежи!$D:$D,"Мне должны",Платежи!$A:$A,"&gt;="&amp;$A5,Платежи!$A:$A,"&lt;"&amp;EDATE($A5,1))</f>
         <v/>
       </c>
-      <c r="D5" s="29">
+      <c r="D5" s="28">
         <f>SUMIFS(Операции!$D:$D,Операции!$B:$B,"Расход",Операции!$A:$A,"&gt;="&amp;$A5,Операции!$A:$A,"&lt;"&amp;EDATE($A5,1))</f>
         <v/>
       </c>
-      <c r="E5" s="29">
+      <c r="E5" s="28">
         <f>Подписки!$E$501</f>
         <v/>
       </c>
-      <c r="F5" s="29">
+      <c r="F5" s="28">
         <f>SUMIFS(Платежи!$C:$C,Платежи!$D:$D,"Я должен",Платежи!$A:$A,"&gt;="&amp;$A5,Платежи!$A:$A,"&lt;"&amp;EDATE($A5,1))</f>
         <v/>
       </c>
-      <c r="G5" s="29">
+      <c r="G5" s="28">
         <f>B5+C5-D5-E5-F5</f>
         <v/>
       </c>
@@ -861,31 +3944,31 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="28">
+      <c r="A6" s="36">
         <f>EDATE(A5,1)</f>
         <v/>
       </c>
-      <c r="B6" s="29">
+      <c r="B6" s="28">
         <f>SUMIFS(Операции!$D:$D,Операции!$B:$B,"Доход",Операции!$A:$A,"&gt;="&amp;$A6,Операции!$A:$A,"&lt;"&amp;EDATE($A6,1))</f>
         <v/>
       </c>
-      <c r="C6" s="29">
+      <c r="C6" s="28">
         <f>SUMIFS(Платежи!$C:$C,Платежи!$D:$D,"Мне должны",Платежи!$A:$A,"&gt;="&amp;$A6,Платежи!$A:$A,"&lt;"&amp;EDATE($A6,1))</f>
         <v/>
       </c>
-      <c r="D6" s="29">
+      <c r="D6" s="28">
         <f>SUMIFS(Операции!$D:$D,Операции!$B:$B,"Расход",Операции!$A:$A,"&gt;="&amp;$A6,Операции!$A:$A,"&lt;"&amp;EDATE($A6,1))</f>
         <v/>
       </c>
-      <c r="E6" s="29">
+      <c r="E6" s="28">
         <f>Подписки!$E$501</f>
         <v/>
       </c>
-      <c r="F6" s="29">
+      <c r="F6" s="28">
         <f>SUMIFS(Платежи!$C:$C,Платежи!$D:$D,"Я должен",Платежи!$A:$A,"&gt;="&amp;$A6,Платежи!$A:$A,"&lt;"&amp;EDATE($A6,1))</f>
         <v/>
       </c>
-      <c r="G6" s="29">
+      <c r="G6" s="28">
         <f>B6+C6-D6-E6-F6</f>
         <v/>
       </c>
@@ -895,31 +3978,31 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="28">
+      <c r="A7" s="36">
         <f>EDATE(A6,1)</f>
         <v/>
       </c>
-      <c r="B7" s="29">
+      <c r="B7" s="28">
         <f>SUMIFS(Операции!$D:$D,Операции!$B:$B,"Доход",Операции!$A:$A,"&gt;="&amp;$A7,Операции!$A:$A,"&lt;"&amp;EDATE($A7,1))</f>
         <v/>
       </c>
-      <c r="C7" s="29">
+      <c r="C7" s="28">
         <f>SUMIFS(Платежи!$C:$C,Платежи!$D:$D,"Мне должны",Платежи!$A:$A,"&gt;="&amp;$A7,Платежи!$A:$A,"&lt;"&amp;EDATE($A7,1))</f>
         <v/>
       </c>
-      <c r="D7" s="29">
+      <c r="D7" s="28">
         <f>SUMIFS(Операции!$D:$D,Операции!$B:$B,"Расход",Операции!$A:$A,"&gt;="&amp;$A7,Операции!$A:$A,"&lt;"&amp;EDATE($A7,1))</f>
         <v/>
       </c>
-      <c r="E7" s="29">
+      <c r="E7" s="28">
         <f>Подписки!$E$501</f>
         <v/>
       </c>
-      <c r="F7" s="29">
+      <c r="F7" s="28">
         <f>SUMIFS(Платежи!$C:$C,Платежи!$D:$D,"Я должен",Платежи!$A:$A,"&gt;="&amp;$A7,Платежи!$A:$A,"&lt;"&amp;EDATE($A7,1))</f>
         <v/>
       </c>
-      <c r="G7" s="29">
+      <c r="G7" s="28">
         <f>B7+C7-D7-E7-F7</f>
         <v/>
       </c>
@@ -929,31 +4012,31 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="28">
+      <c r="A8" s="36">
         <f>EDATE(A7,1)</f>
         <v/>
       </c>
-      <c r="B8" s="29">
+      <c r="B8" s="28">
         <f>SUMIFS(Операции!$D:$D,Операции!$B:$B,"Доход",Операции!$A:$A,"&gt;="&amp;$A8,Операции!$A:$A,"&lt;"&amp;EDATE($A8,1))</f>
         <v/>
       </c>
-      <c r="C8" s="29">
+      <c r="C8" s="28">
         <f>SUMIFS(Платежи!$C:$C,Платежи!$D:$D,"Мне должны",Платежи!$A:$A,"&gt;="&amp;$A8,Платежи!$A:$A,"&lt;"&amp;EDATE($A8,1))</f>
         <v/>
       </c>
-      <c r="D8" s="29">
+      <c r="D8" s="28">
         <f>SUMIFS(Операции!$D:$D,Операции!$B:$B,"Расход",Операции!$A:$A,"&gt;="&amp;$A8,Операции!$A:$A,"&lt;"&amp;EDATE($A8,1))</f>
         <v/>
       </c>
-      <c r="E8" s="29">
+      <c r="E8" s="28">
         <f>Подписки!$E$501</f>
         <v/>
       </c>
-      <c r="F8" s="29">
+      <c r="F8" s="28">
         <f>SUMIFS(Платежи!$C:$C,Платежи!$D:$D,"Я должен",Платежи!$A:$A,"&gt;="&amp;$A8,Платежи!$A:$A,"&lt;"&amp;EDATE($A8,1))</f>
         <v/>
       </c>
-      <c r="G8" s="29">
+      <c r="G8" s="28">
         <f>B8+C8-D8-E8-F8</f>
         <v/>
       </c>
@@ -963,31 +4046,31 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="28">
+      <c r="A9" s="36">
         <f>EDATE(A8,1)</f>
         <v/>
       </c>
-      <c r="B9" s="29">
+      <c r="B9" s="28">
         <f>SUMIFS(Операции!$D:$D,Операции!$B:$B,"Доход",Операции!$A:$A,"&gt;="&amp;$A9,Операции!$A:$A,"&lt;"&amp;EDATE($A9,1))</f>
         <v/>
       </c>
-      <c r="C9" s="29">
+      <c r="C9" s="28">
         <f>SUMIFS(Платежи!$C:$C,Платежи!$D:$D,"Мне должны",Платежи!$A:$A,"&gt;="&amp;$A9,Платежи!$A:$A,"&lt;"&amp;EDATE($A9,1))</f>
         <v/>
       </c>
-      <c r="D9" s="29">
+      <c r="D9" s="28">
         <f>SUMIFS(Операции!$D:$D,Операции!$B:$B,"Расход",Операции!$A:$A,"&gt;="&amp;$A9,Операции!$A:$A,"&lt;"&amp;EDATE($A9,1))</f>
         <v/>
       </c>
-      <c r="E9" s="29">
+      <c r="E9" s="28">
         <f>Подписки!$E$501</f>
         <v/>
       </c>
-      <c r="F9" s="29">
+      <c r="F9" s="28">
         <f>SUMIFS(Платежи!$C:$C,Платежи!$D:$D,"Я должен",Платежи!$A:$A,"&gt;="&amp;$A9,Платежи!$A:$A,"&lt;"&amp;EDATE($A9,1))</f>
         <v/>
       </c>
-      <c r="G9" s="29">
+      <c r="G9" s="28">
         <f>B9+C9-D9-E9-F9</f>
         <v/>
       </c>
@@ -997,31 +4080,31 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="28">
+      <c r="A10" s="36">
         <f>EDATE(A9,1)</f>
         <v/>
       </c>
-      <c r="B10" s="29">
+      <c r="B10" s="28">
         <f>SUMIFS(Операции!$D:$D,Операции!$B:$B,"Доход",Операции!$A:$A,"&gt;="&amp;$A10,Операции!$A:$A,"&lt;"&amp;EDATE($A10,1))</f>
         <v/>
       </c>
-      <c r="C10" s="29">
+      <c r="C10" s="28">
         <f>SUMIFS(Платежи!$C:$C,Платежи!$D:$D,"Мне должны",Платежи!$A:$A,"&gt;="&amp;$A10,Платежи!$A:$A,"&lt;"&amp;EDATE($A10,1))</f>
         <v/>
       </c>
-      <c r="D10" s="29">
+      <c r="D10" s="28">
         <f>SUMIFS(Операции!$D:$D,Операции!$B:$B,"Расход",Операции!$A:$A,"&gt;="&amp;$A10,Операции!$A:$A,"&lt;"&amp;EDATE($A10,1))</f>
         <v/>
       </c>
-      <c r="E10" s="29">
+      <c r="E10" s="28">
         <f>Подписки!$E$501</f>
         <v/>
       </c>
-      <c r="F10" s="29">
+      <c r="F10" s="28">
         <f>SUMIFS(Платежи!$C:$C,Платежи!$D:$D,"Я должен",Платежи!$A:$A,"&gt;="&amp;$A10,Платежи!$A:$A,"&lt;"&amp;EDATE($A10,1))</f>
         <v/>
       </c>
-      <c r="G10" s="29">
+      <c r="G10" s="28">
         <f>B10+C10-D10-E10-F10</f>
         <v/>
       </c>
@@ -1031,31 +4114,31 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="28">
+      <c r="A11" s="36">
         <f>EDATE(A10,1)</f>
         <v/>
       </c>
-      <c r="B11" s="29">
+      <c r="B11" s="28">
         <f>SUMIFS(Операции!$D:$D,Операции!$B:$B,"Доход",Операции!$A:$A,"&gt;="&amp;$A11,Операции!$A:$A,"&lt;"&amp;EDATE($A11,1))</f>
         <v/>
       </c>
-      <c r="C11" s="29">
+      <c r="C11" s="28">
         <f>SUMIFS(Платежи!$C:$C,Платежи!$D:$D,"Мне должны",Платежи!$A:$A,"&gt;="&amp;$A11,Платежи!$A:$A,"&lt;"&amp;EDATE($A11,1))</f>
         <v/>
       </c>
-      <c r="D11" s="29">
+      <c r="D11" s="28">
         <f>SUMIFS(Операции!$D:$D,Операции!$B:$B,"Расход",Операции!$A:$A,"&gt;="&amp;$A11,Операции!$A:$A,"&lt;"&amp;EDATE($A11,1))</f>
         <v/>
       </c>
-      <c r="E11" s="29">
+      <c r="E11" s="28">
         <f>Подписки!$E$501</f>
         <v/>
       </c>
-      <c r="F11" s="29">
+      <c r="F11" s="28">
         <f>SUMIFS(Платежи!$C:$C,Платежи!$D:$D,"Я должен",Платежи!$A:$A,"&gt;="&amp;$A11,Платежи!$A:$A,"&lt;"&amp;EDATE($A11,1))</f>
         <v/>
       </c>
-      <c r="G11" s="29">
+      <c r="G11" s="28">
         <f>B11+C11-D11-E11-F11</f>
         <v/>
       </c>
@@ -1065,31 +4148,31 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="28">
+      <c r="A12" s="36">
         <f>EDATE(A11,1)</f>
         <v/>
       </c>
-      <c r="B12" s="29">
+      <c r="B12" s="28">
         <f>SUMIFS(Операции!$D:$D,Операции!$B:$B,"Доход",Операции!$A:$A,"&gt;="&amp;$A12,Операции!$A:$A,"&lt;"&amp;EDATE($A12,1))</f>
         <v/>
       </c>
-      <c r="C12" s="29">
+      <c r="C12" s="28">
         <f>SUMIFS(Платежи!$C:$C,Платежи!$D:$D,"Мне должны",Платежи!$A:$A,"&gt;="&amp;$A12,Платежи!$A:$A,"&lt;"&amp;EDATE($A12,1))</f>
         <v/>
       </c>
-      <c r="D12" s="29">
+      <c r="D12" s="28">
         <f>SUMIFS(Операции!$D:$D,Операции!$B:$B,"Расход",Операции!$A:$A,"&gt;="&amp;$A12,Операции!$A:$A,"&lt;"&amp;EDATE($A12,1))</f>
         <v/>
       </c>
-      <c r="E12" s="29">
+      <c r="E12" s="28">
         <f>Подписки!$E$501</f>
         <v/>
       </c>
-      <c r="F12" s="29">
+      <c r="F12" s="28">
         <f>SUMIFS(Платежи!$C:$C,Платежи!$D:$D,"Я должен",Платежи!$A:$A,"&gt;="&amp;$A12,Платежи!$A:$A,"&lt;"&amp;EDATE($A12,1))</f>
         <v/>
       </c>
-      <c r="G12" s="29">
+      <c r="G12" s="28">
         <f>B12+C12-D12-E12-F12</f>
         <v/>
       </c>
@@ -1099,31 +4182,31 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="28">
+      <c r="A13" s="36">
         <f>EDATE(A12,1)</f>
         <v/>
       </c>
-      <c r="B13" s="29">
+      <c r="B13" s="28">
         <f>SUMIFS(Операции!$D:$D,Операции!$B:$B,"Доход",Операции!$A:$A,"&gt;="&amp;$A13,Операции!$A:$A,"&lt;"&amp;EDATE($A13,1))</f>
         <v/>
       </c>
-      <c r="C13" s="29">
+      <c r="C13" s="28">
         <f>SUMIFS(Платежи!$C:$C,Платежи!$D:$D,"Мне должны",Платежи!$A:$A,"&gt;="&amp;$A13,Платежи!$A:$A,"&lt;"&amp;EDATE($A13,1))</f>
         <v/>
       </c>
-      <c r="D13" s="29">
+      <c r="D13" s="28">
         <f>SUMIFS(Операции!$D:$D,Операции!$B:$B,"Расход",Операции!$A:$A,"&gt;="&amp;$A13,Операции!$A:$A,"&lt;"&amp;EDATE($A13,1))</f>
         <v/>
       </c>
-      <c r="E13" s="29">
+      <c r="E13" s="28">
         <f>Подписки!$E$501</f>
         <v/>
       </c>
-      <c r="F13" s="29">
+      <c r="F13" s="28">
         <f>SUMIFS(Платежи!$C:$C,Платежи!$D:$D,"Я должен",Платежи!$A:$A,"&gt;="&amp;$A13,Платежи!$A:$A,"&lt;"&amp;EDATE($A13,1))</f>
         <v/>
       </c>
-      <c r="G13" s="29">
+      <c r="G13" s="28">
         <f>B13+C13-D13-E13-F13</f>
         <v/>
       </c>
@@ -1138,27 +4221,27 @@
           <t>Итого за 12 месяцев</t>
         </is>
       </c>
-      <c r="B14" s="30">
+      <c r="B14" s="37">
         <f>SUM(B2:B13)</f>
         <v/>
       </c>
-      <c r="C14" s="30">
+      <c r="C14" s="37">
         <f>SUM(C2:C13)</f>
         <v/>
       </c>
-      <c r="D14" s="30">
+      <c r="D14" s="37">
         <f>SUM(D2:D13)</f>
         <v/>
       </c>
-      <c r="E14" s="30">
+      <c r="E14" s="37">
         <f>SUM(E2:E13)</f>
         <v/>
       </c>
-      <c r="F14" s="30">
+      <c r="F14" s="37">
         <f>SUM(F2:F13)</f>
         <v/>
       </c>
-      <c r="G14" s="30">
+      <c r="G14" s="37">
         <f>SUM(G2:G13)</f>
         <v/>
       </c>
@@ -1169,14 +4252,14 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="007F7F7F"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I19"/>
+  <dimension ref="A1:V21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1188,6 +4271,16 @@
     <col width="22" customWidth="1" min="7" max="7"/>
     <col width="22" customWidth="1" min="8" max="8"/>
     <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="36" customWidth="1" min="11" max="11"/>
+    <col width="9" customWidth="1" min="12" max="12"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="18" customWidth="1" min="14" max="14"/>
+    <col width="20" customWidth="1" min="15" max="15"/>
+    <col width="52" customWidth="1" min="16" max="16"/>
+    <col width="16" customWidth="1" min="18" max="18"/>
+    <col width="16" customWidth="1" min="20" max="20"/>
+    <col width="36" customWidth="1" min="21" max="21"/>
+    <col width="10" customWidth="1" min="22" max="22"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -1236,6 +4329,59 @@
           <t>Счёт</t>
         </is>
       </c>
+      <c r="J1" s="4" t="n"/>
+      <c r="K1" s="14" t="inlineStr">
+        <is>
+          <t>Инструмент</t>
+        </is>
+      </c>
+      <c r="L1" s="14" t="inlineStr">
+        <is>
+          <t>Тикер</t>
+        </is>
+      </c>
+      <c r="M1" s="14" t="inlineStr">
+        <is>
+          <t>Тип</t>
+        </is>
+      </c>
+      <c r="N1" s="14" t="inlineStr">
+        <is>
+          <t>Дивиденды / выплаты</t>
+        </is>
+      </c>
+      <c r="O1" s="14" t="inlineStr">
+        <is>
+          <t>Доходность (допущение)</t>
+        </is>
+      </c>
+      <c r="P1" s="14" t="inlineStr">
+        <is>
+          <t>Комментарий</t>
+        </is>
+      </c>
+      <c r="Q1" s="4" t="n"/>
+      <c r="R1" s="14" t="inlineStr">
+        <is>
+          <t>Портфели</t>
+        </is>
+      </c>
+      <c r="S1" s="4" t="n"/>
+      <c r="T1" s="14" t="inlineStr">
+        <is>
+          <t>Портфель</t>
+        </is>
+      </c>
+      <c r="U1" s="14" t="inlineStr">
+        <is>
+          <t>Инструмент</t>
+        </is>
+      </c>
+      <c r="V1" s="14" t="inlineStr">
+        <is>
+          <t>Доля</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="15" t="inlineStr">
@@ -1283,6 +4429,55 @@
           <t>Карта</t>
         </is>
       </c>
+      <c r="J2" s="15" t="n"/>
+      <c r="K2" s="15" t="inlineStr">
+        <is>
+          <t>S&amp;P 500 (ETF, накопительный)</t>
+        </is>
+      </c>
+      <c r="L2" s="15" t="inlineStr">
+        <is>
+          <t>CSPX</t>
+        </is>
+      </c>
+      <c r="M2" s="15" t="inlineStr">
+        <is>
+          <t>ETF</t>
+        </is>
+      </c>
+      <c r="N2" s="15" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="O2" s="26" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="P2" s="15" t="inlineStr">
+        <is>
+          <t>Доход реинвестируется; UCITS-аналог S&amp;P 500 для жителей ЕС</t>
+        </is>
+      </c>
+      <c r="Q2" s="15" t="n"/>
+      <c r="R2" s="15" t="inlineStr">
+        <is>
+          <t>Осторожный</t>
+        </is>
+      </c>
+      <c r="S2" s="15" t="n"/>
+      <c r="T2" s="15" t="inlineStr">
+        <is>
+          <t>Осторожный</t>
+        </is>
+      </c>
+      <c r="U2" s="15" t="inlineStr">
+        <is>
+          <t>Мировой индекс (ETF, накопительный)</t>
+        </is>
+      </c>
+      <c r="V2" s="26" t="n">
+        <v>0.6</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="15" t="inlineStr">
@@ -1329,6 +4524,55 @@
         <is>
           <t>Наличные</t>
         </is>
+      </c>
+      <c r="J3" s="15" t="n"/>
+      <c r="K3" s="15" t="inlineStr">
+        <is>
+          <t>S&amp;P 500 (ETF, распределяющий)</t>
+        </is>
+      </c>
+      <c r="L3" s="15" t="inlineStr">
+        <is>
+          <t>VUSA</t>
+        </is>
+      </c>
+      <c r="M3" s="15" t="inlineStr">
+        <is>
+          <t>ETF</t>
+        </is>
+      </c>
+      <c r="N3" s="15" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="O3" s="26" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="P3" s="15" t="inlineStr">
+        <is>
+          <t>Выплачивает дивиденды</t>
+        </is>
+      </c>
+      <c r="Q3" s="15" t="n"/>
+      <c r="R3" s="15" t="inlineStr">
+        <is>
+          <t>Баланс</t>
+        </is>
+      </c>
+      <c r="S3" s="15" t="n"/>
+      <c r="T3" s="15" t="inlineStr">
+        <is>
+          <t>Осторожный</t>
+        </is>
+      </c>
+      <c r="U3" s="15" t="inlineStr">
+        <is>
+          <t>Дивидендный ETF (мир)</t>
+        </is>
+      </c>
+      <c r="V3" s="26" t="n">
+        <v>0.15</v>
       </c>
     </row>
     <row r="4">
@@ -1361,6 +4605,55 @@
           <t>Основной счёт</t>
         </is>
       </c>
+      <c r="J4" s="15" t="n"/>
+      <c r="K4" s="15" t="inlineStr">
+        <is>
+          <t>Мировой индекс (ETF, накопительный)</t>
+        </is>
+      </c>
+      <c r="L4" s="15" t="inlineStr">
+        <is>
+          <t>VWCE</t>
+        </is>
+      </c>
+      <c r="M4" s="15" t="inlineStr">
+        <is>
+          <t>ETF</t>
+        </is>
+      </c>
+      <c r="N4" s="15" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="O4" s="26" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="P4" s="15" t="inlineStr">
+        <is>
+          <t>Тысячи компаний из развитых и развивающихся стран</t>
+        </is>
+      </c>
+      <c r="Q4" s="15" t="n"/>
+      <c r="R4" s="15" t="inlineStr">
+        <is>
+          <t>Агрессивный</t>
+        </is>
+      </c>
+      <c r="S4" s="15" t="n"/>
+      <c r="T4" s="15" t="inlineStr">
+        <is>
+          <t>Осторожный</t>
+        </is>
+      </c>
+      <c r="U4" s="15" t="inlineStr">
+        <is>
+          <t>Облигации (ETF)</t>
+        </is>
+      </c>
+      <c r="V4" s="26" t="n">
+        <v>0.25</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="15" t="inlineStr">
@@ -1392,6 +4685,55 @@
           <t>Накопления</t>
         </is>
       </c>
+      <c r="J5" s="15" t="n"/>
+      <c r="K5" s="15" t="inlineStr">
+        <is>
+          <t>Дивидендный ETF (мир)</t>
+        </is>
+      </c>
+      <c r="L5" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M5" s="15" t="inlineStr">
+        <is>
+          <t>ETF</t>
+        </is>
+      </c>
+      <c r="N5" s="15" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="O5" s="26" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="P5" s="15" t="inlineStr">
+        <is>
+          <t>Фонд дивидендных компаний; конкретный фонд подберите у брокера</t>
+        </is>
+      </c>
+      <c r="Q5" s="15" t="n"/>
+      <c r="R5" s="15" t="inlineStr">
+        <is>
+          <t>Свой</t>
+        </is>
+      </c>
+      <c r="S5" s="15" t="n"/>
+      <c r="T5" s="15" t="inlineStr">
+        <is>
+          <t>Баланс</t>
+        </is>
+      </c>
+      <c r="U5" s="15" t="inlineStr">
+        <is>
+          <t>S&amp;P 500 (ETF, накопительный)</t>
+        </is>
+      </c>
+      <c r="V5" s="26" t="n">
+        <v>0.35</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="15" t="inlineStr">
@@ -1419,6 +4761,51 @@
         </is>
       </c>
       <c r="I6" s="15" t="n"/>
+      <c r="J6" s="15" t="n"/>
+      <c r="K6" s="15" t="inlineStr">
+        <is>
+          <t>Облигации (ETF)</t>
+        </is>
+      </c>
+      <c r="L6" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M6" s="15" t="inlineStr">
+        <is>
+          <t>ETF</t>
+        </is>
+      </c>
+      <c r="N6" s="15" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="O6" s="26" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="P6" s="15" t="inlineStr">
+        <is>
+          <t>Доход в виде купонов; стабилизирует портфель</t>
+        </is>
+      </c>
+      <c r="Q6" s="15" t="n"/>
+      <c r="R6" s="15" t="n"/>
+      <c r="S6" s="15" t="n"/>
+      <c r="T6" s="15" t="inlineStr">
+        <is>
+          <t>Баланс</t>
+        </is>
+      </c>
+      <c r="U6" s="15" t="inlineStr">
+        <is>
+          <t>Мировой индекс (ETF, накопительный)</t>
+        </is>
+      </c>
+      <c r="V6" s="26" t="n">
+        <v>0.25</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="15" t="inlineStr">
@@ -1442,6 +4829,51 @@
       </c>
       <c r="H7" s="15" t="n"/>
       <c r="I7" s="15" t="n"/>
+      <c r="J7" s="15" t="n"/>
+      <c r="K7" s="15" t="inlineStr">
+        <is>
+          <t>Депозит / вклад</t>
+        </is>
+      </c>
+      <c r="L7" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M7" s="15" t="inlineStr">
+        <is>
+          <t>Вклад</t>
+        </is>
+      </c>
+      <c r="N7" s="15" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="O7" s="26" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="P7" s="15" t="inlineStr">
+        <is>
+          <t>Проценты по вкладу; деньги под рукой</t>
+        </is>
+      </c>
+      <c r="Q7" s="15" t="n"/>
+      <c r="R7" s="15" t="n"/>
+      <c r="S7" s="15" t="n"/>
+      <c r="T7" s="15" t="inlineStr">
+        <is>
+          <t>Баланс</t>
+        </is>
+      </c>
+      <c r="U7" s="15" t="inlineStr">
+        <is>
+          <t>Дивидендный ETF (мир)</t>
+        </is>
+      </c>
+      <c r="V7" s="26" t="n">
+        <v>0.15</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="15" t="inlineStr">
@@ -1461,6 +4893,51 @@
       <c r="G8" s="15" t="n"/>
       <c r="H8" s="15" t="n"/>
       <c r="I8" s="15" t="n"/>
+      <c r="J8" s="15" t="n"/>
+      <c r="K8" s="15" t="inlineStr">
+        <is>
+          <t>Apple</t>
+        </is>
+      </c>
+      <c r="L8" s="15" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="M8" s="15" t="inlineStr">
+        <is>
+          <t>Акция</t>
+        </is>
+      </c>
+      <c r="N8" s="15" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="O8" s="26" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="P8" s="15" t="inlineStr">
+        <is>
+          <t>Платит дивиденды</t>
+        </is>
+      </c>
+      <c r="Q8" s="15" t="n"/>
+      <c r="R8" s="15" t="n"/>
+      <c r="S8" s="15" t="n"/>
+      <c r="T8" s="15" t="inlineStr">
+        <is>
+          <t>Баланс</t>
+        </is>
+      </c>
+      <c r="U8" s="15" t="inlineStr">
+        <is>
+          <t>Облигации (ETF)</t>
+        </is>
+      </c>
+      <c r="V8" s="26" t="n">
+        <v>0.2</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="15" t="inlineStr">
@@ -1480,6 +4957,51 @@
       <c r="G9" s="15" t="n"/>
       <c r="H9" s="15" t="n"/>
       <c r="I9" s="15" t="n"/>
+      <c r="J9" s="15" t="n"/>
+      <c r="K9" s="15" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
+      <c r="L9" s="15" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="M9" s="15" t="inlineStr">
+        <is>
+          <t>Акция</t>
+        </is>
+      </c>
+      <c r="N9" s="15" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="O9" s="26" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="P9" s="15" t="inlineStr">
+        <is>
+          <t>Платит дивиденды</t>
+        </is>
+      </c>
+      <c r="Q9" s="15" t="n"/>
+      <c r="R9" s="15" t="n"/>
+      <c r="S9" s="15" t="n"/>
+      <c r="T9" s="15" t="inlineStr">
+        <is>
+          <t>Баланс</t>
+        </is>
+      </c>
+      <c r="U9" s="15" t="inlineStr">
+        <is>
+          <t>Bitcoin</t>
+        </is>
+      </c>
+      <c r="V9" s="26" t="n">
+        <v>0.05</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="15" t="inlineStr">
@@ -1495,6 +5017,51 @@
       <c r="G10" s="15" t="n"/>
       <c r="H10" s="15" t="n"/>
       <c r="I10" s="15" t="n"/>
+      <c r="J10" s="15" t="n"/>
+      <c r="K10" s="15" t="inlineStr">
+        <is>
+          <t>NVIDIA</t>
+        </is>
+      </c>
+      <c r="L10" s="15" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="M10" s="15" t="inlineStr">
+        <is>
+          <t>Акция</t>
+        </is>
+      </c>
+      <c r="N10" s="15" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="O10" s="26" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="P10" s="15" t="inlineStr">
+        <is>
+          <t>Небольшой дивиденд, основной доход — рост</t>
+        </is>
+      </c>
+      <c r="Q10" s="15" t="n"/>
+      <c r="R10" s="15" t="n"/>
+      <c r="S10" s="15" t="n"/>
+      <c r="T10" s="15" t="inlineStr">
+        <is>
+          <t>Агрессивный</t>
+        </is>
+      </c>
+      <c r="U10" s="15" t="inlineStr">
+        <is>
+          <t>S&amp;P 500 (ETF, накопительный)</t>
+        </is>
+      </c>
+      <c r="V10" s="26" t="n">
+        <v>0.4</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="15" t="inlineStr">
@@ -1510,6 +5077,51 @@
       <c r="G11" s="15" t="n"/>
       <c r="H11" s="15" t="n"/>
       <c r="I11" s="15" t="n"/>
+      <c r="J11" s="15" t="n"/>
+      <c r="K11" s="15" t="inlineStr">
+        <is>
+          <t>Alphabet (Google)</t>
+        </is>
+      </c>
+      <c r="L11" s="15" t="inlineStr">
+        <is>
+          <t>GOOGL</t>
+        </is>
+      </c>
+      <c r="M11" s="15" t="inlineStr">
+        <is>
+          <t>Акция</t>
+        </is>
+      </c>
+      <c r="N11" s="15" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="O11" s="26" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="P11" s="15" t="inlineStr">
+        <is>
+          <t>Дивиденды с 2024 года</t>
+        </is>
+      </c>
+      <c r="Q11" s="15" t="n"/>
+      <c r="R11" s="15" t="n"/>
+      <c r="S11" s="15" t="n"/>
+      <c r="T11" s="15" t="inlineStr">
+        <is>
+          <t>Агрессивный</t>
+        </is>
+      </c>
+      <c r="U11" s="15" t="inlineStr">
+        <is>
+          <t>Мировой индекс (ETF, накопительный)</t>
+        </is>
+      </c>
+      <c r="V11" s="26" t="n">
+        <v>0.3</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="15" t="inlineStr">
@@ -1525,6 +5137,51 @@
       <c r="G12" s="15" t="n"/>
       <c r="H12" s="15" t="n"/>
       <c r="I12" s="15" t="n"/>
+      <c r="J12" s="15" t="n"/>
+      <c r="K12" s="15" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="L12" s="15" t="inlineStr">
+        <is>
+          <t>AMZN</t>
+        </is>
+      </c>
+      <c r="M12" s="15" t="inlineStr">
+        <is>
+          <t>Акция</t>
+        </is>
+      </c>
+      <c r="N12" s="15" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="O12" s="26" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="P12" s="15" t="inlineStr">
+        <is>
+          <t>Дивидендов не платит</t>
+        </is>
+      </c>
+      <c r="Q12" s="15" t="n"/>
+      <c r="R12" s="15" t="n"/>
+      <c r="S12" s="15" t="n"/>
+      <c r="T12" s="15" t="inlineStr">
+        <is>
+          <t>Агрессивный</t>
+        </is>
+      </c>
+      <c r="U12" s="15" t="inlineStr">
+        <is>
+          <t>Дивидендный ETF (мир)</t>
+        </is>
+      </c>
+      <c r="V12" s="26" t="n">
+        <v>0.15</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
@@ -1540,6 +5197,51 @@
       <c r="G13" s="15" t="n"/>
       <c r="H13" s="15" t="n"/>
       <c r="I13" s="15" t="n"/>
+      <c r="J13" s="15" t="n"/>
+      <c r="K13" s="15" t="inlineStr">
+        <is>
+          <t>Meta</t>
+        </is>
+      </c>
+      <c r="L13" s="15" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="M13" s="15" t="inlineStr">
+        <is>
+          <t>Акция</t>
+        </is>
+      </c>
+      <c r="N13" s="15" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="O13" s="26" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="P13" s="15" t="inlineStr">
+        <is>
+          <t>Дивиденды с 2024 года</t>
+        </is>
+      </c>
+      <c r="Q13" s="15" t="n"/>
+      <c r="R13" s="15" t="n"/>
+      <c r="S13" s="15" t="n"/>
+      <c r="T13" s="15" t="inlineStr">
+        <is>
+          <t>Агрессивный</t>
+        </is>
+      </c>
+      <c r="U13" s="15" t="inlineStr">
+        <is>
+          <t>Bitcoin</t>
+        </is>
+      </c>
+      <c r="V13" s="26" t="n">
+        <v>0.1</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
@@ -1555,6 +5257,51 @@
       <c r="G14" s="15" t="n"/>
       <c r="H14" s="15" t="n"/>
       <c r="I14" s="15" t="n"/>
+      <c r="J14" s="15" t="n"/>
+      <c r="K14" s="15" t="inlineStr">
+        <is>
+          <t>Tesla</t>
+        </is>
+      </c>
+      <c r="L14" s="15" t="inlineStr">
+        <is>
+          <t>TSLA</t>
+        </is>
+      </c>
+      <c r="M14" s="15" t="inlineStr">
+        <is>
+          <t>Акция</t>
+        </is>
+      </c>
+      <c r="N14" s="15" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="O14" s="26" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="P14" s="15" t="inlineStr">
+        <is>
+          <t>Дивидендов не платит, доход только от роста</t>
+        </is>
+      </c>
+      <c r="Q14" s="15" t="n"/>
+      <c r="R14" s="15" t="n"/>
+      <c r="S14" s="15" t="n"/>
+      <c r="T14" s="15" t="inlineStr">
+        <is>
+          <t>Агрессивный</t>
+        </is>
+      </c>
+      <c r="U14" s="15" t="inlineStr">
+        <is>
+          <t>Ethereum</t>
+        </is>
+      </c>
+      <c r="V14" s="26" t="n">
+        <v>0.05</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="15" t="inlineStr">
@@ -1570,6 +5317,41 @@
       <c r="G15" s="15" t="n"/>
       <c r="H15" s="15" t="n"/>
       <c r="I15" s="15" t="n"/>
+      <c r="J15" s="15" t="n"/>
+      <c r="K15" s="15" t="inlineStr">
+        <is>
+          <t>Berkshire Hathaway</t>
+        </is>
+      </c>
+      <c r="L15" s="15" t="inlineStr">
+        <is>
+          <t>BRK.B</t>
+        </is>
+      </c>
+      <c r="M15" s="15" t="inlineStr">
+        <is>
+          <t>Акция</t>
+        </is>
+      </c>
+      <c r="N15" s="15" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="O15" s="26" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="P15" s="15" t="inlineStr">
+        <is>
+          <t>Дивидендов не платит</t>
+        </is>
+      </c>
+      <c r="Q15" s="15" t="n"/>
+      <c r="R15" s="15" t="n"/>
+      <c r="S15" s="15" t="n"/>
+      <c r="T15" s="15" t="n"/>
+      <c r="U15" s="15" t="n"/>
+      <c r="V15" s="15" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="15" t="inlineStr">
@@ -1585,6 +5367,41 @@
       <c r="G16" s="15" t="n"/>
       <c r="H16" s="15" t="n"/>
       <c r="I16" s="15" t="n"/>
+      <c r="J16" s="15" t="n"/>
+      <c r="K16" s="15" t="inlineStr">
+        <is>
+          <t>Coca-Cola</t>
+        </is>
+      </c>
+      <c r="L16" s="15" t="inlineStr">
+        <is>
+          <t>KO</t>
+        </is>
+      </c>
+      <c r="M16" s="15" t="inlineStr">
+        <is>
+          <t>Акция</t>
+        </is>
+      </c>
+      <c r="N16" s="15" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="O16" s="26" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="P16" s="15" t="inlineStr">
+        <is>
+          <t>Платит дивиденды</t>
+        </is>
+      </c>
+      <c r="Q16" s="15" t="n"/>
+      <c r="R16" s="15" t="n"/>
+      <c r="S16" s="15" t="n"/>
+      <c r="T16" s="15" t="n"/>
+      <c r="U16" s="15" t="n"/>
+      <c r="V16" s="15" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="15" t="inlineStr">
@@ -1600,6 +5417,41 @@
       <c r="G17" s="15" t="n"/>
       <c r="H17" s="15" t="n"/>
       <c r="I17" s="15" t="n"/>
+      <c r="J17" s="15" t="n"/>
+      <c r="K17" s="15" t="inlineStr">
+        <is>
+          <t>Johnson &amp; Johnson</t>
+        </is>
+      </c>
+      <c r="L17" s="15" t="inlineStr">
+        <is>
+          <t>JNJ</t>
+        </is>
+      </c>
+      <c r="M17" s="15" t="inlineStr">
+        <is>
+          <t>Акция</t>
+        </is>
+      </c>
+      <c r="N17" s="15" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="O17" s="26" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="P17" s="15" t="inlineStr">
+        <is>
+          <t>Платит дивиденды</t>
+        </is>
+      </c>
+      <c r="Q17" s="15" t="n"/>
+      <c r="R17" s="15" t="n"/>
+      <c r="S17" s="15" t="n"/>
+      <c r="T17" s="15" t="n"/>
+      <c r="U17" s="15" t="n"/>
+      <c r="V17" s="15" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="15" t="inlineStr">
@@ -1615,6 +5467,41 @@
       <c r="G18" s="15" t="n"/>
       <c r="H18" s="15" t="n"/>
       <c r="I18" s="15" t="n"/>
+      <c r="J18" s="15" t="n"/>
+      <c r="K18" s="15" t="inlineStr">
+        <is>
+          <t>ASML</t>
+        </is>
+      </c>
+      <c r="L18" s="15" t="inlineStr">
+        <is>
+          <t>ASML</t>
+        </is>
+      </c>
+      <c r="M18" s="15" t="inlineStr">
+        <is>
+          <t>Акция</t>
+        </is>
+      </c>
+      <c r="N18" s="15" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="O18" s="26" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="P18" s="15" t="inlineStr">
+        <is>
+          <t>Платит дивиденды; европейская компания</t>
+        </is>
+      </c>
+      <c r="Q18" s="15" t="n"/>
+      <c r="R18" s="15" t="n"/>
+      <c r="S18" s="15" t="n"/>
+      <c r="T18" s="15" t="n"/>
+      <c r="U18" s="15" t="n"/>
+      <c r="V18" s="15" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="15" t="inlineStr">
@@ -1630,6 +5517,133 @@
       <c r="G19" s="15" t="n"/>
       <c r="H19" s="15" t="n"/>
       <c r="I19" s="15" t="n"/>
+      <c r="J19" s="15" t="n"/>
+      <c r="K19" s="15" t="inlineStr">
+        <is>
+          <t>Bitcoin</t>
+        </is>
+      </c>
+      <c r="L19" s="15" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="M19" s="15" t="inlineStr">
+        <is>
+          <t>Крипто</t>
+        </is>
+      </c>
+      <c r="N19" s="15" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="O19" s="26" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="P19" s="15" t="inlineStr">
+        <is>
+          <t>Не даёт дохода, только рост цены</t>
+        </is>
+      </c>
+      <c r="Q19" s="15" t="n"/>
+      <c r="R19" s="15" t="n"/>
+      <c r="S19" s="15" t="n"/>
+      <c r="T19" s="15" t="n"/>
+      <c r="U19" s="15" t="n"/>
+      <c r="V19" s="15" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="15" t="n"/>
+      <c r="B20" s="15" t="n"/>
+      <c r="C20" s="15" t="n"/>
+      <c r="D20" s="15" t="n"/>
+      <c r="E20" s="15" t="n"/>
+      <c r="F20" s="15" t="n"/>
+      <c r="G20" s="15" t="n"/>
+      <c r="H20" s="15" t="n"/>
+      <c r="I20" s="15" t="n"/>
+      <c r="J20" s="15" t="n"/>
+      <c r="K20" s="15" t="inlineStr">
+        <is>
+          <t>Ethereum</t>
+        </is>
+      </c>
+      <c r="L20" s="15" t="inlineStr">
+        <is>
+          <t>ETH</t>
+        </is>
+      </c>
+      <c r="M20" s="15" t="inlineStr">
+        <is>
+          <t>Крипто</t>
+        </is>
+      </c>
+      <c r="N20" s="15" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="O20" s="26" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="P20" s="15" t="inlineStr">
+        <is>
+          <t>Стейкинг даёт доход, но это не дивиденды</t>
+        </is>
+      </c>
+      <c r="Q20" s="15" t="n"/>
+      <c r="R20" s="15" t="n"/>
+      <c r="S20" s="15" t="n"/>
+      <c r="T20" s="15" t="n"/>
+      <c r="U20" s="15" t="n"/>
+      <c r="V20" s="15" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="15" t="n"/>
+      <c r="B21" s="15" t="n"/>
+      <c r="C21" s="15" t="n"/>
+      <c r="D21" s="15" t="n"/>
+      <c r="E21" s="15" t="n"/>
+      <c r="F21" s="15" t="n"/>
+      <c r="G21" s="15" t="n"/>
+      <c r="H21" s="15" t="n"/>
+      <c r="I21" s="15" t="n"/>
+      <c r="J21" s="15" t="n"/>
+      <c r="K21" s="15" t="inlineStr">
+        <is>
+          <t>Solana</t>
+        </is>
+      </c>
+      <c r="L21" s="15" t="inlineStr">
+        <is>
+          <t>SOL</t>
+        </is>
+      </c>
+      <c r="M21" s="15" t="inlineStr">
+        <is>
+          <t>Крипто</t>
+        </is>
+      </c>
+      <c r="N21" s="15" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="O21" s="26" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="P21" s="15" t="inlineStr">
+        <is>
+          <t>Стейкинг даёт доход, но это не дивиденды</t>
+        </is>
+      </c>
+      <c r="Q21" s="15" t="n"/>
+      <c r="R21" s="15" t="n"/>
+      <c r="S21" s="15" t="n"/>
+      <c r="T21" s="15" t="n"/>
+      <c r="U21" s="15" t="n"/>
+      <c r="V21" s="15" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2100,20 +6114,60 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="21" t="n"/>
-      <c r="B2" s="15" t="n"/>
-      <c r="C2" s="15" t="n"/>
-      <c r="D2" s="22" t="n"/>
-      <c r="E2" s="15" t="n"/>
-      <c r="F2" s="15" t="n"/>
+      <c r="A2" s="21" t="n">
+        <v>46324</v>
+      </c>
+      <c r="B2" s="15" t="inlineStr">
+        <is>
+          <t>Расход</t>
+        </is>
+      </c>
+      <c r="C2" s="15" t="inlineStr">
+        <is>
+          <t>Продукты</t>
+        </is>
+      </c>
+      <c r="D2" s="22" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="E2" s="15" t="inlineStr">
+        <is>
+          <t>Основной счёт</t>
+        </is>
+      </c>
+      <c r="F2" s="15" t="inlineStr">
+        <is>
+          <t>Coca-Cola, шоколадка, покушать</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="21" t="n"/>
-      <c r="B3" s="15" t="n"/>
-      <c r="C3" s="15" t="n"/>
-      <c r="D3" s="22" t="n"/>
-      <c r="E3" s="15" t="n"/>
-      <c r="F3" s="15" t="n"/>
+      <c r="A3" s="21" t="n">
+        <v>46324</v>
+      </c>
+      <c r="B3" s="15" t="inlineStr">
+        <is>
+          <t>Расход</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>Транспорт</t>
+        </is>
+      </c>
+      <c r="D3" s="22" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="E3" s="15" t="inlineStr">
+        <is>
+          <t>Основной счёт</t>
+        </is>
+      </c>
+      <c r="F3" s="15" t="inlineStr">
+        <is>
+          <t>EasyPark Italia</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="21" t="n"/>
@@ -33368,3048 +37422,880 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D501"/>
+  <dimension ref="A1:G38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="34" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="14" t="inlineStr">
         <is>
-          <t>Тип актива</t>
+          <t>Портфель и прогноз</t>
         </is>
       </c>
-      <c r="B1" s="14" t="inlineStr">
-        <is>
-          <t>Название</t>
-        </is>
-      </c>
-      <c r="C1" s="14" t="inlineStr">
-        <is>
-          <t>Стоимость (€)</t>
-        </is>
-      </c>
-      <c r="D1" s="14" t="inlineStr">
-        <is>
-          <t>Дата обновления</t>
-        </is>
-      </c>
+      <c r="B1" s="4" t="n"/>
+      <c r="C1" s="4" t="n"/>
+      <c r="D1" s="4" t="n"/>
+      <c r="E1" s="4" t="n"/>
+      <c r="F1" s="4" t="n"/>
+      <c r="G1" s="4" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="15" t="n"/>
       <c r="B2" s="15" t="n"/>
-      <c r="C2" s="22" t="n"/>
-      <c r="D2" s="21" t="n"/>
+      <c r="C2" s="15" t="n"/>
+      <c r="D2" s="15" t="n"/>
+      <c r="E2" s="15" t="n"/>
+      <c r="F2" s="15" t="n"/>
+      <c r="G2" s="15" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="15" t="n"/>
-      <c r="B3" s="15" t="n"/>
-      <c r="C3" s="22" t="n"/>
-      <c r="D3" s="21" t="n"/>
+      <c r="A3" s="15" t="inlineStr">
+        <is>
+          <t>Портфель (выберите из списка)</t>
+        </is>
+      </c>
+      <c r="B3" s="16" t="inlineStr">
+        <is>
+          <t>Баланс</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="n"/>
+      <c r="D3" s="15" t="n"/>
+      <c r="E3" s="15" t="n"/>
+      <c r="F3" s="15" t="n"/>
+      <c r="G3" s="15" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="15" t="n"/>
-      <c r="B4" s="15" t="n"/>
-      <c r="C4" s="22" t="n"/>
-      <c r="D4" s="21" t="n"/>
+      <c r="A4" s="15" t="inlineStr">
+        <is>
+          <t>Сумма в месяц, €</t>
+        </is>
+      </c>
+      <c r="B4" s="17" t="n">
+        <v>500</v>
+      </c>
+      <c r="C4" s="15" t="n"/>
+      <c r="D4" s="15" t="n"/>
+      <c r="E4" s="15" t="n"/>
+      <c r="F4" s="15" t="n"/>
+      <c r="G4" s="15" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="15" t="n"/>
-      <c r="B5" s="15" t="n"/>
-      <c r="C5" s="22" t="n"/>
-      <c r="D5" s="21" t="n"/>
+      <c r="A5" s="15" t="inlineStr">
+        <is>
+          <t>Цель: инвестиционный капитал, €</t>
+        </is>
+      </c>
+      <c r="B5" s="28">
+        <f>Настройки!B4</f>
+        <v/>
+      </c>
+      <c r="C5" s="15" t="n"/>
+      <c r="D5" s="15" t="n"/>
+      <c r="E5" s="15" t="n"/>
+      <c r="F5" s="15" t="n"/>
+      <c r="G5" s="15" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="15" t="n"/>
+      <c r="A6" s="29" t="inlineStr">
+        <is>
+          <t>Выберите «Свой» в B3 и впишите доли в колонке C. Доли в сумме должны быть 100%.</t>
+        </is>
+      </c>
       <c r="B6" s="15" t="n"/>
-      <c r="C6" s="22" t="n"/>
-      <c r="D6" s="21" t="n"/>
+      <c r="C6" s="15" t="n"/>
+      <c r="D6" s="15" t="n"/>
+      <c r="E6" s="15" t="n"/>
+      <c r="F6" s="15" t="n"/>
+      <c r="G6" s="15" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="15" t="n"/>
-      <c r="B7" s="15" t="n"/>
-      <c r="C7" s="22" t="n"/>
-      <c r="D7" s="21" t="n"/>
+      <c r="A7" s="15" t="inlineStr">
+        <is>
+          <t>Инструмент</t>
+        </is>
+      </c>
+      <c r="B7" s="15" t="inlineStr">
+        <is>
+          <t>Дивиденды / выплаты</t>
+        </is>
+      </c>
+      <c r="C7" s="15" t="inlineStr">
+        <is>
+          <t>Своя доля (для «Свой»)</t>
+        </is>
+      </c>
+      <c r="D7" s="15" t="inlineStr">
+        <is>
+          <t>Доля в портфеле</t>
+        </is>
+      </c>
+      <c r="E7" s="15" t="inlineStr">
+        <is>
+          <t>Доходность (допущение)</t>
+        </is>
+      </c>
+      <c r="F7" s="15" t="inlineStr">
+        <is>
+          <t>Вклад в доходность</t>
+        </is>
+      </c>
+      <c r="G7" s="15" t="inlineStr">
+        <is>
+          <t>В месяц, €</t>
+        </is>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" s="15" t="n"/>
-      <c r="B8" s="15" t="n"/>
-      <c r="C8" s="22" t="n"/>
-      <c r="D8" s="21" t="n"/>
+      <c r="A8" s="15">
+        <f>Списки!K2</f>
+        <v/>
+      </c>
+      <c r="B8" s="15">
+        <f>Списки!N2</f>
+        <v/>
+      </c>
+      <c r="C8" s="30" t="n"/>
+      <c r="D8" s="31">
+        <f>IF($B$3="Свой",C8,SUMIFS(Списки!$V$2:$V$15,Списки!$T$2:$T$15,$B$3,Списки!$U$2:$U$15,A8))</f>
+        <v/>
+      </c>
+      <c r="E8" s="26">
+        <f>Списки!O2</f>
+        <v/>
+      </c>
+      <c r="F8" s="32">
+        <f>D8*E8</f>
+        <v/>
+      </c>
+      <c r="G8" s="33">
+        <f>D8*$B$4</f>
+        <v/>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" s="15" t="n"/>
-      <c r="B9" s="15" t="n"/>
-      <c r="C9" s="22" t="n"/>
-      <c r="D9" s="21" t="n"/>
+      <c r="A9" s="15">
+        <f>Списки!K3</f>
+        <v/>
+      </c>
+      <c r="B9" s="15">
+        <f>Списки!N3</f>
+        <v/>
+      </c>
+      <c r="C9" s="30" t="n"/>
+      <c r="D9" s="31">
+        <f>IF($B$3="Свой",C9,SUMIFS(Списки!$V$2:$V$15,Списки!$T$2:$T$15,$B$3,Списки!$U$2:$U$15,A9))</f>
+        <v/>
+      </c>
+      <c r="E9" s="26">
+        <f>Списки!O3</f>
+        <v/>
+      </c>
+      <c r="F9" s="32">
+        <f>D9*E9</f>
+        <v/>
+      </c>
+      <c r="G9" s="33">
+        <f>D9*$B$4</f>
+        <v/>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" s="15" t="n"/>
-      <c r="B10" s="15" t="n"/>
-      <c r="C10" s="22" t="n"/>
-      <c r="D10" s="21" t="n"/>
+      <c r="A10" s="15">
+        <f>Списки!K4</f>
+        <v/>
+      </c>
+      <c r="B10" s="15">
+        <f>Списки!N4</f>
+        <v/>
+      </c>
+      <c r="C10" s="30" t="n"/>
+      <c r="D10" s="31">
+        <f>IF($B$3="Свой",C10,SUMIFS(Списки!$V$2:$V$15,Списки!$T$2:$T$15,$B$3,Списки!$U$2:$U$15,A10))</f>
+        <v/>
+      </c>
+      <c r="E10" s="26">
+        <f>Списки!O4</f>
+        <v/>
+      </c>
+      <c r="F10" s="32">
+        <f>D10*E10</f>
+        <v/>
+      </c>
+      <c r="G10" s="33">
+        <f>D10*$B$4</f>
+        <v/>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" s="15" t="n"/>
-      <c r="B11" s="15" t="n"/>
-      <c r="C11" s="22" t="n"/>
-      <c r="D11" s="21" t="n"/>
+      <c r="A11" s="15">
+        <f>Списки!K5</f>
+        <v/>
+      </c>
+      <c r="B11" s="15">
+        <f>Списки!N5</f>
+        <v/>
+      </c>
+      <c r="C11" s="30" t="n"/>
+      <c r="D11" s="31">
+        <f>IF($B$3="Свой",C11,SUMIFS(Списки!$V$2:$V$15,Списки!$T$2:$T$15,$B$3,Списки!$U$2:$U$15,A11))</f>
+        <v/>
+      </c>
+      <c r="E11" s="26">
+        <f>Списки!O5</f>
+        <v/>
+      </c>
+      <c r="F11" s="32">
+        <f>D11*E11</f>
+        <v/>
+      </c>
+      <c r="G11" s="33">
+        <f>D11*$B$4</f>
+        <v/>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" s="15" t="n"/>
-      <c r="B12" s="15" t="n"/>
-      <c r="C12" s="22" t="n"/>
-      <c r="D12" s="21" t="n"/>
+      <c r="A12" s="15">
+        <f>Списки!K6</f>
+        <v/>
+      </c>
+      <c r="B12" s="15">
+        <f>Списки!N6</f>
+        <v/>
+      </c>
+      <c r="C12" s="30" t="n"/>
+      <c r="D12" s="31">
+        <f>IF($B$3="Свой",C12,SUMIFS(Списки!$V$2:$V$15,Списки!$T$2:$T$15,$B$3,Списки!$U$2:$U$15,A12))</f>
+        <v/>
+      </c>
+      <c r="E12" s="26">
+        <f>Списки!O6</f>
+        <v/>
+      </c>
+      <c r="F12" s="32">
+        <f>D12*E12</f>
+        <v/>
+      </c>
+      <c r="G12" s="33">
+        <f>D12*$B$4</f>
+        <v/>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" s="15" t="n"/>
-      <c r="B13" s="15" t="n"/>
-      <c r="C13" s="22" t="n"/>
-      <c r="D13" s="21" t="n"/>
+      <c r="A13" s="15">
+        <f>Списки!K7</f>
+        <v/>
+      </c>
+      <c r="B13" s="15">
+        <f>Списки!N7</f>
+        <v/>
+      </c>
+      <c r="C13" s="30" t="n"/>
+      <c r="D13" s="31">
+        <f>IF($B$3="Свой",C13,SUMIFS(Списки!$V$2:$V$15,Списки!$T$2:$T$15,$B$3,Списки!$U$2:$U$15,A13))</f>
+        <v/>
+      </c>
+      <c r="E13" s="26">
+        <f>Списки!O7</f>
+        <v/>
+      </c>
+      <c r="F13" s="32">
+        <f>D13*E13</f>
+        <v/>
+      </c>
+      <c r="G13" s="33">
+        <f>D13*$B$4</f>
+        <v/>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" s="15" t="n"/>
-      <c r="B14" s="15" t="n"/>
-      <c r="C14" s="22" t="n"/>
-      <c r="D14" s="21" t="n"/>
+      <c r="A14" s="15">
+        <f>Списки!K8</f>
+        <v/>
+      </c>
+      <c r="B14" s="15">
+        <f>Списки!N8</f>
+        <v/>
+      </c>
+      <c r="C14" s="30" t="n"/>
+      <c r="D14" s="31">
+        <f>IF($B$3="Свой",C14,SUMIFS(Списки!$V$2:$V$15,Списки!$T$2:$T$15,$B$3,Списки!$U$2:$U$15,A14))</f>
+        <v/>
+      </c>
+      <c r="E14" s="26">
+        <f>Списки!O8</f>
+        <v/>
+      </c>
+      <c r="F14" s="32">
+        <f>D14*E14</f>
+        <v/>
+      </c>
+      <c r="G14" s="33">
+        <f>D14*$B$4</f>
+        <v/>
+      </c>
     </row>
     <row r="15">
-      <c r="A15" s="15" t="n"/>
-      <c r="B15" s="15" t="n"/>
-      <c r="C15" s="22" t="n"/>
-      <c r="D15" s="21" t="n"/>
+      <c r="A15" s="15">
+        <f>Списки!K9</f>
+        <v/>
+      </c>
+      <c r="B15" s="15">
+        <f>Списки!N9</f>
+        <v/>
+      </c>
+      <c r="C15" s="30" t="n"/>
+      <c r="D15" s="31">
+        <f>IF($B$3="Свой",C15,SUMIFS(Списки!$V$2:$V$15,Списки!$T$2:$T$15,$B$3,Списки!$U$2:$U$15,A15))</f>
+        <v/>
+      </c>
+      <c r="E15" s="26">
+        <f>Списки!O9</f>
+        <v/>
+      </c>
+      <c r="F15" s="32">
+        <f>D15*E15</f>
+        <v/>
+      </c>
+      <c r="G15" s="33">
+        <f>D15*$B$4</f>
+        <v/>
+      </c>
     </row>
     <row r="16">
-      <c r="A16" s="15" t="n"/>
-      <c r="B16" s="15" t="n"/>
-      <c r="C16" s="22" t="n"/>
-      <c r="D16" s="21" t="n"/>
+      <c r="A16" s="15">
+        <f>Списки!K10</f>
+        <v/>
+      </c>
+      <c r="B16" s="15">
+        <f>Списки!N10</f>
+        <v/>
+      </c>
+      <c r="C16" s="30" t="n"/>
+      <c r="D16" s="31">
+        <f>IF($B$3="Свой",C16,SUMIFS(Списки!$V$2:$V$15,Списки!$T$2:$T$15,$B$3,Списки!$U$2:$U$15,A16))</f>
+        <v/>
+      </c>
+      <c r="E16" s="26">
+        <f>Списки!O10</f>
+        <v/>
+      </c>
+      <c r="F16" s="32">
+        <f>D16*E16</f>
+        <v/>
+      </c>
+      <c r="G16" s="33">
+        <f>D16*$B$4</f>
+        <v/>
+      </c>
     </row>
     <row r="17">
-      <c r="A17" s="15" t="n"/>
-      <c r="B17" s="15" t="n"/>
-      <c r="C17" s="22" t="n"/>
-      <c r="D17" s="21" t="n"/>
+      <c r="A17" s="15">
+        <f>Списки!K11</f>
+        <v/>
+      </c>
+      <c r="B17" s="15">
+        <f>Списки!N11</f>
+        <v/>
+      </c>
+      <c r="C17" s="30" t="n"/>
+      <c r="D17" s="31">
+        <f>IF($B$3="Свой",C17,SUMIFS(Списки!$V$2:$V$15,Списки!$T$2:$T$15,$B$3,Списки!$U$2:$U$15,A17))</f>
+        <v/>
+      </c>
+      <c r="E17" s="26">
+        <f>Списки!O11</f>
+        <v/>
+      </c>
+      <c r="F17" s="32">
+        <f>D17*E17</f>
+        <v/>
+      </c>
+      <c r="G17" s="33">
+        <f>D17*$B$4</f>
+        <v/>
+      </c>
     </row>
     <row r="18">
-      <c r="A18" s="15" t="n"/>
-      <c r="B18" s="15" t="n"/>
-      <c r="C18" s="22" t="n"/>
-      <c r="D18" s="21" t="n"/>
+      <c r="A18" s="15">
+        <f>Списки!K12</f>
+        <v/>
+      </c>
+      <c r="B18" s="15">
+        <f>Списки!N12</f>
+        <v/>
+      </c>
+      <c r="C18" s="30" t="n"/>
+      <c r="D18" s="31">
+        <f>IF($B$3="Свой",C18,SUMIFS(Списки!$V$2:$V$15,Списки!$T$2:$T$15,$B$3,Списки!$U$2:$U$15,A18))</f>
+        <v/>
+      </c>
+      <c r="E18" s="26">
+        <f>Списки!O12</f>
+        <v/>
+      </c>
+      <c r="F18" s="32">
+        <f>D18*E18</f>
+        <v/>
+      </c>
+      <c r="G18" s="33">
+        <f>D18*$B$4</f>
+        <v/>
+      </c>
     </row>
     <row r="19">
-      <c r="A19" s="15" t="n"/>
-      <c r="B19" s="15" t="n"/>
-      <c r="C19" s="22" t="n"/>
-      <c r="D19" s="21" t="n"/>
+      <c r="A19" s="15">
+        <f>Списки!K13</f>
+        <v/>
+      </c>
+      <c r="B19" s="15">
+        <f>Списки!N13</f>
+        <v/>
+      </c>
+      <c r="C19" s="30" t="n"/>
+      <c r="D19" s="31">
+        <f>IF($B$3="Свой",C19,SUMIFS(Списки!$V$2:$V$15,Списки!$T$2:$T$15,$B$3,Списки!$U$2:$U$15,A19))</f>
+        <v/>
+      </c>
+      <c r="E19" s="26">
+        <f>Списки!O13</f>
+        <v/>
+      </c>
+      <c r="F19" s="32">
+        <f>D19*E19</f>
+        <v/>
+      </c>
+      <c r="G19" s="33">
+        <f>D19*$B$4</f>
+        <v/>
+      </c>
     </row>
     <row r="20">
-      <c r="A20" s="15" t="n"/>
-      <c r="B20" s="15" t="n"/>
-      <c r="C20" s="22" t="n"/>
-      <c r="D20" s="21" t="n"/>
+      <c r="A20" s="15">
+        <f>Списки!K14</f>
+        <v/>
+      </c>
+      <c r="B20" s="15">
+        <f>Списки!N14</f>
+        <v/>
+      </c>
+      <c r="C20" s="30" t="n"/>
+      <c r="D20" s="31">
+        <f>IF($B$3="Свой",C20,SUMIFS(Списки!$V$2:$V$15,Списки!$T$2:$T$15,$B$3,Списки!$U$2:$U$15,A20))</f>
+        <v/>
+      </c>
+      <c r="E20" s="26">
+        <f>Списки!O14</f>
+        <v/>
+      </c>
+      <c r="F20" s="32">
+        <f>D20*E20</f>
+        <v/>
+      </c>
+      <c r="G20" s="33">
+        <f>D20*$B$4</f>
+        <v/>
+      </c>
     </row>
     <row r="21">
-      <c r="A21" s="15" t="n"/>
-      <c r="B21" s="15" t="n"/>
-      <c r="C21" s="22" t="n"/>
-      <c r="D21" s="21" t="n"/>
+      <c r="A21" s="15">
+        <f>Списки!K15</f>
+        <v/>
+      </c>
+      <c r="B21" s="15">
+        <f>Списки!N15</f>
+        <v/>
+      </c>
+      <c r="C21" s="30" t="n"/>
+      <c r="D21" s="31">
+        <f>IF($B$3="Свой",C21,SUMIFS(Списки!$V$2:$V$15,Списки!$T$2:$T$15,$B$3,Списки!$U$2:$U$15,A21))</f>
+        <v/>
+      </c>
+      <c r="E21" s="26">
+        <f>Списки!O15</f>
+        <v/>
+      </c>
+      <c r="F21" s="32">
+        <f>D21*E21</f>
+        <v/>
+      </c>
+      <c r="G21" s="33">
+        <f>D21*$B$4</f>
+        <v/>
+      </c>
     </row>
     <row r="22">
-      <c r="A22" s="15" t="n"/>
-      <c r="B22" s="15" t="n"/>
-      <c r="C22" s="22" t="n"/>
-      <c r="D22" s="21" t="n"/>
+      <c r="A22" s="15">
+        <f>Списки!K16</f>
+        <v/>
+      </c>
+      <c r="B22" s="15">
+        <f>Списки!N16</f>
+        <v/>
+      </c>
+      <c r="C22" s="30" t="n"/>
+      <c r="D22" s="31">
+        <f>IF($B$3="Свой",C22,SUMIFS(Списки!$V$2:$V$15,Списки!$T$2:$T$15,$B$3,Списки!$U$2:$U$15,A22))</f>
+        <v/>
+      </c>
+      <c r="E22" s="26">
+        <f>Списки!O16</f>
+        <v/>
+      </c>
+      <c r="F22" s="32">
+        <f>D22*E22</f>
+        <v/>
+      </c>
+      <c r="G22" s="33">
+        <f>D22*$B$4</f>
+        <v/>
+      </c>
     </row>
     <row r="23">
-      <c r="A23" s="15" t="n"/>
-      <c r="B23" s="15" t="n"/>
-      <c r="C23" s="22" t="n"/>
-      <c r="D23" s="21" t="n"/>
+      <c r="A23" s="15">
+        <f>Списки!K17</f>
+        <v/>
+      </c>
+      <c r="B23" s="15">
+        <f>Списки!N17</f>
+        <v/>
+      </c>
+      <c r="C23" s="30" t="n"/>
+      <c r="D23" s="31">
+        <f>IF($B$3="Свой",C23,SUMIFS(Списки!$V$2:$V$15,Списки!$T$2:$T$15,$B$3,Списки!$U$2:$U$15,A23))</f>
+        <v/>
+      </c>
+      <c r="E23" s="26">
+        <f>Списки!O17</f>
+        <v/>
+      </c>
+      <c r="F23" s="32">
+        <f>D23*E23</f>
+        <v/>
+      </c>
+      <c r="G23" s="33">
+        <f>D23*$B$4</f>
+        <v/>
+      </c>
     </row>
     <row r="24">
-      <c r="A24" s="15" t="n"/>
-      <c r="B24" s="15" t="n"/>
-      <c r="C24" s="22" t="n"/>
-      <c r="D24" s="21" t="n"/>
+      <c r="A24" s="15">
+        <f>Списки!K18</f>
+        <v/>
+      </c>
+      <c r="B24" s="15">
+        <f>Списки!N18</f>
+        <v/>
+      </c>
+      <c r="C24" s="30" t="n"/>
+      <c r="D24" s="31">
+        <f>IF($B$3="Свой",C24,SUMIFS(Списки!$V$2:$V$15,Списки!$T$2:$T$15,$B$3,Списки!$U$2:$U$15,A24))</f>
+        <v/>
+      </c>
+      <c r="E24" s="26">
+        <f>Списки!O18</f>
+        <v/>
+      </c>
+      <c r="F24" s="32">
+        <f>D24*E24</f>
+        <v/>
+      </c>
+      <c r="G24" s="33">
+        <f>D24*$B$4</f>
+        <v/>
+      </c>
     </row>
     <row r="25">
-      <c r="A25" s="15" t="n"/>
-      <c r="B25" s="15" t="n"/>
-      <c r="C25" s="22" t="n"/>
-      <c r="D25" s="21" t="n"/>
+      <c r="A25" s="15">
+        <f>Списки!K19</f>
+        <v/>
+      </c>
+      <c r="B25" s="15">
+        <f>Списки!N19</f>
+        <v/>
+      </c>
+      <c r="C25" s="30" t="n"/>
+      <c r="D25" s="31">
+        <f>IF($B$3="Свой",C25,SUMIFS(Списки!$V$2:$V$15,Списки!$T$2:$T$15,$B$3,Списки!$U$2:$U$15,A25))</f>
+        <v/>
+      </c>
+      <c r="E25" s="26">
+        <f>Списки!O19</f>
+        <v/>
+      </c>
+      <c r="F25" s="32">
+        <f>D25*E25</f>
+        <v/>
+      </c>
+      <c r="G25" s="33">
+        <f>D25*$B$4</f>
+        <v/>
+      </c>
     </row>
     <row r="26">
-      <c r="A26" s="15" t="n"/>
-      <c r="B26" s="15" t="n"/>
-      <c r="C26" s="22" t="n"/>
-      <c r="D26" s="21" t="n"/>
+      <c r="A26" s="15">
+        <f>Списки!K20</f>
+        <v/>
+      </c>
+      <c r="B26" s="15">
+        <f>Списки!N20</f>
+        <v/>
+      </c>
+      <c r="C26" s="30" t="n"/>
+      <c r="D26" s="31">
+        <f>IF($B$3="Свой",C26,SUMIFS(Списки!$V$2:$V$15,Списки!$T$2:$T$15,$B$3,Списки!$U$2:$U$15,A26))</f>
+        <v/>
+      </c>
+      <c r="E26" s="26">
+        <f>Списки!O20</f>
+        <v/>
+      </c>
+      <c r="F26" s="32">
+        <f>D26*E26</f>
+        <v/>
+      </c>
+      <c r="G26" s="33">
+        <f>D26*$B$4</f>
+        <v/>
+      </c>
     </row>
     <row r="27">
-      <c r="A27" s="15" t="n"/>
-      <c r="B27" s="15" t="n"/>
-      <c r="C27" s="22" t="n"/>
-      <c r="D27" s="21" t="n"/>
+      <c r="A27" s="15">
+        <f>Списки!K21</f>
+        <v/>
+      </c>
+      <c r="B27" s="15">
+        <f>Списки!N21</f>
+        <v/>
+      </c>
+      <c r="C27" s="30" t="n"/>
+      <c r="D27" s="31">
+        <f>IF($B$3="Свой",C27,SUMIFS(Списки!$V$2:$V$15,Списки!$T$2:$T$15,$B$3,Списки!$U$2:$U$15,A27))</f>
+        <v/>
+      </c>
+      <c r="E27" s="26">
+        <f>Списки!O21</f>
+        <v/>
+      </c>
+      <c r="F27" s="32">
+        <f>D27*E27</f>
+        <v/>
+      </c>
+      <c r="G27" s="33">
+        <f>D27*$B$4</f>
+        <v/>
+      </c>
     </row>
     <row r="28">
-      <c r="A28" s="15" t="n"/>
+      <c r="A28" s="15" t="inlineStr">
+        <is>
+          <t>Итого</t>
+        </is>
+      </c>
       <c r="B28" s="15" t="n"/>
-      <c r="C28" s="22" t="n"/>
-      <c r="D28" s="21" t="n"/>
+      <c r="C28" s="15" t="n"/>
+      <c r="D28" s="26">
+        <f>SUM(D8:D27)</f>
+        <v/>
+      </c>
+      <c r="E28" s="15">
+        <f>IF(ROUND(D28,4)=1,"OK, 100%","Сумма долей должна быть 100%")</f>
+        <v/>
+      </c>
+      <c r="F28" s="34">
+        <f>SUM(F8:F27)</f>
+        <v/>
+      </c>
+      <c r="G28" s="22">
+        <f>SUM(G8:G27)</f>
+        <v/>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="15" t="n"/>
       <c r="B29" s="15" t="n"/>
-      <c r="C29" s="22" t="n"/>
-      <c r="D29" s="21" t="n"/>
+      <c r="C29" s="15" t="n"/>
+      <c r="D29" s="15" t="n"/>
+      <c r="E29" s="15" t="n"/>
+      <c r="F29" s="15" t="n"/>
+      <c r="G29" s="15" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="15" t="n"/>
-      <c r="B30" s="15" t="n"/>
-      <c r="C30" s="22" t="n"/>
-      <c r="D30" s="21" t="n"/>
+      <c r="A30" s="15" t="inlineStr">
+        <is>
+          <t>Ожидаемая доходность портфеля в год</t>
+        </is>
+      </c>
+      <c r="B30" s="34">
+        <f>F28</f>
+        <v/>
+      </c>
+      <c r="C30" s="15" t="n"/>
+      <c r="D30" s="15" t="n"/>
+      <c r="E30" s="15" t="n"/>
+      <c r="F30" s="15" t="n"/>
+      <c r="G30" s="15" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="15" t="n"/>
       <c r="B31" s="15" t="n"/>
-      <c r="C31" s="22" t="n"/>
-      <c r="D31" s="21" t="n"/>
+      <c r="C31" s="15" t="n"/>
+      <c r="D31" s="15" t="n"/>
+      <c r="E31" s="15" t="n"/>
+      <c r="F31" s="15" t="n"/>
+      <c r="G31" s="15" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="15" t="n"/>
+      <c r="A32" s="15" t="inlineStr">
+        <is>
+          <t>Прогноз</t>
+        </is>
+      </c>
       <c r="B32" s="15" t="n"/>
-      <c r="C32" s="22" t="n"/>
-      <c r="D32" s="21" t="n"/>
+      <c r="C32" s="15" t="n"/>
+      <c r="D32" s="15" t="n"/>
+      <c r="E32" s="15" t="n"/>
+      <c r="F32" s="15" t="n"/>
+      <c r="G32" s="15" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="15" t="n"/>
-      <c r="B33" s="15" t="n"/>
-      <c r="C33" s="22" t="n"/>
-      <c r="D33" s="21" t="n"/>
+      <c r="A33" s="15" t="inlineStr">
+        <is>
+          <t>Возраст</t>
+        </is>
+      </c>
+      <c r="B33" s="15" t="inlineStr">
+        <is>
+          <t>Лет</t>
+        </is>
+      </c>
+      <c r="C33" s="15" t="inlineStr">
+        <is>
+          <t>Вложено всего, €</t>
+        </is>
+      </c>
+      <c r="D33" s="15" t="inlineStr">
+        <is>
+          <t>Итог с доходностью, €</t>
+        </is>
+      </c>
+      <c r="E33" s="15" t="inlineStr">
+        <is>
+          <t>Доход от роста, €</t>
+        </is>
+      </c>
+      <c r="F33" s="15" t="n"/>
+      <c r="G33" s="15" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="15" t="n"/>
-      <c r="B34" s="15" t="n"/>
-      <c r="C34" s="22" t="n"/>
-      <c r="D34" s="21" t="n"/>
+      <c r="A34" s="15">
+        <f>Настройки!$B$2+B34</f>
+        <v/>
+      </c>
+      <c r="B34" s="15">
+        <f>MAX(0,Настройки!B3-Настройки!B2)</f>
+        <v/>
+      </c>
+      <c r="C34" s="28">
+        <f>$B$4*12*B34</f>
+        <v/>
+      </c>
+      <c r="D34" s="28">
+        <f>IF($B$30=0,"",$B$4*((1+$B$30)^B34-1)/((1+$B$30)^(1/12)-1))</f>
+        <v/>
+      </c>
+      <c r="E34" s="28">
+        <f>IF(D34="","",D34-C34)</f>
+        <v/>
+      </c>
+      <c r="F34" s="15" t="n"/>
+      <c r="G34" s="15" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="15" t="n"/>
-      <c r="B35" s="15" t="n"/>
-      <c r="C35" s="22" t="n"/>
-      <c r="D35" s="21" t="n"/>
+      <c r="A35" s="15">
+        <f>Настройки!$B$2+B35</f>
+        <v/>
+      </c>
+      <c r="B35" s="15">
+        <f>B34+5</f>
+        <v/>
+      </c>
+      <c r="C35" s="28">
+        <f>$B$4*12*B35</f>
+        <v/>
+      </c>
+      <c r="D35" s="28">
+        <f>IF($B$30=0,"",$B$4*((1+$B$30)^B35-1)/((1+$B$30)^(1/12)-1))</f>
+        <v/>
+      </c>
+      <c r="E35" s="28">
+        <f>IF(D35="","",D35-C35)</f>
+        <v/>
+      </c>
+      <c r="F35" s="15" t="n"/>
+      <c r="G35" s="15" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="15" t="n"/>
-      <c r="B36" s="15" t="n"/>
-      <c r="C36" s="22" t="n"/>
-      <c r="D36" s="21" t="n"/>
+      <c r="A36" s="15">
+        <f>Настройки!$B$2+B36</f>
+        <v/>
+      </c>
+      <c r="B36" s="15">
+        <f>B34+10</f>
+        <v/>
+      </c>
+      <c r="C36" s="28">
+        <f>$B$4*12*B36</f>
+        <v/>
+      </c>
+      <c r="D36" s="28">
+        <f>IF($B$30=0,"",$B$4*((1+$B$30)^B36-1)/((1+$B$30)^(1/12)-1))</f>
+        <v/>
+      </c>
+      <c r="E36" s="28">
+        <f>IF(D36="","",D36-C36)</f>
+        <v/>
+      </c>
+      <c r="F36" s="15" t="n"/>
+      <c r="G36" s="15" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="15" t="n"/>
       <c r="B37" s="15" t="n"/>
-      <c r="C37" s="22" t="n"/>
-      <c r="D37" s="21" t="n"/>
+      <c r="C37" s="15" t="n"/>
+      <c r="D37" s="15" t="n"/>
+      <c r="E37" s="15" t="n"/>
+      <c r="F37" s="15" t="n"/>
+      <c r="G37" s="15" t="n"/>
     </row>
     <row r="38">
-      <c r="A38" s="15" t="n"/>
-      <c r="B38" s="15" t="n"/>
-      <c r="C38" s="22" t="n"/>
-      <c r="D38" s="21" t="n"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="15" t="n"/>
-      <c r="B39" s="15" t="n"/>
-      <c r="C39" s="22" t="n"/>
-      <c r="D39" s="21" t="n"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="15" t="n"/>
-      <c r="B40" s="15" t="n"/>
-      <c r="C40" s="22" t="n"/>
-      <c r="D40" s="21" t="n"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="15" t="n"/>
-      <c r="B41" s="15" t="n"/>
-      <c r="C41" s="22" t="n"/>
-      <c r="D41" s="21" t="n"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="15" t="n"/>
-      <c r="B42" s="15" t="n"/>
-      <c r="C42" s="22" t="n"/>
-      <c r="D42" s="21" t="n"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="15" t="n"/>
-      <c r="B43" s="15" t="n"/>
-      <c r="C43" s="22" t="n"/>
-      <c r="D43" s="21" t="n"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="15" t="n"/>
-      <c r="B44" s="15" t="n"/>
-      <c r="C44" s="22" t="n"/>
-      <c r="D44" s="21" t="n"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="15" t="n"/>
-      <c r="B45" s="15" t="n"/>
-      <c r="C45" s="22" t="n"/>
-      <c r="D45" s="21" t="n"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="15" t="n"/>
-      <c r="B46" s="15" t="n"/>
-      <c r="C46" s="22" t="n"/>
-      <c r="D46" s="21" t="n"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="15" t="n"/>
-      <c r="B47" s="15" t="n"/>
-      <c r="C47" s="22" t="n"/>
-      <c r="D47" s="21" t="n"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="15" t="n"/>
-      <c r="B48" s="15" t="n"/>
-      <c r="C48" s="22" t="n"/>
-      <c r="D48" s="21" t="n"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="15" t="n"/>
-      <c r="B49" s="15" t="n"/>
-      <c r="C49" s="22" t="n"/>
-      <c r="D49" s="21" t="n"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="15" t="n"/>
-      <c r="B50" s="15" t="n"/>
-      <c r="C50" s="22" t="n"/>
-      <c r="D50" s="21" t="n"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="15" t="n"/>
-      <c r="B51" s="15" t="n"/>
-      <c r="C51" s="22" t="n"/>
-      <c r="D51" s="21" t="n"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="15" t="n"/>
-      <c r="B52" s="15" t="n"/>
-      <c r="C52" s="22" t="n"/>
-      <c r="D52" s="21" t="n"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="15" t="n"/>
-      <c r="B53" s="15" t="n"/>
-      <c r="C53" s="22" t="n"/>
-      <c r="D53" s="21" t="n"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="15" t="n"/>
-      <c r="B54" s="15" t="n"/>
-      <c r="C54" s="22" t="n"/>
-      <c r="D54" s="21" t="n"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="15" t="n"/>
-      <c r="B55" s="15" t="n"/>
-      <c r="C55" s="22" t="n"/>
-      <c r="D55" s="21" t="n"/>
-    </row>
-    <row r="56">
-      <c r="A56" s="15" t="n"/>
-      <c r="B56" s="15" t="n"/>
-      <c r="C56" s="22" t="n"/>
-      <c r="D56" s="21" t="n"/>
-    </row>
-    <row r="57">
-      <c r="A57" s="15" t="n"/>
-      <c r="B57" s="15" t="n"/>
-      <c r="C57" s="22" t="n"/>
-      <c r="D57" s="21" t="n"/>
-    </row>
-    <row r="58">
-      <c r="A58" s="15" t="n"/>
-      <c r="B58" s="15" t="n"/>
-      <c r="C58" s="22" t="n"/>
-      <c r="D58" s="21" t="n"/>
-    </row>
-    <row r="59">
-      <c r="A59" s="15" t="n"/>
-      <c r="B59" s="15" t="n"/>
-      <c r="C59" s="22" t="n"/>
-      <c r="D59" s="21" t="n"/>
-    </row>
-    <row r="60">
-      <c r="A60" s="15" t="n"/>
-      <c r="B60" s="15" t="n"/>
-      <c r="C60" s="22" t="n"/>
-      <c r="D60" s="21" t="n"/>
-    </row>
-    <row r="61">
-      <c r="A61" s="15" t="n"/>
-      <c r="B61" s="15" t="n"/>
-      <c r="C61" s="22" t="n"/>
-      <c r="D61" s="21" t="n"/>
-    </row>
-    <row r="62">
-      <c r="A62" s="15" t="n"/>
-      <c r="B62" s="15" t="n"/>
-      <c r="C62" s="22" t="n"/>
-      <c r="D62" s="21" t="n"/>
-    </row>
-    <row r="63">
-      <c r="A63" s="15" t="n"/>
-      <c r="B63" s="15" t="n"/>
-      <c r="C63" s="22" t="n"/>
-      <c r="D63" s="21" t="n"/>
-    </row>
-    <row r="64">
-      <c r="A64" s="15" t="n"/>
-      <c r="B64" s="15" t="n"/>
-      <c r="C64" s="22" t="n"/>
-      <c r="D64" s="21" t="n"/>
-    </row>
-    <row r="65">
-      <c r="A65" s="15" t="n"/>
-      <c r="B65" s="15" t="n"/>
-      <c r="C65" s="22" t="n"/>
-      <c r="D65" s="21" t="n"/>
-    </row>
-    <row r="66">
-      <c r="A66" s="15" t="n"/>
-      <c r="B66" s="15" t="n"/>
-      <c r="C66" s="22" t="n"/>
-      <c r="D66" s="21" t="n"/>
-    </row>
-    <row r="67">
-      <c r="A67" s="15" t="n"/>
-      <c r="B67" s="15" t="n"/>
-      <c r="C67" s="22" t="n"/>
-      <c r="D67" s="21" t="n"/>
-    </row>
-    <row r="68">
-      <c r="A68" s="15" t="n"/>
-      <c r="B68" s="15" t="n"/>
-      <c r="C68" s="22" t="n"/>
-      <c r="D68" s="21" t="n"/>
-    </row>
-    <row r="69">
-      <c r="A69" s="15" t="n"/>
-      <c r="B69" s="15" t="n"/>
-      <c r="C69" s="22" t="n"/>
-      <c r="D69" s="21" t="n"/>
-    </row>
-    <row r="70">
-      <c r="A70" s="15" t="n"/>
-      <c r="B70" s="15" t="n"/>
-      <c r="C70" s="22" t="n"/>
-      <c r="D70" s="21" t="n"/>
-    </row>
-    <row r="71">
-      <c r="A71" s="15" t="n"/>
-      <c r="B71" s="15" t="n"/>
-      <c r="C71" s="22" t="n"/>
-      <c r="D71" s="21" t="n"/>
-    </row>
-    <row r="72">
-      <c r="A72" s="15" t="n"/>
-      <c r="B72" s="15" t="n"/>
-      <c r="C72" s="22" t="n"/>
-      <c r="D72" s="21" t="n"/>
-    </row>
-    <row r="73">
-      <c r="A73" s="15" t="n"/>
-      <c r="B73" s="15" t="n"/>
-      <c r="C73" s="22" t="n"/>
-      <c r="D73" s="21" t="n"/>
-    </row>
-    <row r="74">
-      <c r="A74" s="15" t="n"/>
-      <c r="B74" s="15" t="n"/>
-      <c r="C74" s="22" t="n"/>
-      <c r="D74" s="21" t="n"/>
-    </row>
-    <row r="75">
-      <c r="A75" s="15" t="n"/>
-      <c r="B75" s="15" t="n"/>
-      <c r="C75" s="22" t="n"/>
-      <c r="D75" s="21" t="n"/>
-    </row>
-    <row r="76">
-      <c r="A76" s="15" t="n"/>
-      <c r="B76" s="15" t="n"/>
-      <c r="C76" s="22" t="n"/>
-      <c r="D76" s="21" t="n"/>
-    </row>
-    <row r="77">
-      <c r="A77" s="15" t="n"/>
-      <c r="B77" s="15" t="n"/>
-      <c r="C77" s="22" t="n"/>
-      <c r="D77" s="21" t="n"/>
-    </row>
-    <row r="78">
-      <c r="A78" s="15" t="n"/>
-      <c r="B78" s="15" t="n"/>
-      <c r="C78" s="22" t="n"/>
-      <c r="D78" s="21" t="n"/>
-    </row>
-    <row r="79">
-      <c r="A79" s="15" t="n"/>
-      <c r="B79" s="15" t="n"/>
-      <c r="C79" s="22" t="n"/>
-      <c r="D79" s="21" t="n"/>
-    </row>
-    <row r="80">
-      <c r="A80" s="15" t="n"/>
-      <c r="B80" s="15" t="n"/>
-      <c r="C80" s="22" t="n"/>
-      <c r="D80" s="21" t="n"/>
-    </row>
-    <row r="81">
-      <c r="A81" s="15" t="n"/>
-      <c r="B81" s="15" t="n"/>
-      <c r="C81" s="22" t="n"/>
-      <c r="D81" s="21" t="n"/>
-    </row>
-    <row r="82">
-      <c r="A82" s="15" t="n"/>
-      <c r="B82" s="15" t="n"/>
-      <c r="C82" s="22" t="n"/>
-      <c r="D82" s="21" t="n"/>
-    </row>
-    <row r="83">
-      <c r="A83" s="15" t="n"/>
-      <c r="B83" s="15" t="n"/>
-      <c r="C83" s="22" t="n"/>
-      <c r="D83" s="21" t="n"/>
-    </row>
-    <row r="84">
-      <c r="A84" s="15" t="n"/>
-      <c r="B84" s="15" t="n"/>
-      <c r="C84" s="22" t="n"/>
-      <c r="D84" s="21" t="n"/>
-    </row>
-    <row r="85">
-      <c r="A85" s="15" t="n"/>
-      <c r="B85" s="15" t="n"/>
-      <c r="C85" s="22" t="n"/>
-      <c r="D85" s="21" t="n"/>
-    </row>
-    <row r="86">
-      <c r="A86" s="15" t="n"/>
-      <c r="B86" s="15" t="n"/>
-      <c r="C86" s="22" t="n"/>
-      <c r="D86" s="21" t="n"/>
-    </row>
-    <row r="87">
-      <c r="A87" s="15" t="n"/>
-      <c r="B87" s="15" t="n"/>
-      <c r="C87" s="22" t="n"/>
-      <c r="D87" s="21" t="n"/>
-    </row>
-    <row r="88">
-      <c r="A88" s="15" t="n"/>
-      <c r="B88" s="15" t="n"/>
-      <c r="C88" s="22" t="n"/>
-      <c r="D88" s="21" t="n"/>
-    </row>
-    <row r="89">
-      <c r="A89" s="15" t="n"/>
-      <c r="B89" s="15" t="n"/>
-      <c r="C89" s="22" t="n"/>
-      <c r="D89" s="21" t="n"/>
-    </row>
-    <row r="90">
-      <c r="A90" s="15" t="n"/>
-      <c r="B90" s="15" t="n"/>
-      <c r="C90" s="22" t="n"/>
-      <c r="D90" s="21" t="n"/>
-    </row>
-    <row r="91">
-      <c r="A91" s="15" t="n"/>
-      <c r="B91" s="15" t="n"/>
-      <c r="C91" s="22" t="n"/>
-      <c r="D91" s="21" t="n"/>
-    </row>
-    <row r="92">
-      <c r="A92" s="15" t="n"/>
-      <c r="B92" s="15" t="n"/>
-      <c r="C92" s="22" t="n"/>
-      <c r="D92" s="21" t="n"/>
-    </row>
-    <row r="93">
-      <c r="A93" s="15" t="n"/>
-      <c r="B93" s="15" t="n"/>
-      <c r="C93" s="22" t="n"/>
-      <c r="D93" s="21" t="n"/>
-    </row>
-    <row r="94">
-      <c r="A94" s="15" t="n"/>
-      <c r="B94" s="15" t="n"/>
-      <c r="C94" s="22" t="n"/>
-      <c r="D94" s="21" t="n"/>
-    </row>
-    <row r="95">
-      <c r="A95" s="15" t="n"/>
-      <c r="B95" s="15" t="n"/>
-      <c r="C95" s="22" t="n"/>
-      <c r="D95" s="21" t="n"/>
-    </row>
-    <row r="96">
-      <c r="A96" s="15" t="n"/>
-      <c r="B96" s="15" t="n"/>
-      <c r="C96" s="22" t="n"/>
-      <c r="D96" s="21" t="n"/>
-    </row>
-    <row r="97">
-      <c r="A97" s="15" t="n"/>
-      <c r="B97" s="15" t="n"/>
-      <c r="C97" s="22" t="n"/>
-      <c r="D97" s="21" t="n"/>
-    </row>
-    <row r="98">
-      <c r="A98" s="15" t="n"/>
-      <c r="B98" s="15" t="n"/>
-      <c r="C98" s="22" t="n"/>
-      <c r="D98" s="21" t="n"/>
-    </row>
-    <row r="99">
-      <c r="A99" s="15" t="n"/>
-      <c r="B99" s="15" t="n"/>
-      <c r="C99" s="22" t="n"/>
-      <c r="D99" s="21" t="n"/>
-    </row>
-    <row r="100">
-      <c r="A100" s="15" t="n"/>
-      <c r="B100" s="15" t="n"/>
-      <c r="C100" s="22" t="n"/>
-      <c r="D100" s="21" t="n"/>
-    </row>
-    <row r="101">
-      <c r="A101" s="15" t="n"/>
-      <c r="B101" s="15" t="n"/>
-      <c r="C101" s="22" t="n"/>
-      <c r="D101" s="21" t="n"/>
-    </row>
-    <row r="102">
-      <c r="A102" s="15" t="n"/>
-      <c r="B102" s="15" t="n"/>
-      <c r="C102" s="22" t="n"/>
-      <c r="D102" s="21" t="n"/>
-    </row>
-    <row r="103">
-      <c r="A103" s="15" t="n"/>
-      <c r="B103" s="15" t="n"/>
-      <c r="C103" s="22" t="n"/>
-      <c r="D103" s="21" t="n"/>
-    </row>
-    <row r="104">
-      <c r="A104" s="15" t="n"/>
-      <c r="B104" s="15" t="n"/>
-      <c r="C104" s="22" t="n"/>
-      <c r="D104" s="21" t="n"/>
-    </row>
-    <row r="105">
-      <c r="A105" s="15" t="n"/>
-      <c r="B105" s="15" t="n"/>
-      <c r="C105" s="22" t="n"/>
-      <c r="D105" s="21" t="n"/>
-    </row>
-    <row r="106">
-      <c r="A106" s="15" t="n"/>
-      <c r="B106" s="15" t="n"/>
-      <c r="C106" s="22" t="n"/>
-      <c r="D106" s="21" t="n"/>
-    </row>
-    <row r="107">
-      <c r="A107" s="15" t="n"/>
-      <c r="B107" s="15" t="n"/>
-      <c r="C107" s="22" t="n"/>
-      <c r="D107" s="21" t="n"/>
-    </row>
-    <row r="108">
-      <c r="A108" s="15" t="n"/>
-      <c r="B108" s="15" t="n"/>
-      <c r="C108" s="22" t="n"/>
-      <c r="D108" s="21" t="n"/>
-    </row>
-    <row r="109">
-      <c r="A109" s="15" t="n"/>
-      <c r="B109" s="15" t="n"/>
-      <c r="C109" s="22" t="n"/>
-      <c r="D109" s="21" t="n"/>
-    </row>
-    <row r="110">
-      <c r="A110" s="15" t="n"/>
-      <c r="B110" s="15" t="n"/>
-      <c r="C110" s="22" t="n"/>
-      <c r="D110" s="21" t="n"/>
-    </row>
-    <row r="111">
-      <c r="A111" s="15" t="n"/>
-      <c r="B111" s="15" t="n"/>
-      <c r="C111" s="22" t="n"/>
-      <c r="D111" s="21" t="n"/>
-    </row>
-    <row r="112">
-      <c r="A112" s="15" t="n"/>
-      <c r="B112" s="15" t="n"/>
-      <c r="C112" s="22" t="n"/>
-      <c r="D112" s="21" t="n"/>
-    </row>
-    <row r="113">
-      <c r="A113" s="15" t="n"/>
-      <c r="B113" s="15" t="n"/>
-      <c r="C113" s="22" t="n"/>
-      <c r="D113" s="21" t="n"/>
-    </row>
-    <row r="114">
-      <c r="A114" s="15" t="n"/>
-      <c r="B114" s="15" t="n"/>
-      <c r="C114" s="22" t="n"/>
-      <c r="D114" s="21" t="n"/>
-    </row>
-    <row r="115">
-      <c r="A115" s="15" t="n"/>
-      <c r="B115" s="15" t="n"/>
-      <c r="C115" s="22" t="n"/>
-      <c r="D115" s="21" t="n"/>
-    </row>
-    <row r="116">
-      <c r="A116" s="15" t="n"/>
-      <c r="B116" s="15" t="n"/>
-      <c r="C116" s="22" t="n"/>
-      <c r="D116" s="21" t="n"/>
-    </row>
-    <row r="117">
-      <c r="A117" s="15" t="n"/>
-      <c r="B117" s="15" t="n"/>
-      <c r="C117" s="22" t="n"/>
-      <c r="D117" s="21" t="n"/>
-    </row>
-    <row r="118">
-      <c r="A118" s="15" t="n"/>
-      <c r="B118" s="15" t="n"/>
-      <c r="C118" s="22" t="n"/>
-      <c r="D118" s="21" t="n"/>
-    </row>
-    <row r="119">
-      <c r="A119" s="15" t="n"/>
-      <c r="B119" s="15" t="n"/>
-      <c r="C119" s="22" t="n"/>
-      <c r="D119" s="21" t="n"/>
-    </row>
-    <row r="120">
-      <c r="A120" s="15" t="n"/>
-      <c r="B120" s="15" t="n"/>
-      <c r="C120" s="22" t="n"/>
-      <c r="D120" s="21" t="n"/>
-    </row>
-    <row r="121">
-      <c r="A121" s="15" t="n"/>
-      <c r="B121" s="15" t="n"/>
-      <c r="C121" s="22" t="n"/>
-      <c r="D121" s="21" t="n"/>
-    </row>
-    <row r="122">
-      <c r="A122" s="15" t="n"/>
-      <c r="B122" s="15" t="n"/>
-      <c r="C122" s="22" t="n"/>
-      <c r="D122" s="21" t="n"/>
-    </row>
-    <row r="123">
-      <c r="A123" s="15" t="n"/>
-      <c r="B123" s="15" t="n"/>
-      <c r="C123" s="22" t="n"/>
-      <c r="D123" s="21" t="n"/>
-    </row>
-    <row r="124">
-      <c r="A124" s="15" t="n"/>
-      <c r="B124" s="15" t="n"/>
-      <c r="C124" s="22" t="n"/>
-      <c r="D124" s="21" t="n"/>
-    </row>
-    <row r="125">
-      <c r="A125" s="15" t="n"/>
-      <c r="B125" s="15" t="n"/>
-      <c r="C125" s="22" t="n"/>
-      <c r="D125" s="21" t="n"/>
-    </row>
-    <row r="126">
-      <c r="A126" s="15" t="n"/>
-      <c r="B126" s="15" t="n"/>
-      <c r="C126" s="22" t="n"/>
-      <c r="D126" s="21" t="n"/>
-    </row>
-    <row r="127">
-      <c r="A127" s="15" t="n"/>
-      <c r="B127" s="15" t="n"/>
-      <c r="C127" s="22" t="n"/>
-      <c r="D127" s="21" t="n"/>
-    </row>
-    <row r="128">
-      <c r="A128" s="15" t="n"/>
-      <c r="B128" s="15" t="n"/>
-      <c r="C128" s="22" t="n"/>
-      <c r="D128" s="21" t="n"/>
-    </row>
-    <row r="129">
-      <c r="A129" s="15" t="n"/>
-      <c r="B129" s="15" t="n"/>
-      <c r="C129" s="22" t="n"/>
-      <c r="D129" s="21" t="n"/>
-    </row>
-    <row r="130">
-      <c r="A130" s="15" t="n"/>
-      <c r="B130" s="15" t="n"/>
-      <c r="C130" s="22" t="n"/>
-      <c r="D130" s="21" t="n"/>
-    </row>
-    <row r="131">
-      <c r="A131" s="15" t="n"/>
-      <c r="B131" s="15" t="n"/>
-      <c r="C131" s="22" t="n"/>
-      <c r="D131" s="21" t="n"/>
-    </row>
-    <row r="132">
-      <c r="A132" s="15" t="n"/>
-      <c r="B132" s="15" t="n"/>
-      <c r="C132" s="22" t="n"/>
-      <c r="D132" s="21" t="n"/>
-    </row>
-    <row r="133">
-      <c r="A133" s="15" t="n"/>
-      <c r="B133" s="15" t="n"/>
-      <c r="C133" s="22" t="n"/>
-      <c r="D133" s="21" t="n"/>
-    </row>
-    <row r="134">
-      <c r="A134" s="15" t="n"/>
-      <c r="B134" s="15" t="n"/>
-      <c r="C134" s="22" t="n"/>
-      <c r="D134" s="21" t="n"/>
-    </row>
-    <row r="135">
-      <c r="A135" s="15" t="n"/>
-      <c r="B135" s="15" t="n"/>
-      <c r="C135" s="22" t="n"/>
-      <c r="D135" s="21" t="n"/>
-    </row>
-    <row r="136">
-      <c r="A136" s="15" t="n"/>
-      <c r="B136" s="15" t="n"/>
-      <c r="C136" s="22" t="n"/>
-      <c r="D136" s="21" t="n"/>
-    </row>
-    <row r="137">
-      <c r="A137" s="15" t="n"/>
-      <c r="B137" s="15" t="n"/>
-      <c r="C137" s="22" t="n"/>
-      <c r="D137" s="21" t="n"/>
-    </row>
-    <row r="138">
-      <c r="A138" s="15" t="n"/>
-      <c r="B138" s="15" t="n"/>
-      <c r="C138" s="22" t="n"/>
-      <c r="D138" s="21" t="n"/>
-    </row>
-    <row r="139">
-      <c r="A139" s="15" t="n"/>
-      <c r="B139" s="15" t="n"/>
-      <c r="C139" s="22" t="n"/>
-      <c r="D139" s="21" t="n"/>
-    </row>
-    <row r="140">
-      <c r="A140" s="15" t="n"/>
-      <c r="B140" s="15" t="n"/>
-      <c r="C140" s="22" t="n"/>
-      <c r="D140" s="21" t="n"/>
-    </row>
-    <row r="141">
-      <c r="A141" s="15" t="n"/>
-      <c r="B141" s="15" t="n"/>
-      <c r="C141" s="22" t="n"/>
-      <c r="D141" s="21" t="n"/>
-    </row>
-    <row r="142">
-      <c r="A142" s="15" t="n"/>
-      <c r="B142" s="15" t="n"/>
-      <c r="C142" s="22" t="n"/>
-      <c r="D142" s="21" t="n"/>
-    </row>
-    <row r="143">
-      <c r="A143" s="15" t="n"/>
-      <c r="B143" s="15" t="n"/>
-      <c r="C143" s="22" t="n"/>
-      <c r="D143" s="21" t="n"/>
-    </row>
-    <row r="144">
-      <c r="A144" s="15" t="n"/>
-      <c r="B144" s="15" t="n"/>
-      <c r="C144" s="22" t="n"/>
-      <c r="D144" s="21" t="n"/>
-    </row>
-    <row r="145">
-      <c r="A145" s="15" t="n"/>
-      <c r="B145" s="15" t="n"/>
-      <c r="C145" s="22" t="n"/>
-      <c r="D145" s="21" t="n"/>
-    </row>
-    <row r="146">
-      <c r="A146" s="15" t="n"/>
-      <c r="B146" s="15" t="n"/>
-      <c r="C146" s="22" t="n"/>
-      <c r="D146" s="21" t="n"/>
-    </row>
-    <row r="147">
-      <c r="A147" s="15" t="n"/>
-      <c r="B147" s="15" t="n"/>
-      <c r="C147" s="22" t="n"/>
-      <c r="D147" s="21" t="n"/>
-    </row>
-    <row r="148">
-      <c r="A148" s="15" t="n"/>
-      <c r="B148" s="15" t="n"/>
-      <c r="C148" s="22" t="n"/>
-      <c r="D148" s="21" t="n"/>
-    </row>
-    <row r="149">
-      <c r="A149" s="15" t="n"/>
-      <c r="B149" s="15" t="n"/>
-      <c r="C149" s="22" t="n"/>
-      <c r="D149" s="21" t="n"/>
-    </row>
-    <row r="150">
-      <c r="A150" s="15" t="n"/>
-      <c r="B150" s="15" t="n"/>
-      <c r="C150" s="22" t="n"/>
-      <c r="D150" s="21" t="n"/>
-    </row>
-    <row r="151">
-      <c r="A151" s="15" t="n"/>
-      <c r="B151" s="15" t="n"/>
-      <c r="C151" s="22" t="n"/>
-      <c r="D151" s="21" t="n"/>
-    </row>
-    <row r="152">
-      <c r="A152" s="15" t="n"/>
-      <c r="B152" s="15" t="n"/>
-      <c r="C152" s="22" t="n"/>
-      <c r="D152" s="21" t="n"/>
-    </row>
-    <row r="153">
-      <c r="A153" s="15" t="n"/>
-      <c r="B153" s="15" t="n"/>
-      <c r="C153" s="22" t="n"/>
-      <c r="D153" s="21" t="n"/>
-    </row>
-    <row r="154">
-      <c r="A154" s="15" t="n"/>
-      <c r="B154" s="15" t="n"/>
-      <c r="C154" s="22" t="n"/>
-      <c r="D154" s="21" t="n"/>
-    </row>
-    <row r="155">
-      <c r="A155" s="15" t="n"/>
-      <c r="B155" s="15" t="n"/>
-      <c r="C155" s="22" t="n"/>
-      <c r="D155" s="21" t="n"/>
-    </row>
-    <row r="156">
-      <c r="A156" s="15" t="n"/>
-      <c r="B156" s="15" t="n"/>
-      <c r="C156" s="22" t="n"/>
-      <c r="D156" s="21" t="n"/>
-    </row>
-    <row r="157">
-      <c r="A157" s="15" t="n"/>
-      <c r="B157" s="15" t="n"/>
-      <c r="C157" s="22" t="n"/>
-      <c r="D157" s="21" t="n"/>
-    </row>
-    <row r="158">
-      <c r="A158" s="15" t="n"/>
-      <c r="B158" s="15" t="n"/>
-      <c r="C158" s="22" t="n"/>
-      <c r="D158" s="21" t="n"/>
-    </row>
-    <row r="159">
-      <c r="A159" s="15" t="n"/>
-      <c r="B159" s="15" t="n"/>
-      <c r="C159" s="22" t="n"/>
-      <c r="D159" s="21" t="n"/>
-    </row>
-    <row r="160">
-      <c r="A160" s="15" t="n"/>
-      <c r="B160" s="15" t="n"/>
-      <c r="C160" s="22" t="n"/>
-      <c r="D160" s="21" t="n"/>
-    </row>
-    <row r="161">
-      <c r="A161" s="15" t="n"/>
-      <c r="B161" s="15" t="n"/>
-      <c r="C161" s="22" t="n"/>
-      <c r="D161" s="21" t="n"/>
-    </row>
-    <row r="162">
-      <c r="A162" s="15" t="n"/>
-      <c r="B162" s="15" t="n"/>
-      <c r="C162" s="22" t="n"/>
-      <c r="D162" s="21" t="n"/>
-    </row>
-    <row r="163">
-      <c r="A163" s="15" t="n"/>
-      <c r="B163" s="15" t="n"/>
-      <c r="C163" s="22" t="n"/>
-      <c r="D163" s="21" t="n"/>
-    </row>
-    <row r="164">
-      <c r="A164" s="15" t="n"/>
-      <c r="B164" s="15" t="n"/>
-      <c r="C164" s="22" t="n"/>
-      <c r="D164" s="21" t="n"/>
-    </row>
-    <row r="165">
-      <c r="A165" s="15" t="n"/>
-      <c r="B165" s="15" t="n"/>
-      <c r="C165" s="22" t="n"/>
-      <c r="D165" s="21" t="n"/>
-    </row>
-    <row r="166">
-      <c r="A166" s="15" t="n"/>
-      <c r="B166" s="15" t="n"/>
-      <c r="C166" s="22" t="n"/>
-      <c r="D166" s="21" t="n"/>
-    </row>
-    <row r="167">
-      <c r="A167" s="15" t="n"/>
-      <c r="B167" s="15" t="n"/>
-      <c r="C167" s="22" t="n"/>
-      <c r="D167" s="21" t="n"/>
-    </row>
-    <row r="168">
-      <c r="A168" s="15" t="n"/>
-      <c r="B168" s="15" t="n"/>
-      <c r="C168" s="22" t="n"/>
-      <c r="D168" s="21" t="n"/>
-    </row>
-    <row r="169">
-      <c r="A169" s="15" t="n"/>
-      <c r="B169" s="15" t="n"/>
-      <c r="C169" s="22" t="n"/>
-      <c r="D169" s="21" t="n"/>
-    </row>
-    <row r="170">
-      <c r="A170" s="15" t="n"/>
-      <c r="B170" s="15" t="n"/>
-      <c r="C170" s="22" t="n"/>
-      <c r="D170" s="21" t="n"/>
-    </row>
-    <row r="171">
-      <c r="A171" s="15" t="n"/>
-      <c r="B171" s="15" t="n"/>
-      <c r="C171" s="22" t="n"/>
-      <c r="D171" s="21" t="n"/>
-    </row>
-    <row r="172">
-      <c r="A172" s="15" t="n"/>
-      <c r="B172" s="15" t="n"/>
-      <c r="C172" s="22" t="n"/>
-      <c r="D172" s="21" t="n"/>
-    </row>
-    <row r="173">
-      <c r="A173" s="15" t="n"/>
-      <c r="B173" s="15" t="n"/>
-      <c r="C173" s="22" t="n"/>
-      <c r="D173" s="21" t="n"/>
-    </row>
-    <row r="174">
-      <c r="A174" s="15" t="n"/>
-      <c r="B174" s="15" t="n"/>
-      <c r="C174" s="22" t="n"/>
-      <c r="D174" s="21" t="n"/>
-    </row>
-    <row r="175">
-      <c r="A175" s="15" t="n"/>
-      <c r="B175" s="15" t="n"/>
-      <c r="C175" s="22" t="n"/>
-      <c r="D175" s="21" t="n"/>
-    </row>
-    <row r="176">
-      <c r="A176" s="15" t="n"/>
-      <c r="B176" s="15" t="n"/>
-      <c r="C176" s="22" t="n"/>
-      <c r="D176" s="21" t="n"/>
-    </row>
-    <row r="177">
-      <c r="A177" s="15" t="n"/>
-      <c r="B177" s="15" t="n"/>
-      <c r="C177" s="22" t="n"/>
-      <c r="D177" s="21" t="n"/>
-    </row>
-    <row r="178">
-      <c r="A178" s="15" t="n"/>
-      <c r="B178" s="15" t="n"/>
-      <c r="C178" s="22" t="n"/>
-      <c r="D178" s="21" t="n"/>
-    </row>
-    <row r="179">
-      <c r="A179" s="15" t="n"/>
-      <c r="B179" s="15" t="n"/>
-      <c r="C179" s="22" t="n"/>
-      <c r="D179" s="21" t="n"/>
-    </row>
-    <row r="180">
-      <c r="A180" s="15" t="n"/>
-      <c r="B180" s="15" t="n"/>
-      <c r="C180" s="22" t="n"/>
-      <c r="D180" s="21" t="n"/>
-    </row>
-    <row r="181">
-      <c r="A181" s="15" t="n"/>
-      <c r="B181" s="15" t="n"/>
-      <c r="C181" s="22" t="n"/>
-      <c r="D181" s="21" t="n"/>
-    </row>
-    <row r="182">
-      <c r="A182" s="15" t="n"/>
-      <c r="B182" s="15" t="n"/>
-      <c r="C182" s="22" t="n"/>
-      <c r="D182" s="21" t="n"/>
-    </row>
-    <row r="183">
-      <c r="A183" s="15" t="n"/>
-      <c r="B183" s="15" t="n"/>
-      <c r="C183" s="22" t="n"/>
-      <c r="D183" s="21" t="n"/>
-    </row>
-    <row r="184">
-      <c r="A184" s="15" t="n"/>
-      <c r="B184" s="15" t="n"/>
-      <c r="C184" s="22" t="n"/>
-      <c r="D184" s="21" t="n"/>
-    </row>
-    <row r="185">
-      <c r="A185" s="15" t="n"/>
-      <c r="B185" s="15" t="n"/>
-      <c r="C185" s="22" t="n"/>
-      <c r="D185" s="21" t="n"/>
-    </row>
-    <row r="186">
-      <c r="A186" s="15" t="n"/>
-      <c r="B186" s="15" t="n"/>
-      <c r="C186" s="22" t="n"/>
-      <c r="D186" s="21" t="n"/>
-    </row>
-    <row r="187">
-      <c r="A187" s="15" t="n"/>
-      <c r="B187" s="15" t="n"/>
-      <c r="C187" s="22" t="n"/>
-      <c r="D187" s="21" t="n"/>
-    </row>
-    <row r="188">
-      <c r="A188" s="15" t="n"/>
-      <c r="B188" s="15" t="n"/>
-      <c r="C188" s="22" t="n"/>
-      <c r="D188" s="21" t="n"/>
-    </row>
-    <row r="189">
-      <c r="A189" s="15" t="n"/>
-      <c r="B189" s="15" t="n"/>
-      <c r="C189" s="22" t="n"/>
-      <c r="D189" s="21" t="n"/>
-    </row>
-    <row r="190">
-      <c r="A190" s="15" t="n"/>
-      <c r="B190" s="15" t="n"/>
-      <c r="C190" s="22" t="n"/>
-      <c r="D190" s="21" t="n"/>
-    </row>
-    <row r="191">
-      <c r="A191" s="15" t="n"/>
-      <c r="B191" s="15" t="n"/>
-      <c r="C191" s="22" t="n"/>
-      <c r="D191" s="21" t="n"/>
-    </row>
-    <row r="192">
-      <c r="A192" s="15" t="n"/>
-      <c r="B192" s="15" t="n"/>
-      <c r="C192" s="22" t="n"/>
-      <c r="D192" s="21" t="n"/>
-    </row>
-    <row r="193">
-      <c r="A193" s="15" t="n"/>
-      <c r="B193" s="15" t="n"/>
-      <c r="C193" s="22" t="n"/>
-      <c r="D193" s="21" t="n"/>
-    </row>
-    <row r="194">
-      <c r="A194" s="15" t="n"/>
-      <c r="B194" s="15" t="n"/>
-      <c r="C194" s="22" t="n"/>
-      <c r="D194" s="21" t="n"/>
-    </row>
-    <row r="195">
-      <c r="A195" s="15" t="n"/>
-      <c r="B195" s="15" t="n"/>
-      <c r="C195" s="22" t="n"/>
-      <c r="D195" s="21" t="n"/>
-    </row>
-    <row r="196">
-      <c r="A196" s="15" t="n"/>
-      <c r="B196" s="15" t="n"/>
-      <c r="C196" s="22" t="n"/>
-      <c r="D196" s="21" t="n"/>
-    </row>
-    <row r="197">
-      <c r="A197" s="15" t="n"/>
-      <c r="B197" s="15" t="n"/>
-      <c r="C197" s="22" t="n"/>
-      <c r="D197" s="21" t="n"/>
-    </row>
-    <row r="198">
-      <c r="A198" s="15" t="n"/>
-      <c r="B198" s="15" t="n"/>
-      <c r="C198" s="22" t="n"/>
-      <c r="D198" s="21" t="n"/>
-    </row>
-    <row r="199">
-      <c r="A199" s="15" t="n"/>
-      <c r="B199" s="15" t="n"/>
-      <c r="C199" s="22" t="n"/>
-      <c r="D199" s="21" t="n"/>
-    </row>
-    <row r="200">
-      <c r="A200" s="15" t="n"/>
-      <c r="B200" s="15" t="n"/>
-      <c r="C200" s="22" t="n"/>
-      <c r="D200" s="21" t="n"/>
-    </row>
-    <row r="201">
-      <c r="A201" s="15" t="n"/>
-      <c r="B201" s="15" t="n"/>
-      <c r="C201" s="22" t="n"/>
-      <c r="D201" s="21" t="n"/>
-    </row>
-    <row r="202">
-      <c r="A202" s="15" t="n"/>
-      <c r="B202" s="15" t="n"/>
-      <c r="C202" s="22" t="n"/>
-      <c r="D202" s="21" t="n"/>
-    </row>
-    <row r="203">
-      <c r="A203" s="15" t="n"/>
-      <c r="B203" s="15" t="n"/>
-      <c r="C203" s="22" t="n"/>
-      <c r="D203" s="21" t="n"/>
-    </row>
-    <row r="204">
-      <c r="A204" s="15" t="n"/>
-      <c r="B204" s="15" t="n"/>
-      <c r="C204" s="22" t="n"/>
-      <c r="D204" s="21" t="n"/>
-    </row>
-    <row r="205">
-      <c r="A205" s="15" t="n"/>
-      <c r="B205" s="15" t="n"/>
-      <c r="C205" s="22" t="n"/>
-      <c r="D205" s="21" t="n"/>
-    </row>
-    <row r="206">
-      <c r="A206" s="15" t="n"/>
-      <c r="B206" s="15" t="n"/>
-      <c r="C206" s="22" t="n"/>
-      <c r="D206" s="21" t="n"/>
-    </row>
-    <row r="207">
-      <c r="A207" s="15" t="n"/>
-      <c r="B207" s="15" t="n"/>
-      <c r="C207" s="22" t="n"/>
-      <c r="D207" s="21" t="n"/>
-    </row>
-    <row r="208">
-      <c r="A208" s="15" t="n"/>
-      <c r="B208" s="15" t="n"/>
-      <c r="C208" s="22" t="n"/>
-      <c r="D208" s="21" t="n"/>
-    </row>
-    <row r="209">
-      <c r="A209" s="15" t="n"/>
-      <c r="B209" s="15" t="n"/>
-      <c r="C209" s="22" t="n"/>
-      <c r="D209" s="21" t="n"/>
-    </row>
-    <row r="210">
-      <c r="A210" s="15" t="n"/>
-      <c r="B210" s="15" t="n"/>
-      <c r="C210" s="22" t="n"/>
-      <c r="D210" s="21" t="n"/>
-    </row>
-    <row r="211">
-      <c r="A211" s="15" t="n"/>
-      <c r="B211" s="15" t="n"/>
-      <c r="C211" s="22" t="n"/>
-      <c r="D211" s="21" t="n"/>
-    </row>
-    <row r="212">
-      <c r="A212" s="15" t="n"/>
-      <c r="B212" s="15" t="n"/>
-      <c r="C212" s="22" t="n"/>
-      <c r="D212" s="21" t="n"/>
-    </row>
-    <row r="213">
-      <c r="A213" s="15" t="n"/>
-      <c r="B213" s="15" t="n"/>
-      <c r="C213" s="22" t="n"/>
-      <c r="D213" s="21" t="n"/>
-    </row>
-    <row r="214">
-      <c r="A214" s="15" t="n"/>
-      <c r="B214" s="15" t="n"/>
-      <c r="C214" s="22" t="n"/>
-      <c r="D214" s="21" t="n"/>
-    </row>
-    <row r="215">
-      <c r="A215" s="15" t="n"/>
-      <c r="B215" s="15" t="n"/>
-      <c r="C215" s="22" t="n"/>
-      <c r="D215" s="21" t="n"/>
-    </row>
-    <row r="216">
-      <c r="A216" s="15" t="n"/>
-      <c r="B216" s="15" t="n"/>
-      <c r="C216" s="22" t="n"/>
-      <c r="D216" s="21" t="n"/>
-    </row>
-    <row r="217">
-      <c r="A217" s="15" t="n"/>
-      <c r="B217" s="15" t="n"/>
-      <c r="C217" s="22" t="n"/>
-      <c r="D217" s="21" t="n"/>
-    </row>
-    <row r="218">
-      <c r="A218" s="15" t="n"/>
-      <c r="B218" s="15" t="n"/>
-      <c r="C218" s="22" t="n"/>
-      <c r="D218" s="21" t="n"/>
-    </row>
-    <row r="219">
-      <c r="A219" s="15" t="n"/>
-      <c r="B219" s="15" t="n"/>
-      <c r="C219" s="22" t="n"/>
-      <c r="D219" s="21" t="n"/>
-    </row>
-    <row r="220">
-      <c r="A220" s="15" t="n"/>
-      <c r="B220" s="15" t="n"/>
-      <c r="C220" s="22" t="n"/>
-      <c r="D220" s="21" t="n"/>
-    </row>
-    <row r="221">
-      <c r="A221" s="15" t="n"/>
-      <c r="B221" s="15" t="n"/>
-      <c r="C221" s="22" t="n"/>
-      <c r="D221" s="21" t="n"/>
-    </row>
-    <row r="222">
-      <c r="A222" s="15" t="n"/>
-      <c r="B222" s="15" t="n"/>
-      <c r="C222" s="22" t="n"/>
-      <c r="D222" s="21" t="n"/>
-    </row>
-    <row r="223">
-      <c r="A223" s="15" t="n"/>
-      <c r="B223" s="15" t="n"/>
-      <c r="C223" s="22" t="n"/>
-      <c r="D223" s="21" t="n"/>
-    </row>
-    <row r="224">
-      <c r="A224" s="15" t="n"/>
-      <c r="B224" s="15" t="n"/>
-      <c r="C224" s="22" t="n"/>
-      <c r="D224" s="21" t="n"/>
-    </row>
-    <row r="225">
-      <c r="A225" s="15" t="n"/>
-      <c r="B225" s="15" t="n"/>
-      <c r="C225" s="22" t="n"/>
-      <c r="D225" s="21" t="n"/>
-    </row>
-    <row r="226">
-      <c r="A226" s="15" t="n"/>
-      <c r="B226" s="15" t="n"/>
-      <c r="C226" s="22" t="n"/>
-      <c r="D226" s="21" t="n"/>
-    </row>
-    <row r="227">
-      <c r="A227" s="15" t="n"/>
-      <c r="B227" s="15" t="n"/>
-      <c r="C227" s="22" t="n"/>
-      <c r="D227" s="21" t="n"/>
-    </row>
-    <row r="228">
-      <c r="A228" s="15" t="n"/>
-      <c r="B228" s="15" t="n"/>
-      <c r="C228" s="22" t="n"/>
-      <c r="D228" s="21" t="n"/>
-    </row>
-    <row r="229">
-      <c r="A229" s="15" t="n"/>
-      <c r="B229" s="15" t="n"/>
-      <c r="C229" s="22" t="n"/>
-      <c r="D229" s="21" t="n"/>
-    </row>
-    <row r="230">
-      <c r="A230" s="15" t="n"/>
-      <c r="B230" s="15" t="n"/>
-      <c r="C230" s="22" t="n"/>
-      <c r="D230" s="21" t="n"/>
-    </row>
-    <row r="231">
-      <c r="A231" s="15" t="n"/>
-      <c r="B231" s="15" t="n"/>
-      <c r="C231" s="22" t="n"/>
-      <c r="D231" s="21" t="n"/>
-    </row>
-    <row r="232">
-      <c r="A232" s="15" t="n"/>
-      <c r="B232" s="15" t="n"/>
-      <c r="C232" s="22" t="n"/>
-      <c r="D232" s="21" t="n"/>
-    </row>
-    <row r="233">
-      <c r="A233" s="15" t="n"/>
-      <c r="B233" s="15" t="n"/>
-      <c r="C233" s="22" t="n"/>
-      <c r="D233" s="21" t="n"/>
-    </row>
-    <row r="234">
-      <c r="A234" s="15" t="n"/>
-      <c r="B234" s="15" t="n"/>
-      <c r="C234" s="22" t="n"/>
-      <c r="D234" s="21" t="n"/>
-    </row>
-    <row r="235">
-      <c r="A235" s="15" t="n"/>
-      <c r="B235" s="15" t="n"/>
-      <c r="C235" s="22" t="n"/>
-      <c r="D235" s="21" t="n"/>
-    </row>
-    <row r="236">
-      <c r="A236" s="15" t="n"/>
-      <c r="B236" s="15" t="n"/>
-      <c r="C236" s="22" t="n"/>
-      <c r="D236" s="21" t="n"/>
-    </row>
-    <row r="237">
-      <c r="A237" s="15" t="n"/>
-      <c r="B237" s="15" t="n"/>
-      <c r="C237" s="22" t="n"/>
-      <c r="D237" s="21" t="n"/>
-    </row>
-    <row r="238">
-      <c r="A238" s="15" t="n"/>
-      <c r="B238" s="15" t="n"/>
-      <c r="C238" s="22" t="n"/>
-      <c r="D238" s="21" t="n"/>
-    </row>
-    <row r="239">
-      <c r="A239" s="15" t="n"/>
-      <c r="B239" s="15" t="n"/>
-      <c r="C239" s="22" t="n"/>
-      <c r="D239" s="21" t="n"/>
-    </row>
-    <row r="240">
-      <c r="A240" s="15" t="n"/>
-      <c r="B240" s="15" t="n"/>
-      <c r="C240" s="22" t="n"/>
-      <c r="D240" s="21" t="n"/>
-    </row>
-    <row r="241">
-      <c r="A241" s="15" t="n"/>
-      <c r="B241" s="15" t="n"/>
-      <c r="C241" s="22" t="n"/>
-      <c r="D241" s="21" t="n"/>
-    </row>
-    <row r="242">
-      <c r="A242" s="15" t="n"/>
-      <c r="B242" s="15" t="n"/>
-      <c r="C242" s="22" t="n"/>
-      <c r="D242" s="21" t="n"/>
-    </row>
-    <row r="243">
-      <c r="A243" s="15" t="n"/>
-      <c r="B243" s="15" t="n"/>
-      <c r="C243" s="22" t="n"/>
-      <c r="D243" s="21" t="n"/>
-    </row>
-    <row r="244">
-      <c r="A244" s="15" t="n"/>
-      <c r="B244" s="15" t="n"/>
-      <c r="C244" s="22" t="n"/>
-      <c r="D244" s="21" t="n"/>
-    </row>
-    <row r="245">
-      <c r="A245" s="15" t="n"/>
-      <c r="B245" s="15" t="n"/>
-      <c r="C245" s="22" t="n"/>
-      <c r="D245" s="21" t="n"/>
-    </row>
-    <row r="246">
-      <c r="A246" s="15" t="n"/>
-      <c r="B246" s="15" t="n"/>
-      <c r="C246" s="22" t="n"/>
-      <c r="D246" s="21" t="n"/>
-    </row>
-    <row r="247">
-      <c r="A247" s="15" t="n"/>
-      <c r="B247" s="15" t="n"/>
-      <c r="C247" s="22" t="n"/>
-      <c r="D247" s="21" t="n"/>
-    </row>
-    <row r="248">
-      <c r="A248" s="15" t="n"/>
-      <c r="B248" s="15" t="n"/>
-      <c r="C248" s="22" t="n"/>
-      <c r="D248" s="21" t="n"/>
-    </row>
-    <row r="249">
-      <c r="A249" s="15" t="n"/>
-      <c r="B249" s="15" t="n"/>
-      <c r="C249" s="22" t="n"/>
-      <c r="D249" s="21" t="n"/>
-    </row>
-    <row r="250">
-      <c r="A250" s="15" t="n"/>
-      <c r="B250" s="15" t="n"/>
-      <c r="C250" s="22" t="n"/>
-      <c r="D250" s="21" t="n"/>
-    </row>
-    <row r="251">
-      <c r="A251" s="15" t="n"/>
-      <c r="B251" s="15" t="n"/>
-      <c r="C251" s="22" t="n"/>
-      <c r="D251" s="21" t="n"/>
-    </row>
-    <row r="252">
-      <c r="A252" s="15" t="n"/>
-      <c r="B252" s="15" t="n"/>
-      <c r="C252" s="22" t="n"/>
-      <c r="D252" s="21" t="n"/>
-    </row>
-    <row r="253">
-      <c r="A253" s="15" t="n"/>
-      <c r="B253" s="15" t="n"/>
-      <c r="C253" s="22" t="n"/>
-      <c r="D253" s="21" t="n"/>
-    </row>
-    <row r="254">
-      <c r="A254" s="15" t="n"/>
-      <c r="B254" s="15" t="n"/>
-      <c r="C254" s="22" t="n"/>
-      <c r="D254" s="21" t="n"/>
-    </row>
-    <row r="255">
-      <c r="A255" s="15" t="n"/>
-      <c r="B255" s="15" t="n"/>
-      <c r="C255" s="22" t="n"/>
-      <c r="D255" s="21" t="n"/>
-    </row>
-    <row r="256">
-      <c r="A256" s="15" t="n"/>
-      <c r="B256" s="15" t="n"/>
-      <c r="C256" s="22" t="n"/>
-      <c r="D256" s="21" t="n"/>
-    </row>
-    <row r="257">
-      <c r="A257" s="15" t="n"/>
-      <c r="B257" s="15" t="n"/>
-      <c r="C257" s="22" t="n"/>
-      <c r="D257" s="21" t="n"/>
-    </row>
-    <row r="258">
-      <c r="A258" s="15" t="n"/>
-      <c r="B258" s="15" t="n"/>
-      <c r="C258" s="22" t="n"/>
-      <c r="D258" s="21" t="n"/>
-    </row>
-    <row r="259">
-      <c r="A259" s="15" t="n"/>
-      <c r="B259" s="15" t="n"/>
-      <c r="C259" s="22" t="n"/>
-      <c r="D259" s="21" t="n"/>
-    </row>
-    <row r="260">
-      <c r="A260" s="15" t="n"/>
-      <c r="B260" s="15" t="n"/>
-      <c r="C260" s="22" t="n"/>
-      <c r="D260" s="21" t="n"/>
-    </row>
-    <row r="261">
-      <c r="A261" s="15" t="n"/>
-      <c r="B261" s="15" t="n"/>
-      <c r="C261" s="22" t="n"/>
-      <c r="D261" s="21" t="n"/>
-    </row>
-    <row r="262">
-      <c r="A262" s="15" t="n"/>
-      <c r="B262" s="15" t="n"/>
-      <c r="C262" s="22" t="n"/>
-      <c r="D262" s="21" t="n"/>
-    </row>
-    <row r="263">
-      <c r="A263" s="15" t="n"/>
-      <c r="B263" s="15" t="n"/>
-      <c r="C263" s="22" t="n"/>
-      <c r="D263" s="21" t="n"/>
-    </row>
-    <row r="264">
-      <c r="A264" s="15" t="n"/>
-      <c r="B264" s="15" t="n"/>
-      <c r="C264" s="22" t="n"/>
-      <c r="D264" s="21" t="n"/>
-    </row>
-    <row r="265">
-      <c r="A265" s="15" t="n"/>
-      <c r="B265" s="15" t="n"/>
-      <c r="C265" s="22" t="n"/>
-      <c r="D265" s="21" t="n"/>
-    </row>
-    <row r="266">
-      <c r="A266" s="15" t="n"/>
-      <c r="B266" s="15" t="n"/>
-      <c r="C266" s="22" t="n"/>
-      <c r="D266" s="21" t="n"/>
-    </row>
-    <row r="267">
-      <c r="A267" s="15" t="n"/>
-      <c r="B267" s="15" t="n"/>
-      <c r="C267" s="22" t="n"/>
-      <c r="D267" s="21" t="n"/>
-    </row>
-    <row r="268">
-      <c r="A268" s="15" t="n"/>
-      <c r="B268" s="15" t="n"/>
-      <c r="C268" s="22" t="n"/>
-      <c r="D268" s="21" t="n"/>
-    </row>
-    <row r="269">
-      <c r="A269" s="15" t="n"/>
-      <c r="B269" s="15" t="n"/>
-      <c r="C269" s="22" t="n"/>
-      <c r="D269" s="21" t="n"/>
-    </row>
-    <row r="270">
-      <c r="A270" s="15" t="n"/>
-      <c r="B270" s="15" t="n"/>
-      <c r="C270" s="22" t="n"/>
-      <c r="D270" s="21" t="n"/>
-    </row>
-    <row r="271">
-      <c r="A271" s="15" t="n"/>
-      <c r="B271" s="15" t="n"/>
-      <c r="C271" s="22" t="n"/>
-      <c r="D271" s="21" t="n"/>
-    </row>
-    <row r="272">
-      <c r="A272" s="15" t="n"/>
-      <c r="B272" s="15" t="n"/>
-      <c r="C272" s="22" t="n"/>
-      <c r="D272" s="21" t="n"/>
-    </row>
-    <row r="273">
-      <c r="A273" s="15" t="n"/>
-      <c r="B273" s="15" t="n"/>
-      <c r="C273" s="22" t="n"/>
-      <c r="D273" s="21" t="n"/>
-    </row>
-    <row r="274">
-      <c r="A274" s="15" t="n"/>
-      <c r="B274" s="15" t="n"/>
-      <c r="C274" s="22" t="n"/>
-      <c r="D274" s="21" t="n"/>
-    </row>
-    <row r="275">
-      <c r="A275" s="15" t="n"/>
-      <c r="B275" s="15" t="n"/>
-      <c r="C275" s="22" t="n"/>
-      <c r="D275" s="21" t="n"/>
-    </row>
-    <row r="276">
-      <c r="A276" s="15" t="n"/>
-      <c r="B276" s="15" t="n"/>
-      <c r="C276" s="22" t="n"/>
-      <c r="D276" s="21" t="n"/>
-    </row>
-    <row r="277">
-      <c r="A277" s="15" t="n"/>
-      <c r="B277" s="15" t="n"/>
-      <c r="C277" s="22" t="n"/>
-      <c r="D277" s="21" t="n"/>
-    </row>
-    <row r="278">
-      <c r="A278" s="15" t="n"/>
-      <c r="B278" s="15" t="n"/>
-      <c r="C278" s="22" t="n"/>
-      <c r="D278" s="21" t="n"/>
-    </row>
-    <row r="279">
-      <c r="A279" s="15" t="n"/>
-      <c r="B279" s="15" t="n"/>
-      <c r="C279" s="22" t="n"/>
-      <c r="D279" s="21" t="n"/>
-    </row>
-    <row r="280">
-      <c r="A280" s="15" t="n"/>
-      <c r="B280" s="15" t="n"/>
-      <c r="C280" s="22" t="n"/>
-      <c r="D280" s="21" t="n"/>
-    </row>
-    <row r="281">
-      <c r="A281" s="15" t="n"/>
-      <c r="B281" s="15" t="n"/>
-      <c r="C281" s="22" t="n"/>
-      <c r="D281" s="21" t="n"/>
-    </row>
-    <row r="282">
-      <c r="A282" s="15" t="n"/>
-      <c r="B282" s="15" t="n"/>
-      <c r="C282" s="22" t="n"/>
-      <c r="D282" s="21" t="n"/>
-    </row>
-    <row r="283">
-      <c r="A283" s="15" t="n"/>
-      <c r="B283" s="15" t="n"/>
-      <c r="C283" s="22" t="n"/>
-      <c r="D283" s="21" t="n"/>
-    </row>
-    <row r="284">
-      <c r="A284" s="15" t="n"/>
-      <c r="B284" s="15" t="n"/>
-      <c r="C284" s="22" t="n"/>
-      <c r="D284" s="21" t="n"/>
-    </row>
-    <row r="285">
-      <c r="A285" s="15" t="n"/>
-      <c r="B285" s="15" t="n"/>
-      <c r="C285" s="22" t="n"/>
-      <c r="D285" s="21" t="n"/>
-    </row>
-    <row r="286">
-      <c r="A286" s="15" t="n"/>
-      <c r="B286" s="15" t="n"/>
-      <c r="C286" s="22" t="n"/>
-      <c r="D286" s="21" t="n"/>
-    </row>
-    <row r="287">
-      <c r="A287" s="15" t="n"/>
-      <c r="B287" s="15" t="n"/>
-      <c r="C287" s="22" t="n"/>
-      <c r="D287" s="21" t="n"/>
-    </row>
-    <row r="288">
-      <c r="A288" s="15" t="n"/>
-      <c r="B288" s="15" t="n"/>
-      <c r="C288" s="22" t="n"/>
-      <c r="D288" s="21" t="n"/>
-    </row>
-    <row r="289">
-      <c r="A289" s="15" t="n"/>
-      <c r="B289" s="15" t="n"/>
-      <c r="C289" s="22" t="n"/>
-      <c r="D289" s="21" t="n"/>
-    </row>
-    <row r="290">
-      <c r="A290" s="15" t="n"/>
-      <c r="B290" s="15" t="n"/>
-      <c r="C290" s="22" t="n"/>
-      <c r="D290" s="21" t="n"/>
-    </row>
-    <row r="291">
-      <c r="A291" s="15" t="n"/>
-      <c r="B291" s="15" t="n"/>
-      <c r="C291" s="22" t="n"/>
-      <c r="D291" s="21" t="n"/>
-    </row>
-    <row r="292">
-      <c r="A292" s="15" t="n"/>
-      <c r="B292" s="15" t="n"/>
-      <c r="C292" s="22" t="n"/>
-      <c r="D292" s="21" t="n"/>
-    </row>
-    <row r="293">
-      <c r="A293" s="15" t="n"/>
-      <c r="B293" s="15" t="n"/>
-      <c r="C293" s="22" t="n"/>
-      <c r="D293" s="21" t="n"/>
-    </row>
-    <row r="294">
-      <c r="A294" s="15" t="n"/>
-      <c r="B294" s="15" t="n"/>
-      <c r="C294" s="22" t="n"/>
-      <c r="D294" s="21" t="n"/>
-    </row>
-    <row r="295">
-      <c r="A295" s="15" t="n"/>
-      <c r="B295" s="15" t="n"/>
-      <c r="C295" s="22" t="n"/>
-      <c r="D295" s="21" t="n"/>
-    </row>
-    <row r="296">
-      <c r="A296" s="15" t="n"/>
-      <c r="B296" s="15" t="n"/>
-      <c r="C296" s="22" t="n"/>
-      <c r="D296" s="21" t="n"/>
-    </row>
-    <row r="297">
-      <c r="A297" s="15" t="n"/>
-      <c r="B297" s="15" t="n"/>
-      <c r="C297" s="22" t="n"/>
-      <c r="D297" s="21" t="n"/>
-    </row>
-    <row r="298">
-      <c r="A298" s="15" t="n"/>
-      <c r="B298" s="15" t="n"/>
-      <c r="C298" s="22" t="n"/>
-      <c r="D298" s="21" t="n"/>
-    </row>
-    <row r="299">
-      <c r="A299" s="15" t="n"/>
-      <c r="B299" s="15" t="n"/>
-      <c r="C299" s="22" t="n"/>
-      <c r="D299" s="21" t="n"/>
-    </row>
-    <row r="300">
-      <c r="A300" s="15" t="n"/>
-      <c r="B300" s="15" t="n"/>
-      <c r="C300" s="22" t="n"/>
-      <c r="D300" s="21" t="n"/>
-    </row>
-    <row r="301">
-      <c r="A301" s="15" t="n"/>
-      <c r="B301" s="15" t="n"/>
-      <c r="C301" s="22" t="n"/>
-      <c r="D301" s="21" t="n"/>
-    </row>
-    <row r="302">
-      <c r="A302" s="15" t="n"/>
-      <c r="B302" s="15" t="n"/>
-      <c r="C302" s="22" t="n"/>
-      <c r="D302" s="21" t="n"/>
-    </row>
-    <row r="303">
-      <c r="A303" s="15" t="n"/>
-      <c r="B303" s="15" t="n"/>
-      <c r="C303" s="22" t="n"/>
-      <c r="D303" s="21" t="n"/>
-    </row>
-    <row r="304">
-      <c r="A304" s="15" t="n"/>
-      <c r="B304" s="15" t="n"/>
-      <c r="C304" s="22" t="n"/>
-      <c r="D304" s="21" t="n"/>
-    </row>
-    <row r="305">
-      <c r="A305" s="15" t="n"/>
-      <c r="B305" s="15" t="n"/>
-      <c r="C305" s="22" t="n"/>
-      <c r="D305" s="21" t="n"/>
-    </row>
-    <row r="306">
-      <c r="A306" s="15" t="n"/>
-      <c r="B306" s="15" t="n"/>
-      <c r="C306" s="22" t="n"/>
-      <c r="D306" s="21" t="n"/>
-    </row>
-    <row r="307">
-      <c r="A307" s="15" t="n"/>
-      <c r="B307" s="15" t="n"/>
-      <c r="C307" s="22" t="n"/>
-      <c r="D307" s="21" t="n"/>
-    </row>
-    <row r="308">
-      <c r="A308" s="15" t="n"/>
-      <c r="B308" s="15" t="n"/>
-      <c r="C308" s="22" t="n"/>
-      <c r="D308" s="21" t="n"/>
-    </row>
-    <row r="309">
-      <c r="A309" s="15" t="n"/>
-      <c r="B309" s="15" t="n"/>
-      <c r="C309" s="22" t="n"/>
-      <c r="D309" s="21" t="n"/>
-    </row>
-    <row r="310">
-      <c r="A310" s="15" t="n"/>
-      <c r="B310" s="15" t="n"/>
-      <c r="C310" s="22" t="n"/>
-      <c r="D310" s="21" t="n"/>
-    </row>
-    <row r="311">
-      <c r="A311" s="15" t="n"/>
-      <c r="B311" s="15" t="n"/>
-      <c r="C311" s="22" t="n"/>
-      <c r="D311" s="21" t="n"/>
-    </row>
-    <row r="312">
-      <c r="A312" s="15" t="n"/>
-      <c r="B312" s="15" t="n"/>
-      <c r="C312" s="22" t="n"/>
-      <c r="D312" s="21" t="n"/>
-    </row>
-    <row r="313">
-      <c r="A313" s="15" t="n"/>
-      <c r="B313" s="15" t="n"/>
-      <c r="C313" s="22" t="n"/>
-      <c r="D313" s="21" t="n"/>
-    </row>
-    <row r="314">
-      <c r="A314" s="15" t="n"/>
-      <c r="B314" s="15" t="n"/>
-      <c r="C314" s="22" t="n"/>
-      <c r="D314" s="21" t="n"/>
-    </row>
-    <row r="315">
-      <c r="A315" s="15" t="n"/>
-      <c r="B315" s="15" t="n"/>
-      <c r="C315" s="22" t="n"/>
-      <c r="D315" s="21" t="n"/>
-    </row>
-    <row r="316">
-      <c r="A316" s="15" t="n"/>
-      <c r="B316" s="15" t="n"/>
-      <c r="C316" s="22" t="n"/>
-      <c r="D316" s="21" t="n"/>
-    </row>
-    <row r="317">
-      <c r="A317" s="15" t="n"/>
-      <c r="B317" s="15" t="n"/>
-      <c r="C317" s="22" t="n"/>
-      <c r="D317" s="21" t="n"/>
-    </row>
-    <row r="318">
-      <c r="A318" s="15" t="n"/>
-      <c r="B318" s="15" t="n"/>
-      <c r="C318" s="22" t="n"/>
-      <c r="D318" s="21" t="n"/>
-    </row>
-    <row r="319">
-      <c r="A319" s="15" t="n"/>
-      <c r="B319" s="15" t="n"/>
-      <c r="C319" s="22" t="n"/>
-      <c r="D319" s="21" t="n"/>
-    </row>
-    <row r="320">
-      <c r="A320" s="15" t="n"/>
-      <c r="B320" s="15" t="n"/>
-      <c r="C320" s="22" t="n"/>
-      <c r="D320" s="21" t="n"/>
-    </row>
-    <row r="321">
-      <c r="A321" s="15" t="n"/>
-      <c r="B321" s="15" t="n"/>
-      <c r="C321" s="22" t="n"/>
-      <c r="D321" s="21" t="n"/>
-    </row>
-    <row r="322">
-      <c r="A322" s="15" t="n"/>
-      <c r="B322" s="15" t="n"/>
-      <c r="C322" s="22" t="n"/>
-      <c r="D322" s="21" t="n"/>
-    </row>
-    <row r="323">
-      <c r="A323" s="15" t="n"/>
-      <c r="B323" s="15" t="n"/>
-      <c r="C323" s="22" t="n"/>
-      <c r="D323" s="21" t="n"/>
-    </row>
-    <row r="324">
-      <c r="A324" s="15" t="n"/>
-      <c r="B324" s="15" t="n"/>
-      <c r="C324" s="22" t="n"/>
-      <c r="D324" s="21" t="n"/>
-    </row>
-    <row r="325">
-      <c r="A325" s="15" t="n"/>
-      <c r="B325" s="15" t="n"/>
-      <c r="C325" s="22" t="n"/>
-      <c r="D325" s="21" t="n"/>
-    </row>
-    <row r="326">
-      <c r="A326" s="15" t="n"/>
-      <c r="B326" s="15" t="n"/>
-      <c r="C326" s="22" t="n"/>
-      <c r="D326" s="21" t="n"/>
-    </row>
-    <row r="327">
-      <c r="A327" s="15" t="n"/>
-      <c r="B327" s="15" t="n"/>
-      <c r="C327" s="22" t="n"/>
-      <c r="D327" s="21" t="n"/>
-    </row>
-    <row r="328">
-      <c r="A328" s="15" t="n"/>
-      <c r="B328" s="15" t="n"/>
-      <c r="C328" s="22" t="n"/>
-      <c r="D328" s="21" t="n"/>
-    </row>
-    <row r="329">
-      <c r="A329" s="15" t="n"/>
-      <c r="B329" s="15" t="n"/>
-      <c r="C329" s="22" t="n"/>
-      <c r="D329" s="21" t="n"/>
-    </row>
-    <row r="330">
-      <c r="A330" s="15" t="n"/>
-      <c r="B330" s="15" t="n"/>
-      <c r="C330" s="22" t="n"/>
-      <c r="D330" s="21" t="n"/>
-    </row>
-    <row r="331">
-      <c r="A331" s="15" t="n"/>
-      <c r="B331" s="15" t="n"/>
-      <c r="C331" s="22" t="n"/>
-      <c r="D331" s="21" t="n"/>
-    </row>
-    <row r="332">
-      <c r="A332" s="15" t="n"/>
-      <c r="B332" s="15" t="n"/>
-      <c r="C332" s="22" t="n"/>
-      <c r="D332" s="21" t="n"/>
-    </row>
-    <row r="333">
-      <c r="A333" s="15" t="n"/>
-      <c r="B333" s="15" t="n"/>
-      <c r="C333" s="22" t="n"/>
-      <c r="D333" s="21" t="n"/>
-    </row>
-    <row r="334">
-      <c r="A334" s="15" t="n"/>
-      <c r="B334" s="15" t="n"/>
-      <c r="C334" s="22" t="n"/>
-      <c r="D334" s="21" t="n"/>
-    </row>
-    <row r="335">
-      <c r="A335" s="15" t="n"/>
-      <c r="B335" s="15" t="n"/>
-      <c r="C335" s="22" t="n"/>
-      <c r="D335" s="21" t="n"/>
-    </row>
-    <row r="336">
-      <c r="A336" s="15" t="n"/>
-      <c r="B336" s="15" t="n"/>
-      <c r="C336" s="22" t="n"/>
-      <c r="D336" s="21" t="n"/>
-    </row>
-    <row r="337">
-      <c r="A337" s="15" t="n"/>
-      <c r="B337" s="15" t="n"/>
-      <c r="C337" s="22" t="n"/>
-      <c r="D337" s="21" t="n"/>
-    </row>
-    <row r="338">
-      <c r="A338" s="15" t="n"/>
-      <c r="B338" s="15" t="n"/>
-      <c r="C338" s="22" t="n"/>
-      <c r="D338" s="21" t="n"/>
-    </row>
-    <row r="339">
-      <c r="A339" s="15" t="n"/>
-      <c r="B339" s="15" t="n"/>
-      <c r="C339" s="22" t="n"/>
-      <c r="D339" s="21" t="n"/>
-    </row>
-    <row r="340">
-      <c r="A340" s="15" t="n"/>
-      <c r="B340" s="15" t="n"/>
-      <c r="C340" s="22" t="n"/>
-      <c r="D340" s="21" t="n"/>
-    </row>
-    <row r="341">
-      <c r="A341" s="15" t="n"/>
-      <c r="B341" s="15" t="n"/>
-      <c r="C341" s="22" t="n"/>
-      <c r="D341" s="21" t="n"/>
-    </row>
-    <row r="342">
-      <c r="A342" s="15" t="n"/>
-      <c r="B342" s="15" t="n"/>
-      <c r="C342" s="22" t="n"/>
-      <c r="D342" s="21" t="n"/>
-    </row>
-    <row r="343">
-      <c r="A343" s="15" t="n"/>
-      <c r="B343" s="15" t="n"/>
-      <c r="C343" s="22" t="n"/>
-      <c r="D343" s="21" t="n"/>
-    </row>
-    <row r="344">
-      <c r="A344" s="15" t="n"/>
-      <c r="B344" s="15" t="n"/>
-      <c r="C344" s="22" t="n"/>
-      <c r="D344" s="21" t="n"/>
-    </row>
-    <row r="345">
-      <c r="A345" s="15" t="n"/>
-      <c r="B345" s="15" t="n"/>
-      <c r="C345" s="22" t="n"/>
-      <c r="D345" s="21" t="n"/>
-    </row>
-    <row r="346">
-      <c r="A346" s="15" t="n"/>
-      <c r="B346" s="15" t="n"/>
-      <c r="C346" s="22" t="n"/>
-      <c r="D346" s="21" t="n"/>
-    </row>
-    <row r="347">
-      <c r="A347" s="15" t="n"/>
-      <c r="B347" s="15" t="n"/>
-      <c r="C347" s="22" t="n"/>
-      <c r="D347" s="21" t="n"/>
-    </row>
-    <row r="348">
-      <c r="A348" s="15" t="n"/>
-      <c r="B348" s="15" t="n"/>
-      <c r="C348" s="22" t="n"/>
-      <c r="D348" s="21" t="n"/>
-    </row>
-    <row r="349">
-      <c r="A349" s="15" t="n"/>
-      <c r="B349" s="15" t="n"/>
-      <c r="C349" s="22" t="n"/>
-      <c r="D349" s="21" t="n"/>
-    </row>
-    <row r="350">
-      <c r="A350" s="15" t="n"/>
-      <c r="B350" s="15" t="n"/>
-      <c r="C350" s="22" t="n"/>
-      <c r="D350" s="21" t="n"/>
-    </row>
-    <row r="351">
-      <c r="A351" s="15" t="n"/>
-      <c r="B351" s="15" t="n"/>
-      <c r="C351" s="22" t="n"/>
-      <c r="D351" s="21" t="n"/>
-    </row>
-    <row r="352">
-      <c r="A352" s="15" t="n"/>
-      <c r="B352" s="15" t="n"/>
-      <c r="C352" s="22" t="n"/>
-      <c r="D352" s="21" t="n"/>
-    </row>
-    <row r="353">
-      <c r="A353" s="15" t="n"/>
-      <c r="B353" s="15" t="n"/>
-      <c r="C353" s="22" t="n"/>
-      <c r="D353" s="21" t="n"/>
-    </row>
-    <row r="354">
-      <c r="A354" s="15" t="n"/>
-      <c r="B354" s="15" t="n"/>
-      <c r="C354" s="22" t="n"/>
-      <c r="D354" s="21" t="n"/>
-    </row>
-    <row r="355">
-      <c r="A355" s="15" t="n"/>
-      <c r="B355" s="15" t="n"/>
-      <c r="C355" s="22" t="n"/>
-      <c r="D355" s="21" t="n"/>
-    </row>
-    <row r="356">
-      <c r="A356" s="15" t="n"/>
-      <c r="B356" s="15" t="n"/>
-      <c r="C356" s="22" t="n"/>
-      <c r="D356" s="21" t="n"/>
-    </row>
-    <row r="357">
-      <c r="A357" s="15" t="n"/>
-      <c r="B357" s="15" t="n"/>
-      <c r="C357" s="22" t="n"/>
-      <c r="D357" s="21" t="n"/>
-    </row>
-    <row r="358">
-      <c r="A358" s="15" t="n"/>
-      <c r="B358" s="15" t="n"/>
-      <c r="C358" s="22" t="n"/>
-      <c r="D358" s="21" t="n"/>
-    </row>
-    <row r="359">
-      <c r="A359" s="15" t="n"/>
-      <c r="B359" s="15" t="n"/>
-      <c r="C359" s="22" t="n"/>
-      <c r="D359" s="21" t="n"/>
-    </row>
-    <row r="360">
-      <c r="A360" s="15" t="n"/>
-      <c r="B360" s="15" t="n"/>
-      <c r="C360" s="22" t="n"/>
-      <c r="D360" s="21" t="n"/>
-    </row>
-    <row r="361">
-      <c r="A361" s="15" t="n"/>
-      <c r="B361" s="15" t="n"/>
-      <c r="C361" s="22" t="n"/>
-      <c r="D361" s="21" t="n"/>
-    </row>
-    <row r="362">
-      <c r="A362" s="15" t="n"/>
-      <c r="B362" s="15" t="n"/>
-      <c r="C362" s="22" t="n"/>
-      <c r="D362" s="21" t="n"/>
-    </row>
-    <row r="363">
-      <c r="A363" s="15" t="n"/>
-      <c r="B363" s="15" t="n"/>
-      <c r="C363" s="22" t="n"/>
-      <c r="D363" s="21" t="n"/>
-    </row>
-    <row r="364">
-      <c r="A364" s="15" t="n"/>
-      <c r="B364" s="15" t="n"/>
-      <c r="C364" s="22" t="n"/>
-      <c r="D364" s="21" t="n"/>
-    </row>
-    <row r="365">
-      <c r="A365" s="15" t="n"/>
-      <c r="B365" s="15" t="n"/>
-      <c r="C365" s="22" t="n"/>
-      <c r="D365" s="21" t="n"/>
-    </row>
-    <row r="366">
-      <c r="A366" s="15" t="n"/>
-      <c r="B366" s="15" t="n"/>
-      <c r="C366" s="22" t="n"/>
-      <c r="D366" s="21" t="n"/>
-    </row>
-    <row r="367">
-      <c r="A367" s="15" t="n"/>
-      <c r="B367" s="15" t="n"/>
-      <c r="C367" s="22" t="n"/>
-      <c r="D367" s="21" t="n"/>
-    </row>
-    <row r="368">
-      <c r="A368" s="15" t="n"/>
-      <c r="B368" s="15" t="n"/>
-      <c r="C368" s="22" t="n"/>
-      <c r="D368" s="21" t="n"/>
-    </row>
-    <row r="369">
-      <c r="A369" s="15" t="n"/>
-      <c r="B369" s="15" t="n"/>
-      <c r="C369" s="22" t="n"/>
-      <c r="D369" s="21" t="n"/>
-    </row>
-    <row r="370">
-      <c r="A370" s="15" t="n"/>
-      <c r="B370" s="15" t="n"/>
-      <c r="C370" s="22" t="n"/>
-      <c r="D370" s="21" t="n"/>
-    </row>
-    <row r="371">
-      <c r="A371" s="15" t="n"/>
-      <c r="B371" s="15" t="n"/>
-      <c r="C371" s="22" t="n"/>
-      <c r="D371" s="21" t="n"/>
-    </row>
-    <row r="372">
-      <c r="A372" s="15" t="n"/>
-      <c r="B372" s="15" t="n"/>
-      <c r="C372" s="22" t="n"/>
-      <c r="D372" s="21" t="n"/>
-    </row>
-    <row r="373">
-      <c r="A373" s="15" t="n"/>
-      <c r="B373" s="15" t="n"/>
-      <c r="C373" s="22" t="n"/>
-      <c r="D373" s="21" t="n"/>
-    </row>
-    <row r="374">
-      <c r="A374" s="15" t="n"/>
-      <c r="B374" s="15" t="n"/>
-      <c r="C374" s="22" t="n"/>
-      <c r="D374" s="21" t="n"/>
-    </row>
-    <row r="375">
-      <c r="A375" s="15" t="n"/>
-      <c r="B375" s="15" t="n"/>
-      <c r="C375" s="22" t="n"/>
-      <c r="D375" s="21" t="n"/>
-    </row>
-    <row r="376">
-      <c r="A376" s="15" t="n"/>
-      <c r="B376" s="15" t="n"/>
-      <c r="C376" s="22" t="n"/>
-      <c r="D376" s="21" t="n"/>
-    </row>
-    <row r="377">
-      <c r="A377" s="15" t="n"/>
-      <c r="B377" s="15" t="n"/>
-      <c r="C377" s="22" t="n"/>
-      <c r="D377" s="21" t="n"/>
-    </row>
-    <row r="378">
-      <c r="A378" s="15" t="n"/>
-      <c r="B378" s="15" t="n"/>
-      <c r="C378" s="22" t="n"/>
-      <c r="D378" s="21" t="n"/>
-    </row>
-    <row r="379">
-      <c r="A379" s="15" t="n"/>
-      <c r="B379" s="15" t="n"/>
-      <c r="C379" s="22" t="n"/>
-      <c r="D379" s="21" t="n"/>
-    </row>
-    <row r="380">
-      <c r="A380" s="15" t="n"/>
-      <c r="B380" s="15" t="n"/>
-      <c r="C380" s="22" t="n"/>
-      <c r="D380" s="21" t="n"/>
-    </row>
-    <row r="381">
-      <c r="A381" s="15" t="n"/>
-      <c r="B381" s="15" t="n"/>
-      <c r="C381" s="22" t="n"/>
-      <c r="D381" s="21" t="n"/>
-    </row>
-    <row r="382">
-      <c r="A382" s="15" t="n"/>
-      <c r="B382" s="15" t="n"/>
-      <c r="C382" s="22" t="n"/>
-      <c r="D382" s="21" t="n"/>
-    </row>
-    <row r="383">
-      <c r="A383" s="15" t="n"/>
-      <c r="B383" s="15" t="n"/>
-      <c r="C383" s="22" t="n"/>
-      <c r="D383" s="21" t="n"/>
-    </row>
-    <row r="384">
-      <c r="A384" s="15" t="n"/>
-      <c r="B384" s="15" t="n"/>
-      <c r="C384" s="22" t="n"/>
-      <c r="D384" s="21" t="n"/>
-    </row>
-    <row r="385">
-      <c r="A385" s="15" t="n"/>
-      <c r="B385" s="15" t="n"/>
-      <c r="C385" s="22" t="n"/>
-      <c r="D385" s="21" t="n"/>
-    </row>
-    <row r="386">
-      <c r="A386" s="15" t="n"/>
-      <c r="B386" s="15" t="n"/>
-      <c r="C386" s="22" t="n"/>
-      <c r="D386" s="21" t="n"/>
-    </row>
-    <row r="387">
-      <c r="A387" s="15" t="n"/>
-      <c r="B387" s="15" t="n"/>
-      <c r="C387" s="22" t="n"/>
-      <c r="D387" s="21" t="n"/>
-    </row>
-    <row r="388">
-      <c r="A388" s="15" t="n"/>
-      <c r="B388" s="15" t="n"/>
-      <c r="C388" s="22" t="n"/>
-      <c r="D388" s="21" t="n"/>
-    </row>
-    <row r="389">
-      <c r="A389" s="15" t="n"/>
-      <c r="B389" s="15" t="n"/>
-      <c r="C389" s="22" t="n"/>
-      <c r="D389" s="21" t="n"/>
-    </row>
-    <row r="390">
-      <c r="A390" s="15" t="n"/>
-      <c r="B390" s="15" t="n"/>
-      <c r="C390" s="22" t="n"/>
-      <c r="D390" s="21" t="n"/>
-    </row>
-    <row r="391">
-      <c r="A391" s="15" t="n"/>
-      <c r="B391" s="15" t="n"/>
-      <c r="C391" s="22" t="n"/>
-      <c r="D391" s="21" t="n"/>
-    </row>
-    <row r="392">
-      <c r="A392" s="15" t="n"/>
-      <c r="B392" s="15" t="n"/>
-      <c r="C392" s="22" t="n"/>
-      <c r="D392" s="21" t="n"/>
-    </row>
-    <row r="393">
-      <c r="A393" s="15" t="n"/>
-      <c r="B393" s="15" t="n"/>
-      <c r="C393" s="22" t="n"/>
-      <c r="D393" s="21" t="n"/>
-    </row>
-    <row r="394">
-      <c r="A394" s="15" t="n"/>
-      <c r="B394" s="15" t="n"/>
-      <c r="C394" s="22" t="n"/>
-      <c r="D394" s="21" t="n"/>
-    </row>
-    <row r="395">
-      <c r="A395" s="15" t="n"/>
-      <c r="B395" s="15" t="n"/>
-      <c r="C395" s="22" t="n"/>
-      <c r="D395" s="21" t="n"/>
-    </row>
-    <row r="396">
-      <c r="A396" s="15" t="n"/>
-      <c r="B396" s="15" t="n"/>
-      <c r="C396" s="22" t="n"/>
-      <c r="D396" s="21" t="n"/>
-    </row>
-    <row r="397">
-      <c r="A397" s="15" t="n"/>
-      <c r="B397" s="15" t="n"/>
-      <c r="C397" s="22" t="n"/>
-      <c r="D397" s="21" t="n"/>
-    </row>
-    <row r="398">
-      <c r="A398" s="15" t="n"/>
-      <c r="B398" s="15" t="n"/>
-      <c r="C398" s="22" t="n"/>
-      <c r="D398" s="21" t="n"/>
-    </row>
-    <row r="399">
-      <c r="A399" s="15" t="n"/>
-      <c r="B399" s="15" t="n"/>
-      <c r="C399" s="22" t="n"/>
-      <c r="D399" s="21" t="n"/>
-    </row>
-    <row r="400">
-      <c r="A400" s="15" t="n"/>
-      <c r="B400" s="15" t="n"/>
-      <c r="C400" s="22" t="n"/>
-      <c r="D400" s="21" t="n"/>
-    </row>
-    <row r="401">
-      <c r="A401" s="15" t="n"/>
-      <c r="B401" s="15" t="n"/>
-      <c r="C401" s="22" t="n"/>
-      <c r="D401" s="21" t="n"/>
-    </row>
-    <row r="402">
-      <c r="A402" s="15" t="n"/>
-      <c r="B402" s="15" t="n"/>
-      <c r="C402" s="22" t="n"/>
-      <c r="D402" s="21" t="n"/>
-    </row>
-    <row r="403">
-      <c r="A403" s="15" t="n"/>
-      <c r="B403" s="15" t="n"/>
-      <c r="C403" s="22" t="n"/>
-      <c r="D403" s="21" t="n"/>
-    </row>
-    <row r="404">
-      <c r="A404" s="15" t="n"/>
-      <c r="B404" s="15" t="n"/>
-      <c r="C404" s="22" t="n"/>
-      <c r="D404" s="21" t="n"/>
-    </row>
-    <row r="405">
-      <c r="A405" s="15" t="n"/>
-      <c r="B405" s="15" t="n"/>
-      <c r="C405" s="22" t="n"/>
-      <c r="D405" s="21" t="n"/>
-    </row>
-    <row r="406">
-      <c r="A406" s="15" t="n"/>
-      <c r="B406" s="15" t="n"/>
-      <c r="C406" s="22" t="n"/>
-      <c r="D406" s="21" t="n"/>
-    </row>
-    <row r="407">
-      <c r="A407" s="15" t="n"/>
-      <c r="B407" s="15" t="n"/>
-      <c r="C407" s="22" t="n"/>
-      <c r="D407" s="21" t="n"/>
-    </row>
-    <row r="408">
-      <c r="A408" s="15" t="n"/>
-      <c r="B408" s="15" t="n"/>
-      <c r="C408" s="22" t="n"/>
-      <c r="D408" s="21" t="n"/>
-    </row>
-    <row r="409">
-      <c r="A409" s="15" t="n"/>
-      <c r="B409" s="15" t="n"/>
-      <c r="C409" s="22" t="n"/>
-      <c r="D409" s="21" t="n"/>
-    </row>
-    <row r="410">
-      <c r="A410" s="15" t="n"/>
-      <c r="B410" s="15" t="n"/>
-      <c r="C410" s="22" t="n"/>
-      <c r="D410" s="21" t="n"/>
-    </row>
-    <row r="411">
-      <c r="A411" s="15" t="n"/>
-      <c r="B411" s="15" t="n"/>
-      <c r="C411" s="22" t="n"/>
-      <c r="D411" s="21" t="n"/>
-    </row>
-    <row r="412">
-      <c r="A412" s="15" t="n"/>
-      <c r="B412" s="15" t="n"/>
-      <c r="C412" s="22" t="n"/>
-      <c r="D412" s="21" t="n"/>
-    </row>
-    <row r="413">
-      <c r="A413" s="15" t="n"/>
-      <c r="B413" s="15" t="n"/>
-      <c r="C413" s="22" t="n"/>
-      <c r="D413" s="21" t="n"/>
-    </row>
-    <row r="414">
-      <c r="A414" s="15" t="n"/>
-      <c r="B414" s="15" t="n"/>
-      <c r="C414" s="22" t="n"/>
-      <c r="D414" s="21" t="n"/>
-    </row>
-    <row r="415">
-      <c r="A415" s="15" t="n"/>
-      <c r="B415" s="15" t="n"/>
-      <c r="C415" s="22" t="n"/>
-      <c r="D415" s="21" t="n"/>
-    </row>
-    <row r="416">
-      <c r="A416" s="15" t="n"/>
-      <c r="B416" s="15" t="n"/>
-      <c r="C416" s="22" t="n"/>
-      <c r="D416" s="21" t="n"/>
-    </row>
-    <row r="417">
-      <c r="A417" s="15" t="n"/>
-      <c r="B417" s="15" t="n"/>
-      <c r="C417" s="22" t="n"/>
-      <c r="D417" s="21" t="n"/>
-    </row>
-    <row r="418">
-      <c r="A418" s="15" t="n"/>
-      <c r="B418" s="15" t="n"/>
-      <c r="C418" s="22" t="n"/>
-      <c r="D418" s="21" t="n"/>
-    </row>
-    <row r="419">
-      <c r="A419" s="15" t="n"/>
-      <c r="B419" s="15" t="n"/>
-      <c r="C419" s="22" t="n"/>
-      <c r="D419" s="21" t="n"/>
-    </row>
-    <row r="420">
-      <c r="A420" s="15" t="n"/>
-      <c r="B420" s="15" t="n"/>
-      <c r="C420" s="22" t="n"/>
-      <c r="D420" s="21" t="n"/>
-    </row>
-    <row r="421">
-      <c r="A421" s="15" t="n"/>
-      <c r="B421" s="15" t="n"/>
-      <c r="C421" s="22" t="n"/>
-      <c r="D421" s="21" t="n"/>
-    </row>
-    <row r="422">
-      <c r="A422" s="15" t="n"/>
-      <c r="B422" s="15" t="n"/>
-      <c r="C422" s="22" t="n"/>
-      <c r="D422" s="21" t="n"/>
-    </row>
-    <row r="423">
-      <c r="A423" s="15" t="n"/>
-      <c r="B423" s="15" t="n"/>
-      <c r="C423" s="22" t="n"/>
-      <c r="D423" s="21" t="n"/>
-    </row>
-    <row r="424">
-      <c r="A424" s="15" t="n"/>
-      <c r="B424" s="15" t="n"/>
-      <c r="C424" s="22" t="n"/>
-      <c r="D424" s="21" t="n"/>
-    </row>
-    <row r="425">
-      <c r="A425" s="15" t="n"/>
-      <c r="B425" s="15" t="n"/>
-      <c r="C425" s="22" t="n"/>
-      <c r="D425" s="21" t="n"/>
-    </row>
-    <row r="426">
-      <c r="A426" s="15" t="n"/>
-      <c r="B426" s="15" t="n"/>
-      <c r="C426" s="22" t="n"/>
-      <c r="D426" s="21" t="n"/>
-    </row>
-    <row r="427">
-      <c r="A427" s="15" t="n"/>
-      <c r="B427" s="15" t="n"/>
-      <c r="C427" s="22" t="n"/>
-      <c r="D427" s="21" t="n"/>
-    </row>
-    <row r="428">
-      <c r="A428" s="15" t="n"/>
-      <c r="B428" s="15" t="n"/>
-      <c r="C428" s="22" t="n"/>
-      <c r="D428" s="21" t="n"/>
-    </row>
-    <row r="429">
-      <c r="A429" s="15" t="n"/>
-      <c r="B429" s="15" t="n"/>
-      <c r="C429" s="22" t="n"/>
-      <c r="D429" s="21" t="n"/>
-    </row>
-    <row r="430">
-      <c r="A430" s="15" t="n"/>
-      <c r="B430" s="15" t="n"/>
-      <c r="C430" s="22" t="n"/>
-      <c r="D430" s="21" t="n"/>
-    </row>
-    <row r="431">
-      <c r="A431" s="15" t="n"/>
-      <c r="B431" s="15" t="n"/>
-      <c r="C431" s="22" t="n"/>
-      <c r="D431" s="21" t="n"/>
-    </row>
-    <row r="432">
-      <c r="A432" s="15" t="n"/>
-      <c r="B432" s="15" t="n"/>
-      <c r="C432" s="22" t="n"/>
-      <c r="D432" s="21" t="n"/>
-    </row>
-    <row r="433">
-      <c r="A433" s="15" t="n"/>
-      <c r="B433" s="15" t="n"/>
-      <c r="C433" s="22" t="n"/>
-      <c r="D433" s="21" t="n"/>
-    </row>
-    <row r="434">
-      <c r="A434" s="15" t="n"/>
-      <c r="B434" s="15" t="n"/>
-      <c r="C434" s="22" t="n"/>
-      <c r="D434" s="21" t="n"/>
-    </row>
-    <row r="435">
-      <c r="A435" s="15" t="n"/>
-      <c r="B435" s="15" t="n"/>
-      <c r="C435" s="22" t="n"/>
-      <c r="D435" s="21" t="n"/>
-    </row>
-    <row r="436">
-      <c r="A436" s="15" t="n"/>
-      <c r="B436" s="15" t="n"/>
-      <c r="C436" s="22" t="n"/>
-      <c r="D436" s="21" t="n"/>
-    </row>
-    <row r="437">
-      <c r="A437" s="15" t="n"/>
-      <c r="B437" s="15" t="n"/>
-      <c r="C437" s="22" t="n"/>
-      <c r="D437" s="21" t="n"/>
-    </row>
-    <row r="438">
-      <c r="A438" s="15" t="n"/>
-      <c r="B438" s="15" t="n"/>
-      <c r="C438" s="22" t="n"/>
-      <c r="D438" s="21" t="n"/>
-    </row>
-    <row r="439">
-      <c r="A439" s="15" t="n"/>
-      <c r="B439" s="15" t="n"/>
-      <c r="C439" s="22" t="n"/>
-      <c r="D439" s="21" t="n"/>
-    </row>
-    <row r="440">
-      <c r="A440" s="15" t="n"/>
-      <c r="B440" s="15" t="n"/>
-      <c r="C440" s="22" t="n"/>
-      <c r="D440" s="21" t="n"/>
-    </row>
-    <row r="441">
-      <c r="A441" s="15" t="n"/>
-      <c r="B441" s="15" t="n"/>
-      <c r="C441" s="22" t="n"/>
-      <c r="D441" s="21" t="n"/>
-    </row>
-    <row r="442">
-      <c r="A442" s="15" t="n"/>
-      <c r="B442" s="15" t="n"/>
-      <c r="C442" s="22" t="n"/>
-      <c r="D442" s="21" t="n"/>
-    </row>
-    <row r="443">
-      <c r="A443" s="15" t="n"/>
-      <c r="B443" s="15" t="n"/>
-      <c r="C443" s="22" t="n"/>
-      <c r="D443" s="21" t="n"/>
-    </row>
-    <row r="444">
-      <c r="A444" s="15" t="n"/>
-      <c r="B444" s="15" t="n"/>
-      <c r="C444" s="22" t="n"/>
-      <c r="D444" s="21" t="n"/>
-    </row>
-    <row r="445">
-      <c r="A445" s="15" t="n"/>
-      <c r="B445" s="15" t="n"/>
-      <c r="C445" s="22" t="n"/>
-      <c r="D445" s="21" t="n"/>
-    </row>
-    <row r="446">
-      <c r="A446" s="15" t="n"/>
-      <c r="B446" s="15" t="n"/>
-      <c r="C446" s="22" t="n"/>
-      <c r="D446" s="21" t="n"/>
-    </row>
-    <row r="447">
-      <c r="A447" s="15" t="n"/>
-      <c r="B447" s="15" t="n"/>
-      <c r="C447" s="22" t="n"/>
-      <c r="D447" s="21" t="n"/>
-    </row>
-    <row r="448">
-      <c r="A448" s="15" t="n"/>
-      <c r="B448" s="15" t="n"/>
-      <c r="C448" s="22" t="n"/>
-      <c r="D448" s="21" t="n"/>
-    </row>
-    <row r="449">
-      <c r="A449" s="15" t="n"/>
-      <c r="B449" s="15" t="n"/>
-      <c r="C449" s="22" t="n"/>
-      <c r="D449" s="21" t="n"/>
-    </row>
-    <row r="450">
-      <c r="A450" s="15" t="n"/>
-      <c r="B450" s="15" t="n"/>
-      <c r="C450" s="22" t="n"/>
-      <c r="D450" s="21" t="n"/>
-    </row>
-    <row r="451">
-      <c r="A451" s="15" t="n"/>
-      <c r="B451" s="15" t="n"/>
-      <c r="C451" s="22" t="n"/>
-      <c r="D451" s="21" t="n"/>
-    </row>
-    <row r="452">
-      <c r="A452" s="15" t="n"/>
-      <c r="B452" s="15" t="n"/>
-      <c r="C452" s="22" t="n"/>
-      <c r="D452" s="21" t="n"/>
-    </row>
-    <row r="453">
-      <c r="A453" s="15" t="n"/>
-      <c r="B453" s="15" t="n"/>
-      <c r="C453" s="22" t="n"/>
-      <c r="D453" s="21" t="n"/>
-    </row>
-    <row r="454">
-      <c r="A454" s="15" t="n"/>
-      <c r="B454" s="15" t="n"/>
-      <c r="C454" s="22" t="n"/>
-      <c r="D454" s="21" t="n"/>
-    </row>
-    <row r="455">
-      <c r="A455" s="15" t="n"/>
-      <c r="B455" s="15" t="n"/>
-      <c r="C455" s="22" t="n"/>
-      <c r="D455" s="21" t="n"/>
-    </row>
-    <row r="456">
-      <c r="A456" s="15" t="n"/>
-      <c r="B456" s="15" t="n"/>
-      <c r="C456" s="22" t="n"/>
-      <c r="D456" s="21" t="n"/>
-    </row>
-    <row r="457">
-      <c r="A457" s="15" t="n"/>
-      <c r="B457" s="15" t="n"/>
-      <c r="C457" s="22" t="n"/>
-      <c r="D457" s="21" t="n"/>
-    </row>
-    <row r="458">
-      <c r="A458" s="15" t="n"/>
-      <c r="B458" s="15" t="n"/>
-      <c r="C458" s="22" t="n"/>
-      <c r="D458" s="21" t="n"/>
-    </row>
-    <row r="459">
-      <c r="A459" s="15" t="n"/>
-      <c r="B459" s="15" t="n"/>
-      <c r="C459" s="22" t="n"/>
-      <c r="D459" s="21" t="n"/>
-    </row>
-    <row r="460">
-      <c r="A460" s="15" t="n"/>
-      <c r="B460" s="15" t="n"/>
-      <c r="C460" s="22" t="n"/>
-      <c r="D460" s="21" t="n"/>
-    </row>
-    <row r="461">
-      <c r="A461" s="15" t="n"/>
-      <c r="B461" s="15" t="n"/>
-      <c r="C461" s="22" t="n"/>
-      <c r="D461" s="21" t="n"/>
-    </row>
-    <row r="462">
-      <c r="A462" s="15" t="n"/>
-      <c r="B462" s="15" t="n"/>
-      <c r="C462" s="22" t="n"/>
-      <c r="D462" s="21" t="n"/>
-    </row>
-    <row r="463">
-      <c r="A463" s="15" t="n"/>
-      <c r="B463" s="15" t="n"/>
-      <c r="C463" s="22" t="n"/>
-      <c r="D463" s="21" t="n"/>
-    </row>
-    <row r="464">
-      <c r="A464" s="15" t="n"/>
-      <c r="B464" s="15" t="n"/>
-      <c r="C464" s="22" t="n"/>
-      <c r="D464" s="21" t="n"/>
-    </row>
-    <row r="465">
-      <c r="A465" s="15" t="n"/>
-      <c r="B465" s="15" t="n"/>
-      <c r="C465" s="22" t="n"/>
-      <c r="D465" s="21" t="n"/>
-    </row>
-    <row r="466">
-      <c r="A466" s="15" t="n"/>
-      <c r="B466" s="15" t="n"/>
-      <c r="C466" s="22" t="n"/>
-      <c r="D466" s="21" t="n"/>
-    </row>
-    <row r="467">
-      <c r="A467" s="15" t="n"/>
-      <c r="B467" s="15" t="n"/>
-      <c r="C467" s="22" t="n"/>
-      <c r="D467" s="21" t="n"/>
-    </row>
-    <row r="468">
-      <c r="A468" s="15" t="n"/>
-      <c r="B468" s="15" t="n"/>
-      <c r="C468" s="22" t="n"/>
-      <c r="D468" s="21" t="n"/>
-    </row>
-    <row r="469">
-      <c r="A469" s="15" t="n"/>
-      <c r="B469" s="15" t="n"/>
-      <c r="C469" s="22" t="n"/>
-      <c r="D469" s="21" t="n"/>
-    </row>
-    <row r="470">
-      <c r="A470" s="15" t="n"/>
-      <c r="B470" s="15" t="n"/>
-      <c r="C470" s="22" t="n"/>
-      <c r="D470" s="21" t="n"/>
-    </row>
-    <row r="471">
-      <c r="A471" s="15" t="n"/>
-      <c r="B471" s="15" t="n"/>
-      <c r="C471" s="22" t="n"/>
-      <c r="D471" s="21" t="n"/>
-    </row>
-    <row r="472">
-      <c r="A472" s="15" t="n"/>
-      <c r="B472" s="15" t="n"/>
-      <c r="C472" s="22" t="n"/>
-      <c r="D472" s="21" t="n"/>
-    </row>
-    <row r="473">
-      <c r="A473" s="15" t="n"/>
-      <c r="B473" s="15" t="n"/>
-      <c r="C473" s="22" t="n"/>
-      <c r="D473" s="21" t="n"/>
-    </row>
-    <row r="474">
-      <c r="A474" s="15" t="n"/>
-      <c r="B474" s="15" t="n"/>
-      <c r="C474" s="22" t="n"/>
-      <c r="D474" s="21" t="n"/>
-    </row>
-    <row r="475">
-      <c r="A475" s="15" t="n"/>
-      <c r="B475" s="15" t="n"/>
-      <c r="C475" s="22" t="n"/>
-      <c r="D475" s="21" t="n"/>
-    </row>
-    <row r="476">
-      <c r="A476" s="15" t="n"/>
-      <c r="B476" s="15" t="n"/>
-      <c r="C476" s="22" t="n"/>
-      <c r="D476" s="21" t="n"/>
-    </row>
-    <row r="477">
-      <c r="A477" s="15" t="n"/>
-      <c r="B477" s="15" t="n"/>
-      <c r="C477" s="22" t="n"/>
-      <c r="D477" s="21" t="n"/>
-    </row>
-    <row r="478">
-      <c r="A478" s="15" t="n"/>
-      <c r="B478" s="15" t="n"/>
-      <c r="C478" s="22" t="n"/>
-      <c r="D478" s="21" t="n"/>
-    </row>
-    <row r="479">
-      <c r="A479" s="15" t="n"/>
-      <c r="B479" s="15" t="n"/>
-      <c r="C479" s="22" t="n"/>
-      <c r="D479" s="21" t="n"/>
-    </row>
-    <row r="480">
-      <c r="A480" s="15" t="n"/>
-      <c r="B480" s="15" t="n"/>
-      <c r="C480" s="22" t="n"/>
-      <c r="D480" s="21" t="n"/>
-    </row>
-    <row r="481">
-      <c r="A481" s="15" t="n"/>
-      <c r="B481" s="15" t="n"/>
-      <c r="C481" s="22" t="n"/>
-      <c r="D481" s="21" t="n"/>
-    </row>
-    <row r="482">
-      <c r="A482" s="15" t="n"/>
-      <c r="B482" s="15" t="n"/>
-      <c r="C482" s="22" t="n"/>
-      <c r="D482" s="21" t="n"/>
-    </row>
-    <row r="483">
-      <c r="A483" s="15" t="n"/>
-      <c r="B483" s="15" t="n"/>
-      <c r="C483" s="22" t="n"/>
-      <c r="D483" s="21" t="n"/>
-    </row>
-    <row r="484">
-      <c r="A484" s="15" t="n"/>
-      <c r="B484" s="15" t="n"/>
-      <c r="C484" s="22" t="n"/>
-      <c r="D484" s="21" t="n"/>
-    </row>
-    <row r="485">
-      <c r="A485" s="15" t="n"/>
-      <c r="B485" s="15" t="n"/>
-      <c r="C485" s="22" t="n"/>
-      <c r="D485" s="21" t="n"/>
-    </row>
-    <row r="486">
-      <c r="A486" s="15" t="n"/>
-      <c r="B486" s="15" t="n"/>
-      <c r="C486" s="22" t="n"/>
-      <c r="D486" s="21" t="n"/>
-    </row>
-    <row r="487">
-      <c r="A487" s="15" t="n"/>
-      <c r="B487" s="15" t="n"/>
-      <c r="C487" s="22" t="n"/>
-      <c r="D487" s="21" t="n"/>
-    </row>
-    <row r="488">
-      <c r="A488" s="15" t="n"/>
-      <c r="B488" s="15" t="n"/>
-      <c r="C488" s="22" t="n"/>
-      <c r="D488" s="21" t="n"/>
-    </row>
-    <row r="489">
-      <c r="A489" s="15" t="n"/>
-      <c r="B489" s="15" t="n"/>
-      <c r="C489" s="22" t="n"/>
-      <c r="D489" s="21" t="n"/>
-    </row>
-    <row r="490">
-      <c r="A490" s="15" t="n"/>
-      <c r="B490" s="15" t="n"/>
-      <c r="C490" s="22" t="n"/>
-      <c r="D490" s="21" t="n"/>
-    </row>
-    <row r="491">
-      <c r="A491" s="15" t="n"/>
-      <c r="B491" s="15" t="n"/>
-      <c r="C491" s="22" t="n"/>
-      <c r="D491" s="21" t="n"/>
-    </row>
-    <row r="492">
-      <c r="A492" s="15" t="n"/>
-      <c r="B492" s="15" t="n"/>
-      <c r="C492" s="22" t="n"/>
-      <c r="D492" s="21" t="n"/>
-    </row>
-    <row r="493">
-      <c r="A493" s="15" t="n"/>
-      <c r="B493" s="15" t="n"/>
-      <c r="C493" s="22" t="n"/>
-      <c r="D493" s="21" t="n"/>
-    </row>
-    <row r="494">
-      <c r="A494" s="15" t="n"/>
-      <c r="B494" s="15" t="n"/>
-      <c r="C494" s="22" t="n"/>
-      <c r="D494" s="21" t="n"/>
-    </row>
-    <row r="495">
-      <c r="A495" s="15" t="n"/>
-      <c r="B495" s="15" t="n"/>
-      <c r="C495" s="22" t="n"/>
-      <c r="D495" s="21" t="n"/>
-    </row>
-    <row r="496">
-      <c r="A496" s="15" t="n"/>
-      <c r="B496" s="15" t="n"/>
-      <c r="C496" s="22" t="n"/>
-      <c r="D496" s="21" t="n"/>
-    </row>
-    <row r="497">
-      <c r="A497" s="15" t="n"/>
-      <c r="B497" s="15" t="n"/>
-      <c r="C497" s="22" t="n"/>
-      <c r="D497" s="21" t="n"/>
-    </row>
-    <row r="498">
-      <c r="A498" s="15" t="n"/>
-      <c r="B498" s="15" t="n"/>
-      <c r="C498" s="22" t="n"/>
-      <c r="D498" s="21" t="n"/>
-    </row>
-    <row r="499">
-      <c r="A499" s="15" t="n"/>
-      <c r="B499" s="15" t="n"/>
-      <c r="C499" s="22" t="n"/>
-      <c r="D499" s="21" t="n"/>
-    </row>
-    <row r="500">
-      <c r="A500" s="15" t="n"/>
-      <c r="B500" s="15" t="n"/>
-      <c r="C500" s="22" t="n"/>
-      <c r="D500" s="21" t="n"/>
-    </row>
-    <row r="501">
-      <c r="A501" s="4" t="n"/>
-      <c r="B501" s="24" t="inlineStr">
+      <c r="A38" s="15" t="inlineStr">
         <is>
-          <t>Итого активов:</t>
+          <t>Нужно откладывать в месяц, чтобы к возрасту из «Настроек» накопить цель</t>
         </is>
       </c>
-      <c r="C501" s="23">
-        <f>SUM(C2:C500)</f>
-        <v/>
-      </c>
-      <c r="D501" s="4" t="n"/>
+      <c r="B38" s="35">
+        <f>IF($B$30=0,"",PMT((1+$B$30)^(1/12)-1,12*B34,0,-Настройки!$B$4))</f>
+        <v/>
+      </c>
+      <c r="C38" s="15" t="n"/>
+      <c r="D38" s="15" t="n"/>
+      <c r="E38" s="15" t="n"/>
+      <c r="F38" s="15" t="n"/>
+      <c r="G38" s="15" t="n"/>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation sqref="A2:A500" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Нет в списке" error="Выберите значение из списка. Новые значения добавьте на листе «Списки»." type="list">
-      <formula1>Списки!$H$2:$H$6</formula1>
+    <dataValidation sqref="B3" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Нет в списке" error="Выберите значение из списка. Новые значения добавьте на листе «Списки»." type="list">
+      <formula1>Списки!$R$2:$R$5</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
